--- a/Financial Analysis/Models (Defence).xlsx
+++ b/Financial Analysis/Models (Defence).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C21B19-EAD8-4770-BAFE-DD2AFCC6848F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F0E585-9AED-4F95-96EB-78DC192A4C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
   </bookViews>
@@ -27,6 +27,7 @@
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t>Company</t>
   </si>
@@ -257,6 +258,12 @@
   </si>
   <si>
     <t>2024 EV/R</t>
+  </si>
+  <si>
+    <t>Air</t>
+  </si>
+  <si>
+    <t>Embraer</t>
   </si>
 </sst>
 </file>
@@ -507,6 +514,21 @@
           <cell r="Z19">
             <v>4774</v>
           </cell>
+          <cell r="AA19">
+            <v>5935.5916480000114</v>
+          </cell>
+          <cell r="AB19">
+            <v>6317.3871904000098</v>
+          </cell>
+          <cell r="AC19">
+            <v>6584.8417255040049</v>
+          </cell>
+          <cell r="AD19">
+            <v>6768.4778666953616</v>
+          </cell>
+          <cell r="AK19">
+            <v>8025.7232492214553</v>
+          </cell>
         </row>
         <row r="25">
           <cell r="Y25">
@@ -516,6 +538,11 @@
             <v>0.17147417295414979</v>
           </cell>
         </row>
+        <row r="26">
+          <cell r="AO26">
+            <v>0.06</v>
+          </cell>
+        </row>
         <row r="28">
           <cell r="Z28">
             <v>0.19086427704426664</v>
@@ -524,6 +551,16 @@
         <row r="31">
           <cell r="Z31">
             <v>8.2612896034085559E-2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="AO32">
+            <v>-0.50646520170582687</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AO33" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -546,103 +583,98 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>46.45</v>
+            <v>212.27</v>
           </cell>
           <cell r="E3">
-            <v>45736</v>
+            <v>45771</v>
           </cell>
           <cell r="G3">
-            <v>45868</v>
+            <v>45771</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>26736.620000000003</v>
+            <v>39970.441000000006</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-267</v>
+            <v>-11621</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>27003.620000000003</v>
+            <v>51591.441000000006</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="Y3">
-            <v>17763</v>
+        <row r="5">
+          <cell r="X5">
+            <v>21325</v>
           </cell>
         </row>
         <row r="18">
           <cell r="T18">
-            <v>823</v>
+            <v>1119</v>
           </cell>
           <cell r="U18">
-            <v>239</v>
+            <v>1846</v>
           </cell>
           <cell r="V18">
-            <v>586</v>
+            <v>1062</v>
           </cell>
           <cell r="W18">
-            <v>927</v>
+            <v>1227</v>
           </cell>
           <cell r="X18">
-            <v>658</v>
+            <v>1502</v>
           </cell>
           <cell r="Y18">
-            <v>1072</v>
+            <v>1666.6471800000006</v>
           </cell>
           <cell r="Z18">
-            <v>1019.06265</v>
+            <v>1795.3686990000031</v>
           </cell>
           <cell r="AA18">
-            <v>1838.0187149999997</v>
+            <v>1911.0909576599986</v>
           </cell>
           <cell r="AB18">
-            <v>1923.3074602500005</v>
-          </cell>
-          <cell r="AC18">
-            <v>2000.3647039200005</v>
-          </cell>
-          <cell r="AJ18">
-            <v>2320.3893824228699</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="X22">
-            <v>3.9284986066743688E-2</v>
-          </cell>
-          <cell r="Y22">
-            <v>0.1616637237590739</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="Y23">
-            <v>0.11349434217193041</v>
+            <v>2010.4950586877997</v>
+          </cell>
+          <cell r="AI18">
+            <v>2738.5046287829741</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="AM24">
+          <cell r="W24">
+            <v>0.13814324229281438</v>
+          </cell>
+          <cell r="X24">
+            <v>9.815129512333276E-2</v>
+          </cell>
+          <cell r="AL24">
             <v>0.08</v>
           </cell>
         </row>
-        <row r="25">
-          <cell r="Y25">
-            <v>6.6430220120475142E-2</v>
+        <row r="27">
+          <cell r="X27">
+            <v>0.25903868698710436</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="X29">
+            <v>8.9941383352872217E-2</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="AM30">
-            <v>-8.2951850912037273E-2</v>
+          <cell r="AL30">
+            <v>-0.58739207901404</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="AM31" t="str">
-            <v>Fairly valued</v>
+          <cell r="AL31" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -652,6 +684,125 @@
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>46.45</v>
+          </cell>
+          <cell r="E3">
+            <v>45736</v>
+          </cell>
+          <cell r="G3">
+            <v>45868</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>26736.620000000003</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-267</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>27003.620000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="Y3">
+            <v>17763</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="T18">
+            <v>823</v>
+          </cell>
+          <cell r="U18">
+            <v>239</v>
+          </cell>
+          <cell r="V18">
+            <v>586</v>
+          </cell>
+          <cell r="W18">
+            <v>927</v>
+          </cell>
+          <cell r="X18">
+            <v>658</v>
+          </cell>
+          <cell r="Y18">
+            <v>1072</v>
+          </cell>
+          <cell r="Z18">
+            <v>1019.06265</v>
+          </cell>
+          <cell r="AA18">
+            <v>1838.0187149999997</v>
+          </cell>
+          <cell r="AB18">
+            <v>1923.3074602500005</v>
+          </cell>
+          <cell r="AC18">
+            <v>2000.3647039200005</v>
+          </cell>
+          <cell r="AJ18">
+            <v>2320.3893824228699</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="X22">
+            <v>3.9284986066743688E-2</v>
+          </cell>
+          <cell r="Y22">
+            <v>0.1616637237590739</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23">
+            <v>0.11349434217193041</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AM24">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25">
+            <v>6.6430220120475142E-2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AM30">
+            <v>-8.2951850912037273E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AM31" t="str">
+            <v>Fairly valued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -790,46 +941,26 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="AU5">
+        <row r="9">
+          <cell r="AU9">
             <v>66517</v>
           </cell>
         </row>
-        <row r="22">
-          <cell r="AP22">
-            <v>-636</v>
-          </cell>
-          <cell r="AQ22">
-            <v>-11873</v>
-          </cell>
-          <cell r="AR22">
-            <v>-4202</v>
-          </cell>
-          <cell r="AS22">
-            <v>-4935</v>
-          </cell>
-          <cell r="AT22">
-            <v>-2222</v>
-          </cell>
-          <cell r="AU22">
-            <v>-11875</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AT28">
+        <row r="32">
+          <cell r="AT32">
             <v>0.16793778525102088</v>
           </cell>
-          <cell r="AU28">
+          <cell r="AU32">
             <v>-0.14495976553461709</v>
           </cell>
         </row>
-        <row r="31">
-          <cell r="AU31">
+        <row r="35">
+          <cell r="AU35">
             <v>-2.9932197784025137E-2</v>
           </cell>
         </row>
-        <row r="34">
-          <cell r="AU34">
+        <row r="38">
+          <cell r="AU38">
             <v>-0.16096636949952645</v>
           </cell>
         </row>
@@ -850,76 +981,56 @@
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="D3">
-            <v>198.32</v>
-          </cell>
-          <cell r="E3">
-            <v>45770</v>
-          </cell>
-          <cell r="G3">
-            <v>45776</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="D5">
-            <v>128888.16799999999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="D8">
-            <v>-20146</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="D9">
-            <v>149034.16800000001</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="Y5">
-            <v>38498</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="T21">
-            <v>6143</v>
-          </cell>
-          <cell r="U21">
-            <v>4779</v>
-          </cell>
-          <cell r="V21">
-            <v>5542</v>
-          </cell>
-          <cell r="W21">
-            <v>4966</v>
-          </cell>
-          <cell r="X21">
-            <v>5658</v>
-          </cell>
-          <cell r="Y21">
-            <v>5705</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="X27">
-            <v>3.3722438391699194E-2</v>
-          </cell>
-          <cell r="Y27">
-            <v>5.0079100976487823E-2</v>
+        <row r="22">
+          <cell r="AP22">
+            <v>-636</v>
+          </cell>
+          <cell r="AQ22">
+            <v>-11873</v>
+          </cell>
+          <cell r="AR22">
+            <v>-4202</v>
+          </cell>
+          <cell r="AS22">
+            <v>-4935</v>
+          </cell>
+          <cell r="AT22">
+            <v>-2222</v>
+          </cell>
+          <cell r="AU22">
+            <v>-11875</v>
+          </cell>
+          <cell r="AV22">
+            <v>-5262.5270000000073</v>
+          </cell>
+          <cell r="AW22">
+            <v>-1942.5023000000067</v>
+          </cell>
+          <cell r="AX22">
+            <v>306.80698350001308</v>
+          </cell>
+          <cell r="AY22">
+            <v>1858.1908228950113</v>
+          </cell>
+          <cell r="BF22">
+            <v>6344.4675178984853</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="Y30">
-            <v>0.38085095329627511</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="Y33">
-            <v>0.19328276793599666</v>
+          <cell r="BJ30">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="BJ36">
+            <v>-0.74615865426916195</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="BJ37" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -942,73 +1053,99 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>462.5</v>
+            <v>227</v>
           </cell>
           <cell r="E3">
-            <v>45723</v>
+            <v>45770</v>
           </cell>
           <cell r="G3">
-            <v>45769</v>
+            <v>45776</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>108872.5</v>
+            <v>147527.29999999999</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-17787</v>
+            <v>-20146</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>126659.5</v>
+            <v>167673.29999999999</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="AC5">
-            <v>71043</v>
+          <cell r="Y5">
+            <v>38498</v>
           </cell>
         </row>
         <row r="21">
+          <cell r="T21">
+            <v>6143</v>
+          </cell>
+          <cell r="U21">
+            <v>4779</v>
+          </cell>
+          <cell r="V21">
+            <v>5542</v>
+          </cell>
+          <cell r="W21">
+            <v>4966</v>
+          </cell>
           <cell r="X21">
-            <v>6230</v>
+            <v>5658</v>
           </cell>
           <cell r="Y21">
-            <v>6888</v>
+            <v>5705</v>
           </cell>
           <cell r="Z21">
-            <v>6315</v>
+            <v>6141.1858699999948</v>
           </cell>
           <cell r="AA21">
-            <v>5732</v>
+            <v>6333.0918057399977</v>
           </cell>
           <cell r="AB21">
-            <v>6920</v>
+            <v>6529.3242899714041</v>
           </cell>
           <cell r="AC21">
-            <v>5336</v>
+            <v>6679.7574899245519</v>
+          </cell>
+          <cell r="AJ21">
+            <v>7412.6978597676443</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AB27">
-            <v>2.4051285160038738E-2</v>
-          </cell>
-          <cell r="AC27">
-            <v>5.1382989744120922E-2</v>
+          <cell r="X27">
+            <v>3.3722438391699194E-2</v>
+          </cell>
+          <cell r="Y27">
+            <v>5.0079100976487823E-2</v>
+          </cell>
+          <cell r="AM27">
+            <v>0.06</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="AC30">
-            <v>8.4089917373984774E-2</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AC31">
-            <v>9.8714862829553926E-2</v>
+          <cell r="Y30">
+            <v>0.38085095329627511</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33">
+            <v>0.19328276793599666</v>
+          </cell>
+          <cell r="AM33">
+            <v>-0.4002901538417406</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AM34" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1031,73 +1168,101 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>137.16</v>
+            <v>462.5</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45723</v>
           </cell>
           <cell r="G3">
-            <v>45777</v>
+            <v>45769</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>108356.4</v>
+            <v>108872.5</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>724</v>
+            <v>-17787</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>107632.4</v>
+            <v>126659.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="J3">
-            <v>69230</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>-1362</v>
-          </cell>
-          <cell r="F22">
-            <v>-1133</v>
-          </cell>
-          <cell r="G22">
-            <v>4213</v>
-          </cell>
-          <cell r="H22">
-            <v>4247</v>
-          </cell>
-          <cell r="I22">
-            <v>3789</v>
-          </cell>
-          <cell r="J22">
-            <v>4232</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="I26">
-            <v>0.11372802613889688</v>
-          </cell>
-          <cell r="J26">
-            <v>5.7818659658344318E-2</v>
+        <row r="5">
+          <cell r="AC5">
+            <v>71043</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="X21">
+            <v>6230</v>
+          </cell>
+          <cell r="Y21">
+            <v>6888</v>
+          </cell>
+          <cell r="Z21">
+            <v>6315</v>
+          </cell>
+          <cell r="AA21">
+            <v>5732</v>
+          </cell>
+          <cell r="AB21">
+            <v>6920</v>
+          </cell>
+          <cell r="AC21">
+            <v>5336</v>
+          </cell>
+          <cell r="AD21">
+            <v>6890.479949999999</v>
+          </cell>
+          <cell r="AE21">
+            <v>6982.5840987000065</v>
+          </cell>
+          <cell r="AF21">
+            <v>7076.3052693629925</v>
+          </cell>
+          <cell r="AG21">
+            <v>7171.6805116229025</v>
+          </cell>
+          <cell r="AN21">
+            <v>7888.9501553994505</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="J27">
-            <v>0.15419615773508594</v>
+          <cell r="AB27">
+            <v>2.4051285160038738E-2</v>
+          </cell>
+          <cell r="AC27">
+            <v>5.1382989744120922E-2</v>
+          </cell>
+          <cell r="AQ27">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AC30">
+            <v>8.4089917373984774E-2</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="J31">
-            <v>6.9391882132023686E-2</v>
+          <cell r="AC31">
+            <v>9.8714862829553926E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AQ33">
+            <v>-0.2341111312648132</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AQ34" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1120,73 +1285,103 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>472.65</v>
+            <v>137.16</v>
           </cell>
           <cell r="E3">
             <v>45771</v>
           </cell>
           <cell r="G3">
-            <v>45862</v>
+            <v>45777</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>68014.335000000006</v>
+            <v>108356.4</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-12482</v>
+            <v>724</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>80496.335000000006</v>
+            <v>107632.4</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="Y5">
-            <v>41033</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="T18">
-            <v>2248</v>
-          </cell>
-          <cell r="U18">
-            <v>3189</v>
-          </cell>
-          <cell r="V18">
-            <v>7005</v>
-          </cell>
-          <cell r="W18">
-            <v>4896</v>
-          </cell>
-          <cell r="X18">
-            <v>2056</v>
-          </cell>
-          <cell r="Y18">
-            <v>4174</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="X24">
-            <v>7.3438609912026775E-2</v>
-          </cell>
-          <cell r="Y24">
-            <v>4.4362433189106598E-2</v>
+        <row r="3">
+          <cell r="J3">
+            <v>69230</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22">
+            <v>-1362</v>
+          </cell>
+          <cell r="F22">
+            <v>-1133</v>
+          </cell>
+          <cell r="G22">
+            <v>4213</v>
+          </cell>
+          <cell r="H22">
+            <v>4247</v>
+          </cell>
+          <cell r="I22">
+            <v>3789</v>
+          </cell>
+          <cell r="J22">
+            <v>4232</v>
+          </cell>
+          <cell r="K22">
+            <v>5238.9075199999988</v>
+          </cell>
+          <cell r="L22">
+            <v>5416.3584256000004</v>
+          </cell>
+          <cell r="M22">
+            <v>5548.7205525119998</v>
+          </cell>
+          <cell r="N22">
+            <v>5683.9702715462408</v>
+          </cell>
+          <cell r="U22">
+            <v>6716.7817173619123</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="I26">
+            <v>0.11372802613889688</v>
+          </cell>
+          <cell r="J26">
+            <v>5.7818659658344318E-2</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="Y27">
-            <v>0.20378719567177639</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="Y29">
-            <v>0.10649964662588648</v>
+          <cell r="J27">
+            <v>0.15419615773508594</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="J31">
+            <v>6.9391882132023686E-2</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34">
+            <v>-0.22219982113568326</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1209,73 +1404,101 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>265.69</v>
+            <v>472.65</v>
           </cell>
           <cell r="E3">
             <v>45771</v>
           </cell>
           <cell r="G3">
-            <v>45861</v>
+            <v>45862</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>71311.195999999996</v>
+            <v>68014.335000000006</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-8367</v>
+            <v>-12482</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>79678.195999999996</v>
+            <v>80496.335000000006</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="AB5">
-            <v>47716</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="W16">
-            <v>3484</v>
-          </cell>
-          <cell r="X16">
-            <v>3167</v>
-          </cell>
-          <cell r="Y16">
-            <v>3257</v>
-          </cell>
-          <cell r="Z16">
-            <v>3390</v>
-          </cell>
-          <cell r="AA16">
-            <v>3315</v>
-          </cell>
-          <cell r="AB16">
-            <v>3782</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="AA22">
-            <v>7.2702819296064147E-2</v>
-          </cell>
-          <cell r="AB22">
-            <v>0.12878501135503417</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="AB25">
-            <v>0.15432978455863861</v>
+          <cell r="Y5">
+            <v>41033</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="T18">
+            <v>2248</v>
+          </cell>
+          <cell r="U18">
+            <v>3189</v>
+          </cell>
+          <cell r="V18">
+            <v>7005</v>
+          </cell>
+          <cell r="W18">
+            <v>4896</v>
+          </cell>
+          <cell r="X18">
+            <v>2056</v>
+          </cell>
+          <cell r="Y18">
+            <v>4174</v>
+          </cell>
+          <cell r="Z18">
+            <v>4444.976592</v>
+          </cell>
+          <cell r="AA18">
+            <v>4619.4424550400017</v>
+          </cell>
+          <cell r="AB18">
+            <v>4740.5026427807952</v>
+          </cell>
+          <cell r="AC18">
+            <v>4864.2707476628157</v>
+          </cell>
+          <cell r="AJ18">
+            <v>5342.3586043759151</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="X24">
+            <v>7.3438609912026775E-2</v>
+          </cell>
+          <cell r="Y24">
+            <v>4.4362433189106598E-2</v>
+          </cell>
+          <cell r="AM24">
+            <v>0.08</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AB27">
-            <v>0.10051135887333389</v>
+          <cell r="Y27">
+            <v>0.20378719567177639</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29">
+            <v>0.10649964662588648</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AM30">
+            <v>-0.31348981866726999</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AM31" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1298,97 +1521,101 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1417</v>
-          </cell>
-          <cell r="F3">
-            <v>45734</v>
-          </cell>
-          <cell r="H3">
-            <v>45455</v>
+            <v>265.69</v>
+          </cell>
+          <cell r="E3">
+            <v>45771</v>
+          </cell>
+          <cell r="G3">
+            <v>45861</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>61540.31</v>
+            <v>71311.195999999996</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-893</v>
+            <v>-8367</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>62433.31</v>
+            <v>79678.195999999996</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="18">
-          <cell r="AC18">
-            <v>7175</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="Z37">
-            <v>-27</v>
-          </cell>
-          <cell r="AA37">
-            <v>291</v>
-          </cell>
-          <cell r="AB37">
-            <v>476</v>
-          </cell>
-          <cell r="AC37">
-            <v>534</v>
-          </cell>
-          <cell r="AD37">
-            <v>717</v>
-          </cell>
-          <cell r="AE37">
-            <v>1183.5057150000023</v>
-          </cell>
-          <cell r="AF37">
-            <v>1446.6646025</v>
-          </cell>
-          <cell r="AG37">
-            <v>1594.3621815874999</v>
-          </cell>
-          <cell r="AN37">
-            <v>1930.9939382407565</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AS46">
-            <v>7.0000000000000007E-2</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="AB49">
-            <v>0.1327089591800672</v>
-          </cell>
-          <cell r="AC49">
-            <v>0.11934477379095165</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="AC51">
-            <v>0.26327526132404183</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="AS52">
-            <v>-0.62242636061307977</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="AS53" t="str">
-            <v>Heavily overvalued</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="AC56">
-            <v>0.11777003484320557</v>
+        <row r="5">
+          <cell r="AB5">
+            <v>47716</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="W16">
+            <v>3484</v>
+          </cell>
+          <cell r="X16">
+            <v>3167</v>
+          </cell>
+          <cell r="Y16">
+            <v>3257</v>
+          </cell>
+          <cell r="Z16">
+            <v>3390</v>
+          </cell>
+          <cell r="AA16">
+            <v>3315</v>
+          </cell>
+          <cell r="AB16">
+            <v>3782</v>
+          </cell>
+          <cell r="AC16">
+            <v>4065.2781650000034</v>
+          </cell>
+          <cell r="AD16">
+            <v>4316.3812148500065</v>
+          </cell>
+          <cell r="AE16">
+            <v>4535.0469065479992</v>
+          </cell>
+          <cell r="AF16">
+            <v>4720.710356326842</v>
+          </cell>
+          <cell r="AM16">
+            <v>5397.949296781786</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="AA22">
+            <v>7.2702819296064147E-2</v>
+          </cell>
+          <cell r="AB22">
+            <v>0.12878501135503417</v>
+          </cell>
+          <cell r="AP22">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="AB25">
+            <v>0.15432978455863861</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AB27">
+            <v>0.10051135887333389</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AP28">
+            <v>-0.28201653867212506</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AP29" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1411,70 +1638,97 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>212.27</v>
-          </cell>
-          <cell r="E3">
-            <v>45771</v>
-          </cell>
-          <cell r="G3">
-            <v>45771</v>
+            <v>1417</v>
+          </cell>
+          <cell r="F3">
+            <v>45734</v>
+          </cell>
+          <cell r="H3">
+            <v>45455</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>39970.441000000006</v>
+            <v>61540.31</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-11621</v>
+            <v>-893</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>51591.441000000006</v>
+            <v>62433.31</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="X5">
-            <v>21325</v>
-          </cell>
-        </row>
         <row r="18">
-          <cell r="T18">
-            <v>1119</v>
-          </cell>
-          <cell r="U18">
-            <v>1846</v>
-          </cell>
-          <cell r="V18">
-            <v>1062</v>
-          </cell>
-          <cell r="W18">
-            <v>1227</v>
-          </cell>
-          <cell r="X18">
-            <v>1502</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="W24">
-            <v>0.13814324229281438</v>
-          </cell>
-          <cell r="X24">
-            <v>9.815129512333276E-2</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="X27">
-            <v>0.25903868698710436</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="X29">
-            <v>8.9941383352872217E-2</v>
+          <cell r="AC18">
+            <v>7175</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="Z37">
+            <v>-27</v>
+          </cell>
+          <cell r="AA37">
+            <v>291</v>
+          </cell>
+          <cell r="AB37">
+            <v>476</v>
+          </cell>
+          <cell r="AC37">
+            <v>534</v>
+          </cell>
+          <cell r="AD37">
+            <v>717</v>
+          </cell>
+          <cell r="AE37">
+            <v>1183.5057150000023</v>
+          </cell>
+          <cell r="AF37">
+            <v>1446.6646025</v>
+          </cell>
+          <cell r="AG37">
+            <v>1594.3621815874999</v>
+          </cell>
+          <cell r="AN37">
+            <v>1930.9939382407565</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AS46">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="AB49">
+            <v>0.1327089591800672</v>
+          </cell>
+          <cell r="AC49">
+            <v>0.11934477379095165</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AC51">
+            <v>0.26327526132404183</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="AS52">
+            <v>-0.62242636061307977</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="AS53" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="AC56">
+            <v>0.11777003484320557</v>
           </cell>
         </row>
       </sheetData>
@@ -1780,7 +2034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
-  <dimension ref="B2:AK21"/>
+  <dimension ref="B2:AK23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -1932,23 +2186,23 @@
       </c>
       <c r="S3" s="7">
         <f t="shared" si="0"/>
-        <v>56.78711737556015</v>
+        <v>24.782129357090753</v>
       </c>
       <c r="T3" s="7">
         <f t="shared" si="0"/>
-        <v>33.722279574921885</v>
+        <v>21.602319676769721</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" si="0"/>
-        <v>28.59846337341207</v>
+        <v>22.538867814060595</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" si="0"/>
-        <v>26.32907424754935</v>
+        <v>22.018917353442966</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="0"/>
-        <v>11.637538166893249</v>
+        <v>16.972993351440959</v>
       </c>
       <c r="X3" s="8"/>
       <c r="Y3" s="21">
@@ -1973,11 +2227,11 @@
       </c>
       <c r="AD3" s="9">
         <f t="shared" si="1"/>
-        <v>0.08</v>
+        <v>7.333333333333332E-2</v>
       </c>
       <c r="AE3" s="9">
         <f t="shared" si="1"/>
-        <v>-0.23973616282793675</v>
+        <v>-0.33193217039371187</v>
       </c>
       <c r="AF3" s="10" t="e">
         <f>INDEX(AF4:AF52,MODE(MATCH(AF4:AF52,AF4:AF52,0)))</f>
@@ -2034,28 +2288,44 @@
       </c>
       <c r="N4" s="14">
         <f>[1]Model!AA$19</f>
-        <v>0</v>
+        <v>5935.5916480000114</v>
       </c>
       <c r="O4" s="14">
         <f>[1]Model!AB$19</f>
-        <v>0</v>
+        <v>6317.3871904000098</v>
       </c>
       <c r="P4" s="14">
         <f>[1]Model!AC$19</f>
-        <v>0</v>
+        <v>6584.8417255040049</v>
       </c>
       <c r="Q4" s="14">
         <f>[1]Model!AD$19</f>
-        <v>0</v>
+        <v>6768.4778666953616</v>
       </c>
       <c r="R4" s="15">
         <f t="shared" ref="R4" si="2">$G4/M4</f>
         <v>40.97080016757436</v>
       </c>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
+      <c r="S4" s="15">
+        <f t="shared" ref="S4" si="3">$G4/N4</f>
+        <v>32.952839682949772</v>
+      </c>
+      <c r="T4" s="15">
+        <f t="shared" ref="T4" si="4">$G4/O4</f>
+        <v>30.961312660593023</v>
+      </c>
+      <c r="U4" s="15">
+        <f t="shared" ref="U4" si="5">$G4/P4</f>
+        <v>29.703766339961522</v>
+      </c>
+      <c r="V4" s="15">
+        <f t="shared" ref="V4" si="6">$G4/Q4</f>
+        <v>28.897870961864726</v>
+      </c>
+      <c r="W4" s="15">
+        <f>G4/[1]Model!$AK$19</f>
+        <v>24.370962457367799</v>
+      </c>
       <c r="X4" s="14">
         <f>[1]Model!$Z$5</f>
         <v>80738</v>
@@ -2079,6 +2349,18 @@
       <c r="AC4" s="16">
         <f>[1]Model!$Z$31</f>
         <v>8.2612896034085559E-2</v>
+      </c>
+      <c r="AD4" s="16">
+        <f>[1]Model!$AO$26</f>
+        <v>0.06</v>
+      </c>
+      <c r="AE4" s="16">
+        <f>[1]Model!$AO$32</f>
+        <v>-0.50646520170582687</v>
+      </c>
+      <c r="AF4" s="11" t="str">
+        <f>[1]Model!$AO$33</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AH4" s="11">
         <v>1922</v>
@@ -2116,72 +2398,99 @@
         <v>161773.932</v>
       </c>
       <c r="H5" s="14">
-        <f>[2]Model!AP$22</f>
+        <f>[3]Model!AP$22</f>
         <v>-636</v>
       </c>
       <c r="I5" s="14">
-        <f>[2]Model!AQ$22</f>
+        <f>[3]Model!AQ$22</f>
         <v>-11873</v>
       </c>
       <c r="J5" s="14">
-        <f>[2]Model!AR$22</f>
+        <f>[3]Model!AR$22</f>
         <v>-4202</v>
       </c>
       <c r="K5" s="14">
-        <f>[2]Model!AS$22</f>
+        <f>[3]Model!AS$22</f>
         <v>-4935</v>
       </c>
       <c r="L5" s="14">
-        <f>[2]Model!AT$22</f>
+        <f>[3]Model!AT$22</f>
         <v>-2222</v>
       </c>
       <c r="M5" s="14">
-        <f>[2]Model!AU$22</f>
+        <f>[3]Model!AU$22</f>
         <v>-11875</v>
       </c>
       <c r="N5" s="14">
-        <f>[2]Model!AV$22</f>
-        <v>0</v>
+        <f>[3]Model!AV$22</f>
+        <v>-5262.5270000000073</v>
       </c>
       <c r="O5" s="14">
-        <f>[2]Model!AW$22</f>
-        <v>0</v>
+        <f>[3]Model!AW$22</f>
+        <v>-1942.5023000000067</v>
       </c>
       <c r="P5" s="14">
-        <f>[2]Model!AX$22</f>
-        <v>0</v>
+        <f>[3]Model!AX$22</f>
+        <v>306.80698350001308</v>
       </c>
       <c r="Q5" s="14">
-        <f>[2]Model!AY$22</f>
-        <v>0</v>
+        <f>[3]Model!AY$22</f>
+        <v>1858.1908228950113</v>
       </c>
       <c r="R5" s="15">
         <f>$G5/M5</f>
         <v>-13.623067957894737</v>
       </c>
+      <c r="U5" s="15">
+        <f t="shared" ref="U5:V6" si="7">$G5/P5</f>
+        <v>527.28243064908304</v>
+      </c>
+      <c r="V5" s="15">
+        <f t="shared" si="7"/>
+        <v>87.059913334390799</v>
+      </c>
+      <c r="W5" s="15">
+        <f>G5/[3]Model!$BF$22</f>
+        <v>25.498425446046781</v>
+      </c>
       <c r="X5" s="14">
-        <f>[2]Model!$AU$5</f>
+        <f>[2]Model!$AU$9</f>
         <v>66517</v>
       </c>
       <c r="Y5" s="20">
-        <f t="shared" ref="Y5:Y8" si="3">G5/X5</f>
+        <f t="shared" ref="Y5:Y8" si="8">G5/X5</f>
         <v>2.4320689748485349</v>
       </c>
       <c r="Z5" s="16">
-        <f>[2]Model!$AT$28</f>
+        <f>[2]Model!$AT$32</f>
         <v>0.16793778525102088</v>
       </c>
       <c r="AA5" s="16">
-        <f>[2]Model!$AU$28</f>
+        <f>[2]Model!$AU$32</f>
         <v>-0.14495976553461709</v>
       </c>
       <c r="AB5" s="16">
-        <f>[2]Model!$AU$31</f>
+        <f>[2]Model!$AU$35</f>
         <v>-2.9932197784025137E-2</v>
       </c>
       <c r="AC5" s="16">
-        <f>[2]Model!$AU$34</f>
+        <f>[2]Model!$AU$38</f>
         <v>-0.16096636949952645</v>
+      </c>
+      <c r="AD5" s="16">
+        <f>[3]Model!$BJ$30</f>
+        <v>0.06</v>
+      </c>
+      <c r="AE5" s="16">
+        <f>[3]Model!$BJ$36</f>
+        <v>-0.74615865426916195</v>
+      </c>
+      <c r="AF5" s="11" t="str">
+        <f>[3]Model!$BJ$37</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="AH5" s="11">
         <v>1916</v>
@@ -2203,98 +2512,130 @@
         <v>61</v>
       </c>
       <c r="D6" s="13">
-        <f>[3]Main!$D$3</f>
-        <v>198.32</v>
+        <f>[4]Main!$D$3</f>
+        <v>227</v>
       </c>
       <c r="E6" s="14">
-        <f>[3]Main!$D$5</f>
-        <v>128888.16799999999</v>
+        <f>[4]Main!$D$5</f>
+        <v>147527.29999999999</v>
       </c>
       <c r="F6" s="14">
-        <f>[3]Main!$D$8</f>
+        <f>[4]Main!$D$8</f>
         <v>-20146</v>
       </c>
       <c r="G6" s="14">
-        <f>[3]Main!$D$9</f>
-        <v>149034.16800000001</v>
+        <f>[4]Main!$D$9</f>
+        <v>167673.29999999999</v>
       </c>
       <c r="H6" s="14">
-        <f>[3]Model!T$21</f>
+        <f>[4]Model!T$21</f>
         <v>6143</v>
       </c>
       <c r="I6" s="14">
-        <f>[3]Model!U$21</f>
+        <f>[4]Model!U$21</f>
         <v>4779</v>
       </c>
       <c r="J6" s="14">
-        <f>[3]Model!V$21</f>
+        <f>[4]Model!V$21</f>
         <v>5542</v>
       </c>
       <c r="K6" s="14">
-        <f>[3]Model!W$21</f>
+        <f>[4]Model!W$21</f>
         <v>4966</v>
       </c>
       <c r="L6" s="14">
-        <f>[3]Model!X$21</f>
+        <f>[4]Model!X$21</f>
         <v>5658</v>
       </c>
       <c r="M6" s="14">
-        <f>[3]Model!Y$21</f>
+        <f>[4]Model!Y$21</f>
         <v>5705</v>
       </c>
       <c r="N6" s="14">
-        <f>[3]Model!Z$21</f>
-        <v>0</v>
+        <f>[4]Model!Z$21</f>
+        <v>6141.1858699999948</v>
       </c>
       <c r="O6" s="14">
-        <f>[3]Model!AA$21</f>
-        <v>0</v>
+        <f>[4]Model!AA$21</f>
+        <v>6333.0918057399977</v>
       </c>
       <c r="P6" s="14">
-        <f>[3]Model!AB$21</f>
-        <v>0</v>
+        <f>[4]Model!AB$21</f>
+        <v>6529.3242899714041</v>
       </c>
       <c r="Q6" s="14">
-        <f>[3]Model!AC$21</f>
-        <v>0</v>
+        <f>[4]Model!AC$21</f>
+        <v>6679.7574899245519</v>
       </c>
       <c r="R6" s="15">
         <f>$G6/M6</f>
-        <v>26.123429973707275</v>
+        <v>29.390587204206835</v>
+      </c>
+      <c r="S6" s="15">
+        <f t="shared" ref="S6:T6" si="9">$G6/N6</f>
+        <v>27.303081774334917</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="9"/>
+        <v>26.475741256115899</v>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="7"/>
+        <v>25.680038630878652</v>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" si="7"/>
+        <v>25.101704703039132</v>
+      </c>
+      <c r="W6" s="15">
+        <f>G6/[4]Model!$AJ$21</f>
+        <v>22.619740231157326</v>
       </c>
       <c r="X6" s="14">
-        <f>[3]Model!$Y$5</f>
+        <f>[4]Model!$Y$5</f>
         <v>38498</v>
       </c>
       <c r="Y6" s="20">
-        <f t="shared" si="3"/>
-        <v>3.8712184529066445</v>
+        <f t="shared" si="8"/>
+        <v>4.3553769026962437</v>
       </c>
       <c r="Z6" s="16">
-        <f>[3]Model!X$27</f>
+        <f>[4]Model!X$27</f>
         <v>3.3722438391699194E-2</v>
       </c>
       <c r="AA6" s="16">
-        <f>[3]Model!Y$27</f>
+        <f>[4]Model!Y$27</f>
         <v>5.0079100976487823E-2</v>
       </c>
       <c r="AB6" s="16">
-        <f>[3]Model!$Y$30</f>
+        <f>[4]Model!$Y$30</f>
         <v>0.38085095329627511</v>
       </c>
       <c r="AC6" s="16">
-        <f>[3]Model!$Y$33</f>
+        <f>[4]Model!$Y$33</f>
         <v>0.19328276793599666</v>
+      </c>
+      <c r="AD6" s="16">
+        <f>[4]Model!$AM$27</f>
+        <v>0.06</v>
+      </c>
+      <c r="AE6" s="16">
+        <f>[4]Model!$AM$33</f>
+        <v>-0.4002901538417406</v>
+      </c>
+      <c r="AF6" s="11" t="str">
+        <f>[4]Model!$AM$34</f>
+        <v>Overvalued</v>
       </c>
       <c r="AH6" s="11">
         <v>1906</v>
       </c>
       <c r="AJ6" s="18">
-        <f>[3]Main!$E$3</f>
+        <f>[4]Main!$E$3</f>
         <v>45770</v>
       </c>
       <c r="AK6" s="18">
-        <f>[3]Main!$G$3</f>
+        <f>[4]Main!$G$3</f>
         <v>45776</v>
       </c>
     </row>
@@ -2306,102 +2647,130 @@
         <v>45</v>
       </c>
       <c r="D7" s="13">
-        <f>[4]Main!$D$3</f>
+        <f>[5]Main!$D$3</f>
         <v>462.5</v>
       </c>
       <c r="E7" s="14">
-        <f>[4]Main!$D$5</f>
+        <f>[5]Main!$D$5</f>
         <v>108872.5</v>
       </c>
       <c r="F7" s="14">
-        <f>[4]Main!$D$8</f>
+        <f>[5]Main!$D$8</f>
         <v>-17787</v>
       </c>
       <c r="G7" s="14">
-        <f>[4]Main!$D$9</f>
+        <f>[5]Main!$D$9</f>
         <v>126659.5</v>
       </c>
       <c r="H7" s="14">
-        <f>[4]Model!X$21</f>
+        <f>[5]Model!X$21</f>
         <v>6230</v>
       </c>
       <c r="I7" s="14">
-        <f>[4]Model!Y$21</f>
+        <f>[5]Model!Y$21</f>
         <v>6888</v>
       </c>
       <c r="J7" s="14">
-        <f>[4]Model!Z$21</f>
+        <f>[5]Model!Z$21</f>
         <v>6315</v>
       </c>
       <c r="K7" s="14">
-        <f>[4]Model!AA$21</f>
+        <f>[5]Model!AA$21</f>
         <v>5732</v>
       </c>
       <c r="L7" s="14">
-        <f>[4]Model!AB$21</f>
+        <f>[5]Model!AB$21</f>
         <v>6920</v>
       </c>
       <c r="M7" s="14">
-        <f>[4]Model!AC$21</f>
+        <f>[5]Model!AC$21</f>
         <v>5336</v>
       </c>
       <c r="N7" s="14">
-        <f>[4]Model!AD$21</f>
-        <v>0</v>
+        <f>[5]Model!AD$21</f>
+        <v>6890.479949999999</v>
       </c>
       <c r="O7" s="14">
-        <f>[4]Model!AE$21</f>
-        <v>0</v>
+        <f>[5]Model!AE$21</f>
+        <v>6982.5840987000065</v>
       </c>
       <c r="P7" s="14">
-        <f>[4]Model!AF$21</f>
-        <v>0</v>
+        <f>[5]Model!AF$21</f>
+        <v>7076.3052693629925</v>
       </c>
       <c r="Q7" s="14">
-        <f>[4]Model!AG$21</f>
-        <v>0</v>
+        <f>[5]Model!AG$21</f>
+        <v>7171.6805116229025</v>
       </c>
       <c r="R7" s="15">
-        <f t="shared" ref="R7:R8" si="4">$G7/M7</f>
+        <f t="shared" ref="R7:R8" si="10">$G7/M7</f>
         <v>23.736787856071963</v>
       </c>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
+      <c r="S7" s="15">
+        <f t="shared" ref="S7" si="11">$G7/N7</f>
+        <v>18.38181097965462</v>
+      </c>
+      <c r="T7" s="15">
+        <f t="shared" ref="T7" si="12">$G7/O7</f>
+        <v>18.139344719611902</v>
+      </c>
+      <c r="U7" s="15">
+        <f t="shared" ref="U7" si="13">$G7/P7</f>
+        <v>17.899100615171999</v>
+      </c>
+      <c r="V7" s="15">
+        <f t="shared" ref="V7" si="14">$G7/Q7</f>
+        <v>17.66106281431907</v>
+      </c>
+      <c r="W7" s="15">
+        <f>G7/[5]Model!$AN$21</f>
+        <v>16.055304889118887</v>
+      </c>
       <c r="X7" s="14">
-        <f>[4]Model!$AC$5</f>
+        <f>[5]Model!$AC$5</f>
         <v>71043</v>
       </c>
       <c r="Y7" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.7828568613374998</v>
       </c>
       <c r="Z7" s="16">
-        <f>[4]Model!$AB$27</f>
+        <f>[5]Model!$AB$27</f>
         <v>2.4051285160038738E-2</v>
       </c>
       <c r="AA7" s="16">
-        <f>[4]Model!$AC$27</f>
+        <f>[5]Model!$AC$27</f>
         <v>5.1382989744120922E-2</v>
       </c>
       <c r="AB7" s="16">
-        <f>[4]Model!$AC$30</f>
+        <f>[5]Model!$AC$30</f>
         <v>8.4089917373984774E-2</v>
       </c>
       <c r="AC7" s="16">
-        <f>[4]Model!$AC$31</f>
+        <f>[5]Model!$AC$31</f>
         <v>9.8714862829553926E-2</v>
+      </c>
+      <c r="AD7" s="16">
+        <f>[5]Model!$AQ$27</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AE7" s="16">
+        <f>[5]Model!$AQ$33</f>
+        <v>-0.2341111312648132</v>
+      </c>
+      <c r="AF7" s="11" t="str">
+        <f>[5]Model!$AQ$34</f>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AH7" s="11">
         <v>1912</v>
       </c>
       <c r="AJ7" s="18">
-        <f>[4]Main!$E$3</f>
+        <f>[5]Main!$E$3</f>
         <v>45723</v>
       </c>
       <c r="AK7" s="18">
-        <f>[4]Main!$G$3</f>
+        <f>[5]Main!$G$3</f>
         <v>45769</v>
       </c>
     </row>
@@ -2413,98 +2782,133 @@
         <v>62</v>
       </c>
       <c r="D8" s="11">
-        <f>[5]Main!$D$3</f>
+        <f>[6]Main!$D$3</f>
         <v>137.16</v>
       </c>
       <c r="E8" s="14">
-        <f>[5]Main!$D$5</f>
+        <f>[6]Main!$D$5</f>
         <v>108356.4</v>
       </c>
       <c r="F8" s="14">
-        <f>[5]Main!$D$8</f>
+        <f>[6]Main!$D$8</f>
         <v>724</v>
       </c>
       <c r="G8" s="14">
-        <f>[5]Main!$D$9</f>
+        <f>[6]Main!$D$9</f>
         <v>107632.4</v>
       </c>
       <c r="H8" s="14">
-        <f>[5]Model!E$22</f>
+        <f>[6]Model!E$22</f>
         <v>-1362</v>
       </c>
       <c r="I8" s="14">
-        <f>[5]Model!F$22</f>
+        <f>[6]Model!F$22</f>
         <v>-1133</v>
       </c>
       <c r="J8" s="14">
-        <f>[5]Model!G$22</f>
+        <f>[6]Model!G$22</f>
         <v>4213</v>
       </c>
       <c r="K8" s="14">
-        <f>[5]Model!H$22</f>
+        <f>[6]Model!H$22</f>
         <v>4247</v>
       </c>
       <c r="L8" s="14">
-        <f>[5]Model!I$22</f>
+        <f>[6]Model!I$22</f>
         <v>3789</v>
       </c>
       <c r="M8" s="14">
-        <f>[5]Model!J$22</f>
+        <f>[6]Model!J$22</f>
         <v>4232</v>
       </c>
       <c r="N8" s="14">
-        <f>[5]Model!K$22</f>
-        <v>0</v>
+        <f>[6]Model!K$22</f>
+        <v>5238.9075199999988</v>
       </c>
       <c r="O8" s="14">
-        <f>[5]Model!L$22</f>
-        <v>0</v>
+        <f>[6]Model!L$22</f>
+        <v>5416.3584256000004</v>
       </c>
       <c r="P8" s="14">
-        <f>[5]Model!M$22</f>
-        <v>0</v>
+        <f>[6]Model!M$22</f>
+        <v>5548.7205525119998</v>
       </c>
       <c r="Q8" s="14">
-        <f>[5]Model!N$22</f>
-        <v>0</v>
+        <f>[6]Model!N$22</f>
+        <v>5683.9702715462408</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>25.432986767485822</v>
       </c>
+      <c r="S8" s="15">
+        <f t="shared" ref="S8" si="15">$G8/N8</f>
+        <v>20.544817710391655</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" ref="T8" si="16">$G8/O8</f>
+        <v>19.871727744471961</v>
+      </c>
+      <c r="U8" s="15">
+        <f t="shared" ref="U8" si="17">$G8/P8</f>
+        <v>19.397696997242541</v>
+      </c>
+      <c r="V8" s="15">
+        <f t="shared" ref="V8" si="18">$G8/Q8</f>
+        <v>18.936130003846795</v>
+      </c>
+      <c r="W8" s="15">
+        <f>G8/[6]Model!$U$22</f>
+        <v>16.024400453834275</v>
+      </c>
       <c r="X8" s="14">
-        <f>[5]Model!$J$3</f>
+        <f>[6]Model!$J$3</f>
         <v>69230</v>
       </c>
       <c r="Y8" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>1.5547074967499639</v>
       </c>
       <c r="Z8" s="16">
-        <f>[5]Model!$I$26</f>
+        <f>[6]Model!$I$26</f>
         <v>0.11372802613889688</v>
       </c>
       <c r="AA8" s="16">
-        <f>[5]Model!$J$26</f>
+        <f>[6]Model!$J$26</f>
         <v>5.7818659658344318E-2</v>
       </c>
       <c r="AB8" s="16">
-        <f>[5]Model!$J$27</f>
+        <f>[6]Model!$J$27</f>
         <v>0.15419615773508594</v>
       </c>
       <c r="AC8" s="16">
-        <f>[5]Model!$J$31</f>
+        <f>[6]Model!$J$31</f>
         <v>6.9391882132023686E-2</v>
+      </c>
+      <c r="AD8" s="16">
+        <f>[6]Model!$Y$28</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AE8" s="16">
+        <f>[6]Model!$Y$34</f>
+        <v>-0.22219982113568326</v>
+      </c>
+      <c r="AF8" s="11" t="str">
+        <f>[6]Model!$Y$35</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AG8" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="AH8" s="11">
         <v>1998</v>
       </c>
       <c r="AJ8" s="18">
-        <f>[5]Main!$E$3</f>
+        <f>[6]Main!$E$3</f>
         <v>45771</v>
       </c>
       <c r="AK8" s="18">
-        <f>[5]Main!$G$3</f>
+        <f>[6]Main!$G$3</f>
         <v>45777</v>
       </c>
     </row>
@@ -2524,98 +2928,130 @@
         <v>60</v>
       </c>
       <c r="D10" s="13">
-        <f>[6]Main!$D$3</f>
+        <f>[7]Main!$D$3</f>
         <v>472.65</v>
       </c>
       <c r="E10" s="14">
-        <f>[6]Main!$D$5</f>
+        <f>[7]Main!$D$5</f>
         <v>68014.335000000006</v>
       </c>
       <c r="F10" s="14">
-        <f>[6]Main!$D$8</f>
+        <f>[7]Main!$D$8</f>
         <v>-12482</v>
       </c>
       <c r="G10" s="14">
-        <f>[6]Main!$D$9</f>
+        <f>[7]Main!$D$9</f>
         <v>80496.335000000006</v>
       </c>
       <c r="H10" s="14">
-        <f>[6]Model!T$18</f>
+        <f>[7]Model!T$18</f>
         <v>2248</v>
       </c>
       <c r="I10" s="14">
-        <f>[6]Model!U$18</f>
+        <f>[7]Model!U$18</f>
         <v>3189</v>
       </c>
       <c r="J10" s="14">
-        <f>[6]Model!V$18</f>
+        <f>[7]Model!V$18</f>
         <v>7005</v>
       </c>
       <c r="K10" s="14">
-        <f>[6]Model!W$18</f>
+        <f>[7]Model!W$18</f>
         <v>4896</v>
       </c>
       <c r="L10" s="14">
-        <f>[6]Model!X$18</f>
+        <f>[7]Model!X$18</f>
         <v>2056</v>
       </c>
       <c r="M10" s="14">
-        <f>[6]Model!Y$18</f>
+        <f>[7]Model!Y$18</f>
         <v>4174</v>
       </c>
       <c r="N10" s="14">
-        <f>[6]Model!Z$18</f>
-        <v>0</v>
+        <f>[7]Model!Z$18</f>
+        <v>4444.976592</v>
       </c>
       <c r="O10" s="14">
-        <f>[6]Model!AA$18</f>
-        <v>0</v>
+        <f>[7]Model!AA$18</f>
+        <v>4619.4424550400017</v>
       </c>
       <c r="P10" s="14">
-        <f>[6]Model!AB$18</f>
-        <v>0</v>
+        <f>[7]Model!AB$18</f>
+        <v>4740.5026427807952</v>
       </c>
       <c r="Q10" s="14">
-        <f>[6]Model!AC$18</f>
-        <v>0</v>
+        <f>[7]Model!AC$18</f>
+        <v>4864.2707476628157</v>
       </c>
       <c r="R10" s="15">
         <f>$G10/M10</f>
         <v>19.285178485864879</v>
       </c>
+      <c r="S10" s="15">
+        <f t="shared" ref="S10:V11" si="19">$G10/N10</f>
+        <v>18.109507065768593</v>
+      </c>
+      <c r="T10" s="15">
+        <f t="shared" si="19"/>
+        <v>17.425552062495161</v>
+      </c>
+      <c r="U10" s="15">
+        <f t="shared" si="19"/>
+        <v>16.980548491537299</v>
+      </c>
+      <c r="V10" s="15">
+        <f t="shared" si="19"/>
+        <v>16.54848983039788</v>
+      </c>
+      <c r="W10" s="15">
+        <f>G10/[7]Model!$AJ$18</f>
+        <v>15.067564901776834</v>
+      </c>
       <c r="X10" s="14">
-        <f>[6]Model!$Y$5</f>
+        <f>[7]Model!$Y$5</f>
         <v>41033</v>
       </c>
       <c r="Y10" s="20">
-        <f t="shared" ref="Y10:Y11" si="5">G10/X10</f>
+        <f t="shared" ref="Y10:Y11" si="20">G10/X10</f>
         <v>1.961746277386494</v>
       </c>
       <c r="Z10" s="16">
-        <f>[6]Model!X$24</f>
+        <f>[7]Model!X$24</f>
         <v>7.3438609912026775E-2</v>
       </c>
       <c r="AA10" s="16">
-        <f>[6]Model!Y$24</f>
+        <f>[7]Model!Y$24</f>
         <v>4.4362433189106598E-2</v>
       </c>
       <c r="AB10" s="16">
-        <f>[6]Model!$Y$27</f>
+        <f>[7]Model!$Y$27</f>
         <v>0.20378719567177639</v>
       </c>
       <c r="AC10" s="16">
-        <f>[6]Model!$Y$29</f>
+        <f>[7]Model!$Y$29</f>
         <v>0.10649964662588648</v>
+      </c>
+      <c r="AD10" s="16">
+        <f>[7]Model!$AM$24</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE10" s="16">
+        <f>[7]Model!$AM$30</f>
+        <v>-0.31348981866726999</v>
+      </c>
+      <c r="AF10" s="11" t="str">
+        <f>[7]Model!$AM$31</f>
+        <v>Overvalued</v>
       </c>
       <c r="AH10" s="11">
         <v>1939</v>
       </c>
       <c r="AJ10" s="18">
-        <f>[6]Main!$E$3</f>
+        <f>[7]Main!$E$3</f>
         <v>45771</v>
       </c>
       <c r="AK10" s="18">
-        <f>[6]Main!$G$3</f>
+        <f>[7]Main!$G$3</f>
         <v>45862</v>
       </c>
     </row>
@@ -2627,98 +3063,130 @@
         <v>65</v>
       </c>
       <c r="D11" s="13">
-        <f>[7]Main!$D$3</f>
+        <f>[8]Main!$D$3</f>
         <v>265.69</v>
       </c>
       <c r="E11" s="14">
-        <f>[7]Main!$D$5</f>
+        <f>[8]Main!$D$5</f>
         <v>71311.195999999996</v>
       </c>
       <c r="F11" s="14">
-        <f>[7]Main!$D$8</f>
+        <f>[8]Main!$D$8</f>
         <v>-8367</v>
       </c>
       <c r="G11" s="14">
-        <f>[7]Main!$D$9</f>
+        <f>[8]Main!$D$9</f>
         <v>79678.195999999996</v>
       </c>
       <c r="H11" s="14">
-        <f>[7]Model!W$16</f>
+        <f>[8]Model!W$16</f>
         <v>3484</v>
       </c>
       <c r="I11" s="14">
-        <f>[7]Model!X$16</f>
+        <f>[8]Model!X$16</f>
         <v>3167</v>
       </c>
       <c r="J11" s="14">
-        <f>[7]Model!Y$16</f>
+        <f>[8]Model!Y$16</f>
         <v>3257</v>
       </c>
       <c r="K11" s="14">
-        <f>[7]Model!Z$16</f>
+        <f>[8]Model!Z$16</f>
         <v>3390</v>
       </c>
       <c r="L11" s="14">
-        <f>[7]Model!AA$16</f>
+        <f>[8]Model!AA$16</f>
         <v>3315</v>
       </c>
       <c r="M11" s="14">
-        <f>[7]Model!AB$16</f>
+        <f>[8]Model!AB$16</f>
         <v>3782</v>
       </c>
       <c r="N11" s="14">
-        <f>[7]Model!AC$16</f>
-        <v>0</v>
+        <f>[8]Model!AC$16</f>
+        <v>4065.2781650000034</v>
       </c>
       <c r="O11" s="14">
-        <f>[7]Model!AD$16</f>
-        <v>0</v>
+        <f>[8]Model!AD$16</f>
+        <v>4316.3812148500065</v>
       </c>
       <c r="P11" s="14">
-        <f>[7]Model!AE$16</f>
-        <v>0</v>
+        <f>[8]Model!AE$16</f>
+        <v>4535.0469065479992</v>
       </c>
       <c r="Q11" s="14">
-        <f>[7]Model!AF$16</f>
-        <v>0</v>
+        <f>[8]Model!AF$16</f>
+        <v>4720.710356326842</v>
       </c>
       <c r="R11" s="15">
-        <f t="shared" ref="R11" si="6">$G11/M11</f>
+        <f t="shared" ref="R11" si="21">$G11/M11</f>
         <v>21.067740877842411</v>
       </c>
+      <c r="S11" s="15">
+        <f t="shared" si="19"/>
+        <v>19.599691033688448</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="19"/>
+        <v>18.459490029721298</v>
+      </c>
+      <c r="U11" s="15">
+        <f t="shared" si="19"/>
+        <v>17.569431505759152</v>
+      </c>
+      <c r="V11" s="15">
+        <f t="shared" si="19"/>
+        <v>16.878433537701124</v>
+      </c>
+      <c r="W11" s="15">
+        <f>G11/[8]Model!$AM$16</f>
+        <v>14.760827051025377</v>
+      </c>
       <c r="X11" s="14">
-        <f>[7]Model!$AB$5</f>
+        <f>[8]Model!$AB$5</f>
         <v>47716</v>
       </c>
       <c r="Y11" s="20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="20"/>
         <v>1.6698423170425014</v>
       </c>
       <c r="Z11" s="16">
-        <f>[7]Model!$AA$22</f>
+        <f>[8]Model!$AA$22</f>
         <v>7.2702819296064147E-2</v>
       </c>
       <c r="AA11" s="16">
-        <f>[7]Model!$AB$22</f>
+        <f>[8]Model!$AB$22</f>
         <v>0.12878501135503417</v>
       </c>
       <c r="AB11" s="16">
-        <f>[7]Model!$AB$25</f>
+        <f>[8]Model!$AB$25</f>
         <v>0.15432978455863861</v>
       </c>
       <c r="AC11" s="16">
-        <f>[7]Model!$AB$27</f>
+        <f>[8]Model!$AB$27</f>
         <v>0.10051135887333389</v>
+      </c>
+      <c r="AD11" s="16">
+        <f>[8]Model!$AP$22</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE11" s="16">
+        <f>[8]Model!$AP$28</f>
+        <v>-0.28201653867212506</v>
+      </c>
+      <c r="AF11" s="11" t="str">
+        <f>[8]Model!$AP$29</f>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AH11" s="11">
         <v>1952</v>
       </c>
       <c r="AJ11" s="18">
-        <f>[7]Main!$E$3</f>
+        <f>[8]Main!$E$3</f>
         <v>45771</v>
       </c>
       <c r="AK11" s="18">
-        <f>[7]Main!$G$3</f>
+        <f>[8]Main!$G$3</f>
         <v>45861</v>
       </c>
     </row>
@@ -2738,56 +3206,56 @@
         <v>41</v>
       </c>
       <c r="D13" s="17">
-        <f>[8]Main!$D$3</f>
+        <f>[9]Main!$D$3</f>
         <v>1417</v>
       </c>
       <c r="E13" s="14">
-        <f>[8]Main!$D$5</f>
+        <f>[9]Main!$D$5</f>
         <v>61540.31</v>
       </c>
       <c r="F13" s="14">
-        <f>[8]Main!$D$8</f>
+        <f>[9]Main!$D$8</f>
         <v>-893</v>
       </c>
       <c r="G13" s="14">
-        <f>[8]Main!$D$9</f>
+        <f>[9]Main!$D$9</f>
         <v>62433.31</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14">
-        <f>[8]Model!Y$37</f>
+        <f>[9]Model!Y$37</f>
         <v>0</v>
       </c>
       <c r="J13" s="14">
-        <f>[8]Model!Z$37</f>
+        <f>[9]Model!Z$37</f>
         <v>-27</v>
       </c>
       <c r="K13" s="14">
-        <f>[8]Model!AA$37</f>
+        <f>[9]Model!AA$37</f>
         <v>291</v>
       </c>
       <c r="L13" s="14">
-        <f>[8]Model!AB$37</f>
+        <f>[9]Model!AB$37</f>
         <v>476</v>
       </c>
       <c r="M13" s="14">
-        <f>[8]Model!AC$37</f>
+        <f>[9]Model!AC$37</f>
         <v>534</v>
       </c>
       <c r="N13" s="14">
-        <f>[8]Model!AD$37</f>
+        <f>[9]Model!AD$37</f>
         <v>717</v>
       </c>
       <c r="O13" s="14">
-        <f>[8]Model!AE$37</f>
+        <f>[9]Model!AE$37</f>
         <v>1183.5057150000023</v>
       </c>
       <c r="P13" s="14">
-        <f>[8]Model!AF$37</f>
+        <f>[9]Model!AF$37</f>
         <v>1446.6646025</v>
       </c>
       <c r="Q13" s="14">
-        <f>[8]Model!AG$37</f>
+        <f>[9]Model!AG$37</f>
         <v>1594.3621815874999</v>
       </c>
       <c r="R13" s="15">
@@ -2795,70 +3263,70 @@
         <v>116.91631086142321</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" ref="S13:V13" si="7">$G13/N13</f>
+        <f t="shared" ref="S13:V14" si="22">$G13/N13</f>
         <v>87.07574616457461</v>
       </c>
       <c r="T13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>52.752858907825278</v>
       </c>
       <c r="U13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>43.156727476505736</v>
       </c>
       <c r="V13" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="22"/>
         <v>39.158800127732214</v>
       </c>
       <c r="W13" s="15">
-        <f>G13/[8]Model!$AN$37</f>
+        <f>G13/[9]Model!$AN$37</f>
         <v>32.332214391558495</v>
       </c>
       <c r="X13" s="14">
-        <f>[8]Model!$AC$18</f>
+        <f>[9]Model!$AC$18</f>
         <v>7175</v>
       </c>
       <c r="Y13" s="20">
-        <f t="shared" ref="Y13:Y14" si="8">G13/X13</f>
+        <f t="shared" ref="Y13:Y14" si="23">G13/X13</f>
         <v>8.7015066202090594</v>
       </c>
       <c r="Z13" s="16">
-        <f>[8]Model!$AB$49</f>
+        <f>[9]Model!$AB$49</f>
         <v>0.1327089591800672</v>
       </c>
       <c r="AA13" s="16">
-        <f>[8]Model!$AC$49</f>
+        <f>[9]Model!$AC$49</f>
         <v>0.11934477379095165</v>
       </c>
       <c r="AB13" s="16">
-        <f>[8]Model!$AC$51</f>
+        <f>[9]Model!$AC$51</f>
         <v>0.26327526132404183</v>
       </c>
       <c r="AC13" s="16">
-        <f>[8]Model!$AC$56</f>
+        <f>[9]Model!$AC$56</f>
         <v>0.11777003484320557</v>
       </c>
       <c r="AD13" s="16">
-        <f>[8]Model!$AS$46</f>
+        <f>[9]Model!$AS$46</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE13" s="16">
-        <f>[8]Model!$AS$52</f>
+        <f>[9]Model!$AS$52</f>
         <v>-0.62242636061307977</v>
       </c>
       <c r="AF13" s="11" t="str">
-        <f>[8]Model!$AS$53</f>
+        <f>[9]Model!$AS$53</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AH13" s="11">
         <v>1927</v>
       </c>
       <c r="AJ13" s="18">
-        <f>[8]Main!$F$3</f>
+        <f>[9]Main!$F$3</f>
         <v>45734</v>
       </c>
       <c r="AK13" s="18">
-        <f>[8]Main!$H$3</f>
+        <f>[9]Main!$H$3</f>
         <v>45455</v>
       </c>
     </row>
@@ -2870,94 +3338,126 @@
         <v>66</v>
       </c>
       <c r="D14" s="13">
-        <f>[9]Main!$D$3</f>
+        <f>[10]Main!$D$3</f>
         <v>212.27</v>
       </c>
       <c r="E14" s="14">
-        <f>[9]Main!$D$5</f>
+        <f>[10]Main!$D$5</f>
         <v>39970.441000000006</v>
       </c>
       <c r="F14" s="14">
-        <f>[9]Main!$D$8</f>
+        <f>[10]Main!$D$8</f>
         <v>-11621</v>
       </c>
       <c r="G14" s="14">
-        <f>[9]Main!$D$9</f>
+        <f>[10]Main!$D$9</f>
         <v>51591.441000000006</v>
       </c>
       <c r="I14" s="14">
-        <f>[9]Model!T$18</f>
+        <f>[10]Model!T$18</f>
         <v>1119</v>
       </c>
       <c r="J14" s="14">
-        <f>[9]Model!U$18</f>
+        <f>[10]Model!U$18</f>
         <v>1846</v>
       </c>
       <c r="K14" s="14">
-        <f>[9]Model!V$18</f>
+        <f>[10]Model!V$18</f>
         <v>1062</v>
       </c>
       <c r="L14" s="14">
-        <f>[9]Model!W$18</f>
+        <f>[10]Model!W$18</f>
         <v>1227</v>
       </c>
       <c r="M14" s="14">
-        <f>[9]Model!X$18</f>
+        <f>[10]Model!X$18</f>
         <v>1502</v>
       </c>
       <c r="N14" s="14">
-        <f>[9]Model!Y$18</f>
-        <v>0</v>
+        <f>[10]Model!Y$18</f>
+        <v>1666.6471800000006</v>
       </c>
       <c r="O14" s="14">
-        <f>[9]Model!Z$18</f>
-        <v>0</v>
+        <f>[10]Model!Z$18</f>
+        <v>1795.3686990000031</v>
       </c>
       <c r="P14" s="14">
-        <f>[9]Model!AA$18</f>
-        <v>0</v>
+        <f>[10]Model!AA$18</f>
+        <v>1911.0909576599986</v>
       </c>
       <c r="Q14" s="14">
-        <f>[9]Model!AB$18</f>
-        <v>0</v>
+        <f>[10]Model!AB$18</f>
+        <v>2010.4950586877997</v>
       </c>
       <c r="R14" s="15">
         <f>$G14/M14</f>
         <v>34.348496005326233</v>
       </c>
+      <c r="S14" s="15">
+        <f t="shared" si="22"/>
+        <v>30.955226528508565</v>
+      </c>
+      <c r="T14" s="15">
+        <f t="shared" si="22"/>
+        <v>28.735847421610817</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="22"/>
+        <v>26.995806135344928</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="22"/>
+        <v>25.661063317247077</v>
+      </c>
+      <c r="W14" s="15">
+        <f>G14/[10]Model!$AI$18</f>
+        <v>18.839274711369718</v>
+      </c>
       <c r="X14" s="14">
-        <f>[9]Model!$X$5</f>
+        <f>[10]Model!$X$5</f>
         <v>21325</v>
       </c>
       <c r="Y14" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="23"/>
         <v>2.4192938335287226</v>
       </c>
       <c r="Z14" s="16">
-        <f>[9]Model!$W$24</f>
+        <f>[10]Model!$W$24</f>
         <v>0.13814324229281438</v>
       </c>
       <c r="AA14" s="16">
-        <f>[9]Model!$X$24</f>
+        <f>[10]Model!$X$24</f>
         <v>9.815129512333276E-2</v>
       </c>
       <c r="AB14" s="16">
-        <f>[9]Model!$X$27</f>
+        <f>[10]Model!$X$27</f>
         <v>0.25903868698710436</v>
       </c>
       <c r="AC14" s="16">
-        <f>[9]Model!$X$29</f>
+        <f>[10]Model!$X$29</f>
         <v>8.9941383352872217E-2</v>
+      </c>
+      <c r="AD14" s="16">
+        <f>[10]Model!$AL$24</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE14" s="16">
+        <f>[10]Model!$AL$30</f>
+        <v>-0.58739207901404</v>
+      </c>
+      <c r="AF14" s="11" t="str">
+        <f>[10]Model!$AL$31</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AH14" s="11">
         <v>1890</v>
       </c>
       <c r="AJ14" s="18">
-        <f>[9]Main!$E$3</f>
+        <f>[10]Main!$E$3</f>
         <v>45771</v>
       </c>
       <c r="AK14" s="18">
-        <f>[9]Main!$G$3</f>
+        <f>[10]Main!$G$3</f>
         <v>45771</v>
       </c>
     </row>
@@ -2993,87 +3493,87 @@
         <v>58</v>
       </c>
       <c r="D18" s="17">
-        <f>[10]Main!$D$3</f>
+        <f>[11]Main!$D$3</f>
         <v>46.45</v>
       </c>
       <c r="E18" s="14">
-        <f>[10]Main!$D$5</f>
+        <f>[11]Main!$D$5</f>
         <v>26736.620000000003</v>
       </c>
       <c r="F18" s="14">
-        <f>[10]Main!$D$8</f>
+        <f>[11]Main!$D$8</f>
         <v>-267</v>
       </c>
       <c r="G18" s="14">
-        <f>[10]Main!$D$9</f>
+        <f>[11]Main!$D$9</f>
         <v>27003.620000000003</v>
       </c>
       <c r="H18" s="14">
-        <f>[10]Model!T$18</f>
+        <f>[11]Model!T$18</f>
         <v>823</v>
       </c>
       <c r="I18" s="14">
-        <f>[10]Model!U$18</f>
+        <f>[11]Model!U$18</f>
         <v>239</v>
       </c>
       <c r="J18" s="14">
-        <f>[10]Model!V$18</f>
+        <f>[11]Model!V$18</f>
         <v>586</v>
       </c>
       <c r="K18" s="14">
-        <f>[10]Model!W$18</f>
+        <f>[11]Model!W$18</f>
         <v>927</v>
       </c>
       <c r="L18" s="14">
-        <f>[10]Model!X$18</f>
+        <f>[11]Model!X$18</f>
         <v>658</v>
       </c>
       <c r="M18" s="14">
-        <f>[10]Model!Y$18</f>
+        <f>[11]Model!Y$18</f>
         <v>1072</v>
       </c>
       <c r="N18" s="14">
-        <f>[10]Model!Z$18</f>
+        <f>[11]Model!Z$18</f>
         <v>1019.06265</v>
       </c>
       <c r="O18" s="14">
-        <f>[10]Model!AA$18</f>
+        <f>[11]Model!AA$18</f>
         <v>1838.0187149999997</v>
       </c>
       <c r="P18" s="14">
-        <f>[10]Model!AB$18</f>
+        <f>[11]Model!AB$18</f>
         <v>1923.3074602500005</v>
       </c>
       <c r="Q18" s="14">
-        <f>[10]Model!AC$18</f>
+        <f>[11]Model!AC$18</f>
         <v>2000.3647039200005</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" ref="R18:V18" si="9">$G18/M18</f>
+        <f t="shared" ref="R18:V18" si="24">$G18/M18</f>
         <v>25.18994402985075</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>26.498488586545687</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>14.691700242018486</v>
       </c>
       <c r="U18" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>14.040199270318405</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="24"/>
         <v>13.499348367366487</v>
       </c>
       <c r="W18" s="15">
-        <f>G18/[10]Model!$AJ$18</f>
+        <f>G18/[11]Model!$AJ$18</f>
         <v>11.637538166893249</v>
       </c>
       <c r="X18" s="14">
-        <f>[10]Model!$Y$3</f>
+        <f>[11]Model!$Y$3</f>
         <v>17763</v>
       </c>
       <c r="Y18" s="20">
@@ -3081,42 +3581,42 @@
         <v>1.5202173056353094</v>
       </c>
       <c r="Z18" s="16">
-        <f>[10]Model!$X$22</f>
+        <f>[11]Model!$X$22</f>
         <v>3.9284986066743688E-2</v>
       </c>
       <c r="AA18" s="16">
-        <f>[10]Model!$Y$22</f>
+        <f>[11]Model!$Y$22</f>
         <v>0.1616637237590739</v>
       </c>
       <c r="AB18" s="16">
-        <f>[10]Model!$Y$23</f>
+        <f>[11]Model!$Y$23</f>
         <v>0.11349434217193041</v>
       </c>
       <c r="AC18" s="16">
-        <f>[10]Model!$Y$25</f>
+        <f>[11]Model!$Y$25</f>
         <v>6.6430220120475142E-2</v>
       </c>
       <c r="AD18" s="16">
-        <f>[10]Model!$AM$24</f>
+        <f>[11]Model!$AM$24</f>
         <v>0.08</v>
       </c>
       <c r="AE18" s="16">
-        <f>[10]Model!$AM$30</f>
+        <f>[11]Model!$AM$30</f>
         <v>-8.2951850912037273E-2</v>
       </c>
       <c r="AF18" s="11" t="str">
-        <f>[10]Model!$AM$31</f>
+        <f>[11]Model!$AM$31</f>
         <v>Fairly valued</v>
       </c>
       <c r="AH18" s="11">
         <v>1996</v>
       </c>
       <c r="AJ18" s="18">
-        <f>[10]Main!$E$3</f>
+        <f>[11]Main!$E$3</f>
         <v>45736</v>
       </c>
       <c r="AK18" s="18">
-        <f>[10]Main!$G$3</f>
+        <f>[11]Main!$G$3</f>
         <v>45868</v>
       </c>
     </row>
@@ -3135,6 +3635,9 @@
       <c r="C20" s="11" t="s">
         <v>71</v>
       </c>
+      <c r="AG20" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
@@ -3144,51 +3647,51 @@
         <v>56</v>
       </c>
       <c r="D21" s="13">
-        <f>[11]Main!$D$3</f>
+        <f>[12]Main!$D$3</f>
         <v>7.21</v>
       </c>
       <c r="E21" s="14">
-        <f>[11]Main!$D$5</f>
+        <f>[12]Main!$D$5</f>
         <v>59.843000000000004</v>
       </c>
       <c r="F21" s="14">
-        <f>[11]Main!$D$8</f>
+        <f>[12]Main!$D$8</f>
         <v>-1.3</v>
       </c>
       <c r="G21" s="14">
-        <f>[11]Main!$D$9</f>
+        <f>[12]Main!$D$9</f>
         <v>61.143000000000001</v>
       </c>
       <c r="L21" s="14">
-        <f>[11]Model!$P$20</f>
+        <f>[12]Model!$P$20</f>
         <v>-1.4</v>
       </c>
       <c r="M21" s="14">
-        <f>[11]Model!Q$20</f>
+        <f>[12]Model!Q$20</f>
         <v>-6.3999999999999995</v>
       </c>
       <c r="N21" s="14">
-        <f>[11]Model!R$20</f>
+        <f>[12]Model!R$20</f>
         <v>-7.4699999999999989</v>
       </c>
       <c r="O21" s="14">
-        <f>[11]Model!S$20</f>
+        <f>[12]Model!S$20</f>
         <v>-9.5558799999999984</v>
       </c>
       <c r="P21" s="14">
-        <f>[11]Model!T$20</f>
+        <f>[12]Model!T$20</f>
         <v>-10.959568000000001</v>
       </c>
       <c r="Q21" s="14">
-        <f>[11]Model!U$20</f>
+        <f>[12]Model!U$20</f>
         <v>-11.357623199999999</v>
       </c>
       <c r="W21" s="15">
-        <f>G21/[11]Model!$AB$20</f>
+        <f>G21/[12]Model!$AB$20</f>
         <v>1.6899351470068711</v>
       </c>
       <c r="X21" s="14">
-        <f>[11]Model!$Q$3</f>
+        <f>[12]Model!$Q$3</f>
         <v>5.5</v>
       </c>
       <c r="Y21" s="20">
@@ -3196,23 +3699,23 @@
         <v>11.116909090909092</v>
       </c>
       <c r="AB21" s="16">
-        <f>[11]Model!$Q$26</f>
+        <f>[12]Model!$Q$26</f>
         <v>0.27272727272727271</v>
       </c>
       <c r="AC21" s="16">
-        <f>[11]Model!$Q$30</f>
+        <f>[12]Model!$Q$30</f>
         <v>-1.0363636363636362</v>
       </c>
       <c r="AD21" s="16">
-        <f>[11]Model!$AF$27</f>
+        <f>[12]Model!$AF$27</f>
         <v>0.13</v>
       </c>
       <c r="AE21" s="16">
-        <f>[11]Model!$AF$33</f>
+        <f>[12]Model!$AF$33</f>
         <v>-0.23973616282793675</v>
       </c>
       <c r="AF21" s="11" t="str">
-        <f>[11]Model!$AF$34</f>
+        <f>[12]Model!$AF$34</f>
         <v>Overvalued</v>
       </c>
       <c r="AG21" s="11" t="s">
@@ -3222,12 +3725,17 @@
         <v>2019</v>
       </c>
       <c r="AJ21" s="18">
-        <f>[11]Main!$E$3</f>
+        <f>[12]Main!$E$3</f>
         <v>45736</v>
       </c>
       <c r="AK21" s="18">
-        <f>[11]Main!$G$3</f>
+        <f>[12]Main!$G$3</f>
         <v>45743</v>
+      </c>
+    </row>
+    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/Models (Defence).xlsx
+++ b/Financial Analysis/Models (Defence).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F0E585-9AED-4F95-96EB-78DC192A4C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1A53C0-7D59-4903-A043-48085823E309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
   </bookViews>
@@ -28,6 +28,18 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
+    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
+    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Company</t>
   </si>
@@ -92,9 +104,6 @@
     <t>2028 EV/E</t>
   </si>
   <si>
-    <t>2023 RevG</t>
-  </si>
-  <si>
     <t>Discount</t>
   </si>
   <si>
@@ -194,27 +203,15 @@
     <t>2035 EV/E</t>
   </si>
   <si>
-    <t>2024 Rev</t>
-  </si>
-  <si>
     <t>2024 RevG</t>
   </si>
   <si>
-    <t>2024 GM%</t>
-  </si>
-  <si>
-    <t>2024 OM%</t>
-  </si>
-  <si>
     <t>Unusual Machines</t>
   </si>
   <si>
     <t>UMAC US</t>
   </si>
   <si>
-    <t>Drones</t>
-  </si>
-  <si>
     <t>LDO IT</t>
   </si>
   <si>
@@ -257,27 +254,76 @@
     <t>RCAT US</t>
   </si>
   <si>
-    <t>2024 EV/R</t>
-  </si>
-  <si>
-    <t>Air</t>
-  </si>
-  <si>
     <t>Embraer</t>
+  </si>
+  <si>
+    <t>Kratos</t>
+  </si>
+  <si>
+    <t>Bombardier</t>
+  </si>
+  <si>
+    <t>Textron</t>
+  </si>
+  <si>
+    <t>TXT US</t>
+  </si>
+  <si>
+    <t>Renk</t>
+  </si>
+  <si>
+    <t>Hensoldt</t>
+  </si>
+  <si>
+    <t>Leidos</t>
+  </si>
+  <si>
+    <t>LDOS US</t>
+  </si>
+  <si>
+    <t>R3NK DE</t>
+  </si>
+  <si>
+    <t>HAG DE</t>
+  </si>
+  <si>
+    <t>ERJ US</t>
+  </si>
+  <si>
+    <t>2025 Rev</t>
+  </si>
+  <si>
+    <t>2025 RevG</t>
+  </si>
+  <si>
+    <t>2025 GM%</t>
+  </si>
+  <si>
+    <t>2025 OM%</t>
+  </si>
+  <si>
+    <t>2025 EV/R</t>
+  </si>
+  <si>
+    <t>KTOS US</t>
+  </si>
+  <si>
+    <t>BBD.A CA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="[$€-2]\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
+    <numFmt numFmtId="169" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +380,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -377,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -432,6 +486,21 @@
     <xf numFmtId="168" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -459,40 +528,41 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Charts"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>119.35</v>
+            <v>157.52000000000001</v>
           </cell>
           <cell r="E3">
-            <v>45770</v>
+            <v>45906</v>
           </cell>
           <cell r="G3">
-            <v>45867</v>
+            <v>45958</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>159451.6</v>
+            <v>210840.52000000002</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-36143</v>
+            <v>-37196</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>195594.6</v>
+            <v>248036.52000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="Z5">
-            <v>80738</v>
+          <cell r="AA5">
+            <v>87203.32</v>
           </cell>
         </row>
         <row r="19">
@@ -515,27 +585,27 @@
             <v>4774</v>
           </cell>
           <cell r="AA19">
-            <v>5935.5916480000114</v>
+            <v>6597.7138400000167</v>
           </cell>
           <cell r="AB19">
-            <v>6317.3871904000098</v>
+            <v>7570.8374651199974</v>
           </cell>
           <cell r="AC19">
-            <v>6584.8417255040049</v>
+            <v>8157.0804411392028</v>
           </cell>
           <cell r="AD19">
-            <v>6768.4778666953616</v>
+            <v>8502.7527649675394</v>
           </cell>
           <cell r="AK19">
-            <v>8025.7232492214553</v>
+            <v>10539.84925860564</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="Y25">
-            <v>2.7521841548140857E-2</v>
-          </cell>
           <cell r="Z25">
             <v>0.17147417295414979</v>
+          </cell>
+          <cell r="AA25">
+            <v>8.0077782456835722E-2</v>
           </cell>
         </row>
         <row r="26">
@@ -544,26 +614,27 @@
           </cell>
         </row>
         <row r="28">
-          <cell r="Z28">
-            <v>0.19086427704426664</v>
+          <cell r="AA28">
+            <v>0.2026911899684555</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="Z31">
-            <v>8.2612896034085559E-2</v>
+          <cell r="AA31">
+            <v>9.8853831482562993E-2</v>
           </cell>
         </row>
         <row r="32">
           <cell r="AO32">
-            <v>-0.50646520170582687</v>
+            <v>-0.47755291681370626</v>
           </cell>
         </row>
         <row r="33">
           <cell r="AO33" t="str">
-            <v>Heavily overvalued</v>
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -583,98 +654,103 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>212.27</v>
+            <v>10.7</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45898</v>
           </cell>
           <cell r="G3">
-            <v>45771</v>
+            <v>46079</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>39970.441000000006</v>
+            <v>90201</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-11621</v>
+            <v>2379</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>51591.441000000006</v>
+            <v>87822</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="X5">
-            <v>21325</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="T18">
-            <v>1119</v>
-          </cell>
-          <cell r="U18">
-            <v>1846</v>
-          </cell>
-          <cell r="V18">
-            <v>1062</v>
-          </cell>
-          <cell r="W18">
-            <v>1227</v>
-          </cell>
-          <cell r="X18">
-            <v>1502</v>
-          </cell>
-          <cell r="Y18">
-            <v>1666.6471800000006</v>
-          </cell>
-          <cell r="Z18">
-            <v>1795.3686990000031</v>
-          </cell>
-          <cell r="AA18">
-            <v>1911.0909576599986</v>
-          </cell>
-          <cell r="AB18">
-            <v>2010.4950586877997</v>
-          </cell>
-          <cell r="AI18">
-            <v>2738.5046287829741</v>
+        <row r="3">
+          <cell r="Q3">
+            <v>18909</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="L16">
+            <v>-1315</v>
+          </cell>
+          <cell r="M16">
+            <v>-3170</v>
+          </cell>
+          <cell r="N16">
+            <v>120</v>
+          </cell>
+          <cell r="O16">
+            <v>-1269</v>
+          </cell>
+          <cell r="P16">
+            <v>2412</v>
+          </cell>
+          <cell r="Q16">
+            <v>1971</v>
+          </cell>
+          <cell r="R16">
+            <v>1792.7340799999997</v>
+          </cell>
+          <cell r="S16">
+            <v>2039.0654464000004</v>
+          </cell>
+          <cell r="T16">
+            <v>2250.0783875840002</v>
+          </cell>
+          <cell r="U16">
+            <v>2444.7265855552005</v>
+          </cell>
+          <cell r="AB16">
+            <v>3492.9910972745047</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="P20">
+            <v>0.21937869822485201</v>
+          </cell>
+          <cell r="Q20">
+            <v>0.14697318937280124</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Q21">
+            <v>0.22322703474535935</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="AE22">
+            <v>7.0000000000000007E-2</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="W24">
-            <v>0.13814324229281438</v>
-          </cell>
-          <cell r="X24">
-            <v>9.815129512333276E-2</v>
-          </cell>
-          <cell r="AL24">
-            <v>0.08</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="X27">
-            <v>0.25903868698710436</v>
+          <cell r="Q24">
+            <v>0.12459675286900418</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AE28">
+            <v>-0.53007610364432378</v>
           </cell>
         </row>
         <row r="29">
-          <cell r="X29">
-            <v>8.9941383352872217E-2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AL30">
-            <v>-0.58739207901404</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AL31" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="AE29" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -697,102 +773,94 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>46.45</v>
+            <v>19.254999999999999</v>
           </cell>
           <cell r="E3">
-            <v>45736</v>
+            <v>45868</v>
           </cell>
           <cell r="G3">
-            <v>45868</v>
+            <v>46072</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>26736.620000000003</v>
+            <v>57765</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-267</v>
+            <v>-4907</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>27003.620000000003</v>
+            <v>62672</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="Y3">
-            <v>17763</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="T18">
-            <v>823</v>
-          </cell>
-          <cell r="U18">
-            <v>239</v>
-          </cell>
-          <cell r="V18">
-            <v>586</v>
-          </cell>
-          <cell r="W18">
-            <v>927</v>
-          </cell>
-          <cell r="X18">
-            <v>658</v>
-          </cell>
-          <cell r="Y18">
-            <v>1072</v>
-          </cell>
-          <cell r="Z18">
-            <v>1019.06265</v>
-          </cell>
-          <cell r="AA18">
-            <v>1838.0187149999997</v>
-          </cell>
-          <cell r="AB18">
-            <v>1923.3074602500005</v>
-          </cell>
-          <cell r="AC18">
-            <v>2000.3647039200005</v>
-          </cell>
-          <cell r="AJ18">
-            <v>2320.3893824228699</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="X22">
-            <v>3.9284986066743688E-2</v>
-          </cell>
-          <cell r="Y22">
-            <v>0.1616637237590739</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="Y23">
-            <v>0.11349434217193041</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="AM24">
-            <v>0.08</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="Y25">
-            <v>6.6430220120475142E-2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AM30">
-            <v>-8.2951850912037273E-2</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AM31" t="str">
+        <row r="13">
+          <cell r="Q13">
+            <v>26312</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="N32">
+            <v>1758</v>
+          </cell>
+          <cell r="O32">
+            <v>1591</v>
+          </cell>
+          <cell r="P32">
+            <v>1857</v>
+          </cell>
+          <cell r="Q32">
+            <v>1956</v>
+          </cell>
+          <cell r="R32">
+            <v>2983.0295450000012</v>
+          </cell>
+          <cell r="S32">
+            <v>3274.0576822999979</v>
+          </cell>
+          <cell r="T32">
+            <v>3558.6704355280026</v>
+          </cell>
+          <cell r="U32">
+            <v>3774.8694653950824</v>
+          </cell>
+          <cell r="AB32">
+            <v>4907.2226055251313</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="AE39">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="P41">
+            <v>8.5614827359111967E-2</v>
+          </cell>
+          <cell r="Q41">
+            <v>0.14013346043851294</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="Q42">
+            <v>0.65472027972027969</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Q45">
+            <v>8.3840072970507759E-2</v>
+          </cell>
+          <cell r="AE45">
+            <v>-7.0527347483917202E-2</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AE46" t="str">
             <v>Fairly valued</v>
           </cell>
         </row>
@@ -816,82 +884,875 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>7.21</v>
+            <v>277.22000000000003</v>
           </cell>
           <cell r="E3">
-            <v>45736</v>
+            <v>45898</v>
           </cell>
           <cell r="G3">
-            <v>45743</v>
+            <v>45953</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>59.843000000000004</v>
+            <v>51867.862000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-1.3</v>
+            <v>-11620</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>61.143000000000001</v>
+            <v>63487.862000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="5">
+          <cell r="X5">
+            <v>21325</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="T18">
+            <v>1119</v>
+          </cell>
+          <cell r="U18">
+            <v>1846</v>
+          </cell>
+          <cell r="V18">
+            <v>1062</v>
+          </cell>
+          <cell r="W18">
+            <v>1227</v>
+          </cell>
+          <cell r="X18">
+            <v>1502</v>
+          </cell>
+          <cell r="Y18">
+            <v>2244.6631800000009</v>
+          </cell>
+          <cell r="Z18">
+            <v>2396.5053390000035</v>
+          </cell>
+          <cell r="AA18">
+            <v>2530.2616968599991</v>
+          </cell>
+          <cell r="AB18">
+            <v>2642.0492126718009</v>
+          </cell>
+          <cell r="AI18">
+            <v>3415.6161640392561</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="W24">
+            <v>0.13814324229281438</v>
+          </cell>
+          <cell r="X24">
+            <v>9.815129512333276E-2</v>
+          </cell>
+          <cell r="AL24">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="X27">
+            <v>0.25903868698710436</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="X29">
+            <v>8.9941383352872217E-2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AL30">
+            <v>-0.5363754386448315</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AL31" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>235.1</v>
+          </cell>
+          <cell r="E3">
+            <v>45868</v>
+          </cell>
+          <cell r="G3">
+            <v>46079</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>48289.54</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-1408.0999999999995</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>49697.64</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="Q3">
-            <v>5.5</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="P20">
-            <v>-1.4</v>
-          </cell>
-          <cell r="Q20">
-            <v>-6.3999999999999995</v>
-          </cell>
-          <cell r="R20">
-            <v>-7.4699999999999989</v>
-          </cell>
-          <cell r="S20">
-            <v>-9.5558799999999984</v>
-          </cell>
-          <cell r="T20">
-            <v>-10.959568000000001</v>
-          </cell>
-          <cell r="U20">
-            <v>-11.357623199999999</v>
-          </cell>
-          <cell r="AB20">
-            <v>36.180678358156783</v>
+          <cell r="P3">
+            <v>20576.599999999999</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>1146.4000000000005</v>
+          </cell>
+          <cell r="L22">
+            <v>491.90000000000072</v>
+          </cell>
+          <cell r="M22">
+            <v>1016.7999999999997</v>
+          </cell>
+          <cell r="N22">
+            <v>1121.8999999999996</v>
+          </cell>
+          <cell r="O22">
+            <v>928.6000000000015</v>
+          </cell>
+          <cell r="P22">
+            <v>932.29999999999723</v>
+          </cell>
+          <cell r="Q22">
+            <v>1473.4199211999967</v>
+          </cell>
+          <cell r="R22">
+            <v>1674.1472117759988</v>
+          </cell>
+          <cell r="S22">
+            <v>1801.8286222247989</v>
+          </cell>
+          <cell r="T22">
+            <v>1905.822140949791</v>
+          </cell>
+          <cell r="AA22">
+            <v>2209.5151424104974</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="Q26">
-            <v>0.27272727272727271</v>
+          <cell r="O26">
+            <v>4.89276444606348E-2</v>
+          </cell>
+          <cell r="P26">
+            <v>0.11657007662086771</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AF27">
-            <v>0.13</v>
+          <cell r="P27">
+            <v>0.26116559587103788</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AD29">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="P31">
+            <v>6.1341523866916652E-2</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AD35">
+            <v>-0.53135711887326365</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="AD36" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>27.18</v>
+          </cell>
+          <cell r="E3">
+            <v>45868</v>
+          </cell>
+          <cell r="G3">
+            <v>46079</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>35695.493999999999</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>1459</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>34236.493999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="7">
+          <cell r="V7">
+            <v>6213.6</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Q23">
+            <v>615.30000000000064</v>
+          </cell>
+          <cell r="R23">
+            <v>491.20000000000067</v>
+          </cell>
+          <cell r="S23">
+            <v>773.79999999999905</v>
+          </cell>
+          <cell r="T23">
+            <v>931.79999999999984</v>
+          </cell>
+          <cell r="U23">
+            <v>1050.8999999999996</v>
+          </cell>
+          <cell r="V23">
+            <v>1200.3000000000002</v>
+          </cell>
+          <cell r="W23">
+            <v>1113.4564026999999</v>
+          </cell>
+          <cell r="X23">
+            <v>1422.1613657599992</v>
+          </cell>
+          <cell r="Y23">
+            <v>1443.7923014975993</v>
+          </cell>
+          <cell r="Z23">
+            <v>1456.7690142637746</v>
+          </cell>
+          <cell r="AG23">
+            <v>1728.8659382205271</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AJ29">
+            <v>0.08</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="Q30">
-            <v>-1.0363636363636362</v>
+          <cell r="U30">
+            <v>5.0500414805923599E-2</v>
+          </cell>
+          <cell r="V30">
+            <v>4.4056860570622192E-2</v>
           </cell>
         </row>
         <row r="33">
-          <cell r="AF33">
-            <v>-0.23973616282793675</v>
+          <cell r="V33">
+            <v>0.83643942320072096</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AJ35">
+            <v>-0.43497641969139733</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="AJ36" t="str">
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="V37">
+            <v>0.2188264452169435</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>47.27</v>
+          </cell>
+          <cell r="E3">
+            <v>45904</v>
+          </cell>
+          <cell r="G3">
+            <v>45868</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>27246.428</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-267</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>27513.428</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="Y3">
+            <v>17763</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="T19">
+            <v>823</v>
+          </cell>
+          <cell r="U19">
+            <v>239</v>
+          </cell>
+          <cell r="V19">
+            <v>586</v>
+          </cell>
+          <cell r="W19">
+            <v>927</v>
+          </cell>
+          <cell r="X19">
+            <v>658</v>
+          </cell>
+          <cell r="Y19">
+            <v>1072</v>
+          </cell>
+          <cell r="Z19">
+            <v>1017.2926499999999</v>
+          </cell>
+          <cell r="AA19">
+            <v>1811.8731149999999</v>
+          </cell>
+          <cell r="AB19">
+            <v>1919.0845944000002</v>
+          </cell>
+          <cell r="AC19">
+            <v>1993.765444011</v>
+          </cell>
+          <cell r="AJ19">
+            <v>2288.9705079177807</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="X23">
+            <v>3.9284986066743688E-2</v>
+          </cell>
+          <cell r="Y23">
+            <v>0.1616637237590739</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24">
+            <v>0.11349434217193041</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="AM25">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26">
+            <v>6.6430220120475142E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AM31">
+            <v>-0.10935664388414268</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="AM32" t="str">
+            <v>Fairly valued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>180.62</v>
+          </cell>
+          <cell r="E3">
+            <v>45898</v>
+          </cell>
+          <cell r="G3">
+            <v>45965</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>23173.546000000002</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-4174</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>27347.546000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="U3">
+            <v>16662</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="P18">
+            <v>667</v>
+          </cell>
+          <cell r="Q18">
+            <v>628</v>
+          </cell>
+          <cell r="R18">
+            <v>753</v>
+          </cell>
+          <cell r="S18">
+            <v>685</v>
+          </cell>
+          <cell r="T18">
+            <v>199</v>
+          </cell>
+          <cell r="U18">
+            <v>1254</v>
+          </cell>
+          <cell r="V18">
+            <v>1488.4593099999986</v>
+          </cell>
+          <cell r="W18">
+            <v>1825.4889705000001</v>
+          </cell>
+          <cell r="X18">
+            <v>1915.7253039600007</v>
+          </cell>
+          <cell r="Y18">
+            <v>1981.3585502100002</v>
+          </cell>
+          <cell r="AF18">
+            <v>2147.6986846902682</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="T22">
+            <v>7.2381217004723553E-2</v>
+          </cell>
+          <cell r="U22">
+            <v>7.9284881461329171E-2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="U23">
+            <v>0.16792701956547834</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AI24">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="U26">
+            <v>0.10731004681310767</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AI30">
+            <v>-0.15132262827852416</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AI31" t="str">
+            <v>Slightly overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>194.63</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>19287.832999999999</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-4448</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>23735.832999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="8">
+          <cell r="V8">
+            <v>9401.5300000000007</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="U23">
+            <v>370</v>
+          </cell>
+          <cell r="V23">
+            <v>501.53600000000051</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="V31">
+            <v>8.5000577034045177E-2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="V32">
+            <v>0.1980854180117492</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="V35">
+            <v>0.11177712563806108</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>78.45</v>
+          </cell>
+          <cell r="E3">
+            <v>45867</v>
+          </cell>
+          <cell r="G3">
+            <v>45953</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>13979.789999999999</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-2300</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>16279.789999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="6">
+          <cell r="U6">
+            <v>13702</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="P22">
+            <v>815</v>
+          </cell>
+          <cell r="Q22">
+            <v>309</v>
+          </cell>
+          <cell r="R22">
+            <v>746</v>
+          </cell>
+          <cell r="S22">
+            <v>861</v>
+          </cell>
+          <cell r="T22">
+            <v>921</v>
+          </cell>
+          <cell r="U22">
+            <v>824</v>
+          </cell>
+          <cell r="V22">
+            <v>1009.4089999999989</v>
+          </cell>
+          <cell r="W22">
+            <v>1260.3274750399985</v>
+          </cell>
+          <cell r="X22">
+            <v>1438.1055164480015</v>
+          </cell>
+          <cell r="Y22">
+            <v>1494.4098756374406</v>
+          </cell>
+          <cell r="AF22">
+            <v>1765.1366695542943</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="T29">
+            <v>6.3252777993628051E-2</v>
+          </cell>
+          <cell r="U29">
+            <v>1.3885843747716287E-3</v>
+          </cell>
+          <cell r="AJ29">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="U32">
+            <v>0.18260108013428697</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="U35">
+            <v>6.23996496861772E-2</v>
+          </cell>
+          <cell r="AJ35">
+            <v>3.5247218209492504E-2</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="AJ36" t="str">
+            <v>Fairly valued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>57.19</v>
+          </cell>
+          <cell r="E3">
+            <v>45903</v>
+          </cell>
+          <cell r="G3">
+            <v>45965</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>10494.365</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-600.00000000000023</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>11094.365</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="V3">
+            <v>7743.8040000000001</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="P22">
+            <v>-322.3</v>
+          </cell>
+          <cell r="Q22">
+            <v>-731.9000000000002</v>
+          </cell>
+          <cell r="R22">
+            <v>-44.700000000000145</v>
+          </cell>
+          <cell r="S22">
+            <v>-185.59999999999982</v>
+          </cell>
+          <cell r="T22">
+            <v>163.90000000000035</v>
+          </cell>
+          <cell r="U22">
+            <v>228.2000000000003</v>
+          </cell>
+          <cell r="V22">
+            <v>743.65658000000008</v>
+          </cell>
+          <cell r="W22">
+            <v>719.25833086000011</v>
+          </cell>
+          <cell r="X22">
+            <v>830.80143681460015</v>
+          </cell>
+          <cell r="Y22">
+            <v>906.37830312002222</v>
+          </cell>
+          <cell r="AF22">
+            <v>1080.8425329828647</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="T26">
+            <v>0.16041143561957627</v>
+          </cell>
+          <cell r="U26">
+            <v>0.21376103255195988</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="U27">
+            <v>0.18032120349664568</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AI28">
+            <v>0.14000000000000001</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="U31">
+            <v>8.4945345364129704E-2</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AF34" t="str">
+          <cell r="AI34">
+            <v>-0.43120780386203839</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AI35" t="str">
             <v>Overvalued</v>
           </cell>
         </row>
@@ -915,53 +1776,633 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>174.98</v>
+            <v>231.01</v>
           </cell>
           <cell r="E3">
-            <v>45770</v>
+            <v>45867</v>
           </cell>
           <cell r="G3">
-            <v>45861</v>
+            <v>45952</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>131829.932</v>
+            <v>174042.93399999998</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-29944</v>
+            <v>-29320</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>161773.932</v>
+            <v>203362.93399999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="16">
+          <cell r="AV16">
+            <v>89475.77</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AP33">
+            <v>-636</v>
+          </cell>
+          <cell r="AQ33">
+            <v>-11873</v>
+          </cell>
+          <cell r="AR33">
+            <v>-4202</v>
+          </cell>
+          <cell r="AS33">
+            <v>-4935</v>
+          </cell>
+          <cell r="AT33">
+            <v>-2222</v>
+          </cell>
+          <cell r="AU33">
+            <v>-11875</v>
+          </cell>
+          <cell r="AV33">
+            <v>-1766.719874999995</v>
+          </cell>
+          <cell r="AW33">
+            <v>2015.174950999997</v>
+          </cell>
+          <cell r="AX33">
+            <v>3280.0064038900064</v>
+          </cell>
+          <cell r="AY33">
+            <v>4389.198277423704</v>
+          </cell>
+          <cell r="BF33">
+            <v>9869.8519171971639</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="AU40">
+            <v>-0.14495976553461709</v>
+          </cell>
+          <cell r="AV40">
+            <v>0.34515642617676701</v>
+          </cell>
+          <cell r="BI40">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="AV43">
+            <v>0.11339720798155752</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AV46">
+            <v>2.0289571131939408E-3</v>
+          </cell>
+          <cell r="BI46">
+            <v>-0.50758168691846905</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="BI47" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>101.2</v>
+          </cell>
+          <cell r="E3">
+            <v>45924</v>
+          </cell>
+          <cell r="G3">
+            <v>45968</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>11739.2</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-498</v>
+          </cell>
+        </row>
         <row r="9">
-          <cell r="AU9">
-            <v>66517</v>
+          <cell r="D9">
+            <v>12237.2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="26">
+          <cell r="V26">
+            <v>2587.8199999999997</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="P43">
+            <v>5.9000000000001167</v>
+          </cell>
+          <cell r="Q43">
+            <v>-65.199999999999903</v>
+          </cell>
+          <cell r="R43">
+            <v>63</v>
+          </cell>
+          <cell r="S43">
+            <v>79</v>
+          </cell>
+          <cell r="T43">
+            <v>58</v>
+          </cell>
+          <cell r="U43">
+            <v>106</v>
+          </cell>
+          <cell r="V43">
+            <v>105.74143999999995</v>
+          </cell>
+          <cell r="W43">
+            <v>144.35987200000005</v>
+          </cell>
+          <cell r="X43">
+            <v>169.88582975999995</v>
+          </cell>
+          <cell r="Y43">
+            <v>189.70135618560002</v>
+          </cell>
+          <cell r="AF43">
+            <v>347.10423159639549</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="U47">
+            <v>0.21277747698971305</v>
+          </cell>
+          <cell r="V47">
+            <v>0.1552767857142856</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="V48">
+            <v>0.22716788648360398</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="AI49">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="V52">
+            <v>9.599848521149075E-2</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="AI55">
+            <v>-0.80686738144951742</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="AI56" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>64.39</v>
+          </cell>
+          <cell r="E3">
+            <v>45904</v>
+          </cell>
+          <cell r="G3">
+            <v>45960</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>10869.032000000001</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>613.79999999999995</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>10255.232000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="5">
+          <cell r="V5">
+            <v>1277.0619999999999</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="P20">
+            <v>10.89999999999997</v>
+          </cell>
+          <cell r="Q20">
+            <v>80.300000000000068</v>
+          </cell>
+          <cell r="R20">
+            <v>0.50000000000003597</v>
+          </cell>
+          <cell r="S20">
+            <v>-33.20000000000001</v>
+          </cell>
+          <cell r="T20">
+            <v>2.3999999999998813</v>
+          </cell>
+          <cell r="U20">
+            <v>16.299999999999944</v>
+          </cell>
+          <cell r="V20">
+            <v>16.054319999999748</v>
+          </cell>
+          <cell r="W20">
+            <v>39.422006400000022</v>
+          </cell>
+          <cell r="X20">
+            <v>60.409628094400034</v>
+          </cell>
+          <cell r="Y20">
+            <v>72.553818362864064</v>
+          </cell>
+          <cell r="AF20">
+            <v>103.09721644808106</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="U26">
+            <v>9.5651335454633113E-2</v>
+          </cell>
+          <cell r="V26">
+            <v>0.12387749713983975</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AI27">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="V29">
+            <v>0.23117585520515044</v>
           </cell>
         </row>
         <row r="32">
-          <cell r="AT32">
-            <v>0.16793778525102088</v>
-          </cell>
-          <cell r="AU32">
-            <v>-0.14495976553461709</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="AU35">
-            <v>-2.9932197784025137E-2</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="AU38">
-            <v>-0.16096636949952645</v>
+          <cell r="V32">
+            <v>1.8102410063097749E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AI33">
+            <v>-0.86431327380599154</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AI34" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>66.63</v>
+          </cell>
+          <cell r="E3">
+            <v>45903</v>
+          </cell>
+          <cell r="G3">
+            <v>45974</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>6663</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-438.4</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>7101.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="V24">
+            <v>1358.33</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>16.199999999999942</v>
+          </cell>
+          <cell r="T39">
+            <v>32.30000000000004</v>
+          </cell>
+          <cell r="U39">
+            <v>53.500000000000057</v>
+          </cell>
+          <cell r="V39">
+            <v>96.823239999999927</v>
+          </cell>
+          <cell r="W39">
+            <v>143.50169249999999</v>
+          </cell>
+          <cell r="X39">
+            <v>179.7296860125</v>
+          </cell>
+          <cell r="Y39">
+            <v>200.07653520599999</v>
+          </cell>
+          <cell r="AF39">
+            <v>315.1137772693595</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="U43">
+            <v>0.23230686115613186</v>
+          </cell>
+          <cell r="V43">
+            <v>0.19099517755370443</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="V44">
+            <v>0.25505171791832615</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AI45">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="V47">
+            <v>0.1261351806998299</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AI51">
+            <v>-0.67267594474014047</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="AI52" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>1178</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>46.100000000000009</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>1131.9000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="O3">
+            <v>12.3</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="O15">
+            <v>-69.325000000000003</v>
+          </cell>
+          <cell r="P15">
+            <v>-91.1815</v>
+          </cell>
+          <cell r="Q15">
+            <v>-110.42588000000001</v>
+          </cell>
+          <cell r="R15">
+            <v>-123.67537759999999</v>
+          </cell>
+          <cell r="Y15">
+            <v>146.02827505986298</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="O20">
+            <v>5.08130081300813E-2</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="AB21">
+            <v>0.11</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="O24">
+            <v>-4.23780487804878</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AB27">
+            <v>-0.85432485058235097</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AB28" t="str">
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>9.0399999999999991</v>
+          </cell>
+          <cell r="E3">
+            <v>45903</v>
+          </cell>
+          <cell r="G3">
+            <v>45974</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>274.81599999999997</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>269.81599999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="Q3">
+            <v>5.6</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="P20">
+            <v>-1.4</v>
+          </cell>
+          <cell r="Q20">
+            <v>-32</v>
+          </cell>
+          <cell r="R20">
+            <v>-27.428000000000001</v>
+          </cell>
+          <cell r="S20">
+            <v>-36.489999999999995</v>
+          </cell>
+          <cell r="T20">
+            <v>-44.738199999999992</v>
+          </cell>
+          <cell r="U20">
+            <v>-36.238919999999993</v>
+          </cell>
+          <cell r="AB20">
+            <v>68.08531453375997</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Q26">
+            <v>0.28571428571428564</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="AF27">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Q30">
+            <v>-3.0535714285714288</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="AF33">
+            <v>-0.78010157110479306</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AF34" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -981,56 +2422,102 @@
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>214.25</v>
+          </cell>
+          <cell r="E3">
+            <v>45906</v>
+          </cell>
+          <cell r="G3">
+            <v>45953</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>136584.375</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>-24408</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>160992.375</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
-        <row r="22">
-          <cell r="AP22">
-            <v>-636</v>
-          </cell>
-          <cell r="AQ22">
-            <v>-11873</v>
-          </cell>
-          <cell r="AR22">
-            <v>-4202</v>
-          </cell>
-          <cell r="AS22">
-            <v>-4935</v>
-          </cell>
-          <cell r="AT22">
-            <v>-2222</v>
-          </cell>
-          <cell r="AU22">
-            <v>-11875</v>
-          </cell>
-          <cell r="AV22">
-            <v>-5262.5270000000073</v>
-          </cell>
-          <cell r="AW22">
-            <v>-1942.5023000000067</v>
-          </cell>
-          <cell r="AX22">
-            <v>306.80698350001308</v>
-          </cell>
-          <cell r="AY22">
-            <v>1858.1908228950113</v>
-          </cell>
-          <cell r="BF22">
-            <v>6344.4675178984853</v>
+        <row r="5">
+          <cell r="Z5">
+            <v>41769.86</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="T21">
+            <v>6143</v>
+          </cell>
+          <cell r="U21">
+            <v>4779</v>
+          </cell>
+          <cell r="V21">
+            <v>5542</v>
+          </cell>
+          <cell r="W21">
+            <v>4966</v>
+          </cell>
+          <cell r="X21">
+            <v>5658</v>
+          </cell>
+          <cell r="Y21">
+            <v>5705</v>
+          </cell>
+          <cell r="Z21">
+            <v>6242.2181160000009</v>
+          </cell>
+          <cell r="AA21">
+            <v>6474.8637126400035</v>
+          </cell>
+          <cell r="AB21">
+            <v>6915.614977584004</v>
+          </cell>
+          <cell r="AC21">
+            <v>7358.4506706088232</v>
+          </cell>
+          <cell r="AJ21">
+            <v>8514.6826348631621</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27">
+            <v>5.0079100976487823E-2</v>
+          </cell>
+          <cell r="Z27">
+            <v>8.4987791573588156E-2</v>
+          </cell>
+          <cell r="AM27">
+            <v>0.06</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="BJ30">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="BJ36">
-            <v>-0.74615865426916195</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="BJ37" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="Z30">
+            <v>0.3822494688754044</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Z33">
+            <v>0.19938196584810197</v>
+          </cell>
+          <cell r="AM33">
+            <v>-0.28128779344854971</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AM34" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1053,99 +2540,103 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>227</v>
+            <v>183.84</v>
           </cell>
           <cell r="E3">
-            <v>45770</v>
+            <v>45906</v>
           </cell>
           <cell r="G3">
-            <v>45776</v>
+            <v>45959</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>147527.29999999999</v>
+            <v>145104.91199999998</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-20146</v>
+            <v>14263</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>167673.29999999999</v>
+            <v>130841.91199999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="Y5">
-            <v>38498</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="T21">
-            <v>6143</v>
-          </cell>
-          <cell r="U21">
-            <v>4779</v>
-          </cell>
-          <cell r="V21">
-            <v>5542</v>
-          </cell>
-          <cell r="W21">
-            <v>4966</v>
-          </cell>
-          <cell r="X21">
-            <v>5658</v>
-          </cell>
-          <cell r="Y21">
-            <v>5705</v>
-          </cell>
-          <cell r="Z21">
-            <v>6141.1858699999948</v>
-          </cell>
-          <cell r="AA21">
-            <v>6333.0918057399977</v>
-          </cell>
-          <cell r="AB21">
-            <v>6529.3242899714041</v>
-          </cell>
-          <cell r="AC21">
-            <v>6679.7574899245519</v>
-          </cell>
-          <cell r="AJ21">
-            <v>7412.6978597676443</v>
+        <row r="3">
+          <cell r="AA3">
+            <v>73427.94</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="U22">
+            <v>-1362</v>
+          </cell>
+          <cell r="V22">
+            <v>-1133</v>
+          </cell>
+          <cell r="W22">
+            <v>4213</v>
+          </cell>
+          <cell r="X22">
+            <v>4247</v>
+          </cell>
+          <cell r="Y22">
+            <v>3789</v>
+          </cell>
+          <cell r="Z22">
+            <v>4232</v>
+          </cell>
+          <cell r="AA22">
+            <v>5270.3283367999993</v>
+          </cell>
+          <cell r="AB22">
+            <v>5759.7684619200008</v>
+          </cell>
+          <cell r="AC22">
+            <v>6515.0674260704018</v>
+          </cell>
+          <cell r="AD22">
+            <v>6668.5547838398097</v>
+          </cell>
+          <cell r="AK22">
+            <v>7839.3378328649687</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Z26">
+            <v>5.7818659658344318E-2</v>
+          </cell>
+          <cell r="AA26">
+            <v>6.063758486205395E-2</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="X27">
-            <v>3.3722438391699194E-2</v>
-          </cell>
-          <cell r="Y27">
-            <v>5.0079100976487823E-2</v>
-          </cell>
-          <cell r="AM27">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="Y30">
-            <v>0.38085095329627511</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="Y33">
-            <v>0.19328276793599666</v>
-          </cell>
-          <cell r="AM33">
-            <v>-0.4002901538417406</v>
+          <cell r="AA27">
+            <v>0.16</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AO28">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AA31">
+            <v>8.4329038510408974E-2</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AM34" t="str">
-            <v>Overvalued</v>
+          <cell r="AO34">
+            <v>-0.2375809557708306</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AO35" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1168,18 +2659,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>462.5</v>
+            <v>421.42</v>
           </cell>
           <cell r="E3">
-            <v>45723</v>
+            <v>45862</v>
           </cell>
           <cell r="G3">
-            <v>45769</v>
+            <v>45958</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>108872.5</v>
+            <v>98401.57</v>
           </cell>
         </row>
         <row r="8">
@@ -1189,7 +2680,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>126659.5</v>
+            <v>116188.57</v>
           </cell>
         </row>
       </sheetData>
@@ -1222,16 +2713,16 @@
             <v>6890.479949999999</v>
           </cell>
           <cell r="AE21">
-            <v>6982.5840987000065</v>
+            <v>7039.1165736000012</v>
           </cell>
           <cell r="AF21">
-            <v>7076.3052693629925</v>
+            <v>7133.4030690119962</v>
           </cell>
           <cell r="AG21">
-            <v>7171.6805116229025</v>
+            <v>7229.3492892684044</v>
           </cell>
           <cell r="AN21">
-            <v>7888.9501553994505</v>
+            <v>7950.7788906259766</v>
           </cell>
         </row>
         <row r="27">
@@ -1257,7 +2748,7 @@
         </row>
         <row r="33">
           <cell r="AQ33">
-            <v>-0.2341111312648132</v>
+            <v>-0.14499673048749862</v>
           </cell>
         </row>
         <row r="34">
@@ -1285,102 +2776,100 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>137.16</v>
+            <v>284.89999999999998</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45898</v>
           </cell>
           <cell r="G3">
-            <v>45777</v>
+            <v>46066</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>108356.4</v>
+            <v>119059.70999999998</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>724</v>
+            <v>3454</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>107632.4</v>
+            <v>115605.70999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="J3">
-            <v>69230</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>-1362</v>
-          </cell>
-          <cell r="F22">
-            <v>-1133</v>
-          </cell>
-          <cell r="G22">
-            <v>4213</v>
-          </cell>
-          <cell r="H22">
-            <v>4247</v>
-          </cell>
-          <cell r="I22">
-            <v>3789</v>
-          </cell>
-          <cell r="J22">
-            <v>4232</v>
-          </cell>
-          <cell r="K22">
-            <v>5238.9075199999988</v>
-          </cell>
-          <cell r="L22">
-            <v>5416.3584256000004</v>
-          </cell>
-          <cell r="M22">
-            <v>5548.7205525119998</v>
-          </cell>
-          <cell r="N22">
-            <v>5683.9702715462408</v>
-          </cell>
-          <cell r="U22">
-            <v>6716.7817173619123</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="I26">
-            <v>0.11372802613889688</v>
-          </cell>
-          <cell r="J26">
-            <v>5.7818659658344318E-2</v>
+        <row r="5">
+          <cell r="Q5">
+            <v>28154</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="J27">
-            <v>0.15419615773508594</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="Y28">
+          <cell r="L27">
+            <v>2665</v>
+          </cell>
+          <cell r="M27">
+            <v>844</v>
+          </cell>
+          <cell r="N27">
+            <v>760</v>
+          </cell>
+          <cell r="O27">
+            <v>1178</v>
+          </cell>
+          <cell r="P27">
+            <v>3444</v>
+          </cell>
+          <cell r="Q27">
+            <v>-667</v>
+          </cell>
+          <cell r="R27">
+            <v>6723.0672399999985</v>
+          </cell>
+          <cell r="S27">
+            <v>4958.320731400001</v>
+          </cell>
+          <cell r="T27">
+            <v>5263.9838682340005</v>
+          </cell>
+          <cell r="U27">
+            <v>5481.8804852950607</v>
+          </cell>
+          <cell r="AB27">
+            <v>6414.0186126697317</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="P31">
+            <v>0.23876765083440299</v>
+          </cell>
+          <cell r="Q31">
+            <v>0.16700518134715026</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Q32">
+            <v>0.19116288982027421</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Q33">
+            <v>0.14889536122753427</v>
+          </cell>
+          <cell r="AF33">
             <v>7.0000000000000007E-2</v>
           </cell>
         </row>
-        <row r="31">
-          <cell r="J31">
-            <v>6.9391882132023686E-2</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="Y34">
-            <v>-0.22219982113568326</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="Y35" t="str">
+        <row r="39">
+          <cell r="AF39">
+            <v>-0.28700962633957428</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="AF40" t="str">
             <v>Slightly overvalued</v>
           </cell>
         </row>
@@ -1404,28 +2893,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>472.65</v>
+            <v>568.5</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45862</v>
           </cell>
           <cell r="G3">
-            <v>45862</v>
+            <v>45953</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>68014.335000000006</v>
+            <v>81409.2</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-12482</v>
+            <v>-13261</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>80496.335000000006</v>
+            <v>94670.2</v>
           </cell>
         </row>
       </sheetData>
@@ -1493,7 +2982,7 @@
         </row>
         <row r="30">
           <cell r="AM30">
-            <v>-0.31348981866726999</v>
+            <v>-0.42365950691793453</v>
           </cell>
         </row>
         <row r="31">
@@ -1521,18 +3010,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>265.69</v>
+            <v>317.10000000000002</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45862</v>
           </cell>
           <cell r="G3">
-            <v>45861</v>
+            <v>45952</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>71311.195999999996</v>
+            <v>85299.900000000009</v>
           </cell>
         </row>
         <row r="8">
@@ -1542,7 +3031,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>79678.195999999996</v>
+            <v>93666.900000000009</v>
           </cell>
         </row>
       </sheetData>
@@ -1572,19 +3061,19 @@
             <v>3782</v>
           </cell>
           <cell r="AC16">
-            <v>4065.2781650000034</v>
+            <v>4243.5310400000008</v>
           </cell>
           <cell r="AD16">
-            <v>4316.3812148500065</v>
+            <v>4623.3326656000045</v>
           </cell>
           <cell r="AE16">
-            <v>4535.0469065479992</v>
+            <v>4897.3993508480062</v>
           </cell>
           <cell r="AF16">
-            <v>4720.710356326842</v>
+            <v>5139.2124562518457</v>
           </cell>
           <cell r="AM16">
-            <v>5397.949296781786</v>
+            <v>5952.0470127677636</v>
           </cell>
         </row>
         <row r="22">
@@ -1610,12 +3099,12 @@
         </row>
         <row r="28">
           <cell r="AP28">
-            <v>-0.28201653867212506</v>
+            <v>-0.33344751215489621</v>
           </cell>
         </row>
         <row r="29">
           <cell r="AP29" t="str">
-            <v>Slightly overvalued</v>
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1638,35 +3127,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1417</v>
-          </cell>
-          <cell r="F3">
-            <v>45734</v>
-          </cell>
-          <cell r="H3">
-            <v>45455</v>
+            <v>1744.5</v>
+          </cell>
+          <cell r="E3">
+            <v>45906</v>
+          </cell>
+          <cell r="G3">
+            <v>45967</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>61540.31</v>
+            <v>76478.880000000005</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-893</v>
+            <v>-293</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>62433.31</v>
+            <v>76771.88</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="18">
-          <cell r="AC18">
-            <v>7175</v>
+          <cell r="AE18">
+            <v>12231.94</v>
           </cell>
         </row>
         <row r="37">
@@ -1686,16 +3175,19 @@
             <v>717</v>
           </cell>
           <cell r="AE37">
-            <v>1183.5057150000023</v>
+            <v>1152.8015680000001</v>
           </cell>
           <cell r="AF37">
-            <v>1446.6646025</v>
+            <v>1264.6224175000007</v>
           </cell>
           <cell r="AG37">
-            <v>1594.3621815874999</v>
-          </cell>
-          <cell r="AN37">
-            <v>1930.9939382407565</v>
+            <v>1430.3841434999997</v>
+          </cell>
+          <cell r="AH37">
+            <v>1527.5501896362498</v>
+          </cell>
+          <cell r="AO37">
+            <v>1804.5664601807241</v>
           </cell>
         </row>
         <row r="46">
@@ -1704,21 +3196,21 @@
           </cell>
         </row>
         <row r="49">
-          <cell r="AB49">
-            <v>0.1327089591800672</v>
-          </cell>
-          <cell r="AC49">
-            <v>0.11934477379095165</v>
+          <cell r="AD49">
+            <v>0.35902439024390254</v>
+          </cell>
+          <cell r="AE49">
+            <v>0.25442928930366127</v>
           </cell>
         </row>
         <row r="51">
-          <cell r="AC51">
-            <v>0.26327526132404183</v>
+          <cell r="AE51">
+            <v>0.28072109575423032</v>
           </cell>
         </row>
         <row r="52">
           <cell r="AS52">
-            <v>-0.62242636061307977</v>
+            <v>-0.71543396756112809</v>
           </cell>
         </row>
         <row r="53">
@@ -1727,8 +3219,8 @@
           </cell>
         </row>
         <row r="56">
-          <cell r="AC56">
-            <v>0.11777003484320557</v>
+          <cell r="AE56">
+            <v>0.16228117534912698</v>
           </cell>
         </row>
       </sheetData>
@@ -2034,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
-  <dimension ref="B2:AK23"/>
+  <dimension ref="B2:AK30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -2074,16 +3566,16 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>6</v>
@@ -2119,51 +3611,51 @@
         <v>16</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="X2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AH2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="AJ2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2181,86 +3673,86 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="7">
-        <f t="shared" ref="R3:Y3" si="0">TRIMMEAN(R4:R1048576,80%)</f>
-        <v>25.311465398668286</v>
+        <f t="shared" ref="R3:W3" si="0">TRIMMEAN(R4:R1048576,80%)</f>
+        <v>34.421156571947499</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" si="0"/>
-        <v>24.782129357090753</v>
+        <v>26.461248999924155</v>
       </c>
       <c r="T3" s="7">
         <f t="shared" si="0"/>
-        <v>21.602319676769721</v>
+        <v>23.092730697287529</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" si="0"/>
-        <v>22.538867814060595</v>
+        <v>22.349828165413104</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" si="0"/>
-        <v>22.018917353442966</v>
+        <v>21.596966763334482</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="0"/>
-        <v>16.972993351440959</v>
+        <v>17.986032733432616</v>
       </c>
       <c r="X3" s="8"/>
       <c r="Y3" s="21">
-        <f t="shared" si="0"/>
-        <v>2.2678747573429807</v>
+        <f t="shared" ref="Y3:AE3" si="1">TRIMMEAN(Y4:Y1048576,80%)</f>
+        <v>2.8329303433229946</v>
       </c>
       <c r="Z3" s="9">
-        <f t="shared" ref="Z3:AE3" si="1">TRIMMEAN(Z4:Z1048576,80%)</f>
-        <v>7.3070714604045461E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.9957761805311917E-2</v>
       </c>
       <c r="AA3" s="9">
         <f t="shared" si="1"/>
-        <v>7.7984977390838539E-2</v>
+        <v>0.11541965295193875</v>
       </c>
       <c r="AB3" s="9">
         <f t="shared" si="1"/>
-        <v>0.18299375242489391</v>
+        <v>0.20768693578353645</v>
       </c>
       <c r="AC3" s="9">
         <f t="shared" si="1"/>
-        <v>9.0423047405503901E-2</v>
+        <v>9.48275445189906E-2</v>
       </c>
       <c r="AD3" s="9">
         <f t="shared" si="1"/>
-        <v>7.333333333333332E-2</v>
+        <v>0.08</v>
       </c>
       <c r="AE3" s="9">
         <f t="shared" si="1"/>
-        <v>-0.33193217039371187</v>
+        <v>-0.45499566684070913</v>
       </c>
       <c r="AF3" s="10" t="e">
-        <f>INDEX(AF4:AF52,MODE(MATCH(AF4:AF52,AF4:AF52,0)))</f>
+        <f>INDEX(AF4:AF23,MODE(MATCH(AF4:AF23,AF4:AF23,0)))</f>
         <v>#N/A</v>
       </c>
       <c r="AG3" s="2"/>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
-        <v>24</v>
+      <c r="B4" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="13">
         <f>[1]Main!$D$3</f>
-        <v>119.35</v>
+        <v>157.52000000000001</v>
       </c>
       <c r="E4" s="14">
         <f>[1]Main!$D$5</f>
-        <v>159451.6</v>
+        <v>210840.52000000002</v>
       </c>
       <c r="F4" s="14">
         <f>[1]Main!$D$8</f>
-        <v>-36143</v>
+        <v>-37196</v>
       </c>
       <c r="G4" s="14">
         <f>[1]Main!$D$9</f>
-        <v>195594.6</v>
+        <v>248036.52000000002</v>
       </c>
       <c r="H4" s="14">
         <f>[1]Model!U$19</f>
@@ -2288,67 +3780,67 @@
       </c>
       <c r="N4" s="14">
         <f>[1]Model!AA$19</f>
-        <v>5935.5916480000114</v>
+        <v>6597.7138400000167</v>
       </c>
       <c r="O4" s="14">
         <f>[1]Model!AB$19</f>
-        <v>6317.3871904000098</v>
+        <v>7570.8374651199974</v>
       </c>
       <c r="P4" s="14">
         <f>[1]Model!AC$19</f>
-        <v>6584.8417255040049</v>
+        <v>8157.0804411392028</v>
       </c>
       <c r="Q4" s="14">
         <f>[1]Model!AD$19</f>
-        <v>6768.4778666953616</v>
+        <v>8502.7527649675394</v>
       </c>
       <c r="R4" s="15">
         <f t="shared" ref="R4" si="2">$G4/M4</f>
-        <v>40.97080016757436</v>
+        <v>51.955701717637204</v>
       </c>
       <c r="S4" s="15">
         <f t="shared" ref="S4" si="3">$G4/N4</f>
-        <v>32.952839682949772</v>
+        <v>37.59431312346814</v>
       </c>
       <c r="T4" s="15">
         <f t="shared" ref="T4" si="4">$G4/O4</f>
-        <v>30.961312660593023</v>
+        <v>32.762098135476037</v>
       </c>
       <c r="U4" s="15">
         <f t="shared" ref="U4" si="5">$G4/P4</f>
-        <v>29.703766339961522</v>
+        <v>30.407511828504134</v>
       </c>
       <c r="V4" s="15">
         <f t="shared" ref="V4" si="6">$G4/Q4</f>
-        <v>28.897870961864726</v>
+        <v>29.171319789744228</v>
       </c>
       <c r="W4" s="15">
         <f>G4/[1]Model!$AK$19</f>
-        <v>24.370962457367799</v>
+        <v>23.533213228593535</v>
       </c>
       <c r="X4" s="14">
-        <f>[1]Model!$Z$5</f>
-        <v>80738</v>
+        <f>[1]Model!$AA$5</f>
+        <v>87203.32</v>
       </c>
       <c r="Y4" s="20">
         <f>G4/X4</f>
-        <v>2.422584161113726</v>
+        <v>2.8443472106337238</v>
       </c>
       <c r="Z4" s="16">
-        <f>[1]Model!$Y$25</f>
-        <v>2.7521841548140857E-2</v>
+        <f>[1]Model!Z$25</f>
+        <v>0.17147417295414979</v>
       </c>
       <c r="AA4" s="16">
-        <f>[1]Model!$Z$25</f>
-        <v>0.17147417295414979</v>
+        <f>[1]Model!AA$25</f>
+        <v>8.0077782456835722E-2</v>
       </c>
       <c r="AB4" s="16">
-        <f>[1]Model!$Z$28</f>
-        <v>0.19086427704426664</v>
+        <f>[1]Model!$AA$28</f>
+        <v>0.2026911899684555</v>
       </c>
       <c r="AC4" s="16">
-        <f>[1]Model!$Z$31</f>
-        <v>8.2612896034085559E-2</v>
+        <f>[1]Model!$AA$31</f>
+        <v>9.8853831482562993E-2</v>
       </c>
       <c r="AD4" s="16">
         <f>[1]Model!$AO$26</f>
@@ -2356,592 +3848,713 @@
       </c>
       <c r="AE4" s="16">
         <f>[1]Model!$AO$32</f>
-        <v>-0.50646520170582687</v>
+        <v>-0.47755291681370626</v>
       </c>
       <c r="AF4" s="11" t="str">
         <f>[1]Model!$AO$33</f>
-        <v>Heavily overvalued</v>
+        <v>Overvalued</v>
       </c>
       <c r="AH4" s="11">
         <v>1922</v>
       </c>
       <c r="AJ4" s="18">
         <f>[1]Main!$E$3</f>
-        <v>45770</v>
+        <v>45906</v>
       </c>
       <c r="AK4" s="18">
         <f>[1]Main!$G$3</f>
-        <v>45867</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="5" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
-        <v>30</v>
+      <c r="B5" s="19" t="s">
+        <v>29</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D5" s="13">
         <f>[2]Main!$D$3</f>
-        <v>174.98</v>
+        <v>231.01</v>
       </c>
       <c r="E5" s="14">
         <f>[2]Main!$D$5</f>
-        <v>131829.932</v>
+        <v>174042.93399999998</v>
       </c>
       <c r="F5" s="14">
         <f>[2]Main!$D$8</f>
-        <v>-29944</v>
+        <v>-29320</v>
       </c>
       <c r="G5" s="14">
         <f>[2]Main!$D$9</f>
-        <v>161773.932</v>
+        <v>203362.93399999998</v>
       </c>
       <c r="H5" s="14">
-        <f>[3]Model!AP$22</f>
+        <f>[2]Model!AP$33</f>
         <v>-636</v>
       </c>
       <c r="I5" s="14">
-        <f>[3]Model!AQ$22</f>
+        <f>[2]Model!AQ$33</f>
         <v>-11873</v>
       </c>
       <c r="J5" s="14">
-        <f>[3]Model!AR$22</f>
+        <f>[2]Model!AR$33</f>
         <v>-4202</v>
       </c>
       <c r="K5" s="14">
-        <f>[3]Model!AS$22</f>
+        <f>[2]Model!AS$33</f>
         <v>-4935</v>
       </c>
       <c r="L5" s="14">
-        <f>[3]Model!AT$22</f>
+        <f>[2]Model!AT$33</f>
         <v>-2222</v>
       </c>
       <c r="M5" s="14">
-        <f>[3]Model!AU$22</f>
+        <f>[2]Model!AU$33</f>
         <v>-11875</v>
       </c>
       <c r="N5" s="14">
-        <f>[3]Model!AV$22</f>
-        <v>-5262.5270000000073</v>
+        <f>[2]Model!AV$33</f>
+        <v>-1766.719874999995</v>
       </c>
       <c r="O5" s="14">
-        <f>[3]Model!AW$22</f>
-        <v>-1942.5023000000067</v>
+        <f>[2]Model!AW$33</f>
+        <v>2015.174950999997</v>
       </c>
       <c r="P5" s="14">
-        <f>[3]Model!AX$22</f>
-        <v>306.80698350001308</v>
+        <f>[2]Model!AX$33</f>
+        <v>3280.0064038900064</v>
       </c>
       <c r="Q5" s="14">
-        <f>[3]Model!AY$22</f>
-        <v>1858.1908228950113</v>
+        <f>[2]Model!AY$33</f>
+        <v>4389.198277423704</v>
       </c>
       <c r="R5" s="15">
         <f>$G5/M5</f>
-        <v>-13.623067957894737</v>
+        <v>-17.125299705263156</v>
       </c>
       <c r="U5" s="15">
         <f t="shared" ref="U5:V6" si="7">$G5/P5</f>
-        <v>527.28243064908304</v>
+        <v>62.00077346154464</v>
       </c>
       <c r="V5" s="15">
         <f t="shared" si="7"/>
-        <v>87.059913334390799</v>
+        <v>46.332592228976829</v>
       </c>
       <c r="W5" s="15">
-        <f>G5/[3]Model!$BF$22</f>
-        <v>25.498425446046781</v>
+        <f>G5/[2]Model!$BF$33</f>
+        <v>20.60445645042169</v>
       </c>
       <c r="X5" s="14">
-        <f>[2]Model!$AU$9</f>
-        <v>66517</v>
+        <f>[2]Model!$AV$16</f>
+        <v>89475.77</v>
       </c>
       <c r="Y5" s="20">
         <f t="shared" ref="Y5:Y8" si="8">G5/X5</f>
-        <v>2.4320689748485349</v>
+        <v>2.2728268669830944</v>
       </c>
       <c r="Z5" s="16">
-        <f>[2]Model!$AT$32</f>
-        <v>0.16793778525102088</v>
+        <f>[2]Model!AU$40</f>
+        <v>-0.14495976553461709</v>
       </c>
       <c r="AA5" s="16">
-        <f>[2]Model!$AU$32</f>
-        <v>-0.14495976553461709</v>
+        <f>[2]Model!AV$40</f>
+        <v>0.34515642617676701</v>
       </c>
       <c r="AB5" s="16">
-        <f>[2]Model!$AU$35</f>
-        <v>-2.9932197784025137E-2</v>
+        <f>[2]Model!$AV$43</f>
+        <v>0.11339720798155752</v>
       </c>
       <c r="AC5" s="16">
-        <f>[2]Model!$AU$38</f>
-        <v>-0.16096636949952645</v>
+        <f>[2]Model!$AV$46</f>
+        <v>2.0289571131939408E-3</v>
       </c>
       <c r="AD5" s="16">
-        <f>[3]Model!$BJ$30</f>
+        <f>[2]Model!$BI$40</f>
         <v>0.06</v>
       </c>
       <c r="AE5" s="16">
-        <f>[3]Model!$BJ$36</f>
-        <v>-0.74615865426916195</v>
+        <f>[2]Model!$BI$46</f>
+        <v>-0.50758168691846905</v>
       </c>
       <c r="AF5" s="11" t="str">
-        <f>[3]Model!$BJ$37</f>
+        <f>[2]Model!$BI$47</f>
         <v>Heavily overvalued</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>73</v>
       </c>
       <c r="AH5" s="11">
         <v>1916</v>
       </c>
       <c r="AJ5" s="18">
         <f>[2]Main!$E$3</f>
-        <v>45770</v>
+        <v>45867</v>
       </c>
       <c r="AK5" s="18">
         <f>[2]Main!$G$3</f>
-        <v>45861</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B6" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D6" s="13">
-        <f>[4]Main!$D$3</f>
-        <v>227</v>
+        <f>[3]Main!$D$3</f>
+        <v>214.25</v>
       </c>
       <c r="E6" s="14">
-        <f>[4]Main!$D$5</f>
-        <v>147527.29999999999</v>
+        <f>[3]Main!$D$5</f>
+        <v>136584.375</v>
       </c>
       <c r="F6" s="14">
-        <f>[4]Main!$D$8</f>
-        <v>-20146</v>
+        <f>[3]Main!$D$8</f>
+        <v>-24408</v>
       </c>
       <c r="G6" s="14">
-        <f>[4]Main!$D$9</f>
-        <v>167673.29999999999</v>
+        <f>[3]Main!$D$9</f>
+        <v>160992.375</v>
       </c>
       <c r="H6" s="14">
-        <f>[4]Model!T$21</f>
+        <f>[3]Model!T$21</f>
         <v>6143</v>
       </c>
       <c r="I6" s="14">
-        <f>[4]Model!U$21</f>
+        <f>[3]Model!U$21</f>
         <v>4779</v>
       </c>
       <c r="J6" s="14">
-        <f>[4]Model!V$21</f>
+        <f>[3]Model!V$21</f>
         <v>5542</v>
       </c>
       <c r="K6" s="14">
-        <f>[4]Model!W$21</f>
+        <f>[3]Model!W$21</f>
         <v>4966</v>
       </c>
       <c r="L6" s="14">
-        <f>[4]Model!X$21</f>
+        <f>[3]Model!X$21</f>
         <v>5658</v>
       </c>
       <c r="M6" s="14">
-        <f>[4]Model!Y$21</f>
+        <f>[3]Model!Y$21</f>
         <v>5705</v>
       </c>
       <c r="N6" s="14">
-        <f>[4]Model!Z$21</f>
-        <v>6141.1858699999948</v>
+        <f>[3]Model!Z$21</f>
+        <v>6242.2181160000009</v>
       </c>
       <c r="O6" s="14">
-        <f>[4]Model!AA$21</f>
-        <v>6333.0918057399977</v>
+        <f>[3]Model!AA$21</f>
+        <v>6474.8637126400035</v>
       </c>
       <c r="P6" s="14">
-        <f>[4]Model!AB$21</f>
-        <v>6529.3242899714041</v>
+        <f>[3]Model!AB$21</f>
+        <v>6915.614977584004</v>
       </c>
       <c r="Q6" s="14">
-        <f>[4]Model!AC$21</f>
-        <v>6679.7574899245519</v>
+        <f>[3]Model!AC$21</f>
+        <v>7358.4506706088232</v>
       </c>
       <c r="R6" s="15">
         <f>$G6/M6</f>
-        <v>29.390587204206835</v>
+        <v>28.219522348816827</v>
       </c>
       <c r="S6" s="15">
         <f t="shared" ref="S6:T6" si="9">$G6/N6</f>
-        <v>27.303081774334917</v>
+        <v>25.790892277113116</v>
       </c>
       <c r="T6" s="15">
         <f t="shared" si="9"/>
-        <v>26.475741256115899</v>
+        <v>24.864210606582542</v>
       </c>
       <c r="U6" s="15">
         <f t="shared" si="7"/>
-        <v>25.680038630878652</v>
+        <v>23.279545712396395</v>
       </c>
       <c r="V6" s="15">
         <f t="shared" si="7"/>
-        <v>25.101704703039132</v>
+        <v>21.878569580283646</v>
       </c>
       <c r="W6" s="15">
-        <f>G6/[4]Model!$AJ$21</f>
-        <v>22.619740231157326</v>
+        <f>G6/[3]Model!$AJ$21</f>
+        <v>18.907618980514979</v>
       </c>
       <c r="X6" s="14">
-        <f>[4]Model!$Y$5</f>
-        <v>38498</v>
+        <f>[3]Model!$Z$5</f>
+        <v>41769.86</v>
       </c>
       <c r="Y6" s="20">
         <f t="shared" si="8"/>
-        <v>4.3553769026962437</v>
-      </c>
-      <c r="Z6" s="16">
-        <f>[4]Model!X$27</f>
-        <v>3.3722438391699194E-2</v>
-      </c>
-      <c r="AA6" s="16">
-        <f>[4]Model!Y$27</f>
+        <v>3.854271357385445</v>
+      </c>
+      <c r="Z6" s="25">
+        <f>[3]Model!Y$27</f>
         <v>5.0079100976487823E-2</v>
       </c>
+      <c r="AA6" s="25">
+        <f>[3]Model!Z$27</f>
+        <v>8.4987791573588156E-2</v>
+      </c>
       <c r="AB6" s="16">
-        <f>[4]Model!$Y$30</f>
-        <v>0.38085095329627511</v>
+        <f>[3]Model!$Z$30</f>
+        <v>0.3822494688754044</v>
       </c>
       <c r="AC6" s="16">
-        <f>[4]Model!$Y$33</f>
-        <v>0.19328276793599666</v>
+        <f>[3]Model!$Z$33</f>
+        <v>0.19938196584810197</v>
       </c>
       <c r="AD6" s="16">
-        <f>[4]Model!$AM$27</f>
+        <f>[3]Model!$AM$27</f>
         <v>0.06</v>
       </c>
       <c r="AE6" s="16">
-        <f>[4]Model!$AM$33</f>
-        <v>-0.4002901538417406</v>
+        <f>[3]Model!$AM$33</f>
+        <v>-0.28128779344854971</v>
       </c>
       <c r="AF6" s="11" t="str">
-        <f>[4]Model!$AM$34</f>
-        <v>Overvalued</v>
+        <f>[3]Model!$AM$34</f>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AH6" s="11">
         <v>1906</v>
       </c>
       <c r="AJ6" s="18">
-        <f>[4]Main!$E$3</f>
-        <v>45770</v>
+        <f>[3]Main!$E$3</f>
+        <v>45906</v>
       </c>
       <c r="AK6" s="18">
-        <f>[4]Main!$G$3</f>
-        <v>45776</v>
+        <f>[3]Main!$G$3</f>
+        <v>45953</v>
       </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
-        <v>25</v>
+      <c r="B7" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="13">
-        <f>[5]Main!$D$3</f>
-        <v>462.5</v>
+        <v>57</v>
+      </c>
+      <c r="D7" s="17">
+        <f>[4]Main!$D$3</f>
+        <v>183.84</v>
       </c>
       <c r="E7" s="14">
-        <f>[5]Main!$D$5</f>
-        <v>108872.5</v>
+        <f>[4]Main!$D$5</f>
+        <v>145104.91199999998</v>
       </c>
       <c r="F7" s="14">
-        <f>[5]Main!$D$8</f>
-        <v>-17787</v>
+        <f>[4]Main!$D$8</f>
+        <v>14263</v>
       </c>
       <c r="G7" s="14">
-        <f>[5]Main!$D$9</f>
-        <v>126659.5</v>
+        <f>[4]Main!$D$9</f>
+        <v>130841.91199999998</v>
       </c>
       <c r="H7" s="14">
-        <f>[5]Model!X$21</f>
-        <v>6230</v>
+        <f>[4]Model!U$22</f>
+        <v>-1362</v>
       </c>
       <c r="I7" s="14">
-        <f>[5]Model!Y$21</f>
-        <v>6888</v>
+        <f>[4]Model!V$22</f>
+        <v>-1133</v>
       </c>
       <c r="J7" s="14">
-        <f>[5]Model!Z$21</f>
-        <v>6315</v>
+        <f>[4]Model!W$22</f>
+        <v>4213</v>
       </c>
       <c r="K7" s="14">
-        <f>[5]Model!AA$21</f>
-        <v>5732</v>
+        <f>[4]Model!X$22</f>
+        <v>4247</v>
       </c>
       <c r="L7" s="14">
-        <f>[5]Model!AB$21</f>
-        <v>6920</v>
+        <f>[4]Model!Y$22</f>
+        <v>3789</v>
       </c>
       <c r="M7" s="14">
-        <f>[5]Model!AC$21</f>
-        <v>5336</v>
+        <f>[4]Model!Z$22</f>
+        <v>4232</v>
       </c>
       <c r="N7" s="14">
-        <f>[5]Model!AD$21</f>
-        <v>6890.479949999999</v>
+        <f>[4]Model!AA$22</f>
+        <v>5270.3283367999993</v>
       </c>
       <c r="O7" s="14">
-        <f>[5]Model!AE$21</f>
-        <v>6982.5840987000065</v>
+        <f>[4]Model!AB$22</f>
+        <v>5759.7684619200008</v>
       </c>
       <c r="P7" s="14">
-        <f>[5]Model!AF$21</f>
-        <v>7076.3052693629925</v>
+        <f>[4]Model!AC$22</f>
+        <v>6515.0674260704018</v>
       </c>
       <c r="Q7" s="14">
-        <f>[5]Model!AG$21</f>
-        <v>7171.6805116229025</v>
+        <f>[4]Model!AD$22</f>
+        <v>6668.5547838398097</v>
       </c>
       <c r="R7" s="15">
-        <f t="shared" ref="R7:R8" si="10">$G7/M7</f>
-        <v>23.736787856071963</v>
+        <f>$G7/M7</f>
+        <v>30.917275992438558</v>
       </c>
       <c r="S7" s="15">
-        <f t="shared" ref="S7" si="11">$G7/N7</f>
-        <v>18.38181097965462</v>
+        <f>$G7/N7</f>
+        <v>24.826140543540337</v>
       </c>
       <c r="T7" s="15">
-        <f t="shared" ref="T7" si="12">$G7/O7</f>
-        <v>18.139344719611902</v>
+        <f>$G7/O7</f>
+        <v>22.71652287154339</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" ref="U7" si="13">$G7/P7</f>
-        <v>17.899100615171999</v>
+        <f>$G7/P7</f>
+        <v>20.082971279227113</v>
       </c>
       <c r="V7" s="15">
-        <f t="shared" ref="V7" si="14">$G7/Q7</f>
-        <v>17.66106281431907</v>
+        <f>$G7/Q7</f>
+        <v>19.620729864448997</v>
       </c>
       <c r="W7" s="15">
-        <f>G7/[5]Model!$AN$21</f>
-        <v>16.055304889118887</v>
+        <f>G7/[4]Model!$AK$22</f>
+        <v>16.69042906295855</v>
       </c>
       <c r="X7" s="14">
-        <f>[5]Model!$AC$5</f>
-        <v>71043</v>
+        <f>[4]Model!$AA$3</f>
+        <v>73427.94</v>
       </c>
       <c r="Y7" s="20">
-        <f t="shared" si="8"/>
-        <v>1.7828568613374998</v>
+        <f>G7/X7</f>
+        <v>1.781909066221931</v>
       </c>
       <c r="Z7" s="16">
-        <f>[5]Model!$AB$27</f>
-        <v>2.4051285160038738E-2</v>
+        <f>[4]Model!Z$26</f>
+        <v>5.7818659658344318E-2</v>
       </c>
       <c r="AA7" s="16">
-        <f>[5]Model!$AC$27</f>
-        <v>5.1382989744120922E-2</v>
+        <f>[4]Model!AA$26</f>
+        <v>6.063758486205395E-2</v>
       </c>
       <c r="AB7" s="16">
-        <f>[5]Model!$AC$30</f>
-        <v>8.4089917373984774E-2</v>
+        <f>[4]Model!$AA$27</f>
+        <v>0.16</v>
       </c>
       <c r="AC7" s="16">
-        <f>[5]Model!$AC$31</f>
-        <v>9.8714862829553926E-2</v>
+        <f>[4]Model!$AA$31</f>
+        <v>8.4329038510408974E-2</v>
       </c>
       <c r="AD7" s="16">
-        <f>[5]Model!$AQ$27</f>
+        <f>[4]Model!$AO$28</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE7" s="16">
-        <f>[5]Model!$AQ$33</f>
-        <v>-0.2341111312648132</v>
+        <f>[4]Model!$AO$34</f>
+        <v>-0.2375809557708306</v>
       </c>
       <c r="AF7" s="11" t="str">
-        <f>[5]Model!$AQ$34</f>
+        <f>[4]Model!$AO$35</f>
         <v>Slightly overvalued</v>
       </c>
       <c r="AH7" s="11">
-        <v>1912</v>
+        <v>1998</v>
       </c>
       <c r="AJ7" s="18">
-        <f>[5]Main!$E$3</f>
-        <v>45723</v>
+        <f>[4]Main!$E$3</f>
+        <v>45906</v>
       </c>
       <c r="AK7" s="18">
-        <f>[5]Main!$G$3</f>
-        <v>45769</v>
+        <f>[4]Main!$G$3</f>
+        <v>45959</v>
       </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B8" s="19" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="11">
-        <f>[6]Main!$D$3</f>
-        <v>137.16</v>
+        <v>44</v>
+      </c>
+      <c r="D8" s="13">
+        <f>[5]Main!$D$3</f>
+        <v>421.42</v>
       </c>
       <c r="E8" s="14">
-        <f>[6]Main!$D$5</f>
-        <v>108356.4</v>
+        <f>[5]Main!$D$5</f>
+        <v>98401.57</v>
       </c>
       <c r="F8" s="14">
-        <f>[6]Main!$D$8</f>
-        <v>724</v>
+        <f>[5]Main!$D$8</f>
+        <v>-17787</v>
       </c>
       <c r="G8" s="14">
-        <f>[6]Main!$D$9</f>
-        <v>107632.4</v>
+        <f>[5]Main!$D$9</f>
+        <v>116188.57</v>
       </c>
       <c r="H8" s="14">
-        <f>[6]Model!E$22</f>
-        <v>-1362</v>
+        <f>[5]Model!X$21</f>
+        <v>6230</v>
       </c>
       <c r="I8" s="14">
-        <f>[6]Model!F$22</f>
-        <v>-1133</v>
+        <f>[5]Model!Y$21</f>
+        <v>6888</v>
       </c>
       <c r="J8" s="14">
-        <f>[6]Model!G$22</f>
-        <v>4213</v>
+        <f>[5]Model!Z$21</f>
+        <v>6315</v>
       </c>
       <c r="K8" s="14">
-        <f>[6]Model!H$22</f>
-        <v>4247</v>
+        <f>[5]Model!AA$21</f>
+        <v>5732</v>
       </c>
       <c r="L8" s="14">
-        <f>[6]Model!I$22</f>
-        <v>3789</v>
+        <f>[5]Model!AB$21</f>
+        <v>6920</v>
       </c>
       <c r="M8" s="14">
-        <f>[6]Model!J$22</f>
-        <v>4232</v>
+        <f>[5]Model!AC$21</f>
+        <v>5336</v>
       </c>
       <c r="N8" s="14">
-        <f>[6]Model!K$22</f>
-        <v>5238.9075199999988</v>
+        <f>[5]Model!AD$21</f>
+        <v>6890.479949999999</v>
       </c>
       <c r="O8" s="14">
-        <f>[6]Model!L$22</f>
-        <v>5416.3584256000004</v>
+        <f>[5]Model!AE$21</f>
+        <v>7039.1165736000012</v>
       </c>
       <c r="P8" s="14">
-        <f>[6]Model!M$22</f>
-        <v>5548.7205525119998</v>
+        <f>[5]Model!AF$21</f>
+        <v>7133.4030690119962</v>
       </c>
       <c r="Q8" s="14">
-        <f>[6]Model!N$22</f>
-        <v>5683.9702715462408</v>
+        <f>[5]Model!AG$21</f>
+        <v>7229.3492892684044</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" si="10"/>
-        <v>25.432986767485822</v>
+        <f t="shared" ref="R8" si="10">$G8/M8</f>
+        <v>21.774469640179912</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" ref="S8" si="15">$G8/N8</f>
-        <v>20.544817710391655</v>
+        <f t="shared" ref="S8" si="11">$G8/N8</f>
+        <v>16.862188242779812</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" ref="T8" si="16">$G8/O8</f>
-        <v>19.871727744471961</v>
+        <f t="shared" ref="T8" si="12">$G8/O8</f>
+        <v>16.506129538436941</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" ref="U8" si="17">$G8/P8</f>
-        <v>19.397696997242541</v>
+        <f t="shared" ref="U8" si="13">$G8/P8</f>
+        <v>16.287958058157589</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" ref="V8" si="18">$G8/Q8</f>
-        <v>18.936130003846795</v>
+        <f t="shared" ref="V8" si="14">$G8/Q8</f>
+        <v>16.071788116874632</v>
       </c>
       <c r="W8" s="15">
-        <f>G8/[6]Model!$U$22</f>
-        <v>16.024400453834275</v>
-      </c>
-      <c r="X8" s="14">
-        <f>[6]Model!$J$3</f>
-        <v>69230</v>
-      </c>
-      <c r="Y8" s="20">
+        <f>G8/[5]Model!$AN$21</f>
+        <v>14.613482728967238</v>
+      </c>
+      <c r="X8" s="23">
+        <f>[5]Model!$AC$5</f>
+        <v>71043</v>
+      </c>
+      <c r="Y8" s="26">
         <f t="shared" si="8"/>
-        <v>1.5547074967499639</v>
-      </c>
-      <c r="Z8" s="16">
-        <f>[6]Model!$I$26</f>
-        <v>0.11372802613889688</v>
-      </c>
-      <c r="AA8" s="16">
-        <f>[6]Model!$J$26</f>
-        <v>5.7818659658344318E-2</v>
-      </c>
-      <c r="AB8" s="16">
-        <f>[6]Model!$J$27</f>
-        <v>0.15419615773508594</v>
-      </c>
-      <c r="AC8" s="16">
-        <f>[6]Model!$J$31</f>
-        <v>6.9391882132023686E-2</v>
+        <v>1.6354682375462748</v>
+      </c>
+      <c r="Z8" s="25">
+        <f>[5]Model!$AB$27</f>
+        <v>2.4051285160038738E-2</v>
+      </c>
+      <c r="AA8" s="25">
+        <f>[5]Model!$AC$27</f>
+        <v>5.1382989744120922E-2</v>
+      </c>
+      <c r="AB8" s="25">
+        <f>[5]Model!$AC$30</f>
+        <v>8.4089917373984774E-2</v>
+      </c>
+      <c r="AC8" s="25">
+        <f>[5]Model!$AC$31</f>
+        <v>9.8714862829553926E-2</v>
       </c>
       <c r="AD8" s="16">
-        <f>[6]Model!$Y$28</f>
+        <f>[5]Model!$AQ$27</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE8" s="16">
-        <f>[6]Model!$Y$34</f>
-        <v>-0.22219982113568326</v>
+        <f>[5]Model!$AQ$33</f>
+        <v>-0.14499673048749862</v>
       </c>
       <c r="AF8" s="11" t="str">
-        <f>[6]Model!$Y$35</f>
+        <f>[5]Model!$AQ$34</f>
         <v>Slightly overvalued</v>
       </c>
-      <c r="AG8" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="AH8" s="11">
-        <v>1998</v>
+        <v>1912</v>
       </c>
       <c r="AJ8" s="18">
-        <f>[6]Main!$E$3</f>
-        <v>45771</v>
+        <f>[5]Main!$E$3</f>
+        <v>45862</v>
       </c>
       <c r="AK8" s="18">
-        <f>[6]Main!$G$3</f>
-        <v>45777</v>
+        <f>[5]Main!$G$3</f>
+        <v>45958</v>
       </c>
     </row>
     <row r="9" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>34</v>
+      <c r="B9" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="D9" s="17">
+        <f>[6]Main!$D$3</f>
+        <v>284.89999999999998</v>
+      </c>
+      <c r="E9" s="14">
+        <f>[6]Main!$D$5</f>
+        <v>119059.70999999998</v>
+      </c>
+      <c r="F9" s="14">
+        <f>[6]Main!$D$8</f>
+        <v>3454</v>
+      </c>
+      <c r="G9" s="14">
+        <f>[6]Main!$D$9</f>
+        <v>115605.70999999998</v>
+      </c>
+      <c r="H9" s="14">
+        <f>[6]Model!L$27</f>
+        <v>2665</v>
+      </c>
+      <c r="I9" s="14">
+        <f>[6]Model!M$27</f>
+        <v>844</v>
+      </c>
+      <c r="J9" s="14">
+        <f>[6]Model!N$27</f>
+        <v>760</v>
+      </c>
+      <c r="K9" s="14">
+        <f>[6]Model!O$27</f>
+        <v>1178</v>
+      </c>
+      <c r="L9" s="14">
+        <f>[6]Model!P$27</f>
+        <v>3444</v>
+      </c>
+      <c r="M9" s="14">
+        <f>[6]Model!Q$27</f>
+        <v>-667</v>
+      </c>
+      <c r="N9" s="14">
+        <f>[6]Model!R$27</f>
+        <v>6723.0672399999985</v>
+      </c>
+      <c r="O9" s="14">
+        <f>[6]Model!S$27</f>
+        <v>4958.320731400001</v>
+      </c>
+      <c r="P9" s="14">
+        <f>[6]Model!T$27</f>
+        <v>5263.9838682340005</v>
+      </c>
+      <c r="Q9" s="14">
+        <f>[6]Model!U$27</f>
+        <v>5481.8804852950607</v>
+      </c>
+      <c r="R9" s="15">
+        <f t="shared" ref="R9" si="15">$G9/M9</f>
+        <v>-173.32190404797598</v>
+      </c>
+      <c r="S9" s="15">
+        <f t="shared" ref="S9" si="16">$G9/N9</f>
+        <v>17.195382088726515</v>
+      </c>
+      <c r="T9" s="15">
+        <f t="shared" ref="T9" si="17">$G9/O9</f>
+        <v>23.315496568806726</v>
+      </c>
+      <c r="U9" s="15">
+        <f t="shared" ref="U9" si="18">$G9/P9</f>
+        <v>21.961638351065886</v>
+      </c>
+      <c r="V9" s="15">
+        <f t="shared" ref="V9" si="19">$G9/Q9</f>
+        <v>21.088695806139512</v>
+      </c>
+      <c r="W9" s="15">
+        <f>G9/[6]Model!$AB$27</f>
+        <v>18.023912461314321</v>
+      </c>
+      <c r="X9" s="23">
+        <f>[6]Model!$Q$5</f>
+        <v>28154</v>
+      </c>
+      <c r="Y9" s="26">
+        <f t="shared" ref="Y9" si="20">G9/X9</f>
+        <v>4.1061913049655461</v>
+      </c>
+      <c r="Z9" s="25">
+        <f>[6]Model!P$31</f>
+        <v>0.23876765083440299</v>
+      </c>
+      <c r="AA9" s="25">
+        <f>[6]Model!Q$31</f>
+        <v>0.16700518134715026</v>
+      </c>
+      <c r="AB9" s="25">
+        <f>[6]Model!$Q$32</f>
+        <v>0.19116288982027421</v>
+      </c>
+      <c r="AC9" s="25">
+        <f>[6]Model!$Q$33</f>
+        <v>0.14889536122753427</v>
+      </c>
+      <c r="AD9" s="16">
+        <f>[6]Model!$AF$33</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AE9" s="16">
+        <f>[6]Model!$AF$39</f>
+        <v>-0.28700962633957428</v>
+      </c>
+      <c r="AF9" s="11" t="str">
+        <f>[6]Model!$AF$40</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AH9" s="11">
+        <v>1924</v>
+      </c>
+      <c r="AJ9" s="18">
+        <f>[6]Main!$E$3</f>
+        <v>45898</v>
+      </c>
+      <c r="AK9" s="18">
+        <f>[6]Main!$G$3</f>
+        <v>46066</v>
       </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B10" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D10" s="13">
         <f>[7]Main!$D$3</f>
-        <v>472.65</v>
+        <v>568.5</v>
       </c>
       <c r="E10" s="14">
         <f>[7]Main!$D$5</f>
-        <v>68014.335000000006</v>
+        <v>81409.2</v>
       </c>
       <c r="F10" s="14">
         <f>[7]Main!$D$8</f>
-        <v>-12482</v>
+        <v>-13261</v>
       </c>
       <c r="G10" s="14">
         <f>[7]Main!$D$9</f>
-        <v>80496.335000000006</v>
+        <v>94670.2</v>
       </c>
       <c r="H10" s="14">
         <f>[7]Model!T$18</f>
@@ -2985,49 +4598,49 @@
       </c>
       <c r="R10" s="15">
         <f>$G10/M10</f>
-        <v>19.285178485864879</v>
+        <v>22.680929563967418</v>
       </c>
       <c r="S10" s="15">
-        <f t="shared" ref="S10:V11" si="19">$G10/N10</f>
-        <v>18.109507065768593</v>
+        <f t="shared" ref="S10:V14" si="21">$G10/N10</f>
+        <v>21.298244892984577</v>
       </c>
       <c r="T10" s="15">
-        <f t="shared" si="19"/>
-        <v>17.425552062495161</v>
+        <f t="shared" si="21"/>
+        <v>20.49385849513309</v>
       </c>
       <c r="U10" s="15">
-        <f t="shared" si="19"/>
-        <v>16.980548491537299</v>
+        <f t="shared" si="21"/>
+        <v>19.97049830658171</v>
       </c>
       <c r="V10" s="15">
-        <f t="shared" si="19"/>
-        <v>16.54848983039788</v>
+        <f t="shared" si="21"/>
+        <v>19.462362378880147</v>
       </c>
       <c r="W10" s="15">
         <f>G10/[7]Model!$AJ$18</f>
-        <v>15.067564901776834</v>
-      </c>
-      <c r="X10" s="14">
+        <v>17.720674894878048</v>
+      </c>
+      <c r="X10" s="23">
         <f>[7]Model!$Y$5</f>
         <v>41033</v>
       </c>
-      <c r="Y10" s="20">
-        <f t="shared" ref="Y10:Y11" si="20">G10/X10</f>
-        <v>1.961746277386494</v>
-      </c>
-      <c r="Z10" s="16">
+      <c r="Y10" s="26">
+        <f t="shared" ref="Y10:Y14" si="22">G10/X10</f>
+        <v>2.3071722759729973</v>
+      </c>
+      <c r="Z10" s="25">
         <f>[7]Model!X$24</f>
         <v>7.3438609912026775E-2</v>
       </c>
-      <c r="AA10" s="16">
+      <c r="AA10" s="25">
         <f>[7]Model!Y$24</f>
         <v>4.4362433189106598E-2</v>
       </c>
-      <c r="AB10" s="16">
+      <c r="AB10" s="25">
         <f>[7]Model!$Y$27</f>
         <v>0.20378719567177639</v>
       </c>
-      <c r="AC10" s="16">
+      <c r="AC10" s="25">
         <f>[7]Model!$Y$29</f>
         <v>0.10649964662588648</v>
       </c>
@@ -3037,7 +4650,7 @@
       </c>
       <c r="AE10" s="16">
         <f>[7]Model!$AM$30</f>
-        <v>-0.31348981866726999</v>
+        <v>-0.42365950691793453</v>
       </c>
       <c r="AF10" s="11" t="str">
         <f>[7]Model!$AM$31</f>
@@ -3048,27 +4661,27 @@
       </c>
       <c r="AJ10" s="18">
         <f>[7]Main!$E$3</f>
-        <v>45771</v>
+        <v>45862</v>
       </c>
       <c r="AK10" s="18">
         <f>[7]Main!$G$3</f>
-        <v>45862</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D11" s="13">
         <f>[8]Main!$D$3</f>
-        <v>265.69</v>
+        <v>317.10000000000002</v>
       </c>
       <c r="E11" s="14">
         <f>[8]Main!$D$5</f>
-        <v>71311.195999999996</v>
+        <v>85299.900000000009</v>
       </c>
       <c r="F11" s="14">
         <f>[8]Main!$D$8</f>
@@ -3076,7 +4689,7 @@
       </c>
       <c r="G11" s="14">
         <f>[8]Main!$D$9</f>
-        <v>79678.195999999996</v>
+        <v>93666.900000000009</v>
       </c>
       <c r="H11" s="14">
         <f>[8]Model!W$16</f>
@@ -3104,65 +4717,65 @@
       </c>
       <c r="N11" s="14">
         <f>[8]Model!AC$16</f>
-        <v>4065.2781650000034</v>
+        <v>4243.5310400000008</v>
       </c>
       <c r="O11" s="14">
         <f>[8]Model!AD$16</f>
-        <v>4316.3812148500065</v>
+        <v>4623.3326656000045</v>
       </c>
       <c r="P11" s="14">
         <f>[8]Model!AE$16</f>
-        <v>4535.0469065479992</v>
+        <v>4897.3993508480062</v>
       </c>
       <c r="Q11" s="14">
         <f>[8]Model!AF$16</f>
-        <v>4720.710356326842</v>
+        <v>5139.2124562518457</v>
       </c>
       <c r="R11" s="15">
-        <f t="shared" ref="R11" si="21">$G11/M11</f>
-        <v>21.067740877842411</v>
+        <f t="shared" ref="R11" si="23">$G11/M11</f>
+        <v>24.766499206768909</v>
       </c>
       <c r="S11" s="15">
-        <f t="shared" si="19"/>
-        <v>19.599691033688448</v>
+        <f t="shared" si="21"/>
+        <v>22.07286788221537</v>
       </c>
       <c r="T11" s="15">
-        <f t="shared" si="19"/>
-        <v>18.459490029721298</v>
+        <f t="shared" si="21"/>
+        <v>20.259606386737079</v>
       </c>
       <c r="U11" s="15">
-        <f t="shared" si="19"/>
-        <v>17.569431505759152</v>
+        <f t="shared" si="21"/>
+        <v>19.125844818797791</v>
       </c>
       <c r="V11" s="15">
-        <f t="shared" si="19"/>
-        <v>16.878433537701124</v>
+        <f t="shared" si="21"/>
+        <v>18.225924846919753</v>
       </c>
       <c r="W11" s="15">
         <f>G11/[8]Model!$AM$16</f>
-        <v>14.760827051025377</v>
-      </c>
-      <c r="X11" s="14">
+        <v>15.736922070520395</v>
+      </c>
+      <c r="X11" s="23">
         <f>[8]Model!$AB$5</f>
         <v>47716</v>
       </c>
-      <c r="Y11" s="20">
-        <f t="shared" si="20"/>
-        <v>1.6698423170425014</v>
-      </c>
-      <c r="Z11" s="16">
+      <c r="Y11" s="26">
+        <f t="shared" si="22"/>
+        <v>1.9630082152737029</v>
+      </c>
+      <c r="Z11" s="25">
         <f>[8]Model!$AA$22</f>
         <v>7.2702819296064147E-2</v>
       </c>
-      <c r="AA11" s="16">
+      <c r="AA11" s="25">
         <f>[8]Model!$AB$22</f>
         <v>0.12878501135503417</v>
       </c>
-      <c r="AB11" s="16">
+      <c r="AB11" s="25">
         <f>[8]Model!$AB$25</f>
         <v>0.15432978455863861</v>
       </c>
-      <c r="AC11" s="16">
+      <c r="AC11" s="25">
         <f>[8]Model!$AB$27</f>
         <v>0.10051135887333389</v>
       </c>
@@ -3172,586 +4785,2095 @@
       </c>
       <c r="AE11" s="16">
         <f>[8]Model!$AP$28</f>
-        <v>-0.28201653867212506</v>
+        <v>-0.33344751215489621</v>
       </c>
       <c r="AF11" s="11" t="str">
         <f>[8]Model!$AP$29</f>
-        <v>Slightly overvalued</v>
+        <v>Overvalued</v>
       </c>
       <c r="AH11" s="11">
         <v>1952</v>
       </c>
       <c r="AJ11" s="18">
         <f>[8]Main!$E$3</f>
-        <v>45771</v>
+        <v>45862</v>
       </c>
       <c r="AK11" s="18">
         <f>[8]Main!$G$3</f>
-        <v>45861</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="12" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
-        <v>27</v>
+      <c r="B12" s="19" t="s">
+        <v>28</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="D12" s="17">
+        <f>[9]Main!$D$3</f>
+        <v>1744.5</v>
+      </c>
+      <c r="E12" s="14">
+        <f>[9]Main!$D$5</f>
+        <v>76478.880000000005</v>
+      </c>
+      <c r="F12" s="14">
+        <f>[9]Main!$D$8</f>
+        <v>-293</v>
+      </c>
+      <c r="G12" s="14">
+        <f>[9]Main!$D$9</f>
+        <v>76771.88</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14">
+        <f>[9]Model!Z$37</f>
+        <v>-27</v>
+      </c>
+      <c r="J12" s="14">
+        <f>[9]Model!AA$37</f>
+        <v>291</v>
+      </c>
+      <c r="K12" s="14">
+        <f>[9]Model!AB$37</f>
+        <v>476</v>
+      </c>
+      <c r="L12" s="14">
+        <f>[9]Model!AC$37</f>
+        <v>534</v>
+      </c>
+      <c r="M12" s="14">
+        <f>[9]Model!AD$37</f>
+        <v>717</v>
+      </c>
+      <c r="N12" s="14">
+        <f>[9]Model!AE$37</f>
+        <v>1152.8015680000001</v>
+      </c>
+      <c r="O12" s="14">
+        <f>[9]Model!AF$37</f>
+        <v>1264.6224175000007</v>
+      </c>
+      <c r="P12" s="14">
+        <f>[9]Model!AG$37</f>
+        <v>1430.3841434999997</v>
+      </c>
+      <c r="Q12" s="14">
+        <f>[9]Model!AH$37</f>
+        <v>1527.5501896362498</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" ref="R12:V13" si="24">$G12/M12</f>
+        <v>107.07375174337518</v>
+      </c>
+      <c r="S12" s="15">
+        <f t="shared" si="24"/>
+        <v>66.59591913393372</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="24"/>
+        <v>60.707353386766897</v>
+      </c>
+      <c r="U12" s="15">
+        <f t="shared" si="24"/>
+        <v>53.672211306920168</v>
+      </c>
+      <c r="V12" s="15">
+        <f t="shared" si="24"/>
+        <v>50.258171889122295</v>
+      </c>
+      <c r="W12" s="15">
+        <f>G12/[9]Model!$AO$37</f>
+        <v>42.54311586413472</v>
+      </c>
+      <c r="X12" s="14">
+        <f>[9]Model!$AE$18</f>
+        <v>12231.94</v>
+      </c>
+      <c r="Y12" s="20">
+        <f>G12/X12</f>
+        <v>6.2763453712166672</v>
+      </c>
+      <c r="Z12" s="16">
+        <f>[9]Model!AD$49</f>
+        <v>0.35902439024390254</v>
+      </c>
+      <c r="AA12" s="16">
+        <f>[9]Model!AE$49</f>
+        <v>0.25442928930366127</v>
+      </c>
+      <c r="AB12" s="16">
+        <f>[9]Model!$AE$51</f>
+        <v>0.28072109575423032</v>
+      </c>
+      <c r="AC12" s="16">
+        <f>[9]Model!$AE$56</f>
+        <v>0.16228117534912698</v>
+      </c>
+      <c r="AD12" s="16">
+        <f>[9]Model!$AS$46</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AE12" s="16">
+        <f>[9]Model!$AS$52</f>
+        <v>-0.71543396756112809</v>
+      </c>
+      <c r="AF12" s="11" t="str">
+        <f>[9]Model!$AS$53</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH12" s="11">
+        <v>1927</v>
+      </c>
+      <c r="AJ12" s="18">
+        <f>[9]Main!$E$3</f>
+        <v>45906</v>
+      </c>
+      <c r="AK12" s="18">
+        <f>[9]Main!$G$3</f>
+        <v>45967</v>
       </c>
     </row>
     <row r="13" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
-        <v>29</v>
+      <c r="B13" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="17">
-        <f>[9]Main!$D$3</f>
-        <v>1417</v>
+        <v>62</v>
+      </c>
+      <c r="D13" s="22">
+        <f>[10]Main!$D$3</f>
+        <v>10.7</v>
       </c>
       <c r="E13" s="14">
-        <f>[9]Main!$D$5</f>
-        <v>61540.31</v>
+        <f>[10]Main!$D$5</f>
+        <v>90201</v>
       </c>
       <c r="F13" s="14">
-        <f>[9]Main!$D$8</f>
-        <v>-893</v>
+        <f>[10]Main!$D$8</f>
+        <v>2379</v>
       </c>
       <c r="G13" s="14">
-        <f>[9]Main!$D$9</f>
-        <v>62433.31</v>
-      </c>
-      <c r="H13" s="14"/>
+        <f>[10]Main!$D$9</f>
+        <v>87822</v>
+      </c>
+      <c r="H13" s="14">
+        <f>[10]Model!L$16</f>
+        <v>-1315</v>
+      </c>
       <c r="I13" s="14">
-        <f>[9]Model!Y$37</f>
-        <v>0</v>
+        <f>[10]Model!M$16</f>
+        <v>-3170</v>
       </c>
       <c r="J13" s="14">
-        <f>[9]Model!Z$37</f>
-        <v>-27</v>
+        <f>[10]Model!N$16</f>
+        <v>120</v>
       </c>
       <c r="K13" s="14">
-        <f>[9]Model!AA$37</f>
-        <v>291</v>
+        <f>[10]Model!O$16</f>
+        <v>-1269</v>
       </c>
       <c r="L13" s="14">
-        <f>[9]Model!AB$37</f>
-        <v>476</v>
+        <f>[10]Model!P$16</f>
+        <v>2412</v>
       </c>
       <c r="M13" s="14">
-        <f>[9]Model!AC$37</f>
-        <v>534</v>
+        <f>[10]Model!Q$16</f>
+        <v>1971</v>
       </c>
       <c r="N13" s="14">
-        <f>[9]Model!AD$37</f>
-        <v>717</v>
+        <f>[10]Model!R$16</f>
+        <v>1792.7340799999997</v>
       </c>
       <c r="O13" s="14">
-        <f>[9]Model!AE$37</f>
-        <v>1183.5057150000023</v>
+        <f>[10]Model!S$16</f>
+        <v>2039.0654464000004</v>
       </c>
       <c r="P13" s="14">
-        <f>[9]Model!AF$37</f>
-        <v>1446.6646025</v>
+        <f>[10]Model!T$16</f>
+        <v>2250.0783875840002</v>
       </c>
       <c r="Q13" s="14">
-        <f>[9]Model!AG$37</f>
-        <v>1594.3621815874999</v>
+        <f>[10]Model!U$16</f>
+        <v>2444.7265855552005</v>
       </c>
       <c r="R13" s="15">
-        <f>$G13/M13</f>
-        <v>116.91631086142321</v>
+        <f t="shared" si="24"/>
+        <v>44.557077625570777</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" ref="S13:V14" si="22">$G13/N13</f>
-        <v>87.07574616457461</v>
+        <f t="shared" si="24"/>
+        <v>48.987745020164958</v>
       </c>
       <c r="T13" s="15">
-        <f t="shared" si="22"/>
-        <v>52.752858907825278</v>
+        <f t="shared" si="24"/>
+        <v>43.069730868644271</v>
       </c>
       <c r="U13" s="15">
-        <f t="shared" si="22"/>
-        <v>43.156727476505736</v>
+        <f t="shared" si="24"/>
+        <v>39.03064021440516</v>
       </c>
       <c r="V13" s="15">
-        <f t="shared" si="22"/>
-        <v>39.158800127732214</v>
+        <f t="shared" si="24"/>
+        <v>35.923035532439926</v>
       </c>
       <c r="W13" s="15">
-        <f>G13/[9]Model!$AN$37</f>
-        <v>32.332214391558495</v>
-      </c>
-      <c r="X13" s="14">
-        <f>[9]Model!$AC$18</f>
-        <v>7175</v>
-      </c>
-      <c r="Y13" s="20">
-        <f t="shared" ref="Y13:Y14" si="23">G13/X13</f>
-        <v>8.7015066202090594</v>
-      </c>
-      <c r="Z13" s="16">
-        <f>[9]Model!$AB$49</f>
-        <v>0.1327089591800672</v>
-      </c>
-      <c r="AA13" s="16">
-        <f>[9]Model!$AC$49</f>
-        <v>0.11934477379095165</v>
-      </c>
-      <c r="AB13" s="16">
-        <f>[9]Model!$AC$51</f>
-        <v>0.26327526132404183</v>
-      </c>
-      <c r="AC13" s="16">
-        <f>[9]Model!$AC$56</f>
-        <v>0.11777003484320557</v>
+        <f>G13/[10]Model!$AB$16</f>
+        <v>25.142348650280088</v>
+      </c>
+      <c r="X13" s="23">
+        <f>[10]Model!$Q$3</f>
+        <v>18909</v>
+      </c>
+      <c r="Y13" s="26">
+        <f>G13/X13</f>
+        <v>4.6444550214183726</v>
+      </c>
+      <c r="Z13" s="25">
+        <f>[10]Model!P$20</f>
+        <v>0.21937869822485201</v>
+      </c>
+      <c r="AA13" s="25">
+        <f>[10]Model!Q$20</f>
+        <v>0.14697318937280124</v>
+      </c>
+      <c r="AB13" s="25">
+        <f>[10]Model!$Q$21</f>
+        <v>0.22322703474535935</v>
+      </c>
+      <c r="AC13" s="25">
+        <f>[10]Model!$Q$24</f>
+        <v>0.12459675286900418</v>
       </c>
       <c r="AD13" s="16">
-        <f>[9]Model!$AS$46</f>
+        <f>[10]Model!$AE$22</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE13" s="16">
-        <f>[9]Model!$AS$52</f>
-        <v>-0.62242636061307977</v>
+        <f>[10]Model!$AE$28</f>
+        <v>-0.53007610364432378</v>
       </c>
       <c r="AF13" s="11" t="str">
-        <f>[9]Model!$AS$53</f>
-        <v>Heavily overvalued</v>
+        <f>[10]Model!$AE$29</f>
+        <v>Overvalued</v>
       </c>
       <c r="AH13" s="11">
-        <v>1927</v>
+        <v>1906</v>
       </c>
       <c r="AJ13" s="18">
-        <f>[9]Main!$F$3</f>
-        <v>45734</v>
+        <f>[10]Main!$E$3</f>
+        <v>45898</v>
       </c>
       <c r="AK13" s="18">
-        <f>[9]Main!$H$3</f>
-        <v>45455</v>
+        <f>[10]Main!$G$3</f>
+        <v>46079</v>
       </c>
     </row>
     <row r="14" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B14" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="13">
-        <f>[10]Main!$D$3</f>
-        <v>212.27</v>
+        <v>54</v>
+      </c>
+      <c r="D14" s="22">
+        <f>[11]Main!$D$3</f>
+        <v>19.254999999999999</v>
       </c>
       <c r="E14" s="14">
-        <f>[10]Main!$D$5</f>
-        <v>39970.441000000006</v>
+        <f>[11]Main!$D$5</f>
+        <v>57765</v>
       </c>
       <c r="F14" s="14">
-        <f>[10]Main!$D$8</f>
-        <v>-11621</v>
+        <f>[11]Main!$D$8</f>
+        <v>-4907</v>
       </c>
       <c r="G14" s="14">
-        <f>[10]Main!$D$9</f>
-        <v>51591.441000000006</v>
-      </c>
-      <c r="I14" s="14">
-        <f>[10]Model!T$18</f>
-        <v>1119</v>
-      </c>
+        <f>[11]Main!$D$9</f>
+        <v>62672</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="14">
-        <f>[10]Model!U$18</f>
-        <v>1846</v>
+        <f>[11]Model!N$32</f>
+        <v>1758</v>
       </c>
       <c r="K14" s="14">
-        <f>[10]Model!V$18</f>
-        <v>1062</v>
+        <f>[11]Model!O$32</f>
+        <v>1591</v>
       </c>
       <c r="L14" s="14">
-        <f>[10]Model!W$18</f>
-        <v>1227</v>
+        <f>[11]Model!P$32</f>
+        <v>1857</v>
       </c>
       <c r="M14" s="14">
-        <f>[10]Model!X$18</f>
-        <v>1502</v>
+        <f>[11]Model!Q$32</f>
+        <v>1956</v>
       </c>
       <c r="N14" s="14">
-        <f>[10]Model!Y$18</f>
-        <v>1666.6471800000006</v>
+        <f>[11]Model!R$32</f>
+        <v>2983.0295450000012</v>
       </c>
       <c r="O14" s="14">
-        <f>[10]Model!Z$18</f>
-        <v>1795.3686990000031</v>
+        <f>[11]Model!S$32</f>
+        <v>3274.0576822999979</v>
       </c>
       <c r="P14" s="14">
-        <f>[10]Model!AA$18</f>
-        <v>1911.0909576599986</v>
+        <f>[11]Model!T$32</f>
+        <v>3558.6704355280026</v>
       </c>
       <c r="Q14" s="14">
-        <f>[10]Model!AB$18</f>
-        <v>2010.4950586877997</v>
+        <f>[11]Model!U$32</f>
+        <v>3774.8694653950824</v>
       </c>
       <c r="R14" s="15">
-        <f>$G14/M14</f>
-        <v>34.348496005326233</v>
+        <f t="shared" ref="R14" si="25">$G14/M14</f>
+        <v>32.040899795501019</v>
       </c>
       <c r="S14" s="15">
+        <f t="shared" si="21"/>
+        <v>21.00951366876253</v>
+      </c>
+      <c r="T14" s="15">
+        <f t="shared" si="21"/>
+        <v>19.141996287607689</v>
+      </c>
+      <c r="U14" s="15">
+        <f t="shared" si="21"/>
+        <v>17.611071644711409</v>
+      </c>
+      <c r="V14" s="15">
+        <f t="shared" si="21"/>
+        <v>16.60242839508112</v>
+      </c>
+      <c r="W14" s="15">
+        <f>G14/[11]Model!$AB$32</f>
+        <v>12.771379054505589</v>
+      </c>
+      <c r="X14" s="23">
+        <f>[11]Model!$Q$13</f>
+        <v>26312</v>
+      </c>
+      <c r="Y14" s="26">
         <f t="shared" si="22"/>
-        <v>30.955226528508565</v>
-      </c>
-      <c r="T14" s="15">
-        <f t="shared" si="22"/>
-        <v>28.735847421610817</v>
-      </c>
-      <c r="U14" s="15">
-        <f t="shared" si="22"/>
-        <v>26.995806135344928</v>
-      </c>
-      <c r="V14" s="15">
-        <f t="shared" si="22"/>
-        <v>25.661063317247077</v>
-      </c>
-      <c r="W14" s="15">
-        <f>G14/[10]Model!$AI$18</f>
-        <v>18.839274711369718</v>
-      </c>
-      <c r="X14" s="14">
-        <f>[10]Model!$X$5</f>
-        <v>21325</v>
-      </c>
-      <c r="Y14" s="20">
-        <f t="shared" si="23"/>
-        <v>2.4192938335287226</v>
-      </c>
-      <c r="Z14" s="16">
-        <f>[10]Model!$W$24</f>
-        <v>0.13814324229281438</v>
-      </c>
-      <c r="AA14" s="16">
-        <f>[10]Model!$X$24</f>
-        <v>9.815129512333276E-2</v>
-      </c>
-      <c r="AB14" s="16">
-        <f>[10]Model!$X$27</f>
-        <v>0.25903868698710436</v>
-      </c>
-      <c r="AC14" s="16">
-        <f>[10]Model!$X$29</f>
-        <v>8.9941383352872217E-2</v>
+        <v>2.3818789905746427</v>
+      </c>
+      <c r="Z14" s="25">
+        <f>[11]Model!P$41</f>
+        <v>8.5614827359111967E-2</v>
+      </c>
+      <c r="AA14" s="25">
+        <f>[11]Model!Q$41</f>
+        <v>0.14013346043851294</v>
+      </c>
+      <c r="AB14" s="25">
+        <f>[11]Model!$Q$42</f>
+        <v>0.65472027972027969</v>
+      </c>
+      <c r="AC14" s="25">
+        <f>[11]Model!$Q$45</f>
+        <v>8.3840072970507759E-2</v>
       </c>
       <c r="AD14" s="16">
-        <f>[10]Model!$AL$24</f>
-        <v>0.08</v>
+        <f>[11]Model!$AE$39</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AE14" s="16">
-        <f>[10]Model!$AL$30</f>
-        <v>-0.58739207901404</v>
+        <f>[11]Model!$AE$45</f>
+        <v>-7.0527347483917202E-2</v>
       </c>
       <c r="AF14" s="11" t="str">
-        <f>[10]Model!$AL$31</f>
-        <v>Heavily overvalued</v>
+        <f>[11]Model!$AE$46</f>
+        <v>Fairly valued</v>
       </c>
       <c r="AH14" s="11">
-        <v>1890</v>
+        <v>1953</v>
       </c>
       <c r="AJ14" s="18">
-        <f>[10]Main!$E$3</f>
-        <v>45771</v>
+        <f>[11]Main!$E$3</f>
+        <v>45868</v>
       </c>
       <c r="AK14" s="18">
-        <f>[10]Main!$G$3</f>
-        <v>45771</v>
+        <f>[11]Main!$G$3</f>
+        <v>46072</v>
       </c>
     </row>
     <row r="15" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
-        <v>35</v>
+      <c r="B15" s="19" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="D15" s="13">
+        <f>[12]Main!$D$3</f>
+        <v>277.22000000000003</v>
+      </c>
+      <c r="E15" s="14">
+        <f>[12]Main!$D$5</f>
+        <v>51867.862000000001</v>
+      </c>
+      <c r="F15" s="14">
+        <f>[12]Main!$D$8</f>
+        <v>-11620</v>
+      </c>
+      <c r="G15" s="14">
+        <f>[12]Main!$D$9</f>
+        <v>63487.862000000001</v>
+      </c>
+      <c r="I15" s="14">
+        <f>[12]Model!T$18</f>
+        <v>1119</v>
+      </c>
+      <c r="J15" s="14">
+        <f>[12]Model!U$18</f>
+        <v>1846</v>
+      </c>
+      <c r="K15" s="14">
+        <f>[12]Model!V$18</f>
+        <v>1062</v>
+      </c>
+      <c r="L15" s="14">
+        <f>[12]Model!W$18</f>
+        <v>1227</v>
+      </c>
+      <c r="M15" s="14">
+        <f>[12]Model!X$18</f>
+        <v>1502</v>
+      </c>
+      <c r="N15" s="14">
+        <f>[12]Model!Y$18</f>
+        <v>2244.6631800000009</v>
+      </c>
+      <c r="O15" s="14">
+        <f>[12]Model!Z$18</f>
+        <v>2396.5053390000035</v>
+      </c>
+      <c r="P15" s="14">
+        <f>[12]Model!AA$18</f>
+        <v>2530.2616968599991</v>
+      </c>
+      <c r="Q15" s="14">
+        <f>[12]Model!AB$18</f>
+        <v>2642.0492126718009</v>
+      </c>
+      <c r="R15" s="15">
+        <f>$G15/M15</f>
+        <v>42.268882822902796</v>
+      </c>
+      <c r="S15" s="15">
+        <f t="shared" ref="S15:V17" si="26">$G15/N15</f>
+        <v>28.283914738602331</v>
+      </c>
+      <c r="T15" s="15">
+        <f t="shared" si="26"/>
+        <v>26.49185084915845</v>
+      </c>
+      <c r="U15" s="15">
+        <f t="shared" si="26"/>
+        <v>25.091421207058183</v>
+      </c>
+      <c r="V15" s="15">
+        <f t="shared" si="26"/>
+        <v>24.029780253713447</v>
+      </c>
+      <c r="W15" s="15">
+        <f>G15/[12]Model!$AI$18</f>
+        <v>18.587528267497191</v>
+      </c>
+      <c r="X15" s="23">
+        <f>[12]Model!$X$5</f>
+        <v>21325</v>
+      </c>
+      <c r="Y15" s="26">
+        <f t="shared" ref="Y15:Y17" si="27">G15/X15</f>
+        <v>2.9771564830011723</v>
+      </c>
+      <c r="Z15" s="25">
+        <f>[12]Model!$W$24</f>
+        <v>0.13814324229281438</v>
+      </c>
+      <c r="AA15" s="25">
+        <f>[12]Model!$X$24</f>
+        <v>9.815129512333276E-2</v>
+      </c>
+      <c r="AB15" s="25">
+        <f>[12]Model!$X$27</f>
+        <v>0.25903868698710436</v>
+      </c>
+      <c r="AC15" s="25">
+        <f>[12]Model!$X$29</f>
+        <v>8.9941383352872217E-2</v>
+      </c>
+      <c r="AD15" s="16">
+        <f>[12]Model!$AL$24</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE15" s="16">
+        <f>[12]Model!$AL$30</f>
+        <v>-0.5363754386448315</v>
+      </c>
+      <c r="AF15" s="11" t="str">
+        <f>[12]Model!$AL$31</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>1890</v>
+      </c>
+      <c r="AJ15" s="18">
+        <f>[12]Main!$E$3</f>
+        <v>45898</v>
+      </c>
+      <c r="AK15" s="18">
+        <f>[12]Main!$G$3</f>
+        <v>45953</v>
       </c>
     </row>
     <row r="16" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
-        <v>36</v>
+      <c r="B16" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="D16" s="17">
+        <f>[13]Main!$D$3</f>
+        <v>235.1</v>
+      </c>
+      <c r="E16" s="14">
+        <f>[13]Main!$D$5</f>
+        <v>48289.54</v>
+      </c>
+      <c r="F16" s="14">
+        <f>[13]Main!$D$8</f>
+        <v>-1408.0999999999995</v>
+      </c>
+      <c r="G16" s="14">
+        <f>[13]Main!$D$9</f>
+        <v>49697.64</v>
+      </c>
+      <c r="H16" s="14">
+        <f>[13]Model!K$22</f>
+        <v>1146.4000000000005</v>
+      </c>
+      <c r="I16" s="14">
+        <f>[13]Model!L$22</f>
+        <v>491.90000000000072</v>
+      </c>
+      <c r="J16" s="14">
+        <f>[13]Model!M$22</f>
+        <v>1016.7999999999997</v>
+      </c>
+      <c r="K16" s="14">
+        <f>[13]Model!N$22</f>
+        <v>1121.8999999999996</v>
+      </c>
+      <c r="L16" s="14">
+        <f>[13]Model!O$22</f>
+        <v>928.6000000000015</v>
+      </c>
+      <c r="M16" s="14">
+        <f>[13]Model!P$22</f>
+        <v>932.29999999999723</v>
+      </c>
+      <c r="N16" s="14">
+        <f>[13]Model!Q$22</f>
+        <v>1473.4199211999967</v>
+      </c>
+      <c r="O16" s="14">
+        <f>[13]Model!R$22</f>
+        <v>1674.1472117759988</v>
+      </c>
+      <c r="P16" s="14">
+        <f>[13]Model!S$22</f>
+        <v>1801.8286222247989</v>
+      </c>
+      <c r="Q16" s="14">
+        <f>[13]Model!T$22</f>
+        <v>1905.822140949791</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" ref="R16" si="28">$G16/M16</f>
+        <v>53.306489327469855</v>
+      </c>
+      <c r="S16" s="15">
+        <f t="shared" si="26"/>
+        <v>33.729447583092792</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" si="26"/>
+        <v>29.685346456049619</v>
+      </c>
+      <c r="U16" s="15">
+        <f t="shared" si="26"/>
+        <v>27.581779635976748</v>
+      </c>
+      <c r="V16" s="15">
+        <f t="shared" si="26"/>
+        <v>26.076746057338038</v>
+      </c>
+      <c r="W16" s="15">
+        <f>G16/[13]Model!$AA$22</f>
+        <v>22.492554608963555</v>
+      </c>
+      <c r="X16" s="23">
+        <f>[13]Model!$P$3</f>
+        <v>20576.599999999999</v>
+      </c>
+      <c r="Y16" s="26">
+        <f t="shared" si="27"/>
+        <v>2.4152503329024233</v>
+      </c>
+      <c r="Z16" s="25">
+        <f>[13]Model!O$26</f>
+        <v>4.89276444606348E-2</v>
+      </c>
+      <c r="AA16" s="25">
+        <f>[13]Model!P$26</f>
+        <v>0.11657007662086771</v>
+      </c>
+      <c r="AB16" s="25">
+        <f>[13]Model!$P$27</f>
+        <v>0.26116559587103788</v>
+      </c>
+      <c r="AC16" s="25">
+        <f>[13]Model!$P$31</f>
+        <v>6.1341523866916652E-2</v>
+      </c>
+      <c r="AD16" s="16">
+        <f>[13]Model!$AD$29</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE16" s="16">
+        <f>[13]Model!$AD$35</f>
+        <v>-0.53135711887326365</v>
+      </c>
+      <c r="AF16" s="11" t="str">
+        <f>[13]Model!$AD$36</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH16" s="11">
+        <v>1949</v>
+      </c>
+      <c r="AJ16" s="18">
+        <f>[13]Main!$E$3</f>
+        <v>45868</v>
+      </c>
+      <c r="AK16" s="18">
+        <f>[13]Main!$G$3</f>
+        <v>46079</v>
       </c>
     </row>
     <row r="17" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
-        <v>37</v>
+      <c r="B17" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>69</v>
+        <v>64</v>
+      </c>
+      <c r="D17" s="17">
+        <f>[14]Main!$D$3</f>
+        <v>27.18</v>
+      </c>
+      <c r="E17" s="14">
+        <f>[14]Main!$D$5</f>
+        <v>35695.493999999999</v>
+      </c>
+      <c r="F17" s="14">
+        <f>[14]Main!$D$8</f>
+        <v>1459</v>
+      </c>
+      <c r="G17" s="14">
+        <f>[14]Main!$D$9</f>
+        <v>34236.493999999999</v>
+      </c>
+      <c r="H17" s="14">
+        <f>[14]Model!Q$23</f>
+        <v>615.30000000000064</v>
+      </c>
+      <c r="I17" s="14">
+        <f>[14]Model!R$23</f>
+        <v>491.20000000000067</v>
+      </c>
+      <c r="J17" s="14">
+        <f>[14]Model!S$23</f>
+        <v>773.79999999999905</v>
+      </c>
+      <c r="K17" s="14">
+        <f>[14]Model!T$23</f>
+        <v>931.79999999999984</v>
+      </c>
+      <c r="L17" s="14">
+        <f>[14]Model!U$23</f>
+        <v>1050.8999999999996</v>
+      </c>
+      <c r="M17" s="14">
+        <f>[14]Model!V$23</f>
+        <v>1200.3000000000002</v>
+      </c>
+      <c r="N17" s="14">
+        <f>[14]Model!W$23</f>
+        <v>1113.4564026999999</v>
+      </c>
+      <c r="O17" s="14">
+        <f>[14]Model!X$23</f>
+        <v>1422.1613657599992</v>
+      </c>
+      <c r="P17" s="14">
+        <f>[14]Model!Y$23</f>
+        <v>1443.7923014975993</v>
+      </c>
+      <c r="Q17" s="14">
+        <f>[14]Model!Z$23</f>
+        <v>1456.7690142637746</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" ref="R17" si="29">$G17/M17</f>
+        <v>28.523280846455048</v>
+      </c>
+      <c r="S17" s="15">
+        <f t="shared" si="26"/>
+        <v>30.747942997121896</v>
+      </c>
+      <c r="T17" s="15">
+        <f t="shared" si="26"/>
+        <v>24.073564944371913</v>
+      </c>
+      <c r="U17" s="15">
+        <f t="shared" si="26"/>
+        <v>23.712894136149352</v>
+      </c>
+      <c r="V17" s="15">
+        <f t="shared" si="26"/>
+        <v>23.501662696541167</v>
+      </c>
+      <c r="W17" s="15">
+        <f>G17/[14]Model!$AG$23</f>
+        <v>19.802862236524049</v>
+      </c>
+      <c r="X17" s="23">
+        <f>[14]Model!$V$7</f>
+        <v>6213.6</v>
+      </c>
+      <c r="Y17" s="26">
+        <f t="shared" si="27"/>
+        <v>5.5099288657139169</v>
+      </c>
+      <c r="Z17" s="25">
+        <f>[14]Model!U$30</f>
+        <v>5.0500414805923599E-2</v>
+      </c>
+      <c r="AA17" s="25">
+        <f>[14]Model!V$30</f>
+        <v>4.4056860570622192E-2</v>
+      </c>
+      <c r="AB17" s="25">
+        <f>[14]Model!$V$33</f>
+        <v>0.83643942320072096</v>
+      </c>
+      <c r="AC17" s="25">
+        <f>[14]Model!$V$37</f>
+        <v>0.2188264452169435</v>
+      </c>
+      <c r="AD17" s="16">
+        <f>[14]Model!$AJ$29</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE17" s="16">
+        <f>[14]Model!$AJ$35</f>
+        <v>-0.43497641969139733</v>
+      </c>
+      <c r="AF17" s="11" t="str">
+        <f>[14]Model!$AJ$36</f>
+        <v>Overvalued</v>
+      </c>
+      <c r="AH17" s="11">
+        <v>1971</v>
+      </c>
+      <c r="AJ17" s="18">
+        <f>[14]Main!$E$3</f>
+        <v>45868</v>
+      </c>
+      <c r="AK17" s="18">
+        <f>[14]Main!$G$3</f>
+        <v>46079</v>
       </c>
     </row>
     <row r="18" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
-        <v>39</v>
+      <c r="B18" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" s="17">
-        <f>[11]Main!$D$3</f>
-        <v>46.45</v>
+        <f>[15]Main!$D$3</f>
+        <v>47.27</v>
       </c>
       <c r="E18" s="14">
-        <f>[11]Main!$D$5</f>
-        <v>26736.620000000003</v>
+        <f>[15]Main!$D$5</f>
+        <v>27246.428</v>
       </c>
       <c r="F18" s="14">
-        <f>[11]Main!$D$8</f>
+        <f>[15]Main!$D$8</f>
         <v>-267</v>
       </c>
       <c r="G18" s="14">
-        <f>[11]Main!$D$9</f>
-        <v>27003.620000000003</v>
+        <f>[15]Main!$D$9</f>
+        <v>27513.428</v>
       </c>
       <c r="H18" s="14">
-        <f>[11]Model!T$18</f>
+        <f>[15]Model!T$19</f>
         <v>823</v>
       </c>
       <c r="I18" s="14">
-        <f>[11]Model!U$18</f>
+        <f>[15]Model!U$19</f>
         <v>239</v>
       </c>
       <c r="J18" s="14">
-        <f>[11]Model!V$18</f>
+        <f>[15]Model!V$19</f>
         <v>586</v>
       </c>
       <c r="K18" s="14">
-        <f>[11]Model!W$18</f>
+        <f>[15]Model!W$19</f>
         <v>927</v>
       </c>
       <c r="L18" s="14">
-        <f>[11]Model!X$18</f>
+        <f>[15]Model!X$19</f>
         <v>658</v>
       </c>
       <c r="M18" s="14">
-        <f>[11]Model!Y$18</f>
+        <f>[15]Model!Y$19</f>
         <v>1072</v>
       </c>
       <c r="N18" s="14">
-        <f>[11]Model!Z$18</f>
-        <v>1019.06265</v>
+        <f>[15]Model!Z$19</f>
+        <v>1017.2926499999999</v>
       </c>
       <c r="O18" s="14">
-        <f>[11]Model!AA$18</f>
-        <v>1838.0187149999997</v>
+        <f>[15]Model!AA$19</f>
+        <v>1811.8731149999999</v>
       </c>
       <c r="P18" s="14">
-        <f>[11]Model!AB$18</f>
-        <v>1923.3074602500005</v>
+        <f>[15]Model!AB$19</f>
+        <v>1919.0845944000002</v>
       </c>
       <c r="Q18" s="14">
-        <f>[11]Model!AC$18</f>
-        <v>2000.3647039200005</v>
+        <f>[15]Model!AC$19</f>
+        <v>1993.765444011</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" ref="R18:V18" si="24">$G18/M18</f>
-        <v>25.18994402985075</v>
+        <f t="shared" ref="R18:V18" si="30">$G18/M18</f>
+        <v>25.66551119402985</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="24"/>
-        <v>26.498488586545687</v>
+        <f t="shared" si="30"/>
+        <v>27.045735560951908</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="24"/>
-        <v>14.691700242018486</v>
+        <f t="shared" si="30"/>
+        <v>15.185074369846259</v>
       </c>
       <c r="U18" s="15">
-        <f t="shared" si="24"/>
-        <v>14.040199270318405</v>
+        <f t="shared" si="30"/>
+        <v>14.336745800724874</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="24"/>
-        <v>13.499348367366487</v>
+        <f t="shared" si="30"/>
+        <v>13.799731599645581</v>
       </c>
       <c r="W18" s="15">
-        <f>G18/[11]Model!$AJ$18</f>
-        <v>11.637538166893249</v>
-      </c>
-      <c r="X18" s="14">
-        <f>[11]Model!$Y$3</f>
+        <f>G18/[15]Model!$AJ$19</f>
+        <v>12.020001089934652</v>
+      </c>
+      <c r="X18" s="23">
+        <f>[15]Model!$Y$3</f>
         <v>17763</v>
       </c>
-      <c r="Y18" s="20">
-        <f>G18/X18</f>
-        <v>1.5202173056353094</v>
-      </c>
-      <c r="Z18" s="16">
-        <f>[11]Model!$X$22</f>
+      <c r="Y18" s="26">
+        <f t="shared" ref="Y18:Y24" si="31">G18/X18</f>
+        <v>1.5489178629735969</v>
+      </c>
+      <c r="Z18" s="25">
+        <f>[15]Model!$X$23</f>
         <v>3.9284986066743688E-2</v>
       </c>
-      <c r="AA18" s="16">
-        <f>[11]Model!$Y$22</f>
+      <c r="AA18" s="25">
+        <f>[15]Model!$Y$23</f>
         <v>0.1616637237590739</v>
       </c>
-      <c r="AB18" s="16">
-        <f>[11]Model!$Y$23</f>
+      <c r="AB18" s="25">
+        <f>[15]Model!$Y$24</f>
         <v>0.11349434217193041</v>
       </c>
-      <c r="AC18" s="16">
-        <f>[11]Model!$Y$25</f>
+      <c r="AC18" s="25">
+        <f>[15]Model!$Y$26</f>
         <v>6.6430220120475142E-2</v>
       </c>
       <c r="AD18" s="16">
-        <f>[11]Model!$AM$24</f>
+        <f>[15]Model!$AM$25</f>
         <v>0.08</v>
       </c>
       <c r="AE18" s="16">
-        <f>[11]Model!$AM$30</f>
-        <v>-8.2951850912037273E-2</v>
+        <f>[15]Model!$AM$31</f>
+        <v>-0.10935664388414268</v>
       </c>
       <c r="AF18" s="11" t="str">
-        <f>[11]Model!$AM$31</f>
+        <f>[15]Model!$AM$32</f>
         <v>Fairly valued</v>
       </c>
       <c r="AH18" s="11">
         <v>1996</v>
       </c>
       <c r="AJ18" s="18">
-        <f>[11]Main!$E$3</f>
-        <v>45736</v>
+        <f>[15]Main!$E$3</f>
+        <v>45904</v>
       </c>
       <c r="AK18" s="18">
-        <f>[11]Main!$G$3</f>
+        <f>[15]Main!$G$3</f>
         <v>45868</v>
       </c>
     </row>
     <row r="19" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
-        <v>38</v>
+      <c r="B19" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>70</v>
+        <v>75</v>
+      </c>
+      <c r="D19" s="17">
+        <f>[16]Main!$D$3</f>
+        <v>180.62</v>
+      </c>
+      <c r="E19" s="14">
+        <f>[16]Main!$D$5</f>
+        <v>23173.546000000002</v>
+      </c>
+      <c r="F19" s="14">
+        <f>[16]Main!$D$8</f>
+        <v>-4174</v>
+      </c>
+      <c r="G19" s="14">
+        <f>[16]Main!$D$9</f>
+        <v>27347.546000000002</v>
+      </c>
+      <c r="H19" s="14">
+        <f>[16]Model!P$18</f>
+        <v>667</v>
+      </c>
+      <c r="I19" s="14">
+        <f>[16]Model!Q$18</f>
+        <v>628</v>
+      </c>
+      <c r="J19" s="14">
+        <f>[16]Model!R$18</f>
+        <v>753</v>
+      </c>
+      <c r="K19" s="14">
+        <f>[16]Model!S$18</f>
+        <v>685</v>
+      </c>
+      <c r="L19" s="14">
+        <f>[16]Model!T$18</f>
+        <v>199</v>
+      </c>
+      <c r="M19" s="14">
+        <f>[16]Model!U$18</f>
+        <v>1254</v>
+      </c>
+      <c r="N19" s="14">
+        <f>[16]Model!V$18</f>
+        <v>1488.4593099999986</v>
+      </c>
+      <c r="O19" s="14">
+        <f>[16]Model!W$18</f>
+        <v>1825.4889705000001</v>
+      </c>
+      <c r="P19" s="14">
+        <f>[16]Model!X$18</f>
+        <v>1915.7253039600007</v>
+      </c>
+      <c r="Q19" s="14">
+        <f>[16]Model!Y$18</f>
+        <v>1981.3585502100002</v>
+      </c>
+      <c r="R19" s="15">
+        <f t="shared" ref="R19" si="32">$G19/M19</f>
+        <v>21.808250398724084</v>
+      </c>
+      <c r="S19" s="15">
+        <f t="shared" ref="S19:S24" si="33">$G19/N19</f>
+        <v>18.373055827774042</v>
+      </c>
+      <c r="T19" s="15">
+        <f t="shared" ref="T19:T24" si="34">$G19/O19</f>
+        <v>14.980942882667502</v>
+      </c>
+      <c r="U19" s="15">
+        <f t="shared" ref="U19:U24" si="35">$G19/P19</f>
+        <v>14.275296120727653</v>
+      </c>
+      <c r="V19" s="15">
+        <f t="shared" ref="V19:V24" si="36">$G19/Q19</f>
+        <v>13.802421574379604</v>
+      </c>
+      <c r="W19" s="15">
+        <f>G19/[16]Model!$AF$18</f>
+        <v>12.733418423610921</v>
+      </c>
+      <c r="X19" s="23">
+        <f>[16]Model!$U$3</f>
+        <v>16662</v>
+      </c>
+      <c r="Y19" s="26">
+        <f t="shared" si="31"/>
+        <v>1.6413123274516865</v>
+      </c>
+      <c r="Z19" s="25">
+        <f>[16]Model!T$22</f>
+        <v>7.2381217004723553E-2</v>
+      </c>
+      <c r="AA19" s="25">
+        <f>[16]Model!U$22</f>
+        <v>7.9284881461329171E-2</v>
+      </c>
+      <c r="AB19" s="25">
+        <f>[16]Model!$U$23</f>
+        <v>0.16792701956547834</v>
+      </c>
+      <c r="AC19" s="25">
+        <f>[16]Model!$U$26</f>
+        <v>0.10731004681310767</v>
+      </c>
+      <c r="AD19" s="16">
+        <f>[16]Model!$AI$24</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE19" s="16">
+        <f>[16]Model!$AI$30</f>
+        <v>-0.15132262827852416</v>
+      </c>
+      <c r="AF19" s="11" t="str">
+        <f>[16]Model!$AI$31</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AH19" s="11">
+        <v>1969</v>
+      </c>
+      <c r="AJ19" s="18">
+        <f>[16]Main!$E$3</f>
+        <v>45898</v>
+      </c>
+      <c r="AK19" s="18">
+        <f>[16]Main!$G$3</f>
+        <v>45965</v>
       </c>
     </row>
     <row r="20" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
-        <v>44</v>
+      <c r="B20" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG20" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D20" s="17">
+        <f>[17]Main!$D$3</f>
+        <v>194.63</v>
+      </c>
+      <c r="E20" s="14">
+        <f>[17]Main!$D$5</f>
+        <v>19287.832999999999</v>
+      </c>
+      <c r="F20" s="14">
+        <f>[17]Main!$D$8</f>
+        <v>-4448</v>
+      </c>
+      <c r="G20" s="14">
+        <f>[17]Main!$D$9</f>
+        <v>23735.832999999999</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14">
+        <f>[17]Model!U$23</f>
+        <v>370</v>
+      </c>
+      <c r="N20" s="14">
+        <f>[17]Model!V$23</f>
+        <v>501.53600000000051</v>
+      </c>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="15">
+        <f t="shared" ref="R20" si="37">$G20/M20</f>
+        <v>64.150899999999993</v>
+      </c>
+      <c r="S20" s="15">
+        <f t="shared" si="33"/>
+        <v>47.326279668857218</v>
+      </c>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="14">
+        <f>[17]Model!$V$8</f>
+        <v>9401.5300000000007</v>
+      </c>
+      <c r="Y20" s="20">
+        <f t="shared" si="31"/>
+        <v>2.5246776854405608</v>
+      </c>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="16">
+        <f>[17]Model!$V$31</f>
+        <v>8.5000577034045177E-2</v>
+      </c>
+      <c r="AB20" s="16">
+        <f>[17]Model!$V$32</f>
+        <v>0.1980854180117492</v>
+      </c>
+      <c r="AC20" s="16">
+        <f>[17]Model!$V$35</f>
+        <v>0.11177712563806108</v>
+      </c>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="18"/>
     </row>
     <row r="21" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B21" s="12" t="s">
-        <v>55</v>
+      <c r="B21" s="19" t="s">
+        <v>70</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D21" s="13">
-        <f>[12]Main!$D$3</f>
-        <v>7.21</v>
+        <f>[18]Main!$D$3</f>
+        <v>78.45</v>
       </c>
       <c r="E21" s="14">
-        <f>[12]Main!$D$5</f>
-        <v>59.843000000000004</v>
+        <f>[18]Main!$D$5</f>
+        <v>13979.789999999999</v>
       </c>
       <c r="F21" s="14">
-        <f>[12]Main!$D$8</f>
-        <v>-1.3</v>
+        <f>[18]Main!$D$8</f>
+        <v>-2300</v>
       </c>
       <c r="G21" s="14">
-        <f>[12]Main!$D$9</f>
-        <v>61.143000000000001</v>
+        <f>[18]Main!$D$9</f>
+        <v>16279.789999999999</v>
+      </c>
+      <c r="H21" s="14">
+        <f>[18]Model!P$22</f>
+        <v>815</v>
+      </c>
+      <c r="I21" s="14">
+        <f>[18]Model!Q$22</f>
+        <v>309</v>
+      </c>
+      <c r="J21" s="14">
+        <f>[18]Model!R$22</f>
+        <v>746</v>
+      </c>
+      <c r="K21" s="14">
+        <f>[18]Model!S$22</f>
+        <v>861</v>
       </c>
       <c r="L21" s="14">
-        <f>[12]Model!$P$20</f>
-        <v>-1.4</v>
+        <f>[18]Model!T$22</f>
+        <v>921</v>
       </c>
       <c r="M21" s="14">
-        <f>[12]Model!Q$20</f>
-        <v>-6.3999999999999995</v>
+        <f>[18]Model!U$22</f>
+        <v>824</v>
       </c>
       <c r="N21" s="14">
-        <f>[12]Model!R$20</f>
-        <v>-7.4699999999999989</v>
+        <f>[18]Model!V$22</f>
+        <v>1009.4089999999989</v>
       </c>
       <c r="O21" s="14">
-        <f>[12]Model!S$20</f>
-        <v>-9.5558799999999984</v>
+        <f>[18]Model!W$22</f>
+        <v>1260.3274750399985</v>
       </c>
       <c r="P21" s="14">
-        <f>[12]Model!T$20</f>
-        <v>-10.959568000000001</v>
+        <f>[18]Model!X$22</f>
+        <v>1438.1055164480015</v>
       </c>
       <c r="Q21" s="14">
-        <f>[12]Model!U$20</f>
-        <v>-11.357623199999999</v>
+        <f>[18]Model!Y$22</f>
+        <v>1494.4098756374406</v>
+      </c>
+      <c r="R21" s="15">
+        <f>$G21/M21</f>
+        <v>19.757026699029126</v>
+      </c>
+      <c r="S21" s="15">
+        <f>$G21/N21</f>
+        <v>16.128041259786684</v>
+      </c>
+      <c r="T21" s="15">
+        <f>$G21/O21</f>
+        <v>12.91711108613524</v>
+      </c>
+      <c r="U21" s="15">
+        <f>$G21/P21</f>
+        <v>11.320302866377773</v>
+      </c>
+      <c r="V21" s="15">
+        <f>$G21/Q21</f>
+        <v>10.893791767172212</v>
       </c>
       <c r="W21" s="15">
-        <f>G21/[12]Model!$AB$20</f>
-        <v>1.6899351470068711</v>
-      </c>
-      <c r="X21" s="14">
-        <f>[12]Model!$Q$3</f>
-        <v>5.5</v>
-      </c>
-      <c r="Y21" s="20">
-        <f>G21/X21</f>
-        <v>11.116909090909092</v>
-      </c>
-      <c r="AB21" s="16">
-        <f>[12]Model!$Q$26</f>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="AC21" s="16">
-        <f>[12]Model!$Q$30</f>
-        <v>-1.0363636363636362</v>
+        <f>G21/[18]Model!$AF$22</f>
+        <v>9.2229628905226502</v>
+      </c>
+      <c r="X21" s="23">
+        <f>[18]Model!$U$6</f>
+        <v>13702</v>
+      </c>
+      <c r="Y21" s="26">
+        <f t="shared" si="31"/>
+        <v>1.1881323894321996</v>
+      </c>
+      <c r="Z21" s="25">
+        <f>[18]Model!T$29</f>
+        <v>6.3252777993628051E-2</v>
+      </c>
+      <c r="AA21" s="25">
+        <f>[18]Model!U$29</f>
+        <v>1.3885843747716287E-3</v>
+      </c>
+      <c r="AB21" s="25">
+        <f>[18]Model!$U$32</f>
+        <v>0.18260108013428697</v>
+      </c>
+      <c r="AC21" s="25">
+        <f>[18]Model!$U$35</f>
+        <v>6.23996496861772E-2</v>
       </c>
       <c r="AD21" s="16">
-        <f>[12]Model!$AF$27</f>
-        <v>0.13</v>
+        <f>[18]Model!$AJ$29</f>
+        <v>0.09</v>
       </c>
       <c r="AE21" s="16">
-        <f>[12]Model!$AF$33</f>
-        <v>-0.23973616282793675</v>
+        <f>[18]Model!$AJ$35</f>
+        <v>3.5247218209492504E-2</v>
       </c>
       <c r="AF21" s="11" t="str">
-        <f>[12]Model!$AF$34</f>
+        <f>[18]Model!$AJ$36</f>
+        <v>Fairly valued</v>
+      </c>
+      <c r="AH21" s="11">
+        <v>1923</v>
+      </c>
+      <c r="AJ21" s="18">
+        <f>[18]Main!$E$3</f>
+        <v>45867</v>
+      </c>
+      <c r="AK21" s="18">
+        <f>[18]Main!$G$3</f>
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B22" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="13">
+        <f>[19]Main!$D$3</f>
+        <v>57.19</v>
+      </c>
+      <c r="E22" s="14">
+        <f>[19]Main!$D$5</f>
+        <v>10494.365</v>
+      </c>
+      <c r="F22" s="14">
+        <f>[19]Main!$D$8</f>
+        <v>-600.00000000000023</v>
+      </c>
+      <c r="G22" s="14">
+        <f>[19]Main!$D$9</f>
+        <v>11094.365</v>
+      </c>
+      <c r="H22" s="14">
+        <f>[19]Model!P$22</f>
+        <v>-322.3</v>
+      </c>
+      <c r="I22" s="14">
+        <f>[19]Model!Q$22</f>
+        <v>-731.9000000000002</v>
+      </c>
+      <c r="J22" s="14">
+        <f>[19]Model!R$22</f>
+        <v>-44.700000000000145</v>
+      </c>
+      <c r="K22" s="14">
+        <f>[19]Model!S$22</f>
+        <v>-185.59999999999982</v>
+      </c>
+      <c r="L22" s="14">
+        <f>[19]Model!T$22</f>
+        <v>163.90000000000035</v>
+      </c>
+      <c r="M22" s="14">
+        <f>[19]Model!U$22</f>
+        <v>228.2000000000003</v>
+      </c>
+      <c r="N22" s="14">
+        <f>[19]Model!V$22</f>
+        <v>743.65658000000008</v>
+      </c>
+      <c r="O22" s="14">
+        <f>[19]Model!W$22</f>
+        <v>719.25833086000011</v>
+      </c>
+      <c r="P22" s="14">
+        <f>[19]Model!X$22</f>
+        <v>830.80143681460015</v>
+      </c>
+      <c r="Q22" s="14">
+        <f>[19]Model!Y$22</f>
+        <v>906.37830312002222</v>
+      </c>
+      <c r="R22" s="15">
+        <f t="shared" ref="R22:V22" si="38">$G22/M22</f>
+        <v>48.616849255039376</v>
+      </c>
+      <c r="S22" s="15">
+        <f t="shared" si="38"/>
+        <v>14.918667162200055</v>
+      </c>
+      <c r="T22" s="15">
+        <f t="shared" si="38"/>
+        <v>15.424729230087236</v>
+      </c>
+      <c r="U22" s="15">
+        <f t="shared" si="38"/>
+        <v>13.353810559761699</v>
+      </c>
+      <c r="V22" s="15">
+        <f t="shared" si="38"/>
+        <v>12.240324996538327</v>
+      </c>
+      <c r="W22" s="15">
+        <f>G22/[19]Model!$AF$22</f>
+        <v>10.264552570282582</v>
+      </c>
+      <c r="X22" s="23">
+        <f>[19]Model!$V$3</f>
+        <v>7743.8040000000001</v>
+      </c>
+      <c r="Y22" s="26">
+        <f t="shared" si="31"/>
+        <v>1.4326763693915807</v>
+      </c>
+      <c r="Z22" s="25">
+        <f>[19]Model!T$26</f>
+        <v>0.16041143561957627</v>
+      </c>
+      <c r="AA22" s="25">
+        <f>[19]Model!U$26</f>
+        <v>0.21376103255195988</v>
+      </c>
+      <c r="AB22" s="25">
+        <f>[19]Model!$U$27</f>
+        <v>0.18032120349664568</v>
+      </c>
+      <c r="AC22" s="25">
+        <f>[19]Model!$U$31</f>
+        <v>8.4945345364129704E-2</v>
+      </c>
+      <c r="AD22" s="16">
+        <f>[19]Model!$AI$28</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AE22" s="16">
+        <f>[19]Model!$AI$34</f>
+        <v>-0.43120780386203839</v>
+      </c>
+      <c r="AF22" s="11" t="str">
+        <f>[19]Model!$AI$35</f>
         <v>Overvalued</v>
       </c>
-      <c r="AG21" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH21" s="11">
-        <v>2019</v>
-      </c>
-      <c r="AJ21" s="18">
-        <f>[12]Main!$E$3</f>
-        <v>45736</v>
-      </c>
-      <c r="AK21" s="18">
-        <f>[12]Main!$G$3</f>
-        <v>45743</v>
+      <c r="AH22" s="11">
+        <v>1969</v>
+      </c>
+      <c r="AJ22" s="18">
+        <f>[19]Main!$E$3</f>
+        <v>45903</v>
+      </c>
+      <c r="AK22" s="18">
+        <f>[19]Main!$G$3</f>
+        <v>45965</v>
       </c>
     </row>
     <row r="23" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="B23" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="17">
+        <f>[20]Main!$D$3</f>
+        <v>101.2</v>
+      </c>
+      <c r="E23" s="14">
+        <f>[20]Main!$D$5</f>
+        <v>11739.2</v>
+      </c>
+      <c r="F23" s="14">
+        <f>[20]Main!$D$8</f>
+        <v>-498</v>
+      </c>
+      <c r="G23" s="14">
+        <f>[20]Main!$D$9</f>
+        <v>12237.2</v>
+      </c>
+      <c r="H23" s="14">
+        <f>[20]Model!P$43</f>
+        <v>5.9000000000001167</v>
+      </c>
+      <c r="I23" s="14">
+        <f>[20]Model!Q$43</f>
+        <v>-65.199999999999903</v>
+      </c>
+      <c r="J23" s="14">
+        <f>[20]Model!R$43</f>
+        <v>63</v>
+      </c>
+      <c r="K23" s="14">
+        <f>[20]Model!S$43</f>
+        <v>79</v>
+      </c>
+      <c r="L23" s="14">
+        <f>[20]Model!T$43</f>
+        <v>58</v>
+      </c>
+      <c r="M23" s="14">
+        <f>[20]Model!U$43</f>
+        <v>106</v>
+      </c>
+      <c r="N23" s="14">
+        <f>[20]Model!V$43</f>
+        <v>105.74143999999995</v>
+      </c>
+      <c r="O23" s="14">
+        <f>[20]Model!W$43</f>
+        <v>144.35987200000005</v>
+      </c>
+      <c r="P23" s="14">
+        <f>[20]Model!X$43</f>
+        <v>169.88582975999995</v>
+      </c>
+      <c r="Q23" s="14">
+        <f>[20]Model!Y$43</f>
+        <v>189.70135618560002</v>
+      </c>
+      <c r="R23" s="15">
+        <f t="shared" ref="R23" si="39">$G23/M23</f>
+        <v>115.44528301886793</v>
+      </c>
+      <c r="S23" s="15">
+        <f t="shared" si="33"/>
+        <v>115.72757095042404</v>
+      </c>
+      <c r="T23" s="15">
+        <f t="shared" si="34"/>
+        <v>84.768709132687491</v>
+      </c>
+      <c r="U23" s="15">
+        <f t="shared" si="35"/>
+        <v>72.031905293617854</v>
+      </c>
+      <c r="V23" s="15">
+        <f t="shared" si="36"/>
+        <v>64.50770962347454</v>
+      </c>
+      <c r="W23" s="15">
+        <f>G23/[20]Model!$AF$43</f>
+        <v>35.255116146867159</v>
+      </c>
+      <c r="X23" s="14">
+        <f>[20]Model!$V$26</f>
+        <v>2587.8199999999997</v>
+      </c>
+      <c r="Y23" s="20">
+        <f t="shared" si="31"/>
+        <v>4.7287678432039328</v>
+      </c>
+      <c r="Z23" s="16">
+        <f>[20]Model!U$47</f>
+        <v>0.21277747698971305</v>
+      </c>
+      <c r="AA23" s="16">
+        <f>[20]Model!V$47</f>
+        <v>0.1552767857142856</v>
+      </c>
+      <c r="AB23" s="16">
+        <f>[20]Model!$V$48</f>
+        <v>0.22716788648360398</v>
+      </c>
+      <c r="AC23" s="16">
+        <f>[20]Model!$V$52</f>
+        <v>9.599848521149075E-2</v>
+      </c>
+      <c r="AD23" s="16">
+        <f>[20]Model!$AI$49</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE23" s="16">
+        <f>[20]Model!$AI$55</f>
+        <v>-0.80686738144951742</v>
+      </c>
+      <c r="AF23" s="11" t="str">
+        <f>[20]Model!$AI$56</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH23" s="11">
+        <v>1892</v>
+      </c>
+      <c r="AJ23" s="18">
+        <f>[20]Main!$E$3</f>
+        <v>45924</v>
+      </c>
+      <c r="AK23" s="18">
+        <f>[20]Main!$G$3</f>
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="24" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B24" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="13">
+        <f>[21]Main!$D$3</f>
+        <v>64.39</v>
+      </c>
+      <c r="E24" s="14">
+        <f>[21]Main!$D$5</f>
+        <v>10869.032000000001</v>
+      </c>
+      <c r="F24" s="14">
+        <f>[21]Main!$D$8</f>
+        <v>613.79999999999995</v>
+      </c>
+      <c r="G24" s="14">
+        <f>[21]Main!$D$9</f>
+        <v>10255.232000000002</v>
+      </c>
+      <c r="H24" s="14">
+        <f>[21]Model!P$20</f>
+        <v>10.89999999999997</v>
+      </c>
+      <c r="I24" s="14">
+        <f>[21]Model!Q$20</f>
+        <v>80.300000000000068</v>
+      </c>
+      <c r="J24" s="14">
+        <f>[21]Model!R$20</f>
+        <v>0.50000000000003597</v>
+      </c>
+      <c r="K24" s="14">
+        <f>[21]Model!S$20</f>
+        <v>-33.20000000000001</v>
+      </c>
+      <c r="L24" s="14">
+        <f>[21]Model!T$20</f>
+        <v>2.3999999999998813</v>
+      </c>
+      <c r="M24" s="14">
+        <f>[21]Model!U$20</f>
+        <v>16.299999999999944</v>
+      </c>
+      <c r="N24" s="14">
+        <f>[21]Model!V$20</f>
+        <v>16.054319999999748</v>
+      </c>
+      <c r="O24" s="14">
+        <f>[21]Model!W$20</f>
+        <v>39.422006400000022</v>
+      </c>
+      <c r="P24" s="14">
+        <f>[21]Model!X$20</f>
+        <v>60.409628094400034</v>
+      </c>
+      <c r="Q24" s="14">
+        <f>[21]Model!Y$20</f>
+        <v>72.553818362864064</v>
+      </c>
+      <c r="R24" s="15">
+        <f t="shared" ref="R24" si="40">$G24/M24</f>
+        <v>629.15533742331513</v>
+      </c>
+      <c r="S24" s="15">
+        <f t="shared" si="33"/>
+        <v>638.7833305926481</v>
+      </c>
+      <c r="T24" s="15">
+        <f t="shared" si="34"/>
+        <v>260.13977817222406</v>
+      </c>
+      <c r="U24" s="15">
+        <f t="shared" si="35"/>
+        <v>169.76154834084571</v>
+      </c>
+      <c r="V24" s="15">
+        <f t="shared" si="36"/>
+        <v>141.34655117268147</v>
+      </c>
+      <c r="W24" s="15">
+        <f>G24/[21]Model!$AF$20</f>
+        <v>99.471473171775258</v>
+      </c>
+      <c r="X24" s="14">
+        <f>[21]Model!$V$5</f>
+        <v>1277.0619999999999</v>
+      </c>
+      <c r="Y24" s="20">
+        <f t="shared" si="31"/>
+        <v>8.0303321216980876</v>
+      </c>
+      <c r="Z24" s="16">
+        <f>[21]Model!U$26</f>
+        <v>9.5651335454633113E-2</v>
+      </c>
+      <c r="AA24" s="16">
+        <f>[21]Model!V$26</f>
+        <v>0.12387749713983975</v>
+      </c>
+      <c r="AB24" s="16">
+        <f>[21]Model!$V$29</f>
+        <v>0.23117585520515044</v>
+      </c>
+      <c r="AC24" s="16">
+        <f>[21]Model!$V$32</f>
+        <v>1.8102410063097749E-2</v>
+      </c>
+      <c r="AD24" s="16">
+        <f>[21]Model!$AI$27</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE24" s="16">
+        <f>[21]Model!$AI$33</f>
+        <v>-0.86431327380599154</v>
+      </c>
+      <c r="AF24" s="11" t="str">
+        <f>[21]Model!$AI$34</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH24" s="11">
+        <v>1994</v>
+      </c>
+      <c r="AJ24" s="18">
+        <f>[21]Main!$E$3</f>
+        <v>45904</v>
+      </c>
+      <c r="AK24" s="18">
+        <f>[21]Main!$G$3</f>
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+    </row>
+    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="17">
+        <f>[22]Main!$D$3</f>
+        <v>66.63</v>
+      </c>
+      <c r="E26" s="14">
+        <f>[22]Main!$D$5</f>
+        <v>6663</v>
+      </c>
+      <c r="F26" s="14">
+        <f>[22]Main!$D$8</f>
+        <v>-438.4</v>
+      </c>
+      <c r="G26" s="14">
+        <f>[22]Main!$D$9</f>
+        <v>7101.4</v>
+      </c>
+      <c r="K26" s="14">
+        <f>[22]Model!S$39</f>
+        <v>16.199999999999942</v>
+      </c>
+      <c r="L26" s="14">
+        <f>[22]Model!T$39</f>
+        <v>32.30000000000004</v>
+      </c>
+      <c r="M26" s="14">
+        <f>[22]Model!U$39</f>
+        <v>53.500000000000057</v>
+      </c>
+      <c r="N26" s="14">
+        <f>[22]Model!V$39</f>
+        <v>96.823239999999927</v>
+      </c>
+      <c r="O26" s="14">
+        <f>[22]Model!W$39</f>
+        <v>143.50169249999999</v>
+      </c>
+      <c r="P26" s="14">
+        <f>[22]Model!X$39</f>
+        <v>179.7296860125</v>
+      </c>
+      <c r="Q26" s="14">
+        <f>[22]Model!Y$39</f>
+        <v>200.07653520599999</v>
+      </c>
+      <c r="R26" s="15">
+        <f t="shared" ref="R26" si="41">$G26/M26</f>
+        <v>132.73644859813069</v>
+      </c>
+      <c r="S26" s="15">
+        <f t="shared" ref="S26" si="42">$G26/N26</f>
+        <v>73.343961635656939</v>
+      </c>
+      <c r="T26" s="15">
+        <f t="shared" ref="T26:T27" si="43">$G26/O26</f>
+        <v>49.486524348833029</v>
+      </c>
+      <c r="U26" s="15">
+        <f t="shared" ref="U26:U27" si="44">$G26/P26</f>
+        <v>39.51155848292143</v>
+      </c>
+      <c r="V26" s="15">
+        <f t="shared" ref="V26:V27" si="45">$G26/Q26</f>
+        <v>35.493417519892354</v>
+      </c>
+      <c r="W26" s="15">
+        <f>G26/[22]Model!$AF$39</f>
+        <v>22.535987037880979</v>
+      </c>
+      <c r="X26" s="14">
+        <f>[22]Model!$V$24</f>
+        <v>1358.33</v>
+      </c>
+      <c r="Y26" s="20">
+        <f>G26/X26</f>
+        <v>5.2280373694168576</v>
+      </c>
+      <c r="Z26" s="16">
+        <f>[22]Model!U$43</f>
+        <v>0.23230686115613186</v>
+      </c>
+      <c r="AA26" s="16">
+        <f>[22]Model!V$43</f>
+        <v>0.19099517755370443</v>
+      </c>
+      <c r="AB26" s="16">
+        <f>[22]Model!$V$44</f>
+        <v>0.25505171791832615</v>
+      </c>
+      <c r="AC26" s="16">
+        <f>[22]Model!$V$47</f>
+        <v>0.1261351806998299</v>
+      </c>
+      <c r="AD26" s="16">
+        <f>[22]Model!$AI$45</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE26" s="16">
+        <f>[22]Model!$AI$51</f>
+        <v>-0.67267594474014047</v>
+      </c>
+      <c r="AF26" s="11" t="str">
+        <f>[22]Model!$AI$52</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH26" s="11">
+        <v>1873</v>
+      </c>
+      <c r="AJ26" s="18">
+        <f>[22]Main!$E$3</f>
+        <v>45903</v>
+      </c>
+      <c r="AK26" s="18">
+        <f>[22]Main!$G$3</f>
+        <v>45974</v>
+      </c>
+    </row>
+    <row r="27" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="13">
+        <f>[23]Main!$D$3</f>
+        <v>10</v>
+      </c>
+      <c r="E27" s="14">
+        <f>[23]Main!$D$5</f>
+        <v>1178</v>
+      </c>
+      <c r="F27" s="14">
+        <f>[23]Main!$D$8</f>
+        <v>46.100000000000009</v>
+      </c>
+      <c r="G27" s="14">
+        <f>[23]Main!$D$9</f>
+        <v>1131.9000000000001</v>
+      </c>
+      <c r="N27" s="14">
+        <f>[23]Model!O$15</f>
+        <v>-69.325000000000003</v>
+      </c>
+      <c r="O27" s="14">
+        <f>[23]Model!P$15</f>
+        <v>-91.1815</v>
+      </c>
+      <c r="P27" s="14">
+        <f>[23]Model!Q$15</f>
+        <v>-110.42588000000001</v>
+      </c>
+      <c r="Q27" s="14">
+        <f>[23]Model!R$15</f>
+        <v>-123.67537759999999</v>
+      </c>
+      <c r="S27" s="15">
+        <f t="shared" ref="S27" si="46">$G27/N27</f>
+        <v>-16.327443202307972</v>
+      </c>
+      <c r="T27" s="15">
+        <f t="shared" si="43"/>
+        <v>-12.413702340935387</v>
+      </c>
+      <c r="U27" s="15">
+        <f t="shared" si="44"/>
+        <v>-10.2503145096059</v>
+      </c>
+      <c r="V27" s="15">
+        <f t="shared" si="45"/>
+        <v>-9.1521855195855917</v>
+      </c>
+      <c r="W27" s="15">
+        <f>G27/[23]Model!$Y$15</f>
+        <v>7.7512385840070213</v>
+      </c>
+      <c r="X27" s="14">
+        <f>[23]Model!$O$3</f>
+        <v>12.3</v>
+      </c>
+      <c r="Y27" s="20">
+        <f>G27/X27</f>
+        <v>92.024390243902445</v>
+      </c>
+      <c r="AB27" s="16">
+        <f>[23]Model!$O$20</f>
+        <v>5.08130081300813E-2</v>
+      </c>
+      <c r="AC27" s="16">
+        <f>[23]Model!$O$24</f>
+        <v>-4.23780487804878</v>
+      </c>
+      <c r="AD27" s="16">
+        <f>[23]Model!$AB$21</f>
+        <v>0.11</v>
+      </c>
+      <c r="AE27" s="16">
+        <f>[23]Model!$AB$27</f>
+        <v>-0.85432485058235097</v>
+      </c>
+      <c r="AF27" s="11" t="str">
+        <f>[23]Model!$AB$28</f>
+        <v>Heavily overvalued</v>
+      </c>
+    </row>
+    <row r="28" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B28" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="13">
+        <f>[24]Main!$D$3</f>
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="E28" s="14">
+        <f>[24]Main!$D$5</f>
+        <v>274.81599999999997</v>
+      </c>
+      <c r="F28" s="14">
+        <f>[24]Main!$D$8</f>
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
+        <f>[24]Main!$D$9</f>
+        <v>269.81599999999997</v>
+      </c>
+      <c r="L28" s="14">
+        <f>[24]Model!$P$20</f>
+        <v>-1.4</v>
+      </c>
+      <c r="M28" s="14">
+        <f>[24]Model!Q$20</f>
+        <v>-32</v>
+      </c>
+      <c r="N28" s="14">
+        <f>[24]Model!R$20</f>
+        <v>-27.428000000000001</v>
+      </c>
+      <c r="O28" s="14">
+        <f>[24]Model!S$20</f>
+        <v>-36.489999999999995</v>
+      </c>
+      <c r="P28" s="14">
+        <f>[24]Model!T$20</f>
+        <v>-44.738199999999992</v>
+      </c>
+      <c r="Q28" s="14">
+        <f>[24]Model!U$20</f>
+        <v>-36.238919999999993</v>
+      </c>
+      <c r="W28" s="15">
+        <f>G28/[24]Model!$AB$20</f>
+        <v>3.9629103845325151</v>
+      </c>
+      <c r="X28" s="23">
+        <f>[24]Model!$Q$3</f>
+        <v>5.6</v>
+      </c>
+      <c r="Y28" s="20">
+        <f>G28/X28</f>
+        <v>48.181428571428569</v>
+      </c>
+      <c r="AB28" s="25">
+        <f>[24]Model!$Q$26</f>
+        <v>0.28571428571428564</v>
+      </c>
+      <c r="AC28" s="25">
+        <f>[24]Model!$Q$30</f>
+        <v>-3.0535714285714288</v>
+      </c>
+      <c r="AD28" s="16">
+        <f>[24]Model!$AF$27</f>
+        <v>0.12</v>
+      </c>
+      <c r="AE28" s="16">
+        <f>[24]Model!$AF$33</f>
+        <v>-0.78010157110479306</v>
+      </c>
+      <c r="AF28" s="11" t="str">
+        <f>[24]Model!$AF$34</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH28" s="11">
+        <v>2019</v>
+      </c>
+      <c r="AJ28" s="18">
+        <f>[24]Main!$E$3</f>
+        <v>45903</v>
+      </c>
+      <c r="AK28" s="18">
+        <f>[24]Main!$G$3</f>
+        <v>45974</v>
+      </c>
+    </row>
+    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="20"/>
+      <c r="AB29" s="16"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18"/>
+    </row>
+    <row r="30" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="20"/>
+      <c r="AB30" s="16"/>
+      <c r="AC30" s="16"/>
+      <c r="AD30" s="16"/>
+      <c r="AE30" s="16"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{9EBE5D6A-1C1D-4975-961D-8BDF60D469F0}"/>
-    <hyperlink ref="B13" r:id="rId2" xr:uid="{1C2D10B8-C1F0-4011-9894-9CA25208770D}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{959B55A2-9FD4-4C66-8ED7-2CA35BBDDBEB}"/>
-    <hyperlink ref="B21" r:id="rId4" xr:uid="{585D8E65-116D-4674-B4B3-00498D6A7848}"/>
+    <hyperlink ref="B12" r:id="rId2" xr:uid="{1C2D10B8-C1F0-4011-9894-9CA25208770D}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{959B55A2-9FD4-4C66-8ED7-2CA35BBDDBEB}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{585D8E65-116D-4674-B4B3-00498D6A7848}"/>
     <hyperlink ref="B18" r:id="rId5" xr:uid="{CFD2CC9C-5B8B-4286-BE47-40E920DADED7}"/>
     <hyperlink ref="B5" r:id="rId6" xr:uid="{A17201AA-5063-4DAA-B4C5-DF50CA314C77}"/>
     <hyperlink ref="B6" r:id="rId7" xr:uid="{66D11DBA-CC4F-47C4-B72D-A167C22CF998}"/>
     <hyperlink ref="B11" r:id="rId8" xr:uid="{68839818-3059-4F3D-A939-24E347A3D924}"/>
     <hyperlink ref="B10" r:id="rId9" xr:uid="{2C804FE1-0AB3-4453-B597-E9A1557EBD6D}"/>
-    <hyperlink ref="B14" r:id="rId10" xr:uid="{60BDF6DB-8BEB-4FB3-8DBA-58358D39164E}"/>
-    <hyperlink ref="B8" r:id="rId11" xr:uid="{2E581798-4486-4631-A533-55B5B7275DFA}"/>
+    <hyperlink ref="B15" r:id="rId10" xr:uid="{60BDF6DB-8BEB-4FB3-8DBA-58358D39164E}"/>
+    <hyperlink ref="B7" r:id="rId11" xr:uid="{2E581798-4486-4631-A533-55B5B7275DFA}"/>
+    <hyperlink ref="B9" r:id="rId12" xr:uid="{A83CC09C-04CF-4224-A8E1-DC20AD3A36C8}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{4D3F764E-9CCB-403D-8E1B-4BE47BABAA33}"/>
+    <hyperlink ref="B13" r:id="rId14" xr:uid="{93CF4EC5-904A-41E3-804E-56C12BA230AB}"/>
+    <hyperlink ref="B21" r:id="rId15" display="txt" xr:uid="{AB07EC75-74EE-4F00-A39A-32F20CF1BEB8}"/>
+    <hyperlink ref="B16" r:id="rId16" xr:uid="{9426D752-2EF5-4AFB-99DA-A8A7D85B06E3}"/>
+    <hyperlink ref="B17" r:id="rId17" xr:uid="{EB265B06-930A-4273-8DCC-B8FC215B734E}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{CC2544BA-50C9-47A6-B396-2DAF4864B854}"/>
+    <hyperlink ref="B26" r:id="rId19" xr:uid="{356138DD-BE1A-4731-B7CC-280B73272B33}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{84017ED8-7373-4D92-B4EF-D5CF532C2353}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{88DB7B22-BB4A-404B-95A6-1AA9663BF5FE}"/>
+    <hyperlink ref="B27" r:id="rId22" xr:uid="{C624A8B5-778E-4C36-8210-19EE1248D3F5}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{BAFD510F-4A1A-4765-B090-822E93B04792}"/>
+    <hyperlink ref="B20" r:id="rId24" xr:uid="{A503C2A2-F761-40EE-A283-D47A823C22F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
--- a/Financial Analysis/Models (Defence).xlsx
+++ b/Financial Analysis/Models (Defence).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1A53C0-7D59-4903-A043-48085823E309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E722360A-2C0B-4F1E-8593-26E9EEF83AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>Company</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>BBD.A CA</t>
+  </si>
+  <si>
+    <t>Anduril</t>
+  </si>
+  <si>
+    <t>ADUI US</t>
   </si>
 </sst>
 </file>
@@ -2005,15 +2011,16 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Forecasts"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>64.39</v>
+            <v>90.08</v>
           </cell>
           <cell r="E3">
-            <v>45904</v>
+            <v>45930</v>
           </cell>
           <cell r="G3">
             <v>45960</v>
@@ -2021,7 +2028,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>10869.032000000001</v>
+            <v>15205.504000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -2031,85 +2038,86 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>10255.232000000002</v>
+            <v>14591.704000000002</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="V5">
-            <v>1277.0619999999999</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="P20">
+        <row r="7">
+          <cell r="V7">
+            <v>1297.6099999999999</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="P22">
             <v>10.89999999999997</v>
           </cell>
-          <cell r="Q20">
+          <cell r="Q22">
             <v>80.300000000000068</v>
           </cell>
-          <cell r="R20">
+          <cell r="R22">
             <v>0.50000000000003597</v>
           </cell>
-          <cell r="S20">
+          <cell r="S22">
             <v>-33.20000000000001</v>
           </cell>
-          <cell r="T20">
+          <cell r="T22">
             <v>2.3999999999998813</v>
           </cell>
-          <cell r="U20">
+          <cell r="U22">
             <v>16.299999999999944</v>
           </cell>
-          <cell r="V20">
-            <v>16.054319999999748</v>
-          </cell>
-          <cell r="W20">
-            <v>39.422006400000022</v>
-          </cell>
-          <cell r="X20">
-            <v>60.409628094400034</v>
-          </cell>
-          <cell r="Y20">
-            <v>72.553818362864064</v>
-          </cell>
-          <cell r="AF20">
-            <v>103.09721644808106</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="U26">
+          <cell r="V22">
+            <v>19.969807999999741</v>
+          </cell>
+          <cell r="W22">
+            <v>47.220326400000076</v>
+          </cell>
+          <cell r="X22">
+            <v>70.794515788799941</v>
+          </cell>
+          <cell r="Y22">
+            <v>85.495337030527935</v>
+          </cell>
+          <cell r="AF22">
+            <v>184.91617130028354</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="U28">
             <v>9.5651335454633113E-2</v>
           </cell>
-          <cell r="V26">
-            <v>0.12387749713983975</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="AI27">
+          <cell r="V28">
+            <v>0.14196074980198881</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="AI29">
             <v>0.09</v>
           </cell>
         </row>
-        <row r="29">
-          <cell r="V29">
-            <v>0.23117585520515044</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="V32">
-            <v>1.8102410063097749E-2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="AI33">
-            <v>-0.86431327380599154</v>
+        <row r="31">
+          <cell r="V31">
+            <v>0.23128695062460972</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AI34" t="str">
+          <cell r="V34">
+            <v>2.1587580243678565E-2</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AI35">
+            <v>-0.87042777033592045</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="AI36" t="str">
             <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3159,9 +3167,6 @@
           </cell>
         </row>
         <row r="37">
-          <cell r="Z37">
-            <v>-27</v>
-          </cell>
           <cell r="AA37">
             <v>291</v>
           </cell>
@@ -3185,6 +3190,9 @@
           </cell>
           <cell r="AH37">
             <v>1527.5501896362498</v>
+          </cell>
+          <cell r="AI37">
+            <v>1588.4162624936125</v>
           </cell>
           <cell r="AO37">
             <v>1804.5664601807241</v>
@@ -3526,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
-  <dimension ref="B2:AK30"/>
+  <dimension ref="B2:AK31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -3707,7 +3715,7 @@
       </c>
       <c r="AA3" s="9">
         <f t="shared" si="1"/>
-        <v>0.11541965295193875</v>
+        <v>0.11843352839563026</v>
       </c>
       <c r="AB3" s="9">
         <f t="shared" si="1"/>
@@ -3726,7 +3734,7 @@
         <v>-0.45499566684070913</v>
       </c>
       <c r="AF3" s="10" t="e">
-        <f>INDEX(AF4:AF23,MODE(MATCH(AF4:AF23,AF4:AF23,0)))</f>
+        <f>INDEX(AF4:AF24,MODE(MATCH(AF4:AF24,AF4:AF24,0)))</f>
         <v>#N/A</v>
       </c>
       <c r="AG3" s="2"/>
@@ -4828,60 +4836,60 @@
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="14">
-        <f>[9]Model!Z$37</f>
-        <v>-27</v>
-      </c>
-      <c r="J12" s="14">
         <f>[9]Model!AA$37</f>
         <v>291</v>
       </c>
-      <c r="K12" s="14">
+      <c r="J12" s="14">
         <f>[9]Model!AB$37</f>
         <v>476</v>
       </c>
-      <c r="L12" s="14">
+      <c r="K12" s="14">
         <f>[9]Model!AC$37</f>
         <v>534</v>
       </c>
-      <c r="M12" s="14">
+      <c r="L12" s="14">
         <f>[9]Model!AD$37</f>
         <v>717</v>
       </c>
-      <c r="N12" s="14">
+      <c r="M12" s="14">
         <f>[9]Model!AE$37</f>
         <v>1152.8015680000001</v>
       </c>
-      <c r="O12" s="14">
+      <c r="N12" s="14">
         <f>[9]Model!AF$37</f>
         <v>1264.6224175000007</v>
       </c>
-      <c r="P12" s="14">
+      <c r="O12" s="14">
         <f>[9]Model!AG$37</f>
         <v>1430.3841434999997</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="P12" s="14">
         <f>[9]Model!AH$37</f>
         <v>1527.5501896362498</v>
       </c>
+      <c r="Q12" s="14">
+        <f>[9]Model!AI$37</f>
+        <v>1588.4162624936125</v>
+      </c>
       <c r="R12" s="15">
         <f t="shared" ref="R12:V13" si="24">$G12/M12</f>
-        <v>107.07375174337518</v>
+        <v>66.59591913393372</v>
       </c>
       <c r="S12" s="15">
         <f t="shared" si="24"/>
-        <v>66.59591913393372</v>
+        <v>60.707353386766897</v>
       </c>
       <c r="T12" s="15">
         <f t="shared" si="24"/>
-        <v>60.707353386766897</v>
+        <v>53.672211306920168</v>
       </c>
       <c r="U12" s="15">
         <f t="shared" si="24"/>
-        <v>53.672211306920168</v>
+        <v>50.258171889122295</v>
       </c>
       <c r="V12" s="15">
         <f t="shared" si="24"/>
-        <v>50.258171889122295</v>
+        <v>48.332343235694317</v>
       </c>
       <c r="W12" s="15">
         <f>G12/[9]Model!$AO$37</f>
@@ -5263,7 +5271,7 @@
         <v>42.268882822902796</v>
       </c>
       <c r="S15" s="15">
-        <f t="shared" ref="S15:V17" si="26">$G15/N15</f>
+        <f t="shared" ref="S15:V18" si="26">$G15/N15</f>
         <v>28.283914738602331</v>
       </c>
       <c r="T15" s="15">
@@ -5287,7 +5295,7 @@
         <v>21325</v>
       </c>
       <c r="Y15" s="26">
-        <f t="shared" ref="Y15:Y17" si="27">G15/X15</f>
+        <f t="shared" ref="Y15:Y18" si="27">G15/X15</f>
         <v>2.9771564830011723</v>
       </c>
       <c r="Z15" s="25">
@@ -5467,1365 +5475,1386 @@
     </row>
     <row r="17" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B17" s="19" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="17">
-        <f>[14]Main!$D$3</f>
-        <v>27.18</v>
-      </c>
-      <c r="E17" s="14">
-        <f>[14]Main!$D$5</f>
-        <v>35695.493999999999</v>
-      </c>
-      <c r="F17" s="14">
-        <f>[14]Main!$D$8</f>
-        <v>1459</v>
-      </c>
-      <c r="G17" s="14">
-        <f>[14]Main!$D$9</f>
-        <v>34236.493999999999</v>
-      </c>
-      <c r="H17" s="14">
-        <f>[14]Model!Q$23</f>
-        <v>615.30000000000064</v>
-      </c>
-      <c r="I17" s="14">
-        <f>[14]Model!R$23</f>
-        <v>491.20000000000067</v>
-      </c>
-      <c r="J17" s="14">
-        <f>[14]Model!S$23</f>
-        <v>773.79999999999905</v>
-      </c>
-      <c r="K17" s="14">
-        <f>[14]Model!T$23</f>
-        <v>931.79999999999984</v>
-      </c>
-      <c r="L17" s="14">
-        <f>[14]Model!U$23</f>
-        <v>1050.8999999999996</v>
-      </c>
-      <c r="M17" s="14">
-        <f>[14]Model!V$23</f>
-        <v>1200.3000000000002</v>
-      </c>
-      <c r="N17" s="14">
-        <f>[14]Model!W$23</f>
-        <v>1113.4564026999999</v>
-      </c>
-      <c r="O17" s="14">
-        <f>[14]Model!X$23</f>
-        <v>1422.1613657599992</v>
-      </c>
-      <c r="P17" s="14">
-        <f>[14]Model!Y$23</f>
-        <v>1443.7923014975993</v>
-      </c>
-      <c r="Q17" s="14">
-        <f>[14]Model!Z$23</f>
-        <v>1456.7690142637746</v>
-      </c>
-      <c r="R17" s="15">
-        <f t="shared" ref="R17" si="29">$G17/M17</f>
-        <v>28.523280846455048</v>
-      </c>
-      <c r="S17" s="15">
-        <f t="shared" si="26"/>
-        <v>30.747942997121896</v>
-      </c>
-      <c r="T17" s="15">
-        <f t="shared" si="26"/>
-        <v>24.073564944371913</v>
-      </c>
-      <c r="U17" s="15">
-        <f t="shared" si="26"/>
-        <v>23.712894136149352</v>
-      </c>
-      <c r="V17" s="15">
-        <f t="shared" si="26"/>
-        <v>23.501662696541167</v>
-      </c>
-      <c r="W17" s="15">
-        <f>G17/[14]Model!$AG$23</f>
-        <v>19.802862236524049</v>
-      </c>
-      <c r="X17" s="23">
-        <f>[14]Model!$V$7</f>
-        <v>6213.6</v>
-      </c>
-      <c r="Y17" s="26">
-        <f t="shared" si="27"/>
-        <v>5.5099288657139169</v>
-      </c>
-      <c r="Z17" s="25">
-        <f>[14]Model!U$30</f>
-        <v>5.0500414805923599E-2</v>
-      </c>
-      <c r="AA17" s="25">
-        <f>[14]Model!V$30</f>
-        <v>4.4056860570622192E-2</v>
-      </c>
-      <c r="AB17" s="25">
-        <f>[14]Model!$V$33</f>
-        <v>0.83643942320072096</v>
-      </c>
-      <c r="AC17" s="25">
-        <f>[14]Model!$V$37</f>
-        <v>0.2188264452169435</v>
-      </c>
-      <c r="AD17" s="16">
-        <f>[14]Model!$AJ$29</f>
-        <v>0.08</v>
-      </c>
-      <c r="AE17" s="16">
-        <f>[14]Model!$AJ$35</f>
-        <v>-0.43497641969139733</v>
-      </c>
-      <c r="AF17" s="11" t="str">
-        <f>[14]Model!$AJ$36</f>
-        <v>Overvalued</v>
-      </c>
-      <c r="AH17" s="11">
-        <v>1971</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D17" s="13">
+        <v>75.61</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
       <c r="AJ17" s="18">
-        <f>[14]Main!$E$3</f>
-        <v>45868</v>
-      </c>
-      <c r="AK17" s="18">
-        <f>[14]Main!$G$3</f>
-        <v>46079</v>
-      </c>
+        <v>45930</v>
+      </c>
+      <c r="AK17" s="18"/>
     </row>
     <row r="18" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B18" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D18" s="17">
-        <f>[15]Main!$D$3</f>
-        <v>47.27</v>
+        <f>[14]Main!$D$3</f>
+        <v>27.18</v>
       </c>
       <c r="E18" s="14">
-        <f>[15]Main!$D$5</f>
-        <v>27246.428</v>
+        <f>[14]Main!$D$5</f>
+        <v>35695.493999999999</v>
       </c>
       <c r="F18" s="14">
-        <f>[15]Main!$D$8</f>
-        <v>-267</v>
+        <f>[14]Main!$D$8</f>
+        <v>1459</v>
       </c>
       <c r="G18" s="14">
-        <f>[15]Main!$D$9</f>
-        <v>27513.428</v>
+        <f>[14]Main!$D$9</f>
+        <v>34236.493999999999</v>
       </c>
       <c r="H18" s="14">
-        <f>[15]Model!T$19</f>
-        <v>823</v>
+        <f>[14]Model!Q$23</f>
+        <v>615.30000000000064</v>
       </c>
       <c r="I18" s="14">
-        <f>[15]Model!U$19</f>
-        <v>239</v>
+        <f>[14]Model!R$23</f>
+        <v>491.20000000000067</v>
       </c>
       <c r="J18" s="14">
-        <f>[15]Model!V$19</f>
-        <v>586</v>
+        <f>[14]Model!S$23</f>
+        <v>773.79999999999905</v>
       </c>
       <c r="K18" s="14">
-        <f>[15]Model!W$19</f>
-        <v>927</v>
+        <f>[14]Model!T$23</f>
+        <v>931.79999999999984</v>
       </c>
       <c r="L18" s="14">
-        <f>[15]Model!X$19</f>
-        <v>658</v>
+        <f>[14]Model!U$23</f>
+        <v>1050.8999999999996</v>
       </c>
       <c r="M18" s="14">
-        <f>[15]Model!Y$19</f>
-        <v>1072</v>
+        <f>[14]Model!V$23</f>
+        <v>1200.3000000000002</v>
       </c>
       <c r="N18" s="14">
-        <f>[15]Model!Z$19</f>
-        <v>1017.2926499999999</v>
+        <f>[14]Model!W$23</f>
+        <v>1113.4564026999999</v>
       </c>
       <c r="O18" s="14">
-        <f>[15]Model!AA$19</f>
-        <v>1811.8731149999999</v>
+        <f>[14]Model!X$23</f>
+        <v>1422.1613657599992</v>
       </c>
       <c r="P18" s="14">
-        <f>[15]Model!AB$19</f>
-        <v>1919.0845944000002</v>
+        <f>[14]Model!Y$23</f>
+        <v>1443.7923014975993</v>
       </c>
       <c r="Q18" s="14">
-        <f>[15]Model!AC$19</f>
-        <v>1993.765444011</v>
+        <f>[14]Model!Z$23</f>
+        <v>1456.7690142637746</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" ref="R18:V18" si="30">$G18/M18</f>
-        <v>25.66551119402985</v>
+        <f t="shared" ref="R18" si="29">$G18/M18</f>
+        <v>28.523280846455048</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="30"/>
-        <v>27.045735560951908</v>
+        <f t="shared" si="26"/>
+        <v>30.747942997121896</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="30"/>
-        <v>15.185074369846259</v>
+        <f t="shared" si="26"/>
+        <v>24.073564944371913</v>
       </c>
       <c r="U18" s="15">
-        <f t="shared" si="30"/>
-        <v>14.336745800724874</v>
+        <f t="shared" si="26"/>
+        <v>23.712894136149352</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="30"/>
-        <v>13.799731599645581</v>
+        <f t="shared" si="26"/>
+        <v>23.501662696541167</v>
       </c>
       <c r="W18" s="15">
-        <f>G18/[15]Model!$AJ$19</f>
-        <v>12.020001089934652</v>
+        <f>G18/[14]Model!$AG$23</f>
+        <v>19.802862236524049</v>
       </c>
       <c r="X18" s="23">
-        <f>[15]Model!$Y$3</f>
-        <v>17763</v>
+        <f>[14]Model!$V$7</f>
+        <v>6213.6</v>
       </c>
       <c r="Y18" s="26">
-        <f t="shared" ref="Y18:Y24" si="31">G18/X18</f>
-        <v>1.5489178629735969</v>
+        <f t="shared" si="27"/>
+        <v>5.5099288657139169</v>
       </c>
       <c r="Z18" s="25">
-        <f>[15]Model!$X$23</f>
-        <v>3.9284986066743688E-2</v>
+        <f>[14]Model!U$30</f>
+        <v>5.0500414805923599E-2</v>
       </c>
       <c r="AA18" s="25">
-        <f>[15]Model!$Y$23</f>
-        <v>0.1616637237590739</v>
+        <f>[14]Model!V$30</f>
+        <v>4.4056860570622192E-2</v>
       </c>
       <c r="AB18" s="25">
-        <f>[15]Model!$Y$24</f>
-        <v>0.11349434217193041</v>
+        <f>[14]Model!$V$33</f>
+        <v>0.83643942320072096</v>
       </c>
       <c r="AC18" s="25">
-        <f>[15]Model!$Y$26</f>
-        <v>6.6430220120475142E-2</v>
+        <f>[14]Model!$V$37</f>
+        <v>0.2188264452169435</v>
       </c>
       <c r="AD18" s="16">
-        <f>[15]Model!$AM$25</f>
+        <f>[14]Model!$AJ$29</f>
         <v>0.08</v>
       </c>
       <c r="AE18" s="16">
-        <f>[15]Model!$AM$31</f>
-        <v>-0.10935664388414268</v>
+        <f>[14]Model!$AJ$35</f>
+        <v>-0.43497641969139733</v>
       </c>
       <c r="AF18" s="11" t="str">
-        <f>[15]Model!$AM$32</f>
-        <v>Fairly valued</v>
+        <f>[14]Model!$AJ$36</f>
+        <v>Overvalued</v>
       </c>
       <c r="AH18" s="11">
-        <v>1996</v>
+        <v>1971</v>
       </c>
       <c r="AJ18" s="18">
-        <f>[15]Main!$E$3</f>
-        <v>45904</v>
+        <f>[14]Main!$E$3</f>
+        <v>45868</v>
       </c>
       <c r="AK18" s="18">
-        <f>[15]Main!$G$3</f>
-        <v>45868</v>
+        <f>[14]Main!$G$3</f>
+        <v>46079</v>
       </c>
     </row>
     <row r="19" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B19" s="19" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D19" s="17">
-        <f>[16]Main!$D$3</f>
-        <v>180.62</v>
+        <f>[15]Main!$D$3</f>
+        <v>47.27</v>
       </c>
       <c r="E19" s="14">
-        <f>[16]Main!$D$5</f>
-        <v>23173.546000000002</v>
+        <f>[15]Main!$D$5</f>
+        <v>27246.428</v>
       </c>
       <c r="F19" s="14">
-        <f>[16]Main!$D$8</f>
-        <v>-4174</v>
+        <f>[15]Main!$D$8</f>
+        <v>-267</v>
       </c>
       <c r="G19" s="14">
-        <f>[16]Main!$D$9</f>
-        <v>27347.546000000002</v>
+        <f>[15]Main!$D$9</f>
+        <v>27513.428</v>
       </c>
       <c r="H19" s="14">
-        <f>[16]Model!P$18</f>
-        <v>667</v>
+        <f>[15]Model!T$19</f>
+        <v>823</v>
       </c>
       <c r="I19" s="14">
-        <f>[16]Model!Q$18</f>
-        <v>628</v>
+        <f>[15]Model!U$19</f>
+        <v>239</v>
       </c>
       <c r="J19" s="14">
-        <f>[16]Model!R$18</f>
-        <v>753</v>
+        <f>[15]Model!V$19</f>
+        <v>586</v>
       </c>
       <c r="K19" s="14">
-        <f>[16]Model!S$18</f>
-        <v>685</v>
+        <f>[15]Model!W$19</f>
+        <v>927</v>
       </c>
       <c r="L19" s="14">
-        <f>[16]Model!T$18</f>
-        <v>199</v>
+        <f>[15]Model!X$19</f>
+        <v>658</v>
       </c>
       <c r="M19" s="14">
-        <f>[16]Model!U$18</f>
-        <v>1254</v>
+        <f>[15]Model!Y$19</f>
+        <v>1072</v>
       </c>
       <c r="N19" s="14">
-        <f>[16]Model!V$18</f>
-        <v>1488.4593099999986</v>
+        <f>[15]Model!Z$19</f>
+        <v>1017.2926499999999</v>
       </c>
       <c r="O19" s="14">
-        <f>[16]Model!W$18</f>
-        <v>1825.4889705000001</v>
+        <f>[15]Model!AA$19</f>
+        <v>1811.8731149999999</v>
       </c>
       <c r="P19" s="14">
-        <f>[16]Model!X$18</f>
-        <v>1915.7253039600007</v>
+        <f>[15]Model!AB$19</f>
+        <v>1919.0845944000002</v>
       </c>
       <c r="Q19" s="14">
-        <f>[16]Model!Y$18</f>
-        <v>1981.3585502100002</v>
+        <f>[15]Model!AC$19</f>
+        <v>1993.765444011</v>
       </c>
       <c r="R19" s="15">
-        <f t="shared" ref="R19" si="32">$G19/M19</f>
-        <v>21.808250398724084</v>
+        <f t="shared" ref="R19:V19" si="30">$G19/M19</f>
+        <v>25.66551119402985</v>
       </c>
       <c r="S19" s="15">
-        <f t="shared" ref="S19:S24" si="33">$G19/N19</f>
-        <v>18.373055827774042</v>
+        <f t="shared" si="30"/>
+        <v>27.045735560951908</v>
       </c>
       <c r="T19" s="15">
-        <f t="shared" ref="T19:T24" si="34">$G19/O19</f>
-        <v>14.980942882667502</v>
+        <f t="shared" si="30"/>
+        <v>15.185074369846259</v>
       </c>
       <c r="U19" s="15">
-        <f t="shared" ref="U19:U24" si="35">$G19/P19</f>
-        <v>14.275296120727653</v>
+        <f t="shared" si="30"/>
+        <v>14.336745800724874</v>
       </c>
       <c r="V19" s="15">
-        <f t="shared" ref="V19:V24" si="36">$G19/Q19</f>
-        <v>13.802421574379604</v>
+        <f t="shared" si="30"/>
+        <v>13.799731599645581</v>
       </c>
       <c r="W19" s="15">
-        <f>G19/[16]Model!$AF$18</f>
-        <v>12.733418423610921</v>
+        <f>G19/[15]Model!$AJ$19</f>
+        <v>12.020001089934652</v>
       </c>
       <c r="X19" s="23">
-        <f>[16]Model!$U$3</f>
-        <v>16662</v>
+        <f>[15]Model!$Y$3</f>
+        <v>17763</v>
       </c>
       <c r="Y19" s="26">
-        <f t="shared" si="31"/>
-        <v>1.6413123274516865</v>
+        <f t="shared" ref="Y19:Y25" si="31">G19/X19</f>
+        <v>1.5489178629735969</v>
       </c>
       <c r="Z19" s="25">
-        <f>[16]Model!T$22</f>
-        <v>7.2381217004723553E-2</v>
+        <f>[15]Model!$X$23</f>
+        <v>3.9284986066743688E-2</v>
       </c>
       <c r="AA19" s="25">
-        <f>[16]Model!U$22</f>
-        <v>7.9284881461329171E-2</v>
+        <f>[15]Model!$Y$23</f>
+        <v>0.1616637237590739</v>
       </c>
       <c r="AB19" s="25">
-        <f>[16]Model!$U$23</f>
-        <v>0.16792701956547834</v>
+        <f>[15]Model!$Y$24</f>
+        <v>0.11349434217193041</v>
       </c>
       <c r="AC19" s="25">
-        <f>[16]Model!$U$26</f>
-        <v>0.10731004681310767</v>
+        <f>[15]Model!$Y$26</f>
+        <v>6.6430220120475142E-2</v>
       </c>
       <c r="AD19" s="16">
-        <f>[16]Model!$AI$24</f>
+        <f>[15]Model!$AM$25</f>
         <v>0.08</v>
       </c>
       <c r="AE19" s="16">
-        <f>[16]Model!$AI$30</f>
-        <v>-0.15132262827852416</v>
+        <f>[15]Model!$AM$31</f>
+        <v>-0.10935664388414268</v>
       </c>
       <c r="AF19" s="11" t="str">
-        <f>[16]Model!$AI$31</f>
-        <v>Slightly overvalued</v>
+        <f>[15]Model!$AM$32</f>
+        <v>Fairly valued</v>
       </c>
       <c r="AH19" s="11">
-        <v>1969</v>
+        <v>1996</v>
       </c>
       <c r="AJ19" s="18">
-        <f>[16]Main!$E$3</f>
-        <v>45898</v>
+        <f>[15]Main!$E$3</f>
+        <v>45904</v>
       </c>
       <c r="AK19" s="18">
-        <f>[16]Main!$G$3</f>
-        <v>45965</v>
+        <f>[15]Main!$G$3</f>
+        <v>45868</v>
       </c>
     </row>
     <row r="20" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B20" s="19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D20" s="17">
-        <f>[17]Main!$D$3</f>
-        <v>194.63</v>
+        <f>[16]Main!$D$3</f>
+        <v>180.62</v>
       </c>
       <c r="E20" s="14">
-        <f>[17]Main!$D$5</f>
-        <v>19287.832999999999</v>
+        <f>[16]Main!$D$5</f>
+        <v>23173.546000000002</v>
       </c>
       <c r="F20" s="14">
-        <f>[17]Main!$D$8</f>
-        <v>-4448</v>
+        <f>[16]Main!$D$8</f>
+        <v>-4174</v>
       </c>
       <c r="G20" s="14">
-        <f>[17]Main!$D$9</f>
-        <v>23735.832999999999</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
+        <f>[16]Main!$D$9</f>
+        <v>27347.546000000002</v>
+      </c>
+      <c r="H20" s="14">
+        <f>[16]Model!P$18</f>
+        <v>667</v>
+      </c>
+      <c r="I20" s="14">
+        <f>[16]Model!Q$18</f>
+        <v>628</v>
+      </c>
+      <c r="J20" s="14">
+        <f>[16]Model!R$18</f>
+        <v>753</v>
+      </c>
+      <c r="K20" s="14">
+        <f>[16]Model!S$18</f>
+        <v>685</v>
+      </c>
+      <c r="L20" s="14">
+        <f>[16]Model!T$18</f>
+        <v>199</v>
+      </c>
       <c r="M20" s="14">
-        <f>[17]Model!U$23</f>
-        <v>370</v>
+        <f>[16]Model!U$18</f>
+        <v>1254</v>
       </c>
       <c r="N20" s="14">
-        <f>[17]Model!V$23</f>
-        <v>501.53600000000051</v>
-      </c>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
+        <f>[16]Model!V$18</f>
+        <v>1488.4593099999986</v>
+      </c>
+      <c r="O20" s="14">
+        <f>[16]Model!W$18</f>
+        <v>1825.4889705000001</v>
+      </c>
+      <c r="P20" s="14">
+        <f>[16]Model!X$18</f>
+        <v>1915.7253039600007</v>
+      </c>
+      <c r="Q20" s="14">
+        <f>[16]Model!Y$18</f>
+        <v>1981.3585502100002</v>
+      </c>
       <c r="R20" s="15">
-        <f t="shared" ref="R20" si="37">$G20/M20</f>
-        <v>64.150899999999993</v>
+        <f t="shared" ref="R20" si="32">$G20/M20</f>
+        <v>21.808250398724084</v>
       </c>
       <c r="S20" s="15">
-        <f t="shared" si="33"/>
-        <v>47.326279668857218</v>
-      </c>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="14">
-        <f>[17]Model!$V$8</f>
-        <v>9401.5300000000007</v>
-      </c>
-      <c r="Y20" s="20">
+        <f t="shared" ref="S20:S25" si="33">$G20/N20</f>
+        <v>18.373055827774042</v>
+      </c>
+      <c r="T20" s="15">
+        <f t="shared" ref="T20:T25" si="34">$G20/O20</f>
+        <v>14.980942882667502</v>
+      </c>
+      <c r="U20" s="15">
+        <f t="shared" ref="U20:U25" si="35">$G20/P20</f>
+        <v>14.275296120727653</v>
+      </c>
+      <c r="V20" s="15">
+        <f t="shared" ref="V20:V25" si="36">$G20/Q20</f>
+        <v>13.802421574379604</v>
+      </c>
+      <c r="W20" s="15">
+        <f>G20/[16]Model!$AF$18</f>
+        <v>12.733418423610921</v>
+      </c>
+      <c r="X20" s="23">
+        <f>[16]Model!$U$3</f>
+        <v>16662</v>
+      </c>
+      <c r="Y20" s="26">
         <f t="shared" si="31"/>
-        <v>2.5246776854405608</v>
-      </c>
-      <c r="Z20" s="25"/>
-      <c r="AA20" s="16">
-        <f>[17]Model!$V$31</f>
-        <v>8.5000577034045177E-2</v>
-      </c>
-      <c r="AB20" s="16">
-        <f>[17]Model!$V$32</f>
-        <v>0.1980854180117492</v>
-      </c>
-      <c r="AC20" s="16">
-        <f>[17]Model!$V$35</f>
-        <v>0.11177712563806108</v>
-      </c>
-      <c r="AD20" s="16"/>
-      <c r="AE20" s="16"/>
-      <c r="AJ20" s="18"/>
-      <c r="AK20" s="18"/>
+        <v>1.6413123274516865</v>
+      </c>
+      <c r="Z20" s="25">
+        <f>[16]Model!T$22</f>
+        <v>7.2381217004723553E-2</v>
+      </c>
+      <c r="AA20" s="25">
+        <f>[16]Model!U$22</f>
+        <v>7.9284881461329171E-2</v>
+      </c>
+      <c r="AB20" s="25">
+        <f>[16]Model!$U$23</f>
+        <v>0.16792701956547834</v>
+      </c>
+      <c r="AC20" s="25">
+        <f>[16]Model!$U$26</f>
+        <v>0.10731004681310767</v>
+      </c>
+      <c r="AD20" s="16">
+        <f>[16]Model!$AI$24</f>
+        <v>0.08</v>
+      </c>
+      <c r="AE20" s="16">
+        <f>[16]Model!$AI$30</f>
+        <v>-0.15132262827852416</v>
+      </c>
+      <c r="AF20" s="11" t="str">
+        <f>[16]Model!$AI$31</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AH20" s="11">
+        <v>1969</v>
+      </c>
+      <c r="AJ20" s="18">
+        <f>[16]Main!$E$3</f>
+        <v>45898</v>
+      </c>
+      <c r="AK20" s="18">
+        <f>[16]Main!$G$3</f>
+        <v>45965</v>
+      </c>
     </row>
     <row r="21" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B21" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="13">
-        <f>[18]Main!$D$3</f>
-        <v>78.45</v>
+        <v>85</v>
+      </c>
+      <c r="D21" s="17">
+        <f>[17]Main!$D$3</f>
+        <v>194.63</v>
       </c>
       <c r="E21" s="14">
-        <f>[18]Main!$D$5</f>
-        <v>13979.789999999999</v>
+        <f>[17]Main!$D$5</f>
+        <v>19287.832999999999</v>
       </c>
       <c r="F21" s="14">
-        <f>[18]Main!$D$8</f>
-        <v>-2300</v>
+        <f>[17]Main!$D$8</f>
+        <v>-4448</v>
       </c>
       <c r="G21" s="14">
-        <f>[18]Main!$D$9</f>
-        <v>16279.789999999999</v>
-      </c>
-      <c r="H21" s="14">
-        <f>[18]Model!P$22</f>
-        <v>815</v>
-      </c>
-      <c r="I21" s="14">
-        <f>[18]Model!Q$22</f>
-        <v>309</v>
-      </c>
-      <c r="J21" s="14">
-        <f>[18]Model!R$22</f>
-        <v>746</v>
-      </c>
-      <c r="K21" s="14">
-        <f>[18]Model!S$22</f>
-        <v>861</v>
-      </c>
-      <c r="L21" s="14">
-        <f>[18]Model!T$22</f>
-        <v>921</v>
-      </c>
+        <f>[17]Main!$D$9</f>
+        <v>23735.832999999999</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
       <c r="M21" s="14">
-        <f>[18]Model!U$22</f>
-        <v>824</v>
+        <f>[17]Model!U$23</f>
+        <v>370</v>
       </c>
       <c r="N21" s="14">
-        <f>[18]Model!V$22</f>
-        <v>1009.4089999999989</v>
-      </c>
-      <c r="O21" s="14">
-        <f>[18]Model!W$22</f>
-        <v>1260.3274750399985</v>
-      </c>
-      <c r="P21" s="14">
-        <f>[18]Model!X$22</f>
-        <v>1438.1055164480015</v>
-      </c>
-      <c r="Q21" s="14">
-        <f>[18]Model!Y$22</f>
-        <v>1494.4098756374406</v>
-      </c>
+        <f>[17]Model!V$23</f>
+        <v>501.53600000000051</v>
+      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
       <c r="R21" s="15">
-        <f>$G21/M21</f>
-        <v>19.757026699029126</v>
+        <f t="shared" ref="R21" si="37">$G21/M21</f>
+        <v>64.150899999999993</v>
       </c>
       <c r="S21" s="15">
-        <f>$G21/N21</f>
-        <v>16.128041259786684</v>
-      </c>
-      <c r="T21" s="15">
-        <f>$G21/O21</f>
-        <v>12.91711108613524</v>
-      </c>
-      <c r="U21" s="15">
-        <f>$G21/P21</f>
-        <v>11.320302866377773</v>
-      </c>
-      <c r="V21" s="15">
-        <f>$G21/Q21</f>
-        <v>10.893791767172212</v>
-      </c>
-      <c r="W21" s="15">
-        <f>G21/[18]Model!$AF$22</f>
-        <v>9.2229628905226502</v>
-      </c>
-      <c r="X21" s="23">
-        <f>[18]Model!$U$6</f>
-        <v>13702</v>
-      </c>
-      <c r="Y21" s="26">
+        <f t="shared" si="33"/>
+        <v>47.326279668857218</v>
+      </c>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="14">
+        <f>[17]Model!$V$8</f>
+        <v>9401.5300000000007</v>
+      </c>
+      <c r="Y21" s="20">
         <f t="shared" si="31"/>
-        <v>1.1881323894321996</v>
-      </c>
-      <c r="Z21" s="25">
-        <f>[18]Model!T$29</f>
-        <v>6.3252777993628051E-2</v>
-      </c>
-      <c r="AA21" s="25">
-        <f>[18]Model!U$29</f>
-        <v>1.3885843747716287E-3</v>
-      </c>
-      <c r="AB21" s="25">
-        <f>[18]Model!$U$32</f>
-        <v>0.18260108013428697</v>
-      </c>
-      <c r="AC21" s="25">
-        <f>[18]Model!$U$35</f>
-        <v>6.23996496861772E-2</v>
-      </c>
-      <c r="AD21" s="16">
-        <f>[18]Model!$AJ$29</f>
-        <v>0.09</v>
-      </c>
-      <c r="AE21" s="16">
-        <f>[18]Model!$AJ$35</f>
-        <v>3.5247218209492504E-2</v>
-      </c>
-      <c r="AF21" s="11" t="str">
-        <f>[18]Model!$AJ$36</f>
-        <v>Fairly valued</v>
-      </c>
-      <c r="AH21" s="11">
-        <v>1923</v>
-      </c>
-      <c r="AJ21" s="18">
-        <f>[18]Main!$E$3</f>
-        <v>45867</v>
-      </c>
-      <c r="AK21" s="18">
-        <f>[18]Main!$G$3</f>
-        <v>45953</v>
-      </c>
+        <v>2.5246776854405608</v>
+      </c>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="16">
+        <f>[17]Model!$V$31</f>
+        <v>8.5000577034045177E-2</v>
+      </c>
+      <c r="AB21" s="16">
+        <f>[17]Model!$V$32</f>
+        <v>0.1980854180117492</v>
+      </c>
+      <c r="AC21" s="16">
+        <f>[17]Model!$V$35</f>
+        <v>0.11177712563806108</v>
+      </c>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="18"/>
     </row>
     <row r="22" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B22" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D22" s="13">
-        <f>[19]Main!$D$3</f>
-        <v>57.19</v>
+        <f>[18]Main!$D$3</f>
+        <v>78.45</v>
       </c>
       <c r="E22" s="14">
-        <f>[19]Main!$D$5</f>
-        <v>10494.365</v>
+        <f>[18]Main!$D$5</f>
+        <v>13979.789999999999</v>
       </c>
       <c r="F22" s="14">
-        <f>[19]Main!$D$8</f>
-        <v>-600.00000000000023</v>
+        <f>[18]Main!$D$8</f>
+        <v>-2300</v>
       </c>
       <c r="G22" s="14">
-        <f>[19]Main!$D$9</f>
-        <v>11094.365</v>
+        <f>[18]Main!$D$9</f>
+        <v>16279.789999999999</v>
       </c>
       <c r="H22" s="14">
-        <f>[19]Model!P$22</f>
-        <v>-322.3</v>
+        <f>[18]Model!P$22</f>
+        <v>815</v>
       </c>
       <c r="I22" s="14">
-        <f>[19]Model!Q$22</f>
-        <v>-731.9000000000002</v>
+        <f>[18]Model!Q$22</f>
+        <v>309</v>
       </c>
       <c r="J22" s="14">
-        <f>[19]Model!R$22</f>
-        <v>-44.700000000000145</v>
+        <f>[18]Model!R$22</f>
+        <v>746</v>
       </c>
       <c r="K22" s="14">
-        <f>[19]Model!S$22</f>
-        <v>-185.59999999999982</v>
+        <f>[18]Model!S$22</f>
+        <v>861</v>
       </c>
       <c r="L22" s="14">
-        <f>[19]Model!T$22</f>
-        <v>163.90000000000035</v>
+        <f>[18]Model!T$22</f>
+        <v>921</v>
       </c>
       <c r="M22" s="14">
-        <f>[19]Model!U$22</f>
-        <v>228.2000000000003</v>
+        <f>[18]Model!U$22</f>
+        <v>824</v>
       </c>
       <c r="N22" s="14">
-        <f>[19]Model!V$22</f>
-        <v>743.65658000000008</v>
+        <f>[18]Model!V$22</f>
+        <v>1009.4089999999989</v>
       </c>
       <c r="O22" s="14">
-        <f>[19]Model!W$22</f>
-        <v>719.25833086000011</v>
+        <f>[18]Model!W$22</f>
+        <v>1260.3274750399985</v>
       </c>
       <c r="P22" s="14">
-        <f>[19]Model!X$22</f>
-        <v>830.80143681460015</v>
+        <f>[18]Model!X$22</f>
+        <v>1438.1055164480015</v>
       </c>
       <c r="Q22" s="14">
-        <f>[19]Model!Y$22</f>
-        <v>906.37830312002222</v>
+        <f>[18]Model!Y$22</f>
+        <v>1494.4098756374406</v>
       </c>
       <c r="R22" s="15">
-        <f t="shared" ref="R22:V22" si="38">$G22/M22</f>
-        <v>48.616849255039376</v>
+        <f>$G22/M22</f>
+        <v>19.757026699029126</v>
       </c>
       <c r="S22" s="15">
-        <f t="shared" si="38"/>
-        <v>14.918667162200055</v>
+        <f>$G22/N22</f>
+        <v>16.128041259786684</v>
       </c>
       <c r="T22" s="15">
-        <f t="shared" si="38"/>
-        <v>15.424729230087236</v>
+        <f>$G22/O22</f>
+        <v>12.91711108613524</v>
       </c>
       <c r="U22" s="15">
-        <f t="shared" si="38"/>
-        <v>13.353810559761699</v>
+        <f>$G22/P22</f>
+        <v>11.320302866377773</v>
       </c>
       <c r="V22" s="15">
-        <f t="shared" si="38"/>
-        <v>12.240324996538327</v>
+        <f>$G22/Q22</f>
+        <v>10.893791767172212</v>
       </c>
       <c r="W22" s="15">
-        <f>G22/[19]Model!$AF$22</f>
-        <v>10.264552570282582</v>
+        <f>G22/[18]Model!$AF$22</f>
+        <v>9.2229628905226502</v>
       </c>
       <c r="X22" s="23">
-        <f>[19]Model!$V$3</f>
-        <v>7743.8040000000001</v>
+        <f>[18]Model!$U$6</f>
+        <v>13702</v>
       </c>
       <c r="Y22" s="26">
         <f t="shared" si="31"/>
-        <v>1.4326763693915807</v>
+        <v>1.1881323894321996</v>
       </c>
       <c r="Z22" s="25">
-        <f>[19]Model!T$26</f>
-        <v>0.16041143561957627</v>
+        <f>[18]Model!T$29</f>
+        <v>6.3252777993628051E-2</v>
       </c>
       <c r="AA22" s="25">
-        <f>[19]Model!U$26</f>
-        <v>0.21376103255195988</v>
+        <f>[18]Model!U$29</f>
+        <v>1.3885843747716287E-3</v>
       </c>
       <c r="AB22" s="25">
-        <f>[19]Model!$U$27</f>
-        <v>0.18032120349664568</v>
+        <f>[18]Model!$U$32</f>
+        <v>0.18260108013428697</v>
       </c>
       <c r="AC22" s="25">
-        <f>[19]Model!$U$31</f>
-        <v>8.4945345364129704E-2</v>
+        <f>[18]Model!$U$35</f>
+        <v>6.23996496861772E-2</v>
       </c>
       <c r="AD22" s="16">
-        <f>[19]Model!$AI$28</f>
-        <v>0.14000000000000001</v>
+        <f>[18]Model!$AJ$29</f>
+        <v>0.09</v>
       </c>
       <c r="AE22" s="16">
-        <f>[19]Model!$AI$34</f>
-        <v>-0.43120780386203839</v>
+        <f>[18]Model!$AJ$35</f>
+        <v>3.5247218209492504E-2</v>
       </c>
       <c r="AF22" s="11" t="str">
-        <f>[19]Model!$AI$35</f>
-        <v>Overvalued</v>
+        <f>[18]Model!$AJ$36</f>
+        <v>Fairly valued</v>
       </c>
       <c r="AH22" s="11">
-        <v>1969</v>
+        <v>1923</v>
       </c>
       <c r="AJ22" s="18">
-        <f>[19]Main!$E$3</f>
-        <v>45903</v>
+        <f>[18]Main!$E$3</f>
+        <v>45867</v>
       </c>
       <c r="AK22" s="18">
-        <f>[19]Main!$G$3</f>
-        <v>45965</v>
+        <f>[18]Main!$G$3</f>
+        <v>45953</v>
       </c>
     </row>
     <row r="23" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B23" s="19" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="17">
-        <f>[20]Main!$D$3</f>
-        <v>101.2</v>
+        <v>78</v>
+      </c>
+      <c r="D23" s="13">
+        <f>[19]Main!$D$3</f>
+        <v>57.19</v>
       </c>
       <c r="E23" s="14">
-        <f>[20]Main!$D$5</f>
-        <v>11739.2</v>
+        <f>[19]Main!$D$5</f>
+        <v>10494.365</v>
       </c>
       <c r="F23" s="14">
-        <f>[20]Main!$D$8</f>
-        <v>-498</v>
+        <f>[19]Main!$D$8</f>
+        <v>-600.00000000000023</v>
       </c>
       <c r="G23" s="14">
-        <f>[20]Main!$D$9</f>
-        <v>12237.2</v>
+        <f>[19]Main!$D$9</f>
+        <v>11094.365</v>
       </c>
       <c r="H23" s="14">
-        <f>[20]Model!P$43</f>
-        <v>5.9000000000001167</v>
+        <f>[19]Model!P$22</f>
+        <v>-322.3</v>
       </c>
       <c r="I23" s="14">
-        <f>[20]Model!Q$43</f>
-        <v>-65.199999999999903</v>
+        <f>[19]Model!Q$22</f>
+        <v>-731.9000000000002</v>
       </c>
       <c r="J23" s="14">
-        <f>[20]Model!R$43</f>
-        <v>63</v>
+        <f>[19]Model!R$22</f>
+        <v>-44.700000000000145</v>
       </c>
       <c r="K23" s="14">
-        <f>[20]Model!S$43</f>
-        <v>79</v>
+        <f>[19]Model!S$22</f>
+        <v>-185.59999999999982</v>
       </c>
       <c r="L23" s="14">
-        <f>[20]Model!T$43</f>
-        <v>58</v>
+        <f>[19]Model!T$22</f>
+        <v>163.90000000000035</v>
       </c>
       <c r="M23" s="14">
-        <f>[20]Model!U$43</f>
-        <v>106</v>
+        <f>[19]Model!U$22</f>
+        <v>228.2000000000003</v>
       </c>
       <c r="N23" s="14">
-        <f>[20]Model!V$43</f>
-        <v>105.74143999999995</v>
+        <f>[19]Model!V$22</f>
+        <v>743.65658000000008</v>
       </c>
       <c r="O23" s="14">
-        <f>[20]Model!W$43</f>
-        <v>144.35987200000005</v>
+        <f>[19]Model!W$22</f>
+        <v>719.25833086000011</v>
       </c>
       <c r="P23" s="14">
-        <f>[20]Model!X$43</f>
-        <v>169.88582975999995</v>
+        <f>[19]Model!X$22</f>
+        <v>830.80143681460015</v>
       </c>
       <c r="Q23" s="14">
-        <f>[20]Model!Y$43</f>
-        <v>189.70135618560002</v>
+        <f>[19]Model!Y$22</f>
+        <v>906.37830312002222</v>
       </c>
       <c r="R23" s="15">
-        <f t="shared" ref="R23" si="39">$G23/M23</f>
-        <v>115.44528301886793</v>
+        <f t="shared" ref="R23:V23" si="38">$G23/M23</f>
+        <v>48.616849255039376</v>
       </c>
       <c r="S23" s="15">
-        <f t="shared" si="33"/>
-        <v>115.72757095042404</v>
+        <f t="shared" si="38"/>
+        <v>14.918667162200055</v>
       </c>
       <c r="T23" s="15">
-        <f t="shared" si="34"/>
-        <v>84.768709132687491</v>
+        <f t="shared" si="38"/>
+        <v>15.424729230087236</v>
       </c>
       <c r="U23" s="15">
-        <f t="shared" si="35"/>
-        <v>72.031905293617854</v>
+        <f t="shared" si="38"/>
+        <v>13.353810559761699</v>
       </c>
       <c r="V23" s="15">
-        <f t="shared" si="36"/>
-        <v>64.50770962347454</v>
+        <f t="shared" si="38"/>
+        <v>12.240324996538327</v>
       </c>
       <c r="W23" s="15">
-        <f>G23/[20]Model!$AF$43</f>
-        <v>35.255116146867159</v>
-      </c>
-      <c r="X23" s="14">
-        <f>[20]Model!$V$26</f>
-        <v>2587.8199999999997</v>
-      </c>
-      <c r="Y23" s="20">
+        <f>G23/[19]Model!$AF$22</f>
+        <v>10.264552570282582</v>
+      </c>
+      <c r="X23" s="23">
+        <f>[19]Model!$V$3</f>
+        <v>7743.8040000000001</v>
+      </c>
+      <c r="Y23" s="26">
         <f t="shared" si="31"/>
-        <v>4.7287678432039328</v>
-      </c>
-      <c r="Z23" s="16">
-        <f>[20]Model!U$47</f>
-        <v>0.21277747698971305</v>
-      </c>
-      <c r="AA23" s="16">
-        <f>[20]Model!V$47</f>
-        <v>0.1552767857142856</v>
-      </c>
-      <c r="AB23" s="16">
-        <f>[20]Model!$V$48</f>
-        <v>0.22716788648360398</v>
-      </c>
-      <c r="AC23" s="16">
-        <f>[20]Model!$V$52</f>
-        <v>9.599848521149075E-2</v>
+        <v>1.4326763693915807</v>
+      </c>
+      <c r="Z23" s="25">
+        <f>[19]Model!T$26</f>
+        <v>0.16041143561957627</v>
+      </c>
+      <c r="AA23" s="25">
+        <f>[19]Model!U$26</f>
+        <v>0.21376103255195988</v>
+      </c>
+      <c r="AB23" s="25">
+        <f>[19]Model!$U$27</f>
+        <v>0.18032120349664568</v>
+      </c>
+      <c r="AC23" s="25">
+        <f>[19]Model!$U$31</f>
+        <v>8.4945345364129704E-2</v>
       </c>
       <c r="AD23" s="16">
-        <f>[20]Model!$AI$49</f>
-        <v>0.09</v>
+        <f>[19]Model!$AI$28</f>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AE23" s="16">
-        <f>[20]Model!$AI$55</f>
-        <v>-0.80686738144951742</v>
+        <f>[19]Model!$AI$34</f>
+        <v>-0.43120780386203839</v>
       </c>
       <c r="AF23" s="11" t="str">
-        <f>[20]Model!$AI$56</f>
-        <v>Heavily overvalued</v>
+        <f>[19]Model!$AI$35</f>
+        <v>Overvalued</v>
       </c>
       <c r="AH23" s="11">
-        <v>1892</v>
+        <v>1969</v>
       </c>
       <c r="AJ23" s="18">
-        <f>[20]Main!$E$3</f>
-        <v>45924</v>
+        <f>[19]Main!$E$3</f>
+        <v>45903</v>
       </c>
       <c r="AK23" s="18">
-        <f>[20]Main!$G$3</f>
-        <v>45968</v>
+        <f>[19]Main!$G$3</f>
+        <v>45965</v>
       </c>
     </row>
     <row r="24" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B24" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="17">
+        <f>[20]Main!$D$3</f>
+        <v>101.2</v>
+      </c>
+      <c r="E24" s="14">
+        <f>[20]Main!$D$5</f>
+        <v>11739.2</v>
+      </c>
+      <c r="F24" s="14">
+        <f>[20]Main!$D$8</f>
+        <v>-498</v>
+      </c>
+      <c r="G24" s="14">
+        <f>[20]Main!$D$9</f>
+        <v>12237.2</v>
+      </c>
+      <c r="H24" s="14">
+        <f>[20]Model!P$43</f>
+        <v>5.9000000000001167</v>
+      </c>
+      <c r="I24" s="14">
+        <f>[20]Model!Q$43</f>
+        <v>-65.199999999999903</v>
+      </c>
+      <c r="J24" s="14">
+        <f>[20]Model!R$43</f>
+        <v>63</v>
+      </c>
+      <c r="K24" s="14">
+        <f>[20]Model!S$43</f>
+        <v>79</v>
+      </c>
+      <c r="L24" s="14">
+        <f>[20]Model!T$43</f>
+        <v>58</v>
+      </c>
+      <c r="M24" s="14">
+        <f>[20]Model!U$43</f>
+        <v>106</v>
+      </c>
+      <c r="N24" s="14">
+        <f>[20]Model!V$43</f>
+        <v>105.74143999999995</v>
+      </c>
+      <c r="O24" s="14">
+        <f>[20]Model!W$43</f>
+        <v>144.35987200000005</v>
+      </c>
+      <c r="P24" s="14">
+        <f>[20]Model!X$43</f>
+        <v>169.88582975999995</v>
+      </c>
+      <c r="Q24" s="14">
+        <f>[20]Model!Y$43</f>
+        <v>189.70135618560002</v>
+      </c>
+      <c r="R24" s="15">
+        <f t="shared" ref="R24" si="39">$G24/M24</f>
+        <v>115.44528301886793</v>
+      </c>
+      <c r="S24" s="15">
+        <f t="shared" si="33"/>
+        <v>115.72757095042404</v>
+      </c>
+      <c r="T24" s="15">
+        <f t="shared" si="34"/>
+        <v>84.768709132687491</v>
+      </c>
+      <c r="U24" s="15">
+        <f t="shared" si="35"/>
+        <v>72.031905293617854</v>
+      </c>
+      <c r="V24" s="15">
+        <f t="shared" si="36"/>
+        <v>64.50770962347454</v>
+      </c>
+      <c r="W24" s="15">
+        <f>G24/[20]Model!$AF$43</f>
+        <v>35.255116146867159</v>
+      </c>
+      <c r="X24" s="14">
+        <f>[20]Model!$V$26</f>
+        <v>2587.8199999999997</v>
+      </c>
+      <c r="Y24" s="20">
+        <f t="shared" si="31"/>
+        <v>4.7287678432039328</v>
+      </c>
+      <c r="Z24" s="16">
+        <f>[20]Model!U$47</f>
+        <v>0.21277747698971305</v>
+      </c>
+      <c r="AA24" s="16">
+        <f>[20]Model!V$47</f>
+        <v>0.1552767857142856</v>
+      </c>
+      <c r="AB24" s="16">
+        <f>[20]Model!$V$48</f>
+        <v>0.22716788648360398</v>
+      </c>
+      <c r="AC24" s="16">
+        <f>[20]Model!$V$52</f>
+        <v>9.599848521149075E-2</v>
+      </c>
+      <c r="AD24" s="16">
+        <f>[20]Model!$AI$49</f>
+        <v>0.09</v>
+      </c>
+      <c r="AE24" s="16">
+        <f>[20]Model!$AI$55</f>
+        <v>-0.80686738144951742</v>
+      </c>
+      <c r="AF24" s="11" t="str">
+        <f>[20]Model!$AI$56</f>
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AH24" s="11">
+        <v>1892</v>
+      </c>
+      <c r="AJ24" s="18">
+        <f>[20]Main!$E$3</f>
+        <v>45924</v>
+      </c>
+      <c r="AK24" s="18">
+        <f>[20]Main!$G$3</f>
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B25" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D25" s="13">
         <f>[21]Main!$D$3</f>
-        <v>64.39</v>
-      </c>
-      <c r="E24" s="14">
+        <v>90.08</v>
+      </c>
+      <c r="E25" s="14">
         <f>[21]Main!$D$5</f>
-        <v>10869.032000000001</v>
-      </c>
-      <c r="F24" s="14">
+        <v>15205.504000000001</v>
+      </c>
+      <c r="F25" s="14">
         <f>[21]Main!$D$8</f>
         <v>613.79999999999995</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G25" s="14">
         <f>[21]Main!$D$9</f>
-        <v>10255.232000000002</v>
-      </c>
-      <c r="H24" s="14">
-        <f>[21]Model!P$20</f>
+        <v>14591.704000000002</v>
+      </c>
+      <c r="H25" s="14">
+        <f>[21]Model!P$22</f>
         <v>10.89999999999997</v>
       </c>
-      <c r="I24" s="14">
-        <f>[21]Model!Q$20</f>
+      <c r="I25" s="14">
+        <f>[21]Model!Q$22</f>
         <v>80.300000000000068</v>
       </c>
-      <c r="J24" s="14">
-        <f>[21]Model!R$20</f>
+      <c r="J25" s="14">
+        <f>[21]Model!R$22</f>
         <v>0.50000000000003597</v>
       </c>
-      <c r="K24" s="14">
-        <f>[21]Model!S$20</f>
+      <c r="K25" s="14">
+        <f>[21]Model!S$22</f>
         <v>-33.20000000000001</v>
       </c>
-      <c r="L24" s="14">
-        <f>[21]Model!T$20</f>
+      <c r="L25" s="14">
+        <f>[21]Model!T$22</f>
         <v>2.3999999999998813</v>
       </c>
-      <c r="M24" s="14">
-        <f>[21]Model!U$20</f>
+      <c r="M25" s="14">
+        <f>[21]Model!U$22</f>
         <v>16.299999999999944</v>
       </c>
-      <c r="N24" s="14">
-        <f>[21]Model!V$20</f>
-        <v>16.054319999999748</v>
-      </c>
-      <c r="O24" s="14">
-        <f>[21]Model!W$20</f>
-        <v>39.422006400000022</v>
-      </c>
-      <c r="P24" s="14">
-        <f>[21]Model!X$20</f>
-        <v>60.409628094400034</v>
-      </c>
-      <c r="Q24" s="14">
-        <f>[21]Model!Y$20</f>
-        <v>72.553818362864064</v>
-      </c>
-      <c r="R24" s="15">
-        <f t="shared" ref="R24" si="40">$G24/M24</f>
-        <v>629.15533742331513</v>
-      </c>
-      <c r="S24" s="15">
+      <c r="N25" s="14">
+        <f>[21]Model!V$22</f>
+        <v>19.969807999999741</v>
+      </c>
+      <c r="O25" s="14">
+        <f>[21]Model!W$22</f>
+        <v>47.220326400000076</v>
+      </c>
+      <c r="P25" s="14">
+        <f>[21]Model!X$22</f>
+        <v>70.794515788799941</v>
+      </c>
+      <c r="Q25" s="14">
+        <f>[21]Model!Y$22</f>
+        <v>85.495337030527935</v>
+      </c>
+      <c r="R25" s="15">
+        <f t="shared" ref="R25" si="40">$G25/M25</f>
+        <v>895.19656441718109</v>
+      </c>
+      <c r="S25" s="15">
         <f t="shared" si="33"/>
-        <v>638.7833305926481</v>
-      </c>
-      <c r="T24" s="15">
+        <v>730.68824697764694</v>
+      </c>
+      <c r="T25" s="15">
         <f t="shared" si="34"/>
-        <v>260.13977817222406</v>
-      </c>
-      <c r="U24" s="15">
+        <v>309.01319648650241</v>
+      </c>
+      <c r="U25" s="15">
         <f t="shared" si="35"/>
-        <v>169.76154834084571</v>
-      </c>
-      <c r="V24" s="15">
+        <v>206.11347980020346</v>
+      </c>
+      <c r="V25" s="15">
         <f t="shared" si="36"/>
-        <v>141.34655117268147</v>
-      </c>
-      <c r="W24" s="15">
-        <f>G24/[21]Model!$AF$20</f>
-        <v>99.471473171775258</v>
-      </c>
-      <c r="X24" s="14">
-        <f>[21]Model!$V$5</f>
-        <v>1277.0619999999999</v>
-      </c>
-      <c r="Y24" s="20">
+        <v>170.67251275692055</v>
+      </c>
+      <c r="W25" s="15">
+        <f>G25/[21]Model!$AF$22</f>
+        <v>78.909831938412125</v>
+      </c>
+      <c r="X25" s="14">
+        <f>[21]Model!$V$7</f>
+        <v>1297.6099999999999</v>
+      </c>
+      <c r="Y25" s="20">
         <f t="shared" si="31"/>
-        <v>8.0303321216980876</v>
-      </c>
-      <c r="Z24" s="16">
-        <f>[21]Model!U$26</f>
+        <v>11.245061305014605</v>
+      </c>
+      <c r="Z25" s="16">
+        <f>[21]Model!U$28</f>
         <v>9.5651335454633113E-2</v>
       </c>
-      <c r="AA24" s="16">
-        <f>[21]Model!V$26</f>
-        <v>0.12387749713983975</v>
-      </c>
-      <c r="AB24" s="16">
-        <f>[21]Model!$V$29</f>
-        <v>0.23117585520515044</v>
-      </c>
-      <c r="AC24" s="16">
-        <f>[21]Model!$V$32</f>
-        <v>1.8102410063097749E-2</v>
-      </c>
-      <c r="AD24" s="16">
-        <f>[21]Model!$AI$27</f>
+      <c r="AA25" s="16">
+        <f>[21]Model!V$28</f>
+        <v>0.14196074980198881</v>
+      </c>
+      <c r="AB25" s="16">
+        <f>[21]Model!$V$31</f>
+        <v>0.23128695062460972</v>
+      </c>
+      <c r="AC25" s="16">
+        <f>[21]Model!$V$34</f>
+        <v>2.1587580243678565E-2</v>
+      </c>
+      <c r="AD25" s="16">
+        <f>[21]Model!$AI$29</f>
         <v>0.09</v>
       </c>
-      <c r="AE24" s="16">
-        <f>[21]Model!$AI$33</f>
-        <v>-0.86431327380599154</v>
-      </c>
-      <c r="AF24" s="11" t="str">
-        <f>[21]Model!$AI$34</f>
+      <c r="AE25" s="16">
+        <f>[21]Model!$AI$35</f>
+        <v>-0.87042777033592045</v>
+      </c>
+      <c r="AF25" s="11" t="str">
+        <f>[21]Model!$AI$36</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH24" s="11">
+      <c r="AH25" s="11">
         <v>1994</v>
       </c>
-      <c r="AJ24" s="18">
+      <c r="AJ25" s="18">
         <f>[21]Main!$E$3</f>
-        <v>45904</v>
-      </c>
-      <c r="AK24" s="18">
+        <v>45930</v>
+      </c>
+      <c r="AK25" s="18">
         <f>[21]Main!$G$3</f>
         <v>45960</v>
       </c>
     </row>
-    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
+    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C26" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-    </row>
-    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B26" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="17">
-        <f>[22]Main!$D$3</f>
-        <v>66.63</v>
-      </c>
-      <c r="E26" s="14">
-        <f>[22]Main!$D$5</f>
-        <v>6663</v>
-      </c>
-      <c r="F26" s="14">
-        <f>[22]Main!$D$8</f>
-        <v>-438.4</v>
-      </c>
-      <c r="G26" s="14">
-        <f>[22]Main!$D$9</f>
-        <v>7101.4</v>
-      </c>
-      <c r="K26" s="14">
-        <f>[22]Model!S$39</f>
-        <v>16.199999999999942</v>
-      </c>
-      <c r="L26" s="14">
-        <f>[22]Model!T$39</f>
-        <v>32.30000000000004</v>
-      </c>
-      <c r="M26" s="14">
-        <f>[22]Model!U$39</f>
-        <v>53.500000000000057</v>
-      </c>
-      <c r="N26" s="14">
-        <f>[22]Model!V$39</f>
-        <v>96.823239999999927</v>
-      </c>
-      <c r="O26" s="14">
-        <f>[22]Model!W$39</f>
-        <v>143.50169249999999</v>
-      </c>
-      <c r="P26" s="14">
-        <f>[22]Model!X$39</f>
-        <v>179.7296860125</v>
-      </c>
-      <c r="Q26" s="14">
-        <f>[22]Model!Y$39</f>
-        <v>200.07653520599999</v>
-      </c>
-      <c r="R26" s="15">
-        <f t="shared" ref="R26" si="41">$G26/M26</f>
-        <v>132.73644859813069</v>
-      </c>
-      <c r="S26" s="15">
-        <f t="shared" ref="S26" si="42">$G26/N26</f>
-        <v>73.343961635656939</v>
-      </c>
-      <c r="T26" s="15">
-        <f t="shared" ref="T26:T27" si="43">$G26/O26</f>
-        <v>49.486524348833029</v>
-      </c>
-      <c r="U26" s="15">
-        <f t="shared" ref="U26:U27" si="44">$G26/P26</f>
-        <v>39.51155848292143</v>
-      </c>
-      <c r="V26" s="15">
-        <f t="shared" ref="V26:V27" si="45">$G26/Q26</f>
-        <v>35.493417519892354</v>
-      </c>
-      <c r="W26" s="15">
-        <f>G26/[22]Model!$AF$39</f>
-        <v>22.535987037880979</v>
-      </c>
-      <c r="X26" s="14">
-        <f>[22]Model!$V$24</f>
-        <v>1358.33</v>
-      </c>
-      <c r="Y26" s="20">
-        <f>G26/X26</f>
-        <v>5.2280373694168576</v>
-      </c>
-      <c r="Z26" s="16">
-        <f>[22]Model!U$43</f>
-        <v>0.23230686115613186</v>
-      </c>
-      <c r="AA26" s="16">
-        <f>[22]Model!V$43</f>
-        <v>0.19099517755370443</v>
-      </c>
-      <c r="AB26" s="16">
-        <f>[22]Model!$V$44</f>
-        <v>0.25505171791832615</v>
-      </c>
-      <c r="AC26" s="16">
-        <f>[22]Model!$V$47</f>
-        <v>0.1261351806998299</v>
-      </c>
-      <c r="AD26" s="16">
-        <f>[22]Model!$AI$45</f>
-        <v>0.09</v>
-      </c>
-      <c r="AE26" s="16">
-        <f>[22]Model!$AI$51</f>
-        <v>-0.67267594474014047</v>
-      </c>
-      <c r="AF26" s="11" t="str">
-        <f>[22]Model!$AI$52</f>
-        <v>Heavily overvalued</v>
-      </c>
-      <c r="AH26" s="11">
-        <v>1873</v>
-      </c>
-      <c r="AJ26" s="18">
-        <f>[22]Main!$E$3</f>
-        <v>45903</v>
-      </c>
-      <c r="AK26" s="18">
-        <f>[22]Main!$G$3</f>
-        <v>45974</v>
-      </c>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="24"/>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="24"/>
+      <c r="AB26" s="24"/>
+      <c r="AC26" s="24"/>
     </row>
     <row r="27" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B27" s="19" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="13">
-        <f>[23]Main!$D$3</f>
-        <v>10</v>
+        <v>76</v>
+      </c>
+      <c r="D27" s="17">
+        <f>[22]Main!$D$3</f>
+        <v>66.63</v>
       </c>
       <c r="E27" s="14">
-        <f>[23]Main!$D$5</f>
-        <v>1178</v>
+        <f>[22]Main!$D$5</f>
+        <v>6663</v>
       </c>
       <c r="F27" s="14">
-        <f>[23]Main!$D$8</f>
-        <v>46.100000000000009</v>
+        <f>[22]Main!$D$8</f>
+        <v>-438.4</v>
       </c>
       <c r="G27" s="14">
-        <f>[23]Main!$D$9</f>
-        <v>1131.9000000000001</v>
+        <f>[22]Main!$D$9</f>
+        <v>7101.4</v>
+      </c>
+      <c r="K27" s="14">
+        <f>[22]Model!S$39</f>
+        <v>16.199999999999942</v>
+      </c>
+      <c r="L27" s="14">
+        <f>[22]Model!T$39</f>
+        <v>32.30000000000004</v>
+      </c>
+      <c r="M27" s="14">
+        <f>[22]Model!U$39</f>
+        <v>53.500000000000057</v>
       </c>
       <c r="N27" s="14">
-        <f>[23]Model!O$15</f>
-        <v>-69.325000000000003</v>
+        <f>[22]Model!V$39</f>
+        <v>96.823239999999927</v>
       </c>
       <c r="O27" s="14">
-        <f>[23]Model!P$15</f>
-        <v>-91.1815</v>
+        <f>[22]Model!W$39</f>
+        <v>143.50169249999999</v>
       </c>
       <c r="P27" s="14">
-        <f>[23]Model!Q$15</f>
-        <v>-110.42588000000001</v>
+        <f>[22]Model!X$39</f>
+        <v>179.7296860125</v>
       </c>
       <c r="Q27" s="14">
-        <f>[23]Model!R$15</f>
-        <v>-123.67537759999999</v>
+        <f>[22]Model!Y$39</f>
+        <v>200.07653520599999</v>
+      </c>
+      <c r="R27" s="15">
+        <f t="shared" ref="R27" si="41">$G27/M27</f>
+        <v>132.73644859813069</v>
       </c>
       <c r="S27" s="15">
-        <f t="shared" ref="S27" si="46">$G27/N27</f>
-        <v>-16.327443202307972</v>
+        <f t="shared" ref="S27" si="42">$G27/N27</f>
+        <v>73.343961635656939</v>
       </c>
       <c r="T27" s="15">
-        <f t="shared" si="43"/>
-        <v>-12.413702340935387</v>
+        <f t="shared" ref="T27:T28" si="43">$G27/O27</f>
+        <v>49.486524348833029</v>
       </c>
       <c r="U27" s="15">
-        <f t="shared" si="44"/>
-        <v>-10.2503145096059</v>
+        <f t="shared" ref="U27:U28" si="44">$G27/P27</f>
+        <v>39.51155848292143</v>
       </c>
       <c r="V27" s="15">
-        <f t="shared" si="45"/>
-        <v>-9.1521855195855917</v>
+        <f t="shared" ref="V27:V28" si="45">$G27/Q27</f>
+        <v>35.493417519892354</v>
       </c>
       <c r="W27" s="15">
-        <f>G27/[23]Model!$Y$15</f>
-        <v>7.7512385840070213</v>
+        <f>G27/[22]Model!$AF$39</f>
+        <v>22.535987037880979</v>
       </c>
       <c r="X27" s="14">
-        <f>[23]Model!$O$3</f>
-        <v>12.3</v>
+        <f>[22]Model!$V$24</f>
+        <v>1358.33</v>
       </c>
       <c r="Y27" s="20">
         <f>G27/X27</f>
-        <v>92.024390243902445</v>
+        <v>5.2280373694168576</v>
+      </c>
+      <c r="Z27" s="16">
+        <f>[22]Model!U$43</f>
+        <v>0.23230686115613186</v>
+      </c>
+      <c r="AA27" s="16">
+        <f>[22]Model!V$43</f>
+        <v>0.19099517755370443</v>
       </c>
       <c r="AB27" s="16">
-        <f>[23]Model!$O$20</f>
-        <v>5.08130081300813E-2</v>
+        <f>[22]Model!$V$44</f>
+        <v>0.25505171791832615</v>
       </c>
       <c r="AC27" s="16">
-        <f>[23]Model!$O$24</f>
-        <v>-4.23780487804878</v>
+        <f>[22]Model!$V$47</f>
+        <v>0.1261351806998299</v>
       </c>
       <c r="AD27" s="16">
-        <f>[23]Model!$AB$21</f>
-        <v>0.11</v>
+        <f>[22]Model!$AI$45</f>
+        <v>0.09</v>
       </c>
       <c r="AE27" s="16">
-        <f>[23]Model!$AB$27</f>
-        <v>-0.85432485058235097</v>
+        <f>[22]Model!$AI$51</f>
+        <v>-0.67267594474014047</v>
       </c>
       <c r="AF27" s="11" t="str">
-        <f>[23]Model!$AB$28</f>
+        <f>[22]Model!$AI$52</f>
         <v>Heavily overvalued</v>
+      </c>
+      <c r="AH27" s="11">
+        <v>1873</v>
+      </c>
+      <c r="AJ27" s="18">
+        <f>[22]Main!$E$3</f>
+        <v>45903</v>
+      </c>
+      <c r="AK27" s="18">
+        <f>[22]Main!$G$3</f>
+        <v>45974</v>
       </c>
     </row>
     <row r="28" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B28" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="13">
+        <f>[23]Main!$D$3</f>
+        <v>10</v>
+      </c>
+      <c r="E28" s="14">
+        <f>[23]Main!$D$5</f>
+        <v>1178</v>
+      </c>
+      <c r="F28" s="14">
+        <f>[23]Main!$D$8</f>
+        <v>46.100000000000009</v>
+      </c>
+      <c r="G28" s="14">
+        <f>[23]Main!$D$9</f>
+        <v>1131.9000000000001</v>
+      </c>
+      <c r="N28" s="14">
+        <f>[23]Model!O$15</f>
+        <v>-69.325000000000003</v>
+      </c>
+      <c r="O28" s="14">
+        <f>[23]Model!P$15</f>
+        <v>-91.1815</v>
+      </c>
+      <c r="P28" s="14">
+        <f>[23]Model!Q$15</f>
+        <v>-110.42588000000001</v>
+      </c>
+      <c r="Q28" s="14">
+        <f>[23]Model!R$15</f>
+        <v>-123.67537759999999</v>
+      </c>
+      <c r="S28" s="15">
+        <f t="shared" ref="S28" si="46">$G28/N28</f>
+        <v>-16.327443202307972</v>
+      </c>
+      <c r="T28" s="15">
+        <f t="shared" si="43"/>
+        <v>-12.413702340935387</v>
+      </c>
+      <c r="U28" s="15">
+        <f t="shared" si="44"/>
+        <v>-10.2503145096059</v>
+      </c>
+      <c r="V28" s="15">
+        <f t="shared" si="45"/>
+        <v>-9.1521855195855917</v>
+      </c>
+      <c r="W28" s="15">
+        <f>G28/[23]Model!$Y$15</f>
+        <v>7.7512385840070213</v>
+      </c>
+      <c r="X28" s="14">
+        <f>[23]Model!$O$3</f>
+        <v>12.3</v>
+      </c>
+      <c r="Y28" s="20">
+        <f>G28/X28</f>
+        <v>92.024390243902445</v>
+      </c>
+      <c r="AB28" s="16">
+        <f>[23]Model!$O$20</f>
+        <v>5.08130081300813E-2</v>
+      </c>
+      <c r="AC28" s="16">
+        <f>[23]Model!$O$24</f>
+        <v>-4.23780487804878</v>
+      </c>
+      <c r="AD28" s="16">
+        <f>[23]Model!$AB$21</f>
+        <v>0.11</v>
+      </c>
+      <c r="AE28" s="16">
+        <f>[23]Model!$AB$27</f>
+        <v>-0.85432485058235097</v>
+      </c>
+      <c r="AF28" s="11" t="str">
+        <f>[23]Model!$AB$28</f>
+        <v>Heavily overvalued</v>
+      </c>
+    </row>
+    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B29" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D29" s="13">
         <f>[24]Main!$D$3</f>
         <v>9.0399999999999991</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E29" s="14">
         <f>[24]Main!$D$5</f>
         <v>274.81599999999997</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F29" s="14">
         <f>[24]Main!$D$8</f>
         <v>5</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G29" s="14">
         <f>[24]Main!$D$9</f>
         <v>269.81599999999997</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L29" s="14">
         <f>[24]Model!$P$20</f>
         <v>-1.4</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M29" s="14">
         <f>[24]Model!Q$20</f>
         <v>-32</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N29" s="14">
         <f>[24]Model!R$20</f>
         <v>-27.428000000000001</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O29" s="14">
         <f>[24]Model!S$20</f>
         <v>-36.489999999999995</v>
       </c>
-      <c r="P28" s="14">
+      <c r="P29" s="14">
         <f>[24]Model!T$20</f>
         <v>-44.738199999999992</v>
       </c>
-      <c r="Q28" s="14">
+      <c r="Q29" s="14">
         <f>[24]Model!U$20</f>
         <v>-36.238919999999993</v>
       </c>
-      <c r="W28" s="15">
-        <f>G28/[24]Model!$AB$20</f>
+      <c r="W29" s="15">
+        <f>G29/[24]Model!$AB$20</f>
         <v>3.9629103845325151</v>
       </c>
-      <c r="X28" s="23">
+      <c r="X29" s="23">
         <f>[24]Model!$Q$3</f>
         <v>5.6</v>
       </c>
-      <c r="Y28" s="20">
-        <f>G28/X28</f>
+      <c r="Y29" s="20">
+        <f>G29/X29</f>
         <v>48.181428571428569</v>
       </c>
-      <c r="AB28" s="25">
+      <c r="AB29" s="25">
         <f>[24]Model!$Q$26</f>
         <v>0.28571428571428564</v>
       </c>
-      <c r="AC28" s="25">
+      <c r="AC29" s="25">
         <f>[24]Model!$Q$30</f>
         <v>-3.0535714285714288</v>
       </c>
-      <c r="AD28" s="16">
+      <c r="AD29" s="16">
         <f>[24]Model!$AF$27</f>
         <v>0.12</v>
       </c>
-      <c r="AE28" s="16">
+      <c r="AE29" s="16">
         <f>[24]Model!$AF$33</f>
         <v>-0.78010157110479306</v>
       </c>
-      <c r="AF28" s="11" t="str">
+      <c r="AF29" s="11" t="str">
         <f>[24]Model!$AF$34</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH28" s="11">
+      <c r="AH29" s="11">
         <v>2019</v>
       </c>
-      <c r="AJ28" s="18">
+      <c r="AJ29" s="18">
         <f>[24]Main!$E$3</f>
         <v>45903</v>
       </c>
-      <c r="AK28" s="18">
+      <c r="AK29" s="18">
         <f>[24]Main!$G$3</f>
         <v>45974</v>
       </c>
     </row>
-    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
-      <c r="B29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="20"/>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
-      <c r="AE29" s="16"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-    </row>
     <row r="30" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="B30" s="12"/>
       <c r="D30" s="13"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -6846,13 +6875,34 @@
       <c r="AJ30" s="18"/>
       <c r="AK30" s="18"/>
     </row>
+    <row r="31" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="20"/>
+      <c r="AB31" s="16"/>
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AJ31" s="18"/>
+      <c r="AK31" s="18"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{9EBE5D6A-1C1D-4975-961D-8BDF60D469F0}"/>
     <hyperlink ref="B12" r:id="rId2" xr:uid="{1C2D10B8-C1F0-4011-9894-9CA25208770D}"/>
     <hyperlink ref="B8" r:id="rId3" xr:uid="{959B55A2-9FD4-4C66-8ED7-2CA35BBDDBEB}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{585D8E65-116D-4674-B4B3-00498D6A7848}"/>
-    <hyperlink ref="B18" r:id="rId5" xr:uid="{CFD2CC9C-5B8B-4286-BE47-40E920DADED7}"/>
+    <hyperlink ref="B29" r:id="rId4" xr:uid="{585D8E65-116D-4674-B4B3-00498D6A7848}"/>
+    <hyperlink ref="B19" r:id="rId5" xr:uid="{CFD2CC9C-5B8B-4286-BE47-40E920DADED7}"/>
     <hyperlink ref="B5" r:id="rId6" xr:uid="{A17201AA-5063-4DAA-B4C5-DF50CA314C77}"/>
     <hyperlink ref="B6" r:id="rId7" xr:uid="{66D11DBA-CC4F-47C4-B72D-A167C22CF998}"/>
     <hyperlink ref="B11" r:id="rId8" xr:uid="{68839818-3059-4F3D-A939-24E347A3D924}"/>
@@ -6862,16 +6912,16 @@
     <hyperlink ref="B9" r:id="rId12" xr:uid="{A83CC09C-04CF-4224-A8E1-DC20AD3A36C8}"/>
     <hyperlink ref="B14" r:id="rId13" xr:uid="{4D3F764E-9CCB-403D-8E1B-4BE47BABAA33}"/>
     <hyperlink ref="B13" r:id="rId14" xr:uid="{93CF4EC5-904A-41E3-804E-56C12BA230AB}"/>
-    <hyperlink ref="B21" r:id="rId15" display="txt" xr:uid="{AB07EC75-74EE-4F00-A39A-32F20CF1BEB8}"/>
+    <hyperlink ref="B22" r:id="rId15" display="txt" xr:uid="{AB07EC75-74EE-4F00-A39A-32F20CF1BEB8}"/>
     <hyperlink ref="B16" r:id="rId16" xr:uid="{9426D752-2EF5-4AFB-99DA-A8A7D85B06E3}"/>
-    <hyperlink ref="B17" r:id="rId17" xr:uid="{EB265B06-930A-4273-8DCC-B8FC215B734E}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{CC2544BA-50C9-47A6-B396-2DAF4864B854}"/>
-    <hyperlink ref="B26" r:id="rId19" xr:uid="{356138DD-BE1A-4731-B7CC-280B73272B33}"/>
-    <hyperlink ref="B23" r:id="rId20" xr:uid="{84017ED8-7373-4D92-B4EF-D5CF532C2353}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{88DB7B22-BB4A-404B-95A6-1AA9663BF5FE}"/>
-    <hyperlink ref="B27" r:id="rId22" xr:uid="{C624A8B5-778E-4C36-8210-19EE1248D3F5}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{BAFD510F-4A1A-4765-B090-822E93B04792}"/>
-    <hyperlink ref="B20" r:id="rId24" xr:uid="{A503C2A2-F761-40EE-A283-D47A823C22F9}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{EB265B06-930A-4273-8DCC-B8FC215B734E}"/>
+    <hyperlink ref="B20" r:id="rId18" xr:uid="{CC2544BA-50C9-47A6-B396-2DAF4864B854}"/>
+    <hyperlink ref="B27" r:id="rId19" xr:uid="{356138DD-BE1A-4731-B7CC-280B73272B33}"/>
+    <hyperlink ref="B24" r:id="rId20" xr:uid="{84017ED8-7373-4D92-B4EF-D5CF532C2353}"/>
+    <hyperlink ref="B23" r:id="rId21" xr:uid="{88DB7B22-BB4A-404B-95A6-1AA9663BF5FE}"/>
+    <hyperlink ref="B28" r:id="rId22" xr:uid="{C624A8B5-778E-4C36-8210-19EE1248D3F5}"/>
+    <hyperlink ref="B25" r:id="rId23" xr:uid="{BAFD510F-4A1A-4765-B090-822E93B04792}"/>
+    <hyperlink ref="B21" r:id="rId24" xr:uid="{A503C2A2-F761-40EE-A283-D47A823C22F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>

--- a/Financial Analysis/Models (Defence).xlsx
+++ b/Financial Analysis/Models (Defence).xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E722360A-2C0B-4F1E-8593-26E9EEF83AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBC367E-ACFD-40E5-91FC-0B39CF49BCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="FY2026 DoD Budget Materials" sheetId="2" r:id="rId2"/>
+    <sheet name="DoD Products" sheetId="3" r:id="rId3"/>
+    <sheet name="Future Products" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
@@ -40,6 +40,9 @@
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
+    <externalReference r:id="rId28"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,8 +53,233 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="AC2" authorId="0" shapeId="0" xr:uid="{FA31A116-56BA-42D9-A8CD-62CA8EBD51AA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+need to think about this</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{A86F8EF5-FB5D-4BC2-B1EC-FDA77AF60FD8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+in future, compare this and budgets etc. to other largest defence spending countries</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{F47928AD-C7E0-418C-B2EA-DCCA6CA2D98F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+In addition to discretionary resources, the Administration assumes at least $150 billion for defense will be enacted in a mandatory
+reconciliation bill later this fiscal year with approximately $113.3 billion spent in FY 2026 for DoD activities</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{9ACA2389-0B8A-46E2-8B15-E57F05938349}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+2 FY 2024 includes supplemental funding for Ukraine ($48.4 billion), Israel ($13 billion), and Indo-Pacific/U.S. Submarine Industrial
+Base (SIB) ($5.9 billion). FY 2025 includes supplemental funding for Virginia-class cost increases and SIB ($5.7 billion), National
+Security System risk reduction ($913 million), and Natural Disasters ($5.2 billion).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D56" authorId="0" shapeId="0" xr:uid="{4CD0B0BD-5AFB-431E-A320-0433DC08277D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+find this</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0" xr:uid="{AC4923BF-4E60-49D5-AAA7-D79F636CF441}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+what does this entail</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{0F089520-C5A9-49EF-99E7-4D161BE84A9A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+check for double-counting</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R57" authorId="0" shapeId="0" xr:uid="{23B9F9C8-7634-49C1-9E56-041E0381DBBE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+compare current budget and unit cost to amount still needed?</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="361">
   <si>
     <t>Company</t>
   </si>
@@ -315,21 +543,841 @@
   </si>
   <si>
     <t>ADUI US</t>
+  </si>
+  <si>
+    <t>2025 EV/B</t>
+  </si>
+  <si>
+    <t>2025 B/EV</t>
+  </si>
+  <si>
+    <t>IS/BS Var</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>2025 NM%</t>
+  </si>
+  <si>
+    <t>SAAB</t>
+  </si>
+  <si>
+    <t>2025 BL/R</t>
+  </si>
+  <si>
+    <t>3 Way Var</t>
+  </si>
+  <si>
+    <t>The estimated cost of this report or study for the Department of Defense is approximately $42,000 for the 2025 Fiscal Year. This includes $11,000 in expenses and $31,000 in DoD labor.</t>
+  </si>
+  <si>
+    <t>U.S. Threats:</t>
+  </si>
+  <si>
+    <t>Unsecured borders</t>
+  </si>
+  <si>
+    <t>Minor threats e.g. Russia, NK, Iran, terrorist orgs</t>
+  </si>
+  <si>
+    <t>Increasingly capable air and missile threats (ergo Golden Dome)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China military buildup (shipbuilding, space, F-47) </t>
+  </si>
+  <si>
+    <t>Discretionary</t>
+  </si>
+  <si>
+    <t>Mandatory</t>
+  </si>
+  <si>
+    <t>Supplemental</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>DoD Budget ($B)</t>
+  </si>
+  <si>
+    <t>Budgeted</t>
+  </si>
+  <si>
+    <t>including</t>
+  </si>
+  <si>
+    <t>Border control</t>
+  </si>
+  <si>
+    <t>Golden Dome</t>
+  </si>
+  <si>
+    <t>Nuclear triad</t>
+  </si>
+  <si>
+    <t>Nuclear triad - the entire military infrastructure that supports, delivers, and controls nuclear warheads, across land, sea and air.</t>
+  </si>
+  <si>
+    <t>Contractors</t>
+  </si>
+  <si>
+    <t>Columbia-class ballistic missile submarine</t>
+  </si>
+  <si>
+    <t>B-21</t>
+  </si>
+  <si>
+    <t>Sentinel/Ground Based Launched Cruise Missile (GBSD)</t>
+  </si>
+  <si>
+    <t>Nuclear Sea Launched Cruise Missile (SLCM-N)</t>
+  </si>
+  <si>
+    <t>Long Range Stand-Off Weapon (LRSO)</t>
+  </si>
+  <si>
+    <t>unaccounted</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>100% operational control of the Southern Border</t>
+  </si>
+  <si>
+    <t>Next-gen missile defence system to protect U.S. from nuclear, hypersonic and conventional weapons</t>
+  </si>
+  <si>
+    <t>Combat credible forces and capabilities in Western Pacific</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>Taiwan Security Cooperation Initiative (TSCI)</t>
+  </si>
+  <si>
+    <t>Replace U.S. stocks of equipment and services for Taiwan</t>
+  </si>
+  <si>
+    <t>Indo-Pacific Command-led training, and Modular Mission Environment (MME)</t>
+  </si>
+  <si>
+    <t>21 F-15 EXs, 47 F-35s, [number] F-47s, B-21, mobility aircraft, KC-46A tankers, unmanned aircraft systems, others?</t>
+  </si>
+  <si>
+    <t>Air power</t>
+  </si>
+  <si>
+    <t>Sea power</t>
+  </si>
+  <si>
+    <t>19 battle force fleet (?) ships, including Columbia-class ballistic missile submarine (are they double-counting?), two Virginia-class attack submarines; two DDG-51 Arleigh Burke-class destroyers; one America-class amphibious assault ship; one LPD-17 San Antonio-class amphibious transport dock; nine McClung-class medium landing ships; two T-AO replenishment oilers; and one T-AGOS 25-class ocean surveillance ship</t>
+  </si>
+  <si>
+    <t>Land power</t>
+  </si>
+  <si>
+    <t>Amphibious Combat Vehicle (ACV), M1E3 Abrams development, XM30 MICV development, others</t>
+  </si>
+  <si>
+    <t>Long-Range</t>
+  </si>
+  <si>
+    <t>ARRW, HACM, LRHW, CPS, SM-6 IB, others?</t>
+  </si>
+  <si>
+    <t>JASSM-ER, LRASM, Joint Strike Missile, Tomahawk, SM-6 IA, others?</t>
+  </si>
+  <si>
+    <t>Space</t>
+  </si>
+  <si>
+    <t>Vital space capabilities, resilient architectures, enhanced space command and control</t>
+  </si>
+  <si>
+    <t>Cyberspace</t>
+  </si>
+  <si>
+    <t>Defend and disrupt the efforts of advanced and persistent cyber adversaries, Zero Trust cybersecurity architecture (?), increase defence of U.S. critical infrastructure and partners against cyber attacks</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>"Science &amp; Technology (S&amp;T)"</t>
+  </si>
+  <si>
+    <t>Autonomous and remotely operated systems across air, land and above and below the sea</t>
+  </si>
+  <si>
+    <t>Strategic Capabilities Office (SCO)</t>
+  </si>
+  <si>
+    <t>Supply of defence</t>
+  </si>
+  <si>
+    <t>Submarine Industrial Base (SIB)</t>
+  </si>
+  <si>
+    <t>Industrial Base Analysis and Sustainment (IBAS) and Defence Protection Act Title III to mitigate cross-cutting supply chain risks in DIB including strategic materials, critical minerals etc.</t>
+  </si>
+  <si>
+    <t>Office of Strategic Capital</t>
+  </si>
+  <si>
+    <t>Soldiers</t>
+  </si>
+  <si>
+    <t>QoL improvements for soldiers</t>
+  </si>
+  <si>
+    <t>3.8% increase on FY 2025</t>
+  </si>
+  <si>
+    <t>Military pay raise</t>
+  </si>
+  <si>
+    <t>Defense Health Program</t>
+  </si>
+  <si>
+    <t>Defense Innovation Unit (DIU) for rapidly prototyping and fielding dual-use technologies</t>
+  </si>
+  <si>
+    <t>Defense Industrial Base (DIB) investments</t>
+  </si>
+  <si>
+    <t>Medical facility improvements, clinical care, staffing increases at casualty locations</t>
+  </si>
+  <si>
+    <t>Support programs for soldiers' families</t>
+  </si>
+  <si>
+    <t>Ops and maintenance</t>
+  </si>
+  <si>
+    <t>Readiness operations, training, and maintenance is a historic high and a 7.8% increase over FY 2025, with increases across each of the military departments</t>
+  </si>
+  <si>
+    <t>Facilities</t>
+  </si>
+  <si>
+    <t>Military construction and family housing programs</t>
+  </si>
+  <si>
+    <t>Facilities sustainment, restoration and modernization (FSRM)</t>
+  </si>
+  <si>
+    <t>Moral support</t>
+  </si>
+  <si>
+    <t>Anti-vaxxers</t>
+  </si>
+  <si>
+    <t>Suicide prevention programs</t>
+  </si>
+  <si>
+    <t>Assault prevention programs</t>
+  </si>
+  <si>
+    <t>Definitions and others:</t>
+  </si>
+  <si>
+    <t>Golden Dome - shield and defence citizens and critical infrastructure against ballistic and hypersonic weapons, advanced cruise missiles, and other next-gen aerial attacks (?); project accountable to Deputy Secretary of Defense (track him?)</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Aircraft</t>
+  </si>
+  <si>
+    <t>F-47</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Units produced</t>
+  </si>
+  <si>
+    <t>Subcontractors</t>
+  </si>
+  <si>
+    <t>J-19</t>
+  </si>
+  <si>
+    <t>Design year</t>
+  </si>
+  <si>
+    <t>Anti-ballistic</t>
+  </si>
+  <si>
+    <t>Decommissioned year</t>
+  </si>
+  <si>
+    <t>Commissioned (planned) year</t>
+  </si>
+  <si>
+    <t>Anti-hypersonic (???)</t>
+  </si>
+  <si>
+    <t>Anti-advanced cruise missiles</t>
+  </si>
+  <si>
+    <t>Anti next-gen aerial attacks</t>
+  </si>
+  <si>
+    <t>Space-based sensing, warning</t>
+  </si>
+  <si>
+    <t>Interceptors</t>
+  </si>
+  <si>
+    <t>C&amp;C</t>
+  </si>
+  <si>
+    <t>Budget used</t>
+  </si>
+  <si>
+    <t>Missile Defeat and Defense (MDD)</t>
+  </si>
+  <si>
+    <t>includes</t>
+  </si>
+  <si>
+    <t>regional and strategic missile defence capabilities outside of MDA</t>
+  </si>
+  <si>
+    <t>advanced technology missile defeat efforts and other left-of-launch activities</t>
+  </si>
+  <si>
+    <t>Next Generation Interceptor (NGI) testing?</t>
+  </si>
+  <si>
+    <t>Ground-Based Midcourse Defense (GMD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ground-Based Interceptors (GBI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Missile Defense Agency (MDA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Other missile defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  accounted for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  unaccounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> accounted for</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> unaccounted</t>
+  </si>
+  <si>
+    <t>Desc/comments</t>
+  </si>
+  <si>
+    <t>Long-Range Discrimination Radar (LRDR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Next Generation Interceptors (NGI)</t>
+  </si>
+  <si>
+    <t>Sea-Based Weapons System</t>
+  </si>
+  <si>
+    <t>Aegis Ballistic Missile Defense (BMD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Standard Missile-3 (SM-3) Block IIA</t>
+  </si>
+  <si>
+    <t>designed to defeat midcourse and ICBM threats</t>
+  </si>
+  <si>
+    <t>Systems against SRBM, MRBM, IRBM</t>
+  </si>
+  <si>
+    <t>Units ordered</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Anti-air/missile defence?</t>
+  </si>
+  <si>
+    <t>DoD 44</t>
+  </si>
+  <si>
+    <t>DoD 20</t>
+  </si>
+  <si>
+    <t>DoD 64</t>
+  </si>
+  <si>
+    <t>identify, test and develop new hypersonic tech, analyse and upgrade capabilties of defence against hypersonic threats</t>
+  </si>
+  <si>
+    <t>Hypersonic defence budget</t>
+  </si>
+  <si>
+    <t>Glide Phase Intercept (GPI)</t>
+  </si>
+  <si>
+    <t>Glide Phase Intercept (GLI)</t>
+  </si>
+  <si>
+    <t>hypersonic defense prototype development acceleration, supporting Golden Dome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  on Aegis BMD ships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  on Aegis ashore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  integration of missiles into Aegis BMD Weapon Systems</t>
+  </si>
+  <si>
+    <t>Terminal High Altitude Area Defense (THAAD)</t>
+  </si>
+  <si>
+    <t>Israeli Cooperative BMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Iron Dome</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> David's Sling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Arrow-3</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Other non-MDA missile defences</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Integrated air and missile defence capabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PAC-3/MSE missiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  M-SHORAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LTAMDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  IFPC Increment 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navy missile defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Aegis BMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Others (p. 2-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Air Force and Space Force</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Wide Area Surveillance in National Capital region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Long-range radar improvements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Next Generation Overhead Persistent Infrared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Resilient Missile Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Missile Tracking Low Earth Orbit and Medium Earth Orbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Upgraded Early Warning Radars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Upgrade of legacy early warning systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Space Development Agency (SDA) missile defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Hypersonic missile tracking layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Data transport layer</t>
+  </si>
+  <si>
+    <t>to enhance several mission areas, including missile defence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Hypersonic and Ballistic Tracking Space Sensor (HBTSS)</t>
+  </si>
+  <si>
+    <t>Left-of-launch - defeat missile threats before they are launched</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Left-of-launch capabilities</t>
+  </si>
+  <si>
+    <t>Counter-unmanned systems (C-UXS)</t>
+  </si>
+  <si>
+    <t>2024 Budget</t>
+  </si>
+  <si>
+    <t>2025 Budget</t>
+  </si>
+  <si>
+    <t>2026 Budget</t>
+  </si>
+  <si>
+    <t>Biodefence</t>
+  </si>
+  <si>
+    <t>Sentinel ICBM</t>
+  </si>
+  <si>
+    <t>Long Range Stand-Off Weapon</t>
+  </si>
+  <si>
+    <t>Columbia-Class Submarines</t>
+  </si>
+  <si>
+    <t>Trident II Missile Mods</t>
+  </si>
+  <si>
+    <t>Nuclear-Armed, Sea-Launched Cruise Missile</t>
+  </si>
+  <si>
+    <t>F-35A</t>
+  </si>
+  <si>
+    <t>E-4C (SAOC)</t>
+  </si>
+  <si>
+    <t>Evolved Strategic Satellite Communication</t>
+  </si>
+  <si>
+    <t>E-130J (TACAMO)</t>
+  </si>
+  <si>
+    <t>Next Gen OPIR (GEO/Polar/Ground)</t>
+  </si>
+  <si>
+    <t>Resilient Missile Warning and Tracking (LEO/MEO/Ground)</t>
+  </si>
+  <si>
+    <t>modernise and replace Minuteman III ICBM of 400 operationally deployed and 450 launch facilities</t>
+  </si>
+  <si>
+    <t>replace bomber-delivered AGM-86B ALCM</t>
+  </si>
+  <si>
+    <t>replace Ohio-class SSBNs</t>
+  </si>
+  <si>
+    <t>low-rate initial production began in FY2024</t>
+  </si>
+  <si>
+    <t>replacing F-15E and other fourth-gen</t>
+  </si>
+  <si>
+    <t>replacing E-4B, militarised version of Boeing 747-8i</t>
+  </si>
+  <si>
+    <t>replacing E-6B</t>
+  </si>
+  <si>
+    <t>SSBN</t>
+  </si>
+  <si>
+    <t>SLCM-N</t>
+  </si>
+  <si>
+    <t>F-35A/B/C</t>
+  </si>
+  <si>
+    <t>F-15EX</t>
+  </si>
+  <si>
+    <t>KC-46A</t>
+  </si>
+  <si>
+    <t>F/A-18E/F</t>
+  </si>
+  <si>
+    <t>CH-53K</t>
+  </si>
+  <si>
+    <t>E-2D</t>
+  </si>
+  <si>
+    <t>AH-64E</t>
+  </si>
+  <si>
+    <t>UH-60</t>
+  </si>
+  <si>
+    <t>V-22</t>
+  </si>
+  <si>
+    <t>MV-75</t>
+  </si>
+  <si>
+    <t>MQ-4C</t>
+  </si>
+  <si>
+    <t>MQ-25A</t>
+  </si>
+  <si>
+    <t>MQ-9</t>
+  </si>
+  <si>
+    <t>E-7A</t>
+  </si>
+  <si>
+    <t>OA-1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint Strike Fighter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eagle Il </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Generation Air Dominance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanker </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super Hornet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">King Stallion Helicopter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Hawkeye (AHE) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apache Helicopter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black Hawk Helicopter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osprey </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Future Long-Range Assault Aircraft (FLRAA) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triton Unmanned Aerial Vehicle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stingray Unmanned Aerial Vehicle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaper </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedgetail </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyraider Il </t>
+  </si>
+  <si>
+    <t>2026 units</t>
+  </si>
+  <si>
+    <t>2025 units</t>
+  </si>
+  <si>
+    <t>Trident II</t>
+  </si>
+  <si>
+    <t>LRSO</t>
+  </si>
+  <si>
+    <t>LGM-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raider </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia-Class Submarine3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear-Armed Sea Launched Cruise Missile </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trident Il Missile Mods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long Range Standoff Weapon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentinel Intercontinental Ballistic Missile </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDG 51 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARLEIGH BURKE Class Destroyer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSTELLATION Class Frigate (FFG 62) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFG 62 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-AGOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMERICA Class Amphibious Assault </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOHN LEWIS Class Fleet Replenishment Oiler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxiliary General Ocean Surveillance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unmanned Surface Vessels (Medium &amp; Large) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium Landing Ship </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSN 774 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CVN 79/80/81 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPD Flight Il </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virginia-class Submarine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 FORD Class Aircraft Carrier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN ANTONIO Class Amphibious Transport </t>
+  </si>
+  <si>
+    <t>Launch Enterprise</t>
+  </si>
+  <si>
+    <t>PNT</t>
+  </si>
+  <si>
+    <t>MW/MT</t>
+  </si>
+  <si>
+    <t>SATCOM</t>
+  </si>
+  <si>
+    <t>Position, Navigation and Timing</t>
+  </si>
+  <si>
+    <t>Space-Based Missile Warning Systems</t>
+  </si>
+  <si>
+    <t>Satellite Communication</t>
+  </si>
+  <si>
+    <t>T-AO</t>
+  </si>
+  <si>
+    <t>Ships (major programs)</t>
+  </si>
+  <si>
+    <t>Space (major programs)</t>
+  </si>
+  <si>
+    <t>Aircraft (major programs)</t>
+  </si>
+  <si>
+    <t>Missile defence/nuclear (major programs)</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>Airforce</t>
+  </si>
+  <si>
+    <t>National Guard</t>
+  </si>
+  <si>
+    <t>Defense-Wide</t>
+  </si>
+  <si>
+    <t>add confidence level later?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="165" formatCode="0\x"/>
     <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="[$€-2]\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
     <numFmt numFmtId="169" formatCode="&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,8 +1442,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,8 +1475,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -432,12 +1505,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -507,12 +1691,402 @@
     <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </top>
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </left>
+        <right style="thin">
+          <color theme="2" tint="-0.749992370372631"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -540,10 +2114,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>157.52000000000001</v>
+            <v>166.58</v>
           </cell>
           <cell r="E3">
-            <v>45906</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45958</v>
@@ -551,7 +2125,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>210840.52000000002</v>
+            <v>222967.33000000002</v>
           </cell>
         </row>
         <row r="8">
@@ -561,7 +2135,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>248036.52000000002</v>
+            <v>260163.33000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -631,12 +2205,27 @@
         </row>
         <row r="32">
           <cell r="AO32">
-            <v>-0.47755291681370626</v>
+            <v>-0.50596791605531888</v>
           </cell>
         </row>
         <row r="33">
           <cell r="AO33" t="str">
-            <v>Overvalued</v>
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AA34">
+            <v>7.5658975369286591E-2</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="P39">
+            <v>1.556568664405076</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="P40">
+            <v>-0.35756126737768923</v>
           </cell>
         </row>
       </sheetData>
@@ -660,10 +2249,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>10.7</v>
+            <v>11.685</v>
           </cell>
           <cell r="E3">
-            <v>45898</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>46079</v>
@@ -671,7 +2260,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>90201</v>
+            <v>98504.55</v>
           </cell>
         </row>
         <row r="8">
@@ -681,14 +2270,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>87822</v>
+            <v>96125.55</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="Q3">
-            <v>18909</v>
+          <cell r="R3">
+            <v>21178.080000000002</v>
           </cell>
         </row>
         <row r="16">
@@ -711,32 +2300,32 @@
             <v>1971</v>
           </cell>
           <cell r="R16">
-            <v>1792.7340799999997</v>
+            <v>1904.7799599999998</v>
           </cell>
           <cell r="S16">
-            <v>2039.0654464000004</v>
+            <v>2166.5070368000002</v>
           </cell>
           <cell r="T16">
-            <v>2250.0783875840002</v>
+            <v>2390.7082868080001</v>
           </cell>
           <cell r="U16">
-            <v>2444.7265855552005</v>
+            <v>2597.5219971524007</v>
           </cell>
           <cell r="AB16">
-            <v>3492.9910972745047</v>
+            <v>3711.3030408541613</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="P20">
-            <v>0.21937869822485201</v>
-          </cell>
           <cell r="Q20">
             <v>0.14697318937280124</v>
           </cell>
+          <cell r="R20">
+            <v>0.12000000000000011</v>
+          </cell>
         </row>
         <row r="21">
-          <cell r="Q21">
-            <v>0.22322703474535935</v>
+          <cell r="R21">
+            <v>0.21999999999999997</v>
           </cell>
         </row>
         <row r="22">
@@ -745,18 +2334,33 @@
           </cell>
         </row>
         <row r="24">
-          <cell r="Q24">
-            <v>0.12459675286900418</v>
+          <cell r="R24">
+            <v>0.12645705370836258</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="R26">
+            <v>8.994110703142115E-2</v>
           </cell>
         </row>
         <row r="28">
           <cell r="AE28">
-            <v>-0.53007610364432378</v>
+            <v>-0.54430385996253983</v>
           </cell>
         </row>
         <row r="29">
           <cell r="AE29" t="str">
-            <v>Overvalued</v>
+            <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="I32">
+            <v>2.5336201897733264</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="I33">
+            <v>-0.60530784999409626</v>
           </cell>
         </row>
       </sheetData>
@@ -779,10 +2383,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>19.254999999999999</v>
+            <v>20.55</v>
           </cell>
           <cell r="E3">
-            <v>45868</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>46072</v>
@@ -790,7 +2394,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>57765</v>
+            <v>61650</v>
           </cell>
         </row>
         <row r="8">
@@ -800,74 +2404,94 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>62672</v>
+            <v>66557</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="13">
-          <cell r="Q13">
-            <v>26312</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="N32">
+        <row r="10">
+          <cell r="I10">
+            <v>75400</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="R22">
+            <v>28248.11</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="N41">
             <v>1758</v>
           </cell>
-          <cell r="O32">
+          <cell r="O41">
             <v>1591</v>
           </cell>
-          <cell r="P32">
+          <cell r="P41">
             <v>1857</v>
           </cell>
-          <cell r="Q32">
+          <cell r="Q41">
             <v>1956</v>
           </cell>
-          <cell r="R32">
+          <cell r="R41">
             <v>2983.0295450000012</v>
           </cell>
-          <cell r="S32">
+          <cell r="S41">
             <v>3274.0576822999979</v>
           </cell>
-          <cell r="T32">
+          <cell r="T41">
             <v>3558.6704355280026</v>
           </cell>
-          <cell r="U32">
+          <cell r="U41">
             <v>3774.8694653950824</v>
           </cell>
-          <cell r="AB32">
+          <cell r="AB41">
             <v>4907.2226055251313</v>
           </cell>
         </row>
-        <row r="39">
-          <cell r="AE39">
+        <row r="48">
+          <cell r="AE48">
             <v>7.0000000000000007E-2</v>
           </cell>
         </row>
-        <row r="41">
-          <cell r="P41">
-            <v>8.5614827359111967E-2</v>
-          </cell>
-          <cell r="Q41">
+        <row r="50">
+          <cell r="Q50">
             <v>0.14013346043851294</v>
           </cell>
-        </row>
-        <row r="42">
-          <cell r="Q42">
-            <v>0.65472027972027969</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="Q45">
-            <v>8.3840072970507759E-2</v>
-          </cell>
-          <cell r="AE45">
-            <v>-7.0527347483917202E-2</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AE46" t="str">
-            <v>Fairly valued</v>
+          <cell r="R50">
+            <v>7.3582775919732502E-2</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="R51">
+            <v>0.65</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="R54">
+            <v>0.12268047313607891</v>
+          </cell>
+          <cell r="AE54">
+            <v>-0.12909995502690153</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="AE55" t="str">
+            <v>Slightly overvalued</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="R56">
+            <v>0.10560103118403324</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="I61">
+            <v>1.8487542012721869</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="I62">
+            <v>-0.45909521162312006</v>
           </cell>
         </row>
       </sheetData>
@@ -890,10 +2514,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>277.22000000000003</v>
+            <v>297.39</v>
           </cell>
           <cell r="E3">
-            <v>45898</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45953</v>
@@ -901,7 +2525,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>51867.862000000001</v>
+            <v>55641.668999999994</v>
           </cell>
         </row>
         <row r="8">
@@ -911,7 +2535,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>63487.862000000001</v>
+            <v>67261.668999999994</v>
           </cell>
         </row>
       </sheetData>
@@ -976,12 +2600,22 @@
         </row>
         <row r="30">
           <cell r="AL30">
-            <v>-0.5363754386448315</v>
+            <v>-0.56782003127583369</v>
           </cell>
         </row>
         <row r="31">
           <cell r="AL31" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="P36">
+            <v>1.6309813045586807</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="P37">
+            <v>-0.38687218718881322</v>
           </cell>
         </row>
       </sheetData>
@@ -1004,18 +2638,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>235.1</v>
+            <v>271</v>
           </cell>
           <cell r="E3">
-            <v>45868</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
-            <v>46079</v>
+            <v>45953</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>48289.54</v>
+            <v>55663.4</v>
           </cell>
         </row>
         <row r="8">
@@ -1025,82 +2659,92 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>49697.64</v>
+            <v>57071.5</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="P3">
+        <row r="5">
+          <cell r="P5">
             <v>20576.599999999999</v>
           </cell>
         </row>
-        <row r="22">
-          <cell r="K22">
+        <row r="24">
+          <cell r="K24">
             <v>1146.4000000000005</v>
           </cell>
-          <cell r="L22">
+          <cell r="L24">
             <v>491.90000000000072</v>
           </cell>
-          <cell r="M22">
+          <cell r="M24">
             <v>1016.7999999999997</v>
           </cell>
-          <cell r="N22">
+          <cell r="N24">
             <v>1121.8999999999996</v>
           </cell>
-          <cell r="O22">
+          <cell r="O24">
             <v>928.6000000000015</v>
           </cell>
-          <cell r="P22">
+          <cell r="P24">
             <v>932.29999999999723</v>
           </cell>
-          <cell r="Q22">
+          <cell r="Q24">
             <v>1473.4199211999967</v>
           </cell>
-          <cell r="R22">
+          <cell r="R24">
             <v>1674.1472117759988</v>
           </cell>
-          <cell r="S22">
+          <cell r="S24">
             <v>1801.8286222247989</v>
           </cell>
-          <cell r="T22">
+          <cell r="T24">
             <v>1905.822140949791</v>
           </cell>
-          <cell r="AA22">
+          <cell r="AA24">
             <v>2209.5151424104974</v>
           </cell>
         </row>
-        <row r="26">
-          <cell r="O26">
+        <row r="29">
+          <cell r="O29">
             <v>4.89276444606348E-2</v>
           </cell>
-          <cell r="P26">
+          <cell r="P29">
             <v>0.11657007662086771</v>
           </cell>
         </row>
-        <row r="27">
-          <cell r="P27">
+        <row r="30">
+          <cell r="P30">
             <v>0.26116559587103788</v>
           </cell>
         </row>
-        <row r="29">
-          <cell r="AD29">
+        <row r="32">
+          <cell r="AD32">
             <v>0.08</v>
           </cell>
         </row>
-        <row r="31">
-          <cell r="P31">
+        <row r="34">
+          <cell r="P34">
             <v>6.1341523866916652E-2</v>
           </cell>
         </row>
-        <row r="35">
-          <cell r="AD35">
-            <v>-0.53135711887326365</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="AD36" t="str">
+        <row r="38">
+          <cell r="AD38">
+            <v>-0.59343933080112277</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="AD39" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="G42">
+            <v>1.4676241417440277</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="G43">
+            <v>-0.31862663501046928</v>
           </cell>
         </row>
       </sheetData>
@@ -1123,10 +2767,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>27.18</v>
+            <v>28.96</v>
           </cell>
           <cell r="E3">
-            <v>45868</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>46079</v>
@@ -1134,7 +2778,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>35695.493999999999</v>
+            <v>38033.167999999998</v>
           </cell>
         </row>
         <row r="8">
@@ -1144,14 +2788,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>34236.493999999999</v>
+            <v>36574.167999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="7">
-          <cell r="V7">
-            <v>6213.6</v>
+          <cell r="W7">
+            <v>6448.74</v>
           </cell>
         </row>
         <row r="23">
@@ -1195,21 +2839,21 @@
           </cell>
         </row>
         <row r="30">
-          <cell r="U30">
-            <v>5.0500414805923599E-2</v>
-          </cell>
           <cell r="V30">
             <v>4.4056860570622192E-2</v>
           </cell>
+          <cell r="W30">
+            <v>3.7842796446504456E-2</v>
+          </cell>
         </row>
         <row r="33">
-          <cell r="V33">
-            <v>0.83643942320072096</v>
+          <cell r="W33">
+            <v>0.8307891805220865</v>
           </cell>
         </row>
         <row r="35">
           <cell r="AJ35">
-            <v>-0.43497641969139733</v>
+            <v>-0.46970507897832114</v>
           </cell>
         </row>
         <row r="36">
@@ -1218,8 +2862,23 @@
           </cell>
         </row>
         <row r="37">
-          <cell r="V37">
-            <v>0.2188264452169435</v>
+          <cell r="W37">
+            <v>0.19589976801669784</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="W39">
+            <v>0.17266262908723254</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="L44">
+            <v>2.537177027186392</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="L45">
+            <v>-0.60586116408717761</v>
           </cell>
         </row>
       </sheetData>
@@ -1242,10 +2901,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>47.27</v>
+            <v>55.8</v>
           </cell>
           <cell r="E3">
-            <v>45904</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45868</v>
@@ -1253,7 +2912,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>27246.428</v>
+            <v>32163.119999999995</v>
           </cell>
         </row>
         <row r="8">
@@ -1263,7 +2922,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>27513.428</v>
+            <v>32430.119999999995</v>
           </cell>
         </row>
       </sheetData>
@@ -1333,12 +2992,22 @@
         </row>
         <row r="31">
           <cell r="AM31">
-            <v>-0.10935664388414268</v>
+            <v>-0.24550696337640532</v>
           </cell>
         </row>
         <row r="32">
           <cell r="AM32" t="str">
             <v>Fairly valued</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="O33">
+            <v>0.99186811842427192</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="O34">
+            <v>8.1985512233690994E-3</v>
           </cell>
         </row>
       </sheetData>
@@ -1361,10 +3030,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>180.62</v>
+            <v>195.58</v>
           </cell>
           <cell r="E3">
-            <v>45898</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45965</v>
@@ -1372,7 +3041,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>23173.546000000002</v>
+            <v>25092.914000000004</v>
           </cell>
         </row>
         <row r="8">
@@ -1382,7 +3051,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>27347.546000000002</v>
+            <v>29266.914000000004</v>
           </cell>
         </row>
       </sheetData>
@@ -1452,12 +3121,22 @@
         </row>
         <row r="30">
           <cell r="AI30">
-            <v>-0.15132262827852416</v>
+            <v>-0.21623833275215787</v>
           </cell>
         </row>
         <row r="31">
           <cell r="AI31" t="str">
             <v>Slightly overvalued</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="L34">
+            <v>2.1600792678426455</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35">
+            <v>-0.53705402626324061</v>
           </cell>
         </row>
       </sheetData>
@@ -1500,6 +3179,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="3">
+          <cell r="L3">
+            <v>16100</v>
+          </cell>
+        </row>
         <row r="8">
           <cell r="V8">
             <v>9401.5300000000007</v>
@@ -1526,6 +3210,16 @@
         <row r="35">
           <cell r="V35">
             <v>0.11177712563806108</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="L42">
+            <v>1.845136271766169</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="L43">
+            <v>-0.45803460952897668</v>
           </cell>
         </row>
       </sheetData>
@@ -1548,10 +3242,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>78.45</v>
+            <v>86.85</v>
           </cell>
           <cell r="E3">
-            <v>45867</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45953</v>
@@ -1559,7 +3253,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>13979.789999999999</v>
+            <v>15476.669999999998</v>
           </cell>
         </row>
         <row r="8">
@@ -1569,78 +3263,88 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>16279.789999999999</v>
+            <v>17776.669999999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="6">
-          <cell r="U6">
+        <row r="13">
+          <cell r="U13">
             <v>13702</v>
           </cell>
         </row>
-        <row r="22">
-          <cell r="P22">
+        <row r="29">
+          <cell r="P29">
             <v>815</v>
           </cell>
-          <cell r="Q22">
+          <cell r="Q29">
             <v>309</v>
           </cell>
-          <cell r="R22">
+          <cell r="R29">
             <v>746</v>
           </cell>
-          <cell r="S22">
+          <cell r="S29">
             <v>861</v>
           </cell>
-          <cell r="T22">
+          <cell r="T29">
             <v>921</v>
           </cell>
-          <cell r="U22">
+          <cell r="U29">
             <v>824</v>
           </cell>
-          <cell r="V22">
-            <v>1009.4089999999989</v>
-          </cell>
-          <cell r="W22">
-            <v>1260.3274750399985</v>
-          </cell>
-          <cell r="X22">
-            <v>1438.1055164480015</v>
-          </cell>
-          <cell r="Y22">
-            <v>1494.4098756374406</v>
-          </cell>
-          <cell r="AF22">
-            <v>1765.1366695542943</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="T29">
+          <cell r="V29">
+            <v>995.46496000000059</v>
+          </cell>
+          <cell r="W29">
+            <v>1247.4273649599995</v>
+          </cell>
+          <cell r="X29">
+            <v>1426.3027815039991</v>
+          </cell>
+          <cell r="Y29">
+            <v>1482.6656240783984</v>
+          </cell>
+          <cell r="AF29">
+            <v>1751.8186989261117</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="T42">
             <v>6.3252777993628051E-2</v>
           </cell>
-          <cell r="U29">
+          <cell r="U42">
             <v>1.3885843747716287E-3</v>
           </cell>
-          <cell r="AJ29">
+          <cell r="AJ42">
             <v>0.09</v>
           </cell>
         </row>
-        <row r="32">
-          <cell r="U32">
+        <row r="45">
+          <cell r="U45">
             <v>0.18260108013428697</v>
           </cell>
         </row>
-        <row r="35">
-          <cell r="U35">
+        <row r="48">
+          <cell r="U48">
             <v>6.23996496861772E-2</v>
           </cell>
-          <cell r="AJ35">
-            <v>3.5247218209492504E-2</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="AJ36" t="str">
+          <cell r="AJ48">
+            <v>-7.3710144095904817E-2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="AJ49" t="str">
             <v>Fairly valued</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>1.0410324431951277</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="L56">
+            <v>-3.9415143556132737E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -1663,10 +3367,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>57.19</v>
+            <v>57.35</v>
           </cell>
           <cell r="E3">
-            <v>45903</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45965</v>
@@ -1674,7 +3378,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>10494.365</v>
+            <v>10523.725</v>
           </cell>
         </row>
         <row r="8">
@@ -1684,7 +3388,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>11094.365</v>
+            <v>11123.725</v>
           </cell>
         </row>
       </sheetData>
@@ -1754,12 +3458,22 @@
         </row>
         <row r="34">
           <cell r="AI34">
-            <v>-0.43120780386203839</v>
+            <v>-0.43279466962284185</v>
           </cell>
         </row>
         <row r="35">
           <cell r="AI35" t="str">
             <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="L38">
+            <v>0.92160107705053851</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="L39">
+            <v>8.5068176352795399E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -1782,10 +3496,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>231.01</v>
+            <v>216.3</v>
           </cell>
           <cell r="E3">
-            <v>45867</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45952</v>
@@ -1793,7 +3507,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>174042.93399999998</v>
+            <v>162960.42000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -1803,11 +3517,16 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>203362.93399999998</v>
+            <v>192280.42</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="12">
+          <cell r="AV12">
+            <v>618538</v>
+          </cell>
+        </row>
         <row r="16">
           <cell r="AV16">
             <v>89475.77</v>
@@ -1869,12 +3588,22 @@
             <v>2.0289571131939408E-3</v>
           </cell>
           <cell r="BI46">
-            <v>-0.50758168691846905</v>
+            <v>-0.4740935991448707</v>
           </cell>
         </row>
         <row r="47">
           <cell r="BI47" t="str">
-            <v>Heavily overvalued</v>
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="X53">
+            <v>1.2395591799896855</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="X54">
+            <v>-0.19326159158587242</v>
           </cell>
         </row>
       </sheetData>
@@ -1996,6 +3725,16 @@
             <v>Heavily overvalued</v>
           </cell>
         </row>
+        <row r="59">
+          <cell r="L59">
+            <v>2.6322219832221987</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="L60">
+            <v>-0.62009283169352469</v>
+          </cell>
+        </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
@@ -2017,10 +3756,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>90.08</v>
+            <v>107.54</v>
           </cell>
           <cell r="E3">
-            <v>45930</v>
+            <v>45939</v>
           </cell>
           <cell r="G3">
             <v>45960</v>
@@ -2028,7 +3767,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>15205.504000000001</v>
+            <v>18152.752000000004</v>
           </cell>
         </row>
         <row r="8">
@@ -2038,7 +3777,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>14591.704000000002</v>
+            <v>17538.952000000005</v>
           </cell>
         </row>
       </sheetData>
@@ -2108,7 +3847,7 @@
         </row>
         <row r="35">
           <cell r="AI35">
-            <v>-0.87042777033592045</v>
+            <v>-0.89146488331653073</v>
           </cell>
         </row>
         <row r="36">
@@ -2116,8 +3855,18 @@
             <v>Heavily overvalued</v>
           </cell>
         </row>
+        <row r="45">
+          <cell r="L45">
+            <v>6.7830575859535163</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="L46">
+            <v>-0.85257385960118948</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2227,6 +3976,16 @@
             <v>Heavily overvalued</v>
           </cell>
         </row>
+        <row r="54">
+          <cell r="L54">
+            <v>4.3835802469135796</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="L55">
+            <v>-0.77187596811896242</v>
+          </cell>
+        </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
@@ -2247,12 +4006,12 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>10</v>
+            <v>11.52</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1178</v>
+            <v>1357.0559999999998</v>
           </cell>
         </row>
         <row r="8">
@@ -2262,7 +4021,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>1131.9000000000001</v>
+            <v>1310.9559999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -2306,12 +4065,22 @@
         </row>
         <row r="27">
           <cell r="AB27">
-            <v>-0.85432485058235097</v>
+            <v>-0.87354587724162402</v>
           </cell>
         </row>
         <row r="28">
           <cell r="AB28" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="H31">
+            <v>10.798649093904446</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="H32">
+            <v>-0.90739582411614117</v>
           </cell>
         </row>
       </sheetData>
@@ -2334,10 +4103,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>9.0399999999999991</v>
+            <v>14.97</v>
           </cell>
           <cell r="E3">
-            <v>45903</v>
+            <v>45933</v>
           </cell>
           <cell r="G3">
             <v>45974</v>
@@ -2345,7 +4114,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>274.81599999999997</v>
+            <v>455.08800000000002</v>
           </cell>
         </row>
         <row r="8">
@@ -2355,7 +4124,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>269.81599999999997</v>
+            <v>450.08800000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -2405,12 +4174,22 @@
         </row>
         <row r="33">
           <cell r="AF33">
-            <v>-0.78010157110479306</v>
+            <v>-0.86720896478205278</v>
           </cell>
         </row>
         <row r="34">
           <cell r="AF34" t="str">
             <v>Heavily overvalued</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="L35">
+            <v>8.5894656488549632</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="L36">
+            <v>-0.88357832246138535</v>
           </cell>
         </row>
       </sheetData>
@@ -2433,10 +4212,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>214.25</v>
+            <v>209.05</v>
           </cell>
           <cell r="E3">
-            <v>45906</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45953</v>
@@ -2444,7 +4223,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>136584.375</v>
+            <v>133269.375</v>
           </cell>
         </row>
         <row r="8">
@@ -2454,7 +4233,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>160992.375</v>
+            <v>157677.375</v>
           </cell>
         </row>
       </sheetData>
@@ -2520,12 +4299,22 @@
             <v>0.19938196584810197</v>
           </cell>
           <cell r="AM33">
-            <v>-0.28128779344854971</v>
+            <v>-0.26341023557212051</v>
           </cell>
         </row>
         <row r="34">
           <cell r="AM34" t="str">
             <v>Slightly overvalued</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="P41">
+            <v>2.0107037197617923</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="P42">
+            <v>-0.50266168497541264</v>
           </cell>
         </row>
       </sheetData>
@@ -2548,10 +4337,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>183.84</v>
+            <v>203.55</v>
           </cell>
           <cell r="E3">
-            <v>45906</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45959</v>
@@ -2559,7 +4348,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>145104.91199999998</v>
+            <v>160662.01500000001</v>
           </cell>
         </row>
         <row r="8">
@@ -2569,7 +4358,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>130841.91199999998</v>
+            <v>146399.01500000001</v>
           </cell>
         </row>
       </sheetData>
@@ -2639,12 +4428,22 @@
         </row>
         <row r="34">
           <cell r="AO34">
-            <v>-0.2375809557708306</v>
+            <v>-0.31140694133583646</v>
           </cell>
         </row>
         <row r="35">
           <cell r="AO35" t="str">
-            <v>Slightly overvalued</v>
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="P40">
+            <v>1.1345242947923126</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="P41">
+            <v>-0.11857330460864102</v>
           </cell>
         </row>
       </sheetData>
@@ -2667,10 +4466,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>421.42</v>
+            <v>504.49</v>
           </cell>
           <cell r="E3">
-            <v>45862</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45958</v>
@@ -2678,7 +4477,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>98401.57</v>
+            <v>117798.41500000001</v>
           </cell>
         </row>
         <row r="8">
@@ -2688,14 +4487,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>116188.57</v>
+            <v>135585.41500000001</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="AC5">
-            <v>71043</v>
+          <cell r="AD5">
+            <v>72581.52</v>
           </cell>
         </row>
         <row r="21">
@@ -2756,12 +4555,22 @@
         </row>
         <row r="33">
           <cell r="AQ33">
-            <v>-0.14499673048749862</v>
+            <v>-0.28578271553854717</v>
           </cell>
         </row>
         <row r="34">
           <cell r="AQ34" t="str">
             <v>Slightly overvalued</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="T39">
+            <v>2.3031325802615936</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="T40">
+            <v>-0.56580875605241165</v>
           </cell>
         </row>
       </sheetData>
@@ -2784,10 +4593,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>284.89999999999998</v>
+            <v>303.10000000000002</v>
           </cell>
           <cell r="E3">
-            <v>45898</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>46066</v>
@@ -2795,7 +4604,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>119059.70999999998</v>
+            <v>126665.49</v>
           </cell>
         </row>
         <row r="8">
@@ -2805,14 +4614,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>115605.70999999998</v>
+            <v>123211.49</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="Q5">
-            <v>28154</v>
+          <cell r="R5">
+            <v>31734.280000000002</v>
           </cell>
         </row>
         <row r="27">
@@ -2873,12 +4682,22 @@
         </row>
         <row r="39">
           <cell r="AF39">
-            <v>-0.28700962633957428</v>
+            <v>-0.32982198133996943</v>
           </cell>
         </row>
         <row r="40">
           <cell r="AF40" t="str">
-            <v>Slightly overvalued</v>
+            <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="I41">
+            <v>2.2397202428561043</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="I42">
+            <v>-0.55351566643662864</v>
           </cell>
         </row>
       </sheetData>
@@ -2901,10 +4720,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>568.5</v>
+            <v>609.54</v>
           </cell>
           <cell r="E3">
-            <v>45862</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45953</v>
@@ -2912,7 +4731,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>81409.2</v>
+            <v>87286.127999999982</v>
           </cell>
         </row>
         <row r="8">
@@ -2922,14 +4741,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>94670.2</v>
+            <v>100547.12799999998</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="Y5">
-            <v>41033</v>
+          <cell r="Z5">
+            <v>42508.18</v>
           </cell>
         </row>
         <row r="18">
@@ -2990,12 +4809,22 @@
         </row>
         <row r="30">
           <cell r="AM30">
-            <v>-0.42365950691793453</v>
+            <v>-0.46246420199305338</v>
           </cell>
         </row>
         <row r="31">
           <cell r="AM31" t="str">
             <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="P37">
+            <v>2.0332678408930049</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="P38">
+            <v>-0.50818088011424845</v>
           </cell>
         </row>
       </sheetData>
@@ -3018,10 +4847,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>317.10000000000002</v>
+            <v>343.62</v>
           </cell>
           <cell r="E3">
-            <v>45862</v>
+            <v>45934</v>
           </cell>
           <cell r="G3">
             <v>45952</v>
@@ -3029,7 +4858,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>85299.900000000009</v>
+            <v>92433.78</v>
           </cell>
         </row>
         <row r="8">
@@ -3039,14 +4868,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>93666.900000000009</v>
+            <v>100800.78</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="AB5">
-            <v>47716</v>
+          <cell r="AC5">
+            <v>52106.25</v>
           </cell>
         </row>
         <row r="16">
@@ -3085,34 +4914,47 @@
           </cell>
         </row>
         <row r="22">
-          <cell r="AA22">
-            <v>7.2702819296064147E-2</v>
-          </cell>
           <cell r="AB22">
             <v>0.12878501135503417</v>
           </cell>
+          <cell r="AC22">
+            <v>9.2007921871070542E-2</v>
+          </cell>
           <cell r="AP22">
             <v>0.08</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="AB25">
-            <v>0.15432978455863861</v>
+          <cell r="AC25">
+            <v>0.15384503778337533</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AB27">
-            <v>0.10051135887333389</v>
+          <cell r="AC27">
+            <v>0.10308260525368838</v>
           </cell>
         </row>
         <row r="28">
           <cell r="AP28">
-            <v>-0.33344751215489621</v>
+            <v>-0.38489088558383555</v>
           </cell>
         </row>
         <row r="29">
+          <cell r="AC29">
+            <v>8.1439962384550812E-2</v>
+          </cell>
           <cell r="AP29" t="str">
             <v>Overvalued</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="P34">
+            <v>1.7719163971312051</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="P35">
+            <v>-0.435639287711861</v>
           </cell>
         </row>
       </sheetData>
@@ -3161,6 +5003,11 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="11">
+          <cell r="T11">
+            <v>63165</v>
+          </cell>
+        </row>
         <row r="18">
           <cell r="AE18">
             <v>12231.94</v>
@@ -3229,12 +5076,45 @@
         <row r="56">
           <cell r="AE56">
             <v>0.16228117534912698</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="AE59">
+            <v>9.4245194793303441E-2</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="T63">
+            <v>5.2608702802713632</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="T64">
+            <v>-0.80991738120780687</v>
           </cell>
         </row>
       </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7337AAE5-7064-458D-AFDD-A2725076DED6}" name="Table1" displayName="Table1" ref="B10:E14" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="B10:E14" xr:uid="{7337AAE5-7064-458D-AFDD-A2725076DED6}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{C977E06F-DFD4-4D39-82B1-8C27888035FD}" name="DoD Budget ($B)" totalsRowLabel="Total" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{140B34F1-1E1E-40D8-B0B8-17CC11C52BA6}" name="2024" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8483D97F-115F-4E5D-AA66-3FEA52C9D63E}" name="2025" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{D85534AD-A969-4B09-B951-4030B4B7E18C}" name="2026" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3533,28 +5413,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
-  <dimension ref="B2:AK31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
+  <dimension ref="B1:AR31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="17.21875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="8.88671875" style="11"/>
-    <col min="26" max="27" width="9.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17.33203125" style="11" customWidth="1"/>
-    <col min="33" max="34" width="8.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" style="5"/>
-    <col min="36" max="36" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.88671875" style="5"/>
+    <col min="5" max="23" width="8.88671875" style="11"/>
+    <col min="24" max="24" width="8.88671875" style="20"/>
+    <col min="25" max="26" width="8.88671875" style="16"/>
+    <col min="27" max="29" width="8.88671875" style="14"/>
+    <col min="30" max="31" width="8.88671875" style="11"/>
+    <col min="32" max="33" width="9.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10" style="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10" style="11" customWidth="1"/>
+    <col min="37" max="38" width="8.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.33203125" style="11" customWidth="1"/>
+    <col min="40" max="41" width="8.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.88671875" style="5"/>
+    <col min="43" max="43" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3621,47 +5514,68 @@
       <c r="W2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="AE2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
@@ -3681,65 +5595,84 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="7">
-        <f t="shared" ref="R3:W3" si="0">TRIMMEAN(R4:R1048576,80%)</f>
-        <v>34.421156571947499</v>
+        <f t="shared" ref="R3:Z3" si="0">TRIMMEAN(R4:R1048576,80%)</f>
+        <v>37.145030304683814</v>
       </c>
       <c r="S3" s="7">
         <f t="shared" si="0"/>
-        <v>26.461248999924155</v>
+        <v>28.580534120694068</v>
       </c>
       <c r="T3" s="7">
         <f t="shared" si="0"/>
-        <v>23.092730697287529</v>
+        <v>24.427824579001424</v>
       </c>
       <c r="U3" s="7">
         <f t="shared" si="0"/>
-        <v>22.349828165413104</v>
+        <v>23.633778698262194</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" si="0"/>
-        <v>21.596966763334482</v>
+        <v>22.848814495815787</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="0"/>
-        <v>17.986032733432616</v>
-      </c>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="21">
-        <f t="shared" ref="Y3:AE3" si="1">TRIMMEAN(Y4:Y1048576,80%)</f>
-        <v>2.8329303433229946</v>
+        <v>18.941051843429769</v>
+      </c>
+      <c r="X3" s="21">
+        <f t="shared" si="0"/>
+        <v>2.0229435907319835</v>
+      </c>
+      <c r="Y3" s="9">
+        <f t="shared" si="0"/>
+        <v>-0.50309034649027118</v>
       </c>
       <c r="Z3" s="9">
+        <f t="shared" si="0"/>
+        <v>-0.44652164870768035</v>
+      </c>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="21">
+        <f t="shared" ref="AE3:AL3" si="1">TRIMMEAN(AE4:AE1048576,80%)</f>
+        <v>2.9293484226775894</v>
+      </c>
+      <c r="AF3" s="9">
         <f t="shared" si="1"/>
-        <v>7.9957761805311917E-2</v>
-      </c>
-      <c r="AA3" s="9">
+        <v>0.1016798832038464</v>
+      </c>
+      <c r="AG3" s="9">
         <f t="shared" si="1"/>
-        <v>0.11843352839563026</v>
-      </c>
-      <c r="AB3" s="9">
+        <v>9.9452943703817409E-2</v>
+      </c>
+      <c r="AH3" s="9">
         <f t="shared" si="1"/>
-        <v>0.20768693578353645</v>
-      </c>
-      <c r="AC3" s="9">
+        <v>0.20714909665930989</v>
+      </c>
+      <c r="AI3" s="9">
         <f t="shared" si="1"/>
-        <v>9.48275445189906E-2</v>
-      </c>
-      <c r="AD3" s="9">
+        <v>9.8848469126009128E-2</v>
+      </c>
+      <c r="AJ3" s="9">
+        <f t="shared" si="1"/>
+        <v>9.2093150912362295E-2</v>
+      </c>
+      <c r="AK3" s="9">
         <f t="shared" si="1"/>
         <v>0.08</v>
       </c>
-      <c r="AE3" s="9">
+      <c r="AL3" s="9">
         <f t="shared" si="1"/>
-        <v>-0.45499566684070913</v>
-      </c>
-      <c r="AF3" s="10" t="e">
-        <f>INDEX(AF4:AF24,MODE(MATCH(AF4:AF24,AF4:AF24,0)))</f>
+        <v>-0.46900509315888117</v>
+      </c>
+      <c r="AM3" s="10" t="e">
+        <f>INDEX(AM4:AM24,MODE(MATCH(AM4:AM24,AM4:AM24,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="AG3" s="2"/>
-    </row>
-    <row r="4" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AN3" s="2"/>
+    </row>
+    <row r="4" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -3748,11 +5681,11 @@
       </c>
       <c r="D4" s="13">
         <f>[1]Main!$D$3</f>
-        <v>157.52000000000001</v>
+        <v>166.58</v>
       </c>
       <c r="E4" s="14">
         <f>[1]Main!$D$5</f>
-        <v>210840.52000000002</v>
+        <v>222967.33000000002</v>
       </c>
       <c r="F4" s="14">
         <f>[1]Main!$D$8</f>
@@ -3760,7 +5693,7 @@
       </c>
       <c r="G4" s="14">
         <f>[1]Main!$D$9</f>
-        <v>248036.52000000002</v>
+        <v>260163.33000000002</v>
       </c>
       <c r="H4" s="14">
         <f>[1]Model!U$19</f>
@@ -3804,77 +5737,93 @@
       </c>
       <c r="R4" s="15">
         <f t="shared" ref="R4" si="2">$G4/M4</f>
-        <v>51.955701717637204</v>
+        <v>54.495879765395898</v>
       </c>
       <c r="S4" s="15">
         <f t="shared" ref="S4" si="3">$G4/N4</f>
-        <v>37.59431312346814</v>
+        <v>39.432345250063065</v>
       </c>
       <c r="T4" s="15">
         <f t="shared" ref="T4" si="4">$G4/O4</f>
-        <v>32.762098135476037</v>
+        <v>34.3638773383542</v>
       </c>
       <c r="U4" s="15">
         <f t="shared" ref="U4" si="5">$G4/P4</f>
-        <v>30.407511828504134</v>
+        <v>31.894172415892726</v>
       </c>
       <c r="V4" s="15">
         <f t="shared" ref="V4" si="6">$G4/Q4</f>
-        <v>29.171319789744228</v>
+        <v>30.597541430571425</v>
       </c>
       <c r="W4" s="15">
         <f>G4/[1]Model!$AK$19</f>
-        <v>23.533213228593535</v>
-      </c>
-      <c r="X4" s="14">
+        <v>24.683780917225196</v>
+      </c>
+      <c r="X4" s="20">
+        <f>[1]Model!$P$39</f>
+        <v>1.556568664405076</v>
+      </c>
+      <c r="Y4" s="16">
+        <f>[1]Model!$P$40</f>
+        <v>-0.35756126737768923</v>
+      </c>
+      <c r="Z4" s="16">
+        <f t="shared" ref="Z4:Z16" si="7">AVERAGE(Y4,AL4)</f>
+        <v>-0.43176459171650405</v>
+      </c>
+      <c r="AD4" s="14">
         <f>[1]Model!$AA$5</f>
         <v>87203.32</v>
       </c>
-      <c r="Y4" s="20">
-        <f>G4/X4</f>
-        <v>2.8443472106337238</v>
-      </c>
-      <c r="Z4" s="16">
+      <c r="AE4" s="20">
+        <f>G4/AD4</f>
+        <v>2.9834108380277264</v>
+      </c>
+      <c r="AF4" s="16">
         <f>[1]Model!Z$25</f>
         <v>0.17147417295414979</v>
       </c>
-      <c r="AA4" s="16">
+      <c r="AG4" s="16">
         <f>[1]Model!AA$25</f>
         <v>8.0077782456835722E-2</v>
       </c>
-      <c r="AB4" s="16">
+      <c r="AH4" s="16">
         <f>[1]Model!$AA$28</f>
         <v>0.2026911899684555</v>
       </c>
-      <c r="AC4" s="16">
+      <c r="AI4" s="16">
         <f>[1]Model!$AA$31</f>
         <v>9.8853831482562993E-2</v>
       </c>
-      <c r="AD4" s="16">
+      <c r="AJ4" s="16">
+        <f>[1]Model!$AA$34</f>
+        <v>7.5658975369286591E-2</v>
+      </c>
+      <c r="AK4" s="16">
         <f>[1]Model!$AO$26</f>
         <v>0.06</v>
       </c>
-      <c r="AE4" s="16">
+      <c r="AL4" s="16">
         <f>[1]Model!$AO$32</f>
-        <v>-0.47755291681370626</v>
-      </c>
-      <c r="AF4" s="11" t="str">
+        <v>-0.50596791605531888</v>
+      </c>
+      <c r="AM4" s="11" t="str">
         <f>[1]Model!$AO$33</f>
-        <v>Overvalued</v>
-      </c>
-      <c r="AH4" s="11">
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AO4" s="11">
         <v>1922</v>
       </c>
-      <c r="AJ4" s="18">
+      <c r="AQ4" s="18">
         <f>[1]Main!$E$3</f>
-        <v>45906</v>
-      </c>
-      <c r="AK4" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR4" s="18">
         <f>[1]Main!$G$3</f>
         <v>45958</v>
       </c>
     </row>
-    <row r="5" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B5" s="19" t="s">
         <v>29</v>
       </c>
@@ -3883,11 +5832,11 @@
       </c>
       <c r="D5" s="13">
         <f>[2]Main!$D$3</f>
-        <v>231.01</v>
+        <v>216.3</v>
       </c>
       <c r="E5" s="14">
         <f>[2]Main!$D$5</f>
-        <v>174042.93399999998</v>
+        <v>162960.42000000001</v>
       </c>
       <c r="F5" s="14">
         <f>[2]Main!$D$8</f>
@@ -3895,7 +5844,7 @@
       </c>
       <c r="G5" s="14">
         <f>[2]Main!$D$9</f>
-        <v>203362.93399999998</v>
+        <v>192280.42</v>
       </c>
       <c r="H5" s="14">
         <f>[2]Model!AP$33</f>
@@ -3939,69 +5888,94 @@
       </c>
       <c r="R5" s="15">
         <f>$G5/M5</f>
-        <v>-17.125299705263156</v>
+        <v>-16.192035368421053</v>
       </c>
       <c r="U5" s="15">
-        <f t="shared" ref="U5:V6" si="7">$G5/P5</f>
-        <v>62.00077346154464</v>
+        <f t="shared" ref="U5:V6" si="8">$G5/P5</f>
+        <v>58.621964814446763</v>
       </c>
       <c r="V5" s="15">
-        <f t="shared" si="7"/>
-        <v>46.332592228976829</v>
+        <f t="shared" si="8"/>
+        <v>43.807640449740965</v>
       </c>
       <c r="W5" s="15">
         <f>G5/[2]Model!$BF$33</f>
-        <v>20.60445645042169</v>
-      </c>
-      <c r="X5" s="14">
+        <v>19.48159117412612</v>
+      </c>
+      <c r="X5" s="20">
+        <f>[2]Model!$X$53</f>
+        <v>1.2395591799896855</v>
+      </c>
+      <c r="Y5" s="16">
+        <f>[2]Model!$X$54</f>
+        <v>-0.19326159158587242</v>
+      </c>
+      <c r="Z5" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.33367759536537156</v>
+      </c>
+      <c r="AA5" s="14">
+        <f>[2]Model!$AV$12</f>
+        <v>618538</v>
+      </c>
+      <c r="AB5" s="20">
+        <f>AA5/AD5</f>
+        <v>6.9129106125602489</v>
+      </c>
+      <c r="AC5" s="20">
+        <f>AVERAGE(Y5,AB5,AL5)</f>
+        <v>2.081851807276502</v>
+      </c>
+      <c r="AD5" s="14">
         <f>[2]Model!$AV$16</f>
         <v>89475.77</v>
       </c>
-      <c r="Y5" s="20">
-        <f t="shared" ref="Y5:Y8" si="8">G5/X5</f>
-        <v>2.2728268669830944</v>
-      </c>
-      <c r="Z5" s="16">
+      <c r="AE5" s="20">
+        <f t="shared" ref="AE5:AE8" si="9">G5/AD5</f>
+        <v>2.1489663626253233</v>
+      </c>
+      <c r="AF5" s="16">
         <f>[2]Model!AU$40</f>
         <v>-0.14495976553461709</v>
       </c>
-      <c r="AA5" s="16">
+      <c r="AG5" s="16">
         <f>[2]Model!AV$40</f>
         <v>0.34515642617676701</v>
       </c>
-      <c r="AB5" s="16">
+      <c r="AH5" s="16">
         <f>[2]Model!$AV$43</f>
         <v>0.11339720798155752</v>
       </c>
-      <c r="AC5" s="16">
+      <c r="AI5" s="16">
         <f>[2]Model!$AV$46</f>
         <v>2.0289571131939408E-3</v>
       </c>
-      <c r="AD5" s="16">
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16">
         <f>[2]Model!$BI$40</f>
         <v>0.06</v>
       </c>
-      <c r="AE5" s="16">
+      <c r="AL5" s="16">
         <f>[2]Model!$BI$46</f>
-        <v>-0.50758168691846905</v>
-      </c>
-      <c r="AF5" s="11" t="str">
+        <v>-0.4740935991448707</v>
+      </c>
+      <c r="AM5" s="11" t="str">
         <f>[2]Model!$BI$47</f>
-        <v>Heavily overvalued</v>
-      </c>
-      <c r="AH5" s="11">
+        <v>Overvalued</v>
+      </c>
+      <c r="AO5" s="11">
         <v>1916</v>
       </c>
-      <c r="AJ5" s="18">
+      <c r="AQ5" s="18">
         <f>[2]Main!$E$3</f>
-        <v>45867</v>
-      </c>
-      <c r="AK5" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR5" s="18">
         <f>[2]Main!$G$3</f>
         <v>45952</v>
       </c>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B6" s="19" t="s">
         <v>31</v>
       </c>
@@ -4010,11 +5984,11 @@
       </c>
       <c r="D6" s="13">
         <f>[3]Main!$D$3</f>
-        <v>214.25</v>
+        <v>209.05</v>
       </c>
       <c r="E6" s="14">
         <f>[3]Main!$D$5</f>
-        <v>136584.375</v>
+        <v>133269.375</v>
       </c>
       <c r="F6" s="14">
         <f>[3]Main!$D$8</f>
@@ -4022,7 +5996,7 @@
       </c>
       <c r="G6" s="14">
         <f>[3]Main!$D$9</f>
-        <v>160992.375</v>
+        <v>157677.375</v>
       </c>
       <c r="H6" s="14">
         <f>[3]Model!T$21</f>
@@ -4066,77 +6040,90 @@
       </c>
       <c r="R6" s="15">
         <f>$G6/M6</f>
-        <v>28.219522348816827</v>
+        <v>27.638453111305871</v>
       </c>
       <c r="S6" s="15">
-        <f t="shared" ref="S6:T6" si="9">$G6/N6</f>
-        <v>25.790892277113116</v>
+        <f t="shared" ref="S6:T6" si="10">$G6/N6</f>
+        <v>25.25983105201702</v>
       </c>
       <c r="T6" s="15">
-        <f t="shared" si="9"/>
-        <v>24.864210606582542</v>
+        <f t="shared" si="10"/>
+        <v>24.352230718337395</v>
       </c>
       <c r="U6" s="15">
-        <f t="shared" si="7"/>
-        <v>23.279545712396395</v>
+        <f t="shared" si="8"/>
+        <v>22.800195718108814</v>
       </c>
       <c r="V6" s="15">
-        <f t="shared" si="7"/>
-        <v>21.878569580283646</v>
+        <f t="shared" si="8"/>
+        <v>21.428067137800639</v>
       </c>
       <c r="W6" s="15">
         <f>G6/[3]Model!$AJ$21</f>
-        <v>18.907618980514979</v>
-      </c>
-      <c r="X6" s="14">
+        <v>18.518291492673349</v>
+      </c>
+      <c r="X6" s="20">
+        <f>[3]Model!$P$41</f>
+        <v>2.0107037197617923</v>
+      </c>
+      <c r="Y6" s="16">
+        <f>[3]Model!$P$42</f>
+        <v>-0.50266168497541264</v>
+      </c>
+      <c r="Z6" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.38303596027376657</v>
+      </c>
+      <c r="AD6" s="14">
         <f>[3]Model!$Z$5</f>
         <v>41769.86</v>
       </c>
-      <c r="Y6" s="20">
-        <f t="shared" si="8"/>
-        <v>3.854271357385445</v>
-      </c>
-      <c r="Z6" s="25">
+      <c r="AE6" s="20">
+        <f t="shared" si="9"/>
+        <v>3.7749079120686542</v>
+      </c>
+      <c r="AF6" s="25">
         <f>[3]Model!Y$27</f>
         <v>5.0079100976487823E-2</v>
       </c>
-      <c r="AA6" s="25">
+      <c r="AG6" s="25">
         <f>[3]Model!Z$27</f>
         <v>8.4987791573588156E-2</v>
       </c>
-      <c r="AB6" s="16">
+      <c r="AH6" s="16">
         <f>[3]Model!$Z$30</f>
         <v>0.3822494688754044</v>
       </c>
-      <c r="AC6" s="16">
+      <c r="AI6" s="16">
         <f>[3]Model!$Z$33</f>
         <v>0.19938196584810197</v>
       </c>
-      <c r="AD6" s="16">
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16">
         <f>[3]Model!$AM$27</f>
         <v>0.06</v>
       </c>
-      <c r="AE6" s="16">
+      <c r="AL6" s="16">
         <f>[3]Model!$AM$33</f>
-        <v>-0.28128779344854971</v>
-      </c>
-      <c r="AF6" s="11" t="str">
+        <v>-0.26341023557212051</v>
+      </c>
+      <c r="AM6" s="11" t="str">
         <f>[3]Model!$AM$34</f>
         <v>Slightly overvalued</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AO6" s="11">
         <v>1906</v>
       </c>
-      <c r="AJ6" s="18">
+      <c r="AQ6" s="18">
         <f>[3]Main!$E$3</f>
-        <v>45906</v>
-      </c>
-      <c r="AK6" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR6" s="18">
         <f>[3]Main!$G$3</f>
         <v>45953</v>
       </c>
     </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B7" s="19" t="s">
         <v>32</v>
       </c>
@@ -4145,11 +6132,11 @@
       </c>
       <c r="D7" s="17">
         <f>[4]Main!$D$3</f>
-        <v>183.84</v>
+        <v>203.55</v>
       </c>
       <c r="E7" s="14">
         <f>[4]Main!$D$5</f>
-        <v>145104.91199999998</v>
+        <v>160662.01500000001</v>
       </c>
       <c r="F7" s="14">
         <f>[4]Main!$D$8</f>
@@ -4157,7 +6144,7 @@
       </c>
       <c r="G7" s="14">
         <f>[4]Main!$D$9</f>
-        <v>130841.91199999998</v>
+        <v>146399.01500000001</v>
       </c>
       <c r="H7" s="14">
         <f>[4]Model!U$22</f>
@@ -4201,77 +6188,90 @@
       </c>
       <c r="R7" s="15">
         <f>$G7/M7</f>
-        <v>30.917275992438558</v>
+        <v>34.593340028355392</v>
       </c>
       <c r="S7" s="15">
         <f>$G7/N7</f>
-        <v>24.826140543540337</v>
+        <v>27.777968590262354</v>
       </c>
       <c r="T7" s="15">
         <f>$G7/O7</f>
-        <v>22.71652287154339</v>
+        <v>25.41751738249533</v>
       </c>
       <c r="U7" s="15">
         <f>$G7/P7</f>
-        <v>20.082971279227113</v>
+        <v>22.470836512631671</v>
       </c>
       <c r="V7" s="15">
         <f>$G7/Q7</f>
-        <v>19.620729864448997</v>
+        <v>21.953634594826291</v>
       </c>
       <c r="W7" s="15">
         <f>G7/[4]Model!$AK$22</f>
-        <v>16.69042906295855</v>
-      </c>
-      <c r="X7" s="14">
+        <v>18.674921035581516</v>
+      </c>
+      <c r="X7" s="20">
+        <f>[4]Model!$P$40</f>
+        <v>1.1345242947923126</v>
+      </c>
+      <c r="Y7" s="16">
+        <f>[4]Model!$P$41</f>
+        <v>-0.11857330460864102</v>
+      </c>
+      <c r="Z7" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.21499012297223874</v>
+      </c>
+      <c r="AD7" s="14">
         <f>[4]Model!$AA$3</f>
         <v>73427.94</v>
       </c>
-      <c r="Y7" s="20">
-        <f>G7/X7</f>
-        <v>1.781909066221931</v>
-      </c>
-      <c r="Z7" s="16">
+      <c r="AE7" s="20">
+        <f>G7/AD7</f>
+        <v>1.9937780496089093</v>
+      </c>
+      <c r="AF7" s="16">
         <f>[4]Model!Z$26</f>
         <v>5.7818659658344318E-2</v>
       </c>
-      <c r="AA7" s="16">
+      <c r="AG7" s="16">
         <f>[4]Model!AA$26</f>
         <v>6.063758486205395E-2</v>
       </c>
-      <c r="AB7" s="16">
+      <c r="AH7" s="16">
         <f>[4]Model!$AA$27</f>
         <v>0.16</v>
       </c>
-      <c r="AC7" s="16">
+      <c r="AI7" s="16">
         <f>[4]Model!$AA$31</f>
         <v>8.4329038510408974E-2</v>
       </c>
-      <c r="AD7" s="16">
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16">
         <f>[4]Model!$AO$28</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE7" s="16">
+      <c r="AL7" s="16">
         <f>[4]Model!$AO$34</f>
-        <v>-0.2375809557708306</v>
-      </c>
-      <c r="AF7" s="11" t="str">
+        <v>-0.31140694133583646</v>
+      </c>
+      <c r="AM7" s="11" t="str">
         <f>[4]Model!$AO$35</f>
-        <v>Slightly overvalued</v>
-      </c>
-      <c r="AH7" s="11">
+        <v>Overvalued</v>
+      </c>
+      <c r="AO7" s="11">
         <v>1998</v>
       </c>
-      <c r="AJ7" s="18">
+      <c r="AQ7" s="18">
         <f>[4]Main!$E$3</f>
-        <v>45906</v>
-      </c>
-      <c r="AK7" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR7" s="18">
         <f>[4]Main!$G$3</f>
         <v>45959</v>
       </c>
     </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B8" s="19" t="s">
         <v>24</v>
       </c>
@@ -4280,11 +6280,11 @@
       </c>
       <c r="D8" s="13">
         <f>[5]Main!$D$3</f>
-        <v>421.42</v>
+        <v>504.49</v>
       </c>
       <c r="E8" s="14">
         <f>[5]Main!$D$5</f>
-        <v>98401.57</v>
+        <v>117798.41500000001</v>
       </c>
       <c r="F8" s="14">
         <f>[5]Main!$D$8</f>
@@ -4292,7 +6292,7 @@
       </c>
       <c r="G8" s="14">
         <f>[5]Main!$D$9</f>
-        <v>116188.57</v>
+        <v>135585.41500000001</v>
       </c>
       <c r="H8" s="14">
         <f>[5]Model!X$21</f>
@@ -4335,78 +6335,91 @@
         <v>7229.3492892684044</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" ref="R8" si="10">$G8/M8</f>
-        <v>21.774469640179912</v>
+        <f t="shared" ref="R8" si="11">$G8/M8</f>
+        <v>25.409560532233886</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" ref="S8" si="11">$G8/N8</f>
-        <v>16.862188242779812</v>
+        <f t="shared" ref="S8" si="12">$G8/N8</f>
+        <v>19.677209132580092</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" ref="T8" si="12">$G8/O8</f>
-        <v>16.506129538436941</v>
+        <f t="shared" ref="T8" si="13">$G8/O8</f>
+        <v>19.261708991794382</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" ref="U8" si="13">$G8/P8</f>
-        <v>16.287958058157589</v>
+        <f t="shared" ref="U8" si="14">$G8/P8</f>
+        <v>19.007115354099724</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" ref="V8" si="14">$G8/Q8</f>
-        <v>16.071788116874632</v>
+        <f t="shared" ref="V8" si="15">$G8/Q8</f>
+        <v>18.754857397922322</v>
       </c>
       <c r="W8" s="15">
         <f>G8/[5]Model!$AN$21</f>
-        <v>14.613482728967238</v>
-      </c>
-      <c r="X8" s="23">
-        <f>[5]Model!$AC$5</f>
-        <v>71043</v>
-      </c>
-      <c r="Y8" s="26">
-        <f t="shared" si="8"/>
-        <v>1.6354682375462748</v>
-      </c>
-      <c r="Z8" s="25">
+        <v>17.053098427860466</v>
+      </c>
+      <c r="X8" s="20">
+        <f>[5]Model!$T$39</f>
+        <v>2.3031325802615936</v>
+      </c>
+      <c r="Y8" s="16">
+        <f>[5]Model!$T$40</f>
+        <v>-0.56580875605241165</v>
+      </c>
+      <c r="Z8" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.42579573579547941</v>
+      </c>
+      <c r="AD8" s="14">
+        <f>[5]Model!$AD$5</f>
+        <v>72581.52</v>
+      </c>
+      <c r="AE8" s="20">
+        <f t="shared" si="9"/>
+        <v>1.8680432016303874</v>
+      </c>
+      <c r="AF8" s="25">
         <f>[5]Model!$AB$27</f>
         <v>2.4051285160038738E-2</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AG8" s="25">
         <f>[5]Model!$AC$27</f>
         <v>5.1382989744120922E-2</v>
       </c>
-      <c r="AB8" s="25">
+      <c r="AH8" s="25">
         <f>[5]Model!$AC$30</f>
         <v>8.4089917373984774E-2</v>
       </c>
-      <c r="AC8" s="25">
+      <c r="AI8" s="25">
         <f>[5]Model!$AC$31</f>
         <v>9.8714862829553926E-2</v>
       </c>
-      <c r="AD8" s="16">
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="16">
         <f>[5]Model!$AQ$27</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE8" s="16">
+      <c r="AL8" s="16">
         <f>[5]Model!$AQ$33</f>
-        <v>-0.14499673048749862</v>
-      </c>
-      <c r="AF8" s="11" t="str">
+        <v>-0.28578271553854717</v>
+      </c>
+      <c r="AM8" s="11" t="str">
         <f>[5]Model!$AQ$34</f>
         <v>Slightly overvalued</v>
       </c>
-      <c r="AH8" s="11">
+      <c r="AO8" s="11">
         <v>1912</v>
       </c>
-      <c r="AJ8" s="18">
+      <c r="AQ8" s="18">
         <f>[5]Main!$E$3</f>
-        <v>45862</v>
-      </c>
-      <c r="AK8" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR8" s="18">
         <f>[5]Main!$G$3</f>
         <v>45958</v>
       </c>
     </row>
-    <row r="9" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B9" s="19" t="s">
         <v>33</v>
       </c>
@@ -4415,11 +6428,11 @@
       </c>
       <c r="D9" s="17">
         <f>[6]Main!$D$3</f>
-        <v>284.89999999999998</v>
+        <v>303.10000000000002</v>
       </c>
       <c r="E9" s="14">
         <f>[6]Main!$D$5</f>
-        <v>119059.70999999998</v>
+        <v>126665.49</v>
       </c>
       <c r="F9" s="14">
         <f>[6]Main!$D$8</f>
@@ -4427,7 +6440,7 @@
       </c>
       <c r="G9" s="14">
         <f>[6]Main!$D$9</f>
-        <v>115605.70999999998</v>
+        <v>123211.49</v>
       </c>
       <c r="H9" s="14">
         <f>[6]Model!L$27</f>
@@ -4470,78 +6483,91 @@
         <v>5481.8804852950607</v>
       </c>
       <c r="R9" s="15">
-        <f t="shared" ref="R9" si="15">$G9/M9</f>
-        <v>-173.32190404797598</v>
+        <f t="shared" ref="R9" si="16">$G9/M9</f>
+        <v>-184.72487256371815</v>
       </c>
       <c r="S9" s="15">
-        <f t="shared" ref="S9" si="16">$G9/N9</f>
-        <v>17.195382088726515</v>
+        <f t="shared" ref="S9" si="17">$G9/N9</f>
+        <v>18.326678226112765</v>
       </c>
       <c r="T9" s="15">
-        <f t="shared" ref="T9" si="17">$G9/O9</f>
-        <v>23.315496568806726</v>
+        <f t="shared" ref="T9" si="18">$G9/O9</f>
+        <v>24.849439290953406</v>
       </c>
       <c r="U9" s="15">
-        <f t="shared" ref="U9" si="18">$G9/P9</f>
-        <v>21.961638351065886</v>
+        <f t="shared" ref="U9" si="19">$G9/P9</f>
+        <v>23.406509800216369</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9" si="19">$G9/Q9</f>
-        <v>21.088695806139512</v>
+        <f t="shared" ref="V9" si="20">$G9/Q9</f>
+        <v>22.476135758616085</v>
       </c>
       <c r="W9" s="15">
         <f>G9/[6]Model!$AB$27</f>
-        <v>18.023912461314321</v>
-      </c>
-      <c r="X9" s="23">
-        <f>[6]Model!$Q$5</f>
-        <v>28154</v>
-      </c>
-      <c r="Y9" s="26">
-        <f t="shared" ref="Y9" si="20">G9/X9</f>
-        <v>4.1061913049655461</v>
-      </c>
-      <c r="Z9" s="25">
+        <v>19.209718187692506</v>
+      </c>
+      <c r="X9" s="20">
+        <f>[6]Model!$I$41</f>
+        <v>2.2397202428561043</v>
+      </c>
+      <c r="Y9" s="16">
+        <f>[6]Model!$I$42</f>
+        <v>-0.55351566643662864</v>
+      </c>
+      <c r="Z9" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.44166882388829903</v>
+      </c>
+      <c r="AD9" s="14">
+        <f>[6]Model!$R$5</f>
+        <v>31734.280000000002</v>
+      </c>
+      <c r="AE9" s="20">
+        <f t="shared" ref="AE9" si="21">G9/AD9</f>
+        <v>3.8825991955702159</v>
+      </c>
+      <c r="AF9" s="25">
         <f>[6]Model!P$31</f>
         <v>0.23876765083440299</v>
       </c>
-      <c r="AA9" s="25">
+      <c r="AG9" s="25">
         <f>[6]Model!Q$31</f>
         <v>0.16700518134715026</v>
       </c>
-      <c r="AB9" s="25">
+      <c r="AH9" s="25">
         <f>[6]Model!$Q$32</f>
         <v>0.19116288982027421</v>
       </c>
-      <c r="AC9" s="25">
+      <c r="AI9" s="25">
         <f>[6]Model!$Q$33</f>
         <v>0.14889536122753427</v>
       </c>
-      <c r="AD9" s="16">
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="16">
         <f>[6]Model!$AF$33</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE9" s="16">
+      <c r="AL9" s="16">
         <f>[6]Model!$AF$39</f>
-        <v>-0.28700962633957428</v>
-      </c>
-      <c r="AF9" s="11" t="str">
+        <v>-0.32982198133996943</v>
+      </c>
+      <c r="AM9" s="11" t="str">
         <f>[6]Model!$AF$40</f>
-        <v>Slightly overvalued</v>
-      </c>
-      <c r="AH9" s="11">
+        <v>Overvalued</v>
+      </c>
+      <c r="AO9" s="11">
         <v>1924</v>
       </c>
-      <c r="AJ9" s="18">
+      <c r="AQ9" s="18">
         <f>[6]Main!$E$3</f>
-        <v>45898</v>
-      </c>
-      <c r="AK9" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR9" s="18">
         <f>[6]Main!$G$3</f>
         <v>46066</v>
       </c>
     </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B10" s="19" t="s">
         <v>25</v>
       </c>
@@ -4550,11 +6576,11 @@
       </c>
       <c r="D10" s="13">
         <f>[7]Main!$D$3</f>
-        <v>568.5</v>
+        <v>609.54</v>
       </c>
       <c r="E10" s="14">
         <f>[7]Main!$D$5</f>
-        <v>81409.2</v>
+        <v>87286.127999999982</v>
       </c>
       <c r="F10" s="14">
         <f>[7]Main!$D$8</f>
@@ -4562,7 +6588,7 @@
       </c>
       <c r="G10" s="14">
         <f>[7]Main!$D$9</f>
-        <v>94670.2</v>
+        <v>100547.12799999998</v>
       </c>
       <c r="H10" s="14">
         <f>[7]Model!T$18</f>
@@ -4606,77 +6632,90 @@
       </c>
       <c r="R10" s="15">
         <f>$G10/M10</f>
-        <v>22.680929563967418</v>
+        <v>24.088914230953517</v>
       </c>
       <c r="S10" s="15">
-        <f t="shared" ref="S10:V14" si="21">$G10/N10</f>
-        <v>21.298244892984577</v>
+        <f t="shared" ref="S10:V14" si="22">$G10/N10</f>
+        <v>22.620395387674964</v>
       </c>
       <c r="T10" s="15">
-        <f t="shared" si="21"/>
-        <v>20.49385849513309</v>
+        <f t="shared" si="22"/>
+        <v>21.766074364731814</v>
       </c>
       <c r="U10" s="15">
-        <f t="shared" si="21"/>
-        <v>19.97049830658171</v>
+        <f t="shared" si="22"/>
+        <v>21.210225070356397</v>
       </c>
       <c r="V10" s="15">
-        <f t="shared" si="21"/>
-        <v>19.462362378880147</v>
+        <f t="shared" si="22"/>
+        <v>20.670545127100677</v>
       </c>
       <c r="W10" s="15">
         <f>G10/[7]Model!$AJ$18</f>
-        <v>17.720674894878048</v>
-      </c>
-      <c r="X10" s="23">
-        <f>[7]Model!$Y$5</f>
-        <v>41033</v>
-      </c>
-      <c r="Y10" s="26">
-        <f t="shared" ref="Y10:Y14" si="22">G10/X10</f>
-        <v>2.3071722759729973</v>
-      </c>
-      <c r="Z10" s="25">
+        <v>18.820737327075356</v>
+      </c>
+      <c r="X10" s="20">
+        <f>[7]Model!$P$37</f>
+        <v>2.0332678408930049</v>
+      </c>
+      <c r="Y10" s="16">
+        <f>[7]Model!$P$38</f>
+        <v>-0.50818088011424845</v>
+      </c>
+      <c r="Z10" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.48532254105365091</v>
+      </c>
+      <c r="AD10" s="14">
+        <f>[7]Model!$Z$5</f>
+        <v>42508.18</v>
+      </c>
+      <c r="AE10" s="20">
+        <f t="shared" ref="AE10:AE14" si="23">G10/AD10</f>
+        <v>2.365359514333476</v>
+      </c>
+      <c r="AF10" s="25">
         <f>[7]Model!X$24</f>
         <v>7.3438609912026775E-2</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AG10" s="25">
         <f>[7]Model!Y$24</f>
         <v>4.4362433189106598E-2</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AH10" s="25">
         <f>[7]Model!$Y$27</f>
         <v>0.20378719567177639</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AI10" s="25">
         <f>[7]Model!$Y$29</f>
         <v>0.10649964662588648</v>
       </c>
-      <c r="AD10" s="16">
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="16">
         <f>[7]Model!$AM$24</f>
         <v>0.08</v>
       </c>
-      <c r="AE10" s="16">
+      <c r="AL10" s="16">
         <f>[7]Model!$AM$30</f>
-        <v>-0.42365950691793453</v>
-      </c>
-      <c r="AF10" s="11" t="str">
+        <v>-0.46246420199305338</v>
+      </c>
+      <c r="AM10" s="11" t="str">
         <f>[7]Model!$AM$31</f>
         <v>Overvalued</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AO10" s="11">
         <v>1939</v>
       </c>
-      <c r="AJ10" s="18">
+      <c r="AQ10" s="18">
         <f>[7]Main!$E$3</f>
-        <v>45862</v>
-      </c>
-      <c r="AK10" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR10" s="18">
         <f>[7]Main!$G$3</f>
         <v>45953</v>
       </c>
     </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B11" s="19" t="s">
         <v>30</v>
       </c>
@@ -4685,11 +6724,11 @@
       </c>
       <c r="D11" s="13">
         <f>[8]Main!$D$3</f>
-        <v>317.10000000000002</v>
+        <v>343.62</v>
       </c>
       <c r="E11" s="14">
         <f>[8]Main!$D$5</f>
-        <v>85299.900000000009</v>
+        <v>92433.78</v>
       </c>
       <c r="F11" s="14">
         <f>[8]Main!$D$8</f>
@@ -4697,7 +6736,7 @@
       </c>
       <c r="G11" s="14">
         <f>[8]Main!$D$9</f>
-        <v>93666.900000000009</v>
+        <v>100800.78</v>
       </c>
       <c r="H11" s="14">
         <f>[8]Model!W$16</f>
@@ -4740,78 +6779,94 @@
         <v>5139.2124562518457</v>
       </c>
       <c r="R11" s="15">
-        <f t="shared" ref="R11" si="23">$G11/M11</f>
-        <v>24.766499206768909</v>
+        <f t="shared" ref="R11" si="24">$G11/M11</f>
+        <v>26.652771020624009</v>
       </c>
       <c r="S11" s="15">
-        <f t="shared" si="21"/>
-        <v>22.07286788221537</v>
+        <f t="shared" si="22"/>
+        <v>23.753986727053604</v>
       </c>
       <c r="T11" s="15">
-        <f t="shared" si="21"/>
-        <v>20.259606386737079</v>
+        <f t="shared" si="22"/>
+        <v>21.802623192142356</v>
       </c>
       <c r="U11" s="15">
-        <f t="shared" si="21"/>
-        <v>19.125844818797791</v>
+        <f t="shared" si="22"/>
+        <v>20.582511814672802</v>
       </c>
       <c r="V11" s="15">
-        <f t="shared" si="21"/>
-        <v>18.225924846919753</v>
+        <f t="shared" si="22"/>
+        <v>19.614051930734245</v>
       </c>
       <c r="W11" s="15">
         <f>G11/[8]Model!$AM$16</f>
-        <v>15.736922070520395</v>
-      </c>
-      <c r="X11" s="23">
-        <f>[8]Model!$AB$5</f>
-        <v>47716</v>
-      </c>
-      <c r="Y11" s="26">
-        <f t="shared" si="22"/>
-        <v>1.9630082152737029</v>
-      </c>
-      <c r="Z11" s="25">
-        <f>[8]Model!$AA$22</f>
-        <v>7.2702819296064147E-2</v>
-      </c>
-      <c r="AA11" s="25">
-        <f>[8]Model!$AB$22</f>
+        <v>16.935481151908206</v>
+      </c>
+      <c r="X11" s="20">
+        <f>[8]Model!$P$34</f>
+        <v>1.7719163971312051</v>
+      </c>
+      <c r="Y11" s="16">
+        <f>[8]Model!$P$35</f>
+        <v>-0.435639287711861</v>
+      </c>
+      <c r="Z11" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.41026508664784828</v>
+      </c>
+      <c r="AD11" s="14">
+        <f>[8]Model!$AC$5</f>
+        <v>52106.25</v>
+      </c>
+      <c r="AE11" s="20">
+        <f t="shared" si="23"/>
+        <v>1.9345237855343649</v>
+      </c>
+      <c r="AF11" s="16">
+        <f>[8]Model!AB$22</f>
         <v>0.12878501135503417</v>
       </c>
-      <c r="AB11" s="25">
-        <f>[8]Model!$AB$25</f>
-        <v>0.15432978455863861</v>
-      </c>
-      <c r="AC11" s="25">
-        <f>[8]Model!$AB$27</f>
-        <v>0.10051135887333389</v>
-      </c>
-      <c r="AD11" s="16">
+      <c r="AG11" s="16">
+        <f>[8]Model!AC$22</f>
+        <v>9.2007921871070542E-2</v>
+      </c>
+      <c r="AH11" s="16">
+        <f>[8]Model!$AC$25</f>
+        <v>0.15384503778337533</v>
+      </c>
+      <c r="AI11" s="16">
+        <f>[8]Model!$AC$27</f>
+        <v>0.10308260525368838</v>
+      </c>
+      <c r="AJ11" s="16">
+        <f>[8]Model!$AC$29</f>
+        <v>8.1439962384550812E-2</v>
+      </c>
+      <c r="AK11" s="16">
         <f>[8]Model!$AP$22</f>
         <v>0.08</v>
       </c>
-      <c r="AE11" s="16">
+      <c r="AL11" s="16">
         <f>[8]Model!$AP$28</f>
-        <v>-0.33344751215489621</v>
-      </c>
-      <c r="AF11" s="11" t="str">
+        <v>-0.38489088558383555</v>
+      </c>
+      <c r="AM11" s="11" t="str">
         <f>[8]Model!$AP$29</f>
         <v>Overvalued</v>
       </c>
-      <c r="AH11" s="11">
+      <c r="AO11" s="11">
         <v>1952</v>
       </c>
-      <c r="AJ11" s="18">
+      <c r="AQ11" s="18">
         <f>[8]Main!$E$3</f>
-        <v>45862</v>
-      </c>
-      <c r="AK11" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR11" s="18">
         <f>[8]Main!$G$3</f>
         <v>45952</v>
       </c>
     </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B12" s="19" t="s">
         <v>28</v>
       </c>
@@ -4872,78 +6927,106 @@
         <v>1588.4162624936125</v>
       </c>
       <c r="R12" s="15">
-        <f t="shared" ref="R12:V13" si="24">$G12/M12</f>
+        <f t="shared" ref="R12:V13" si="25">$G12/M12</f>
         <v>66.59591913393372</v>
       </c>
       <c r="S12" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>60.707353386766897</v>
       </c>
       <c r="T12" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>53.672211306920168</v>
       </c>
       <c r="U12" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>50.258171889122295</v>
       </c>
       <c r="V12" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>48.332343235694317</v>
       </c>
       <c r="W12" s="15">
         <f>G12/[9]Model!$AO$37</f>
         <v>42.54311586413472</v>
       </c>
-      <c r="X12" s="14">
+      <c r="X12" s="20">
+        <f>[9]Model!$T$63</f>
+        <v>5.2608702802713632</v>
+      </c>
+      <c r="Y12" s="16">
+        <f>[9]Model!$T$64</f>
+        <v>-0.80991738120780687</v>
+      </c>
+      <c r="Z12" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.76267567438446748</v>
+      </c>
+      <c r="AA12" s="14">
+        <f>[9]Model!$T$11</f>
+        <v>63165</v>
+      </c>
+      <c r="AB12" s="20">
+        <f>AA12/AD12</f>
+        <v>5.1639396530722026</v>
+      </c>
+      <c r="AC12" s="20">
+        <f>AVERAGE(Y12,AB12,AL12)</f>
+        <v>1.2128627681010891</v>
+      </c>
+      <c r="AD12" s="14">
         <f>[9]Model!$AE$18</f>
         <v>12231.94</v>
       </c>
-      <c r="Y12" s="20">
-        <f>G12/X12</f>
+      <c r="AE12" s="20">
+        <f>G12/AD12</f>
         <v>6.2763453712166672</v>
       </c>
-      <c r="Z12" s="16">
+      <c r="AF12" s="16">
         <f>[9]Model!AD$49</f>
         <v>0.35902439024390254</v>
       </c>
-      <c r="AA12" s="16">
+      <c r="AG12" s="16">
         <f>[9]Model!AE$49</f>
         <v>0.25442928930366127</v>
       </c>
-      <c r="AB12" s="16">
+      <c r="AH12" s="16">
         <f>[9]Model!$AE$51</f>
         <v>0.28072109575423032</v>
       </c>
-      <c r="AC12" s="16">
+      <c r="AI12" s="16">
         <f>[9]Model!$AE$56</f>
         <v>0.16228117534912698</v>
       </c>
-      <c r="AD12" s="16">
+      <c r="AJ12" s="16">
+        <f>[9]Model!$AE$59</f>
+        <v>9.4245194793303441E-2</v>
+      </c>
+      <c r="AK12" s="16">
         <f>[9]Model!$AS$46</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE12" s="16">
+      <c r="AL12" s="16">
         <f>[9]Model!$AS$52</f>
         <v>-0.71543396756112809</v>
       </c>
-      <c r="AF12" s="11" t="str">
+      <c r="AM12" s="11" t="str">
         <f>[9]Model!$AS$53</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH12" s="11">
+      <c r="AO12" s="11">
         <v>1927</v>
       </c>
-      <c r="AJ12" s="18">
+      <c r="AQ12" s="18">
         <f>[9]Main!$E$3</f>
         <v>45906</v>
       </c>
-      <c r="AK12" s="18">
+      <c r="AR12" s="18">
         <f>[9]Main!$G$3</f>
         <v>45967</v>
       </c>
     </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B13" s="19" t="s">
         <v>34</v>
       </c>
@@ -4952,11 +7035,11 @@
       </c>
       <c r="D13" s="22">
         <f>[10]Main!$D$3</f>
-        <v>10.7</v>
+        <v>11.685</v>
       </c>
       <c r="E13" s="14">
         <f>[10]Main!$D$5</f>
-        <v>90201</v>
+        <v>98504.55</v>
       </c>
       <c r="F13" s="14">
         <f>[10]Main!$D$8</f>
@@ -4964,7 +7047,7 @@
       </c>
       <c r="G13" s="14">
         <f>[10]Main!$D$9</f>
-        <v>87822</v>
+        <v>96125.55</v>
       </c>
       <c r="H13" s="14">
         <f>[10]Model!L$16</f>
@@ -4992,93 +7075,109 @@
       </c>
       <c r="N13" s="14">
         <f>[10]Model!R$16</f>
-        <v>1792.7340799999997</v>
+        <v>1904.7799599999998</v>
       </c>
       <c r="O13" s="14">
         <f>[10]Model!S$16</f>
-        <v>2039.0654464000004</v>
+        <v>2166.5070368000002</v>
       </c>
       <c r="P13" s="14">
         <f>[10]Model!T$16</f>
-        <v>2250.0783875840002</v>
+        <v>2390.7082868080001</v>
       </c>
       <c r="Q13" s="14">
         <f>[10]Model!U$16</f>
-        <v>2444.7265855552005</v>
+        <v>2597.5219971524007</v>
       </c>
       <c r="R13" s="15">
-        <f t="shared" si="24"/>
-        <v>44.557077625570777</v>
+        <f t="shared" si="25"/>
+        <v>48.769939117199392</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" si="24"/>
-        <v>48.987745020164958</v>
+        <f t="shared" si="25"/>
+        <v>50.465435388137962</v>
       </c>
       <c r="T13" s="15">
-        <f t="shared" si="24"/>
-        <v>43.069730868644271</v>
+        <f t="shared" si="25"/>
+        <v>44.368907355122417</v>
       </c>
       <c r="U13" s="15">
-        <f t="shared" si="24"/>
-        <v>39.03064021440516</v>
+        <f t="shared" si="25"/>
+        <v>40.207979589322406</v>
       </c>
       <c r="V13" s="15">
-        <f t="shared" si="24"/>
-        <v>35.923035532439926</v>
+        <f t="shared" si="25"/>
+        <v>37.006635595532998</v>
       </c>
       <c r="W13" s="15">
         <f>G13/[10]Model!$AB$16</f>
-        <v>25.142348650280088</v>
-      </c>
-      <c r="X13" s="23">
-        <f>[10]Model!$Q$3</f>
-        <v>18909</v>
-      </c>
-      <c r="Y13" s="26">
-        <f>G13/X13</f>
-        <v>4.6444550214183726</v>
-      </c>
-      <c r="Z13" s="25">
-        <f>[10]Model!P$20</f>
-        <v>0.21937869822485201</v>
-      </c>
-      <c r="AA13" s="25">
+        <v>25.900754786619792</v>
+      </c>
+      <c r="X13" s="20">
+        <f>[10]Model!$I$32</f>
+        <v>2.5336201897733264</v>
+      </c>
+      <c r="Y13" s="16">
+        <f>[10]Model!$I$33</f>
+        <v>-0.60530784999409626</v>
+      </c>
+      <c r="Z13" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.57480585497831804</v>
+      </c>
+      <c r="AD13" s="14">
+        <f>[10]Model!$R$3</f>
+        <v>21178.080000000002</v>
+      </c>
+      <c r="AE13" s="20">
+        <f>G13/AD13</f>
+        <v>4.5389171256317855</v>
+      </c>
+      <c r="AF13" s="16">
         <f>[10]Model!Q$20</f>
         <v>0.14697318937280124</v>
       </c>
-      <c r="AB13" s="25">
-        <f>[10]Model!$Q$21</f>
-        <v>0.22322703474535935</v>
-      </c>
-      <c r="AC13" s="25">
-        <f>[10]Model!$Q$24</f>
-        <v>0.12459675286900418</v>
-      </c>
-      <c r="AD13" s="16">
+      <c r="AG13" s="16">
+        <f>[10]Model!R$20</f>
+        <v>0.12000000000000011</v>
+      </c>
+      <c r="AH13" s="16">
+        <f>[10]Model!$R$21</f>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="AI13" s="16">
+        <f>[10]Model!$R$24</f>
+        <v>0.12645705370836258</v>
+      </c>
+      <c r="AJ13" s="16">
+        <f>[10]Model!$R$26</f>
+        <v>8.994110703142115E-2</v>
+      </c>
+      <c r="AK13" s="16">
         <f>[10]Model!$AE$22</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE13" s="16">
+      <c r="AL13" s="16">
         <f>[10]Model!$AE$28</f>
-        <v>-0.53007610364432378</v>
-      </c>
-      <c r="AF13" s="11" t="str">
+        <v>-0.54430385996253983</v>
+      </c>
+      <c r="AM13" s="11" t="str">
         <f>[10]Model!$AE$29</f>
-        <v>Overvalued</v>
-      </c>
-      <c r="AH13" s="11">
+        <v>Heavily overvalued</v>
+      </c>
+      <c r="AO13" s="11">
         <v>1906</v>
       </c>
-      <c r="AJ13" s="18">
+      <c r="AQ13" s="18">
         <f>[10]Main!$E$3</f>
-        <v>45898</v>
-      </c>
-      <c r="AK13" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR13" s="18">
         <f>[10]Main!$G$3</f>
         <v>46079</v>
       </c>
     </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
@@ -5087,11 +7186,11 @@
       </c>
       <c r="D14" s="22">
         <f>[11]Main!$D$3</f>
-        <v>19.254999999999999</v>
+        <v>20.55</v>
       </c>
       <c r="E14" s="14">
         <f>[11]Main!$D$5</f>
-        <v>57765</v>
+        <v>61650</v>
       </c>
       <c r="F14" s="14">
         <f>[11]Main!$D$8</f>
@@ -5099,115 +7198,143 @@
       </c>
       <c r="G14" s="14">
         <f>[11]Main!$D$9</f>
-        <v>62672</v>
+        <v>66557</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14">
-        <f>[11]Model!N$32</f>
+        <f>[11]Model!N$41</f>
         <v>1758</v>
       </c>
       <c r="K14" s="14">
-        <f>[11]Model!O$32</f>
+        <f>[11]Model!O$41</f>
         <v>1591</v>
       </c>
       <c r="L14" s="14">
-        <f>[11]Model!P$32</f>
+        <f>[11]Model!P$41</f>
         <v>1857</v>
       </c>
       <c r="M14" s="14">
-        <f>[11]Model!Q$32</f>
+        <f>[11]Model!Q$41</f>
         <v>1956</v>
       </c>
       <c r="N14" s="14">
-        <f>[11]Model!R$32</f>
+        <f>[11]Model!R$41</f>
         <v>2983.0295450000012</v>
       </c>
       <c r="O14" s="14">
-        <f>[11]Model!S$32</f>
+        <f>[11]Model!S$41</f>
         <v>3274.0576822999979</v>
       </c>
       <c r="P14" s="14">
-        <f>[11]Model!T$32</f>
+        <f>[11]Model!T$41</f>
         <v>3558.6704355280026</v>
       </c>
       <c r="Q14" s="14">
-        <f>[11]Model!U$32</f>
+        <f>[11]Model!U$41</f>
         <v>3774.8694653950824</v>
       </c>
       <c r="R14" s="15">
-        <f t="shared" ref="R14" si="25">$G14/M14</f>
-        <v>32.040899795501019</v>
+        <f t="shared" ref="R14" si="26">$G14/M14</f>
+        <v>34.027096114519431</v>
       </c>
       <c r="S14" s="15">
-        <f t="shared" si="21"/>
-        <v>21.00951366876253</v>
+        <f t="shared" si="22"/>
+        <v>22.311880923727148</v>
       </c>
       <c r="T14" s="15">
-        <f t="shared" si="21"/>
-        <v>19.141996287607689</v>
+        <f t="shared" si="22"/>
+        <v>20.328597250994147</v>
       </c>
       <c r="U14" s="15">
-        <f t="shared" si="21"/>
-        <v>17.611071644711409</v>
+        <f t="shared" si="22"/>
+        <v>18.702771500144515</v>
       </c>
       <c r="V14" s="15">
-        <f t="shared" si="21"/>
-        <v>16.60242839508112</v>
+        <f t="shared" si="22"/>
+        <v>17.631603055454015</v>
       </c>
       <c r="W14" s="15">
-        <f>G14/[11]Model!$AB$32</f>
-        <v>12.771379054505589</v>
-      </c>
-      <c r="X14" s="23">
-        <f>[11]Model!$Q$13</f>
-        <v>26312</v>
-      </c>
-      <c r="Y14" s="26">
-        <f t="shared" si="22"/>
-        <v>2.3818789905746427</v>
-      </c>
-      <c r="Z14" s="25">
-        <f>[11]Model!P$41</f>
-        <v>8.5614827359111967E-2</v>
-      </c>
-      <c r="AA14" s="25">
-        <f>[11]Model!Q$41</f>
+        <f>G14/[11]Model!$AB$41</f>
+        <v>13.563069245129061</v>
+      </c>
+      <c r="X14" s="20">
+        <f>[11]Model!$I$61</f>
+        <v>1.8487542012721869</v>
+      </c>
+      <c r="Y14" s="16">
+        <f>[11]Model!$I$62</f>
+        <v>-0.45909521162312006</v>
+      </c>
+      <c r="Z14" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.29409758332501079</v>
+      </c>
+      <c r="AA14" s="14">
+        <f>[11]Model!$I$10</f>
+        <v>75400</v>
+      </c>
+      <c r="AB14" s="20">
+        <f>AA14/AD14</f>
+        <v>2.6692051255818532</v>
+      </c>
+      <c r="AC14" s="20">
+        <f>AVERAGE(Y14,AB14,AL14)</f>
+        <v>0.6936699863106105</v>
+      </c>
+      <c r="AD14" s="14">
+        <f>[11]Model!$R$22</f>
+        <v>28248.11</v>
+      </c>
+      <c r="AE14" s="20">
+        <f t="shared" si="23"/>
+        <v>2.3561576332009468</v>
+      </c>
+      <c r="AF14" s="16">
+        <f>[11]Model!Q$50</f>
         <v>0.14013346043851294</v>
       </c>
-      <c r="AB14" s="25">
-        <f>[11]Model!$Q$42</f>
-        <v>0.65472027972027969</v>
-      </c>
-      <c r="AC14" s="25">
-        <f>[11]Model!$Q$45</f>
-        <v>8.3840072970507759E-2</v>
-      </c>
-      <c r="AD14" s="16">
-        <f>[11]Model!$AE$39</f>
+      <c r="AG14" s="16">
+        <f>[11]Model!R$50</f>
+        <v>7.3582775919732502E-2</v>
+      </c>
+      <c r="AH14" s="16">
+        <f>[11]Model!$R$51</f>
+        <v>0.65</v>
+      </c>
+      <c r="AI14" s="16">
+        <f>[11]Model!$R$54</f>
+        <v>0.12268047313607891</v>
+      </c>
+      <c r="AJ14" s="16">
+        <f>[11]Model!$R$56</f>
+        <v>0.10560103118403324</v>
+      </c>
+      <c r="AK14" s="16">
+        <f>[11]Model!$AE$48</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AE14" s="16">
-        <f>[11]Model!$AE$45</f>
-        <v>-7.0527347483917202E-2</v>
-      </c>
-      <c r="AF14" s="11" t="str">
-        <f>[11]Model!$AE$46</f>
-        <v>Fairly valued</v>
-      </c>
-      <c r="AH14" s="11">
+      <c r="AL14" s="16">
+        <f>[11]Model!$AE$54</f>
+        <v>-0.12909995502690153</v>
+      </c>
+      <c r="AM14" s="11" t="str">
+        <f>[11]Model!$AE$55</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AO14" s="11">
         <v>1953</v>
       </c>
-      <c r="AJ14" s="18">
+      <c r="AQ14" s="18">
         <f>[11]Main!$E$3</f>
-        <v>45868</v>
-      </c>
-      <c r="AK14" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR14" s="18">
         <f>[11]Main!$G$3</f>
         <v>46072</v>
       </c>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B15" s="19" t="s">
         <v>27</v>
       </c>
@@ -5216,11 +7343,11 @@
       </c>
       <c r="D15" s="13">
         <f>[12]Main!$D$3</f>
-        <v>277.22000000000003</v>
+        <v>297.39</v>
       </c>
       <c r="E15" s="14">
         <f>[12]Main!$D$5</f>
-        <v>51867.862000000001</v>
+        <v>55641.668999999994</v>
       </c>
       <c r="F15" s="14">
         <f>[12]Main!$D$8</f>
@@ -5228,7 +7355,7 @@
       </c>
       <c r="G15" s="14">
         <f>[12]Main!$D$9</f>
-        <v>63487.862000000001</v>
+        <v>67261.668999999994</v>
       </c>
       <c r="I15" s="14">
         <f>[12]Model!T$18</f>
@@ -5268,77 +7395,90 @@
       </c>
       <c r="R15" s="15">
         <f>$G15/M15</f>
-        <v>42.268882822902796</v>
+        <v>44.781404127829553</v>
       </c>
       <c r="S15" s="15">
-        <f t="shared" ref="S15:V18" si="26">$G15/N15</f>
-        <v>28.283914738602331</v>
+        <f t="shared" ref="S15:V18" si="27">$G15/N15</f>
+        <v>29.965150049817257</v>
       </c>
       <c r="T15" s="15">
-        <f t="shared" si="26"/>
-        <v>26.49185084915845</v>
+        <f t="shared" si="27"/>
+        <v>28.066563385194236</v>
       </c>
       <c r="U15" s="15">
-        <f t="shared" si="26"/>
-        <v>25.091421207058183</v>
+        <f t="shared" si="27"/>
+        <v>26.582890253395643</v>
       </c>
       <c r="V15" s="15">
-        <f t="shared" si="26"/>
-        <v>24.029780253713447</v>
+        <f t="shared" si="27"/>
+        <v>25.458143882180341</v>
       </c>
       <c r="W15" s="15">
         <f>G15/[12]Model!$AI$18</f>
-        <v>18.587528267497191</v>
-      </c>
-      <c r="X15" s="23">
+        <v>19.692396853063652</v>
+      </c>
+      <c r="X15" s="20">
+        <f>[12]Model!$P$36</f>
+        <v>1.6309813045586807</v>
+      </c>
+      <c r="Y15" s="16">
+        <f>[12]Model!$P$37</f>
+        <v>-0.38687218718881322</v>
+      </c>
+      <c r="Z15" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.47734610923232346</v>
+      </c>
+      <c r="AD15" s="23">
         <f>[12]Model!$X$5</f>
         <v>21325</v>
       </c>
-      <c r="Y15" s="26">
-        <f t="shared" ref="Y15:Y18" si="27">G15/X15</f>
-        <v>2.9771564830011723</v>
-      </c>
-      <c r="Z15" s="25">
+      <c r="AE15" s="26">
+        <f t="shared" ref="AE15:AE18" si="28">G15/AD15</f>
+        <v>3.154122813599062</v>
+      </c>
+      <c r="AF15" s="25">
         <f>[12]Model!$W$24</f>
         <v>0.13814324229281438</v>
       </c>
-      <c r="AA15" s="25">
+      <c r="AG15" s="25">
         <f>[12]Model!$X$24</f>
         <v>9.815129512333276E-2</v>
       </c>
-      <c r="AB15" s="25">
+      <c r="AH15" s="25">
         <f>[12]Model!$X$27</f>
         <v>0.25903868698710436</v>
       </c>
-      <c r="AC15" s="25">
+      <c r="AI15" s="25">
         <f>[12]Model!$X$29</f>
         <v>8.9941383352872217E-2</v>
       </c>
-      <c r="AD15" s="16">
+      <c r="AJ15" s="25"/>
+      <c r="AK15" s="16">
         <f>[12]Model!$AL$24</f>
         <v>0.08</v>
       </c>
-      <c r="AE15" s="16">
+      <c r="AL15" s="16">
         <f>[12]Model!$AL$30</f>
-        <v>-0.5363754386448315</v>
-      </c>
-      <c r="AF15" s="11" t="str">
+        <v>-0.56782003127583369</v>
+      </c>
+      <c r="AM15" s="11" t="str">
         <f>[12]Model!$AL$31</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH15" s="11">
+      <c r="AO15" s="11">
         <v>1890</v>
       </c>
-      <c r="AJ15" s="18">
+      <c r="AQ15" s="18">
         <f>[12]Main!$E$3</f>
-        <v>45898</v>
-      </c>
-      <c r="AK15" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR15" s="18">
         <f>[12]Main!$G$3</f>
         <v>45953</v>
       </c>
     </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B16" s="19" t="s">
         <v>35</v>
       </c>
@@ -5347,11 +7487,11 @@
       </c>
       <c r="D16" s="17">
         <f>[13]Main!$D$3</f>
-        <v>235.1</v>
+        <v>271</v>
       </c>
       <c r="E16" s="14">
         <f>[13]Main!$D$5</f>
-        <v>48289.54</v>
+        <v>55663.4</v>
       </c>
       <c r="F16" s="14">
         <f>[13]Main!$D$8</f>
@@ -5359,121 +7499,134 @@
       </c>
       <c r="G16" s="14">
         <f>[13]Main!$D$9</f>
-        <v>49697.64</v>
+        <v>57071.5</v>
       </c>
       <c r="H16" s="14">
-        <f>[13]Model!K$22</f>
+        <f>[13]Model!K$24</f>
         <v>1146.4000000000005</v>
       </c>
       <c r="I16" s="14">
-        <f>[13]Model!L$22</f>
+        <f>[13]Model!L$24</f>
         <v>491.90000000000072</v>
       </c>
       <c r="J16" s="14">
-        <f>[13]Model!M$22</f>
+        <f>[13]Model!M$24</f>
         <v>1016.7999999999997</v>
       </c>
       <c r="K16" s="14">
-        <f>[13]Model!N$22</f>
+        <f>[13]Model!N$24</f>
         <v>1121.8999999999996</v>
       </c>
       <c r="L16" s="14">
-        <f>[13]Model!O$22</f>
+        <f>[13]Model!O$24</f>
         <v>928.6000000000015</v>
       </c>
       <c r="M16" s="14">
-        <f>[13]Model!P$22</f>
+        <f>[13]Model!P$24</f>
         <v>932.29999999999723</v>
       </c>
       <c r="N16" s="14">
-        <f>[13]Model!Q$22</f>
+        <f>[13]Model!Q$24</f>
         <v>1473.4199211999967</v>
       </c>
       <c r="O16" s="14">
-        <f>[13]Model!R$22</f>
+        <f>[13]Model!R$24</f>
         <v>1674.1472117759988</v>
       </c>
       <c r="P16" s="14">
-        <f>[13]Model!S$22</f>
+        <f>[13]Model!S$24</f>
         <v>1801.8286222247989</v>
       </c>
       <c r="Q16" s="14">
-        <f>[13]Model!T$22</f>
+        <f>[13]Model!T$24</f>
         <v>1905.822140949791</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" ref="R16" si="28">$G16/M16</f>
-        <v>53.306489327469855</v>
+        <f t="shared" ref="R16" si="29">$G16/M16</f>
+        <v>61.21581036147181</v>
       </c>
       <c r="S16" s="15">
-        <f t="shared" si="26"/>
-        <v>33.729447583092792</v>
+        <f t="shared" si="27"/>
+        <v>38.734035816157068</v>
       </c>
       <c r="T16" s="15">
-        <f t="shared" si="26"/>
-        <v>29.685346456049619</v>
+        <f t="shared" si="27"/>
+        <v>34.089893408750115</v>
       </c>
       <c r="U16" s="15">
-        <f t="shared" si="26"/>
-        <v>27.581779635976748</v>
+        <f t="shared" si="27"/>
+        <v>31.674211018765618</v>
       </c>
       <c r="V16" s="15">
-        <f t="shared" si="26"/>
-        <v>26.076746057338038</v>
+        <f t="shared" si="27"/>
+        <v>29.945868910704167</v>
       </c>
       <c r="W16" s="15">
-        <f>G16/[13]Model!$AA$22</f>
-        <v>22.492554608963555</v>
-      </c>
-      <c r="X16" s="23">
-        <f>[13]Model!$P$3</f>
+        <f>G16/[13]Model!$AA$24</f>
+        <v>25.82987502757603</v>
+      </c>
+      <c r="X16" s="20">
+        <f>[13]Model!$G$42</f>
+        <v>1.4676241417440277</v>
+      </c>
+      <c r="Y16" s="16">
+        <f>[13]Model!$G$43</f>
+        <v>-0.31862663501046928</v>
+      </c>
+      <c r="Z16" s="16">
+        <f t="shared" si="7"/>
+        <v>-0.45603298290579602</v>
+      </c>
+      <c r="AD16" s="23">
+        <f>[13]Model!$P$5</f>
         <v>20576.599999999999</v>
       </c>
-      <c r="Y16" s="26">
-        <f t="shared" si="27"/>
-        <v>2.4152503329024233</v>
-      </c>
-      <c r="Z16" s="25">
-        <f>[13]Model!O$26</f>
+      <c r="AE16" s="26">
+        <f t="shared" si="28"/>
+        <v>2.7736117725960558</v>
+      </c>
+      <c r="AF16" s="25">
+        <f>[13]Model!O$29</f>
         <v>4.89276444606348E-2</v>
       </c>
-      <c r="AA16" s="25">
-        <f>[13]Model!P$26</f>
+      <c r="AG16" s="25">
+        <f>[13]Model!P$29</f>
         <v>0.11657007662086771</v>
       </c>
-      <c r="AB16" s="25">
-        <f>[13]Model!$P$27</f>
+      <c r="AH16" s="25">
+        <f>[13]Model!$P$30</f>
         <v>0.26116559587103788</v>
       </c>
-      <c r="AC16" s="25">
-        <f>[13]Model!$P$31</f>
+      <c r="AI16" s="25">
+        <f>[13]Model!$P$34</f>
         <v>6.1341523866916652E-2</v>
       </c>
-      <c r="AD16" s="16">
-        <f>[13]Model!$AD$29</f>
+      <c r="AJ16" s="25"/>
+      <c r="AK16" s="16">
+        <f>[13]Model!$AD$32</f>
         <v>0.08</v>
       </c>
-      <c r="AE16" s="16">
-        <f>[13]Model!$AD$35</f>
-        <v>-0.53135711887326365</v>
-      </c>
-      <c r="AF16" s="11" t="str">
-        <f>[13]Model!$AD$36</f>
+      <c r="AL16" s="16">
+        <f>[13]Model!$AD$38</f>
+        <v>-0.59343933080112277</v>
+      </c>
+      <c r="AM16" s="11" t="str">
+        <f>[13]Model!$AD$39</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH16" s="11">
+      <c r="AO16" s="11">
         <v>1949</v>
       </c>
-      <c r="AJ16" s="18">
+      <c r="AQ16" s="18">
         <f>[13]Main!$E$3</f>
-        <v>45868</v>
-      </c>
-      <c r="AK16" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR16" s="18">
         <f>[13]Main!$G$3</f>
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="17" spans="2:37" x14ac:dyDescent="0.3">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="17" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B17" s="19" t="s">
         <v>86</v>
       </c>
@@ -5502,20 +7655,21 @@
       <c r="U17" s="15"/>
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AJ17" s="18">
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="26"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
+      <c r="AQ17" s="18">
         <v>45930</v>
       </c>
-      <c r="AK17" s="18"/>
-    </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AR17" s="18"/>
+    </row>
+    <row r="18" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B18" s="19" t="s">
         <v>36</v>
       </c>
@@ -5524,11 +7678,11 @@
       </c>
       <c r="D18" s="17">
         <f>[14]Main!$D$3</f>
-        <v>27.18</v>
+        <v>28.96</v>
       </c>
       <c r="E18" s="14">
         <f>[14]Main!$D$5</f>
-        <v>35695.493999999999</v>
+        <v>38033.167999999998</v>
       </c>
       <c r="F18" s="14">
         <f>[14]Main!$D$8</f>
@@ -5536,7 +7690,7 @@
       </c>
       <c r="G18" s="14">
         <f>[14]Main!$D$9</f>
-        <v>34236.493999999999</v>
+        <v>36574.167999999998</v>
       </c>
       <c r="H18" s="14">
         <f>[14]Model!Q$23</f>
@@ -5579,78 +7733,94 @@
         <v>1456.7690142637746</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" ref="R18" si="29">$G18/M18</f>
-        <v>28.523280846455048</v>
+        <f t="shared" ref="R18" si="30">$G18/M18</f>
+        <v>30.47085561942847</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="26"/>
-        <v>30.747942997121896</v>
+        <f t="shared" si="27"/>
+        <v>32.847418103943696</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="26"/>
-        <v>24.073564944371913</v>
+        <f t="shared" si="27"/>
+        <v>25.717312311078611</v>
       </c>
       <c r="U18" s="15">
-        <f t="shared" si="26"/>
-        <v>23.712894136149352</v>
+        <f t="shared" si="27"/>
+        <v>25.33201483486426</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="26"/>
-        <v>23.501662696541167</v>
+        <f t="shared" si="27"/>
+        <v>25.1063604743707</v>
       </c>
       <c r="W18" s="15">
         <f>G18/[14]Model!$AG$23</f>
-        <v>19.802862236524049</v>
-      </c>
-      <c r="X18" s="23">
-        <f>[14]Model!$V$7</f>
-        <v>6213.6</v>
-      </c>
-      <c r="Y18" s="26">
-        <f t="shared" si="27"/>
-        <v>5.5099288657139169</v>
-      </c>
-      <c r="Z18" s="25">
-        <f>[14]Model!U$30</f>
-        <v>5.0500414805923599E-2</v>
-      </c>
-      <c r="AA18" s="25">
+        <v>21.155005250230538</v>
+      </c>
+      <c r="X18" s="20">
+        <f>[14]Model!$L$44</f>
+        <v>2.537177027186392</v>
+      </c>
+      <c r="Y18" s="16">
+        <f>[14]Model!$L$45</f>
+        <v>-0.60586116408717761</v>
+      </c>
+      <c r="Z18" s="16">
+        <f>AVERAGE(Y18,AL18)</f>
+        <v>-0.53778312153274932</v>
+      </c>
+      <c r="AD18" s="14">
+        <f>[14]Model!$W$7</f>
+        <v>6448.74</v>
+      </c>
+      <c r="AE18" s="20">
+        <f t="shared" si="28"/>
+        <v>5.6715215685544775</v>
+      </c>
+      <c r="AF18" s="16">
         <f>[14]Model!V$30</f>
         <v>4.4056860570622192E-2</v>
       </c>
-      <c r="AB18" s="25">
-        <f>[14]Model!$V$33</f>
-        <v>0.83643942320072096</v>
-      </c>
-      <c r="AC18" s="25">
-        <f>[14]Model!$V$37</f>
-        <v>0.2188264452169435</v>
-      </c>
-      <c r="AD18" s="16">
+      <c r="AG18" s="16">
+        <f>[14]Model!W$30</f>
+        <v>3.7842796446504456E-2</v>
+      </c>
+      <c r="AH18" s="16">
+        <f>[14]Model!$W$33</f>
+        <v>0.8307891805220865</v>
+      </c>
+      <c r="AI18" s="16">
+        <f>[14]Model!$W$37</f>
+        <v>0.19589976801669784</v>
+      </c>
+      <c r="AJ18" s="16">
+        <f>[14]Model!$W$39</f>
+        <v>0.17266262908723254</v>
+      </c>
+      <c r="AK18" s="16">
         <f>[14]Model!$AJ$29</f>
         <v>0.08</v>
       </c>
-      <c r="AE18" s="16">
+      <c r="AL18" s="16">
         <f>[14]Model!$AJ$35</f>
-        <v>-0.43497641969139733</v>
-      </c>
-      <c r="AF18" s="11" t="str">
+        <v>-0.46970507897832114</v>
+      </c>
+      <c r="AM18" s="11" t="str">
         <f>[14]Model!$AJ$36</f>
         <v>Overvalued</v>
       </c>
-      <c r="AH18" s="11">
+      <c r="AO18" s="11">
         <v>1971</v>
       </c>
-      <c r="AJ18" s="18">
+      <c r="AQ18" s="18">
         <f>[14]Main!$E$3</f>
-        <v>45868</v>
-      </c>
-      <c r="AK18" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR18" s="18">
         <f>[14]Main!$G$3</f>
         <v>46079</v>
       </c>
     </row>
-    <row r="19" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B19" s="19" t="s">
         <v>38</v>
       </c>
@@ -5659,11 +7829,11 @@
       </c>
       <c r="D19" s="17">
         <f>[15]Main!$D$3</f>
-        <v>47.27</v>
+        <v>55.8</v>
       </c>
       <c r="E19" s="14">
         <f>[15]Main!$D$5</f>
-        <v>27246.428</v>
+        <v>32163.119999999995</v>
       </c>
       <c r="F19" s="14">
         <f>[15]Main!$D$8</f>
@@ -5671,7 +7841,7 @@
       </c>
       <c r="G19" s="14">
         <f>[15]Main!$D$9</f>
-        <v>27513.428</v>
+        <v>32430.119999999995</v>
       </c>
       <c r="H19" s="14">
         <f>[15]Model!T$19</f>
@@ -5714,78 +7884,91 @@
         <v>1993.765444011</v>
       </c>
       <c r="R19" s="15">
-        <f t="shared" ref="R19:V19" si="30">$G19/M19</f>
-        <v>25.66551119402985</v>
+        <f t="shared" ref="R19:V19" si="31">$G19/M19</f>
+        <v>30.251977611940294</v>
       </c>
       <c r="S19" s="15">
-        <f t="shared" si="30"/>
-        <v>27.045735560951908</v>
+        <f t="shared" si="31"/>
+        <v>31.87885020107046</v>
       </c>
       <c r="T19" s="15">
-        <f t="shared" si="30"/>
-        <v>15.185074369846259</v>
+        <f t="shared" si="31"/>
+        <v>17.898670569986351</v>
       </c>
       <c r="U19" s="15">
-        <f t="shared" si="30"/>
-        <v>14.336745800724874</v>
+        <f t="shared" si="31"/>
+        <v>16.898744377727255</v>
       </c>
       <c r="V19" s="15">
-        <f t="shared" si="30"/>
-        <v>13.799731599645581</v>
+        <f t="shared" si="31"/>
+        <v>16.265764911020835</v>
       </c>
       <c r="W19" s="15">
         <f>G19/[15]Model!$AJ$19</f>
-        <v>12.020001089934652</v>
-      </c>
-      <c r="X19" s="23">
+        <v>14.167993815482081</v>
+      </c>
+      <c r="X19" s="20">
+        <f>[15]Model!$O$33</f>
+        <v>0.99186811842427192</v>
+      </c>
+      <c r="Y19" s="16">
+        <f>[15]Model!$O$34</f>
+        <v>8.1985512233690994E-3</v>
+      </c>
+      <c r="Z19" s="16">
+        <f>AVERAGE(Y19,AL19)</f>
+        <v>-0.11865420607651811</v>
+      </c>
+      <c r="AD19" s="23">
         <f>[15]Model!$Y$3</f>
         <v>17763</v>
       </c>
-      <c r="Y19" s="26">
-        <f t="shared" ref="Y19:Y25" si="31">G19/X19</f>
-        <v>1.5489178629735969</v>
-      </c>
-      <c r="Z19" s="25">
+      <c r="AE19" s="26">
+        <f t="shared" ref="AE19:AE25" si="32">G19/AD19</f>
+        <v>1.8257118729944264</v>
+      </c>
+      <c r="AF19" s="25">
         <f>[15]Model!$X$23</f>
         <v>3.9284986066743688E-2</v>
       </c>
-      <c r="AA19" s="25">
+      <c r="AG19" s="25">
         <f>[15]Model!$Y$23</f>
         <v>0.1616637237590739</v>
       </c>
-      <c r="AB19" s="25">
+      <c r="AH19" s="25">
         <f>[15]Model!$Y$24</f>
         <v>0.11349434217193041</v>
       </c>
-      <c r="AC19" s="25">
+      <c r="AI19" s="25">
         <f>[15]Model!$Y$26</f>
         <v>6.6430220120475142E-2</v>
       </c>
-      <c r="AD19" s="16">
+      <c r="AJ19" s="25"/>
+      <c r="AK19" s="16">
         <f>[15]Model!$AM$25</f>
         <v>0.08</v>
       </c>
-      <c r="AE19" s="16">
+      <c r="AL19" s="16">
         <f>[15]Model!$AM$31</f>
-        <v>-0.10935664388414268</v>
-      </c>
-      <c r="AF19" s="11" t="str">
+        <v>-0.24550696337640532</v>
+      </c>
+      <c r="AM19" s="11" t="str">
         <f>[15]Model!$AM$32</f>
         <v>Fairly valued</v>
       </c>
-      <c r="AH19" s="11">
+      <c r="AO19" s="11">
         <v>1996</v>
       </c>
-      <c r="AJ19" s="18">
+      <c r="AQ19" s="18">
         <f>[15]Main!$E$3</f>
-        <v>45904</v>
-      </c>
-      <c r="AK19" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR19" s="18">
         <f>[15]Main!$G$3</f>
         <v>45868</v>
       </c>
     </row>
-    <row r="20" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B20" s="19" t="s">
         <v>74</v>
       </c>
@@ -5794,11 +7977,11 @@
       </c>
       <c r="D20" s="17">
         <f>[16]Main!$D$3</f>
-        <v>180.62</v>
+        <v>195.58</v>
       </c>
       <c r="E20" s="14">
         <f>[16]Main!$D$5</f>
-        <v>23173.546000000002</v>
+        <v>25092.914000000004</v>
       </c>
       <c r="F20" s="14">
         <f>[16]Main!$D$8</f>
@@ -5806,7 +7989,7 @@
       </c>
       <c r="G20" s="14">
         <f>[16]Main!$D$9</f>
-        <v>27347.546000000002</v>
+        <v>29266.914000000004</v>
       </c>
       <c r="H20" s="14">
         <f>[16]Model!P$18</f>
@@ -5849,78 +8032,91 @@
         <v>1981.3585502100002</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" ref="R20" si="32">$G20/M20</f>
-        <v>21.808250398724084</v>
+        <f t="shared" ref="R20" si="33">$G20/M20</f>
+        <v>23.338846889952155</v>
       </c>
       <c r="S20" s="15">
-        <f t="shared" ref="S20:S25" si="33">$G20/N20</f>
-        <v>18.373055827774042</v>
+        <f t="shared" ref="S20:S25" si="34">$G20/N20</f>
+        <v>19.662555639495466</v>
       </c>
       <c r="T20" s="15">
-        <f t="shared" ref="T20:T25" si="34">$G20/O20</f>
-        <v>14.980942882667502</v>
+        <f t="shared" ref="T20:T25" si="35">$G20/O20</f>
+        <v>16.032369668047799</v>
       </c>
       <c r="U20" s="15">
-        <f t="shared" ref="U20:U25" si="35">$G20/P20</f>
-        <v>14.275296120727653</v>
+        <f t="shared" ref="U20:U25" si="36">$G20/P20</f>
+        <v>15.277197591691403</v>
       </c>
       <c r="V20" s="15">
-        <f t="shared" ref="V20:V25" si="36">$G20/Q20</f>
-        <v>13.802421574379604</v>
+        <f t="shared" ref="V20:V25" si="37">$G20/Q20</f>
+        <v>14.771134682765046</v>
       </c>
       <c r="W20" s="15">
         <f>G20/[16]Model!$AF$18</f>
-        <v>12.733418423610921</v>
-      </c>
-      <c r="X20" s="23">
+        <v>13.627104308731628</v>
+      </c>
+      <c r="X20" s="20">
+        <f>[16]Model!$L$34</f>
+        <v>2.1600792678426455</v>
+      </c>
+      <c r="Y20" s="16">
+        <f>[16]Model!$L$35</f>
+        <v>-0.53705402626324061</v>
+      </c>
+      <c r="Z20" s="16">
+        <f>AVERAGE(Y20,AL20)</f>
+        <v>-0.37664617950769924</v>
+      </c>
+      <c r="AD20" s="23">
         <f>[16]Model!$U$3</f>
         <v>16662</v>
       </c>
-      <c r="Y20" s="26">
-        <f t="shared" si="31"/>
-        <v>1.6413123274516865</v>
-      </c>
-      <c r="Z20" s="25">
+      <c r="AE20" s="26">
+        <f t="shared" si="32"/>
+        <v>1.7565066618653224</v>
+      </c>
+      <c r="AF20" s="25">
         <f>[16]Model!T$22</f>
         <v>7.2381217004723553E-2</v>
       </c>
-      <c r="AA20" s="25">
+      <c r="AG20" s="25">
         <f>[16]Model!U$22</f>
         <v>7.9284881461329171E-2</v>
       </c>
-      <c r="AB20" s="25">
+      <c r="AH20" s="25">
         <f>[16]Model!$U$23</f>
         <v>0.16792701956547834</v>
       </c>
-      <c r="AC20" s="25">
+      <c r="AI20" s="25">
         <f>[16]Model!$U$26</f>
         <v>0.10731004681310767</v>
       </c>
-      <c r="AD20" s="16">
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="16">
         <f>[16]Model!$AI$24</f>
         <v>0.08</v>
       </c>
-      <c r="AE20" s="16">
+      <c r="AL20" s="16">
         <f>[16]Model!$AI$30</f>
-        <v>-0.15132262827852416</v>
-      </c>
-      <c r="AF20" s="11" t="str">
+        <v>-0.21623833275215787</v>
+      </c>
+      <c r="AM20" s="11" t="str">
         <f>[16]Model!$AI$31</f>
         <v>Slightly overvalued</v>
       </c>
-      <c r="AH20" s="11">
+      <c r="AO20" s="11">
         <v>1969</v>
       </c>
-      <c r="AJ20" s="18">
+      <c r="AQ20" s="18">
         <f>[16]Main!$E$3</f>
-        <v>45898</v>
-      </c>
-      <c r="AK20" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR20" s="18">
         <f>[16]Main!$G$3</f>
         <v>45965</v>
       </c>
     </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B21" s="19" t="s">
         <v>69</v>
       </c>
@@ -5960,44 +8156,62 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="15">
-        <f t="shared" ref="R21" si="37">$G21/M21</f>
+        <f t="shared" ref="R21" si="38">$G21/M21</f>
         <v>64.150899999999993</v>
       </c>
       <c r="S21" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>47.326279668857218</v>
       </c>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
       <c r="V21" s="15"/>
       <c r="W21" s="15"/>
-      <c r="X21" s="14">
+      <c r="X21" s="20">
+        <f>[17]Model!$L$42</f>
+        <v>1.845136271766169</v>
+      </c>
+      <c r="Y21" s="16">
+        <f>[17]Model!$L$43</f>
+        <v>-0.45803460952897668</v>
+      </c>
+      <c r="AA21" s="14">
+        <f>[17]Model!$L$3</f>
+        <v>16100</v>
+      </c>
+      <c r="AB21" s="20">
+        <f>AA21/AD21</f>
+        <v>1.7124872228243699</v>
+      </c>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="14">
         <f>[17]Model!$V$8</f>
         <v>9401.5300000000007</v>
       </c>
-      <c r="Y21" s="20">
-        <f t="shared" si="31"/>
+      <c r="AE21" s="20">
+        <f t="shared" si="32"/>
         <v>2.5246776854405608</v>
       </c>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="16">
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="16">
         <f>[17]Model!$V$31</f>
         <v>8.5000577034045177E-2</v>
       </c>
-      <c r="AB21" s="16">
+      <c r="AH21" s="16">
         <f>[17]Model!$V$32</f>
         <v>0.1980854180117492</v>
       </c>
-      <c r="AC21" s="16">
+      <c r="AI21" s="16">
         <f>[17]Model!$V$35</f>
         <v>0.11177712563806108</v>
       </c>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="18"/>
-    </row>
-    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AJ21" s="16"/>
+      <c r="AK21" s="16"/>
+      <c r="AL21" s="16"/>
+      <c r="AQ21" s="18"/>
+      <c r="AR21" s="18"/>
+    </row>
+    <row r="22" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B22" s="19" t="s">
         <v>70</v>
       </c>
@@ -6006,11 +8220,11 @@
       </c>
       <c r="D22" s="13">
         <f>[18]Main!$D$3</f>
-        <v>78.45</v>
+        <v>86.85</v>
       </c>
       <c r="E22" s="14">
         <f>[18]Main!$D$5</f>
-        <v>13979.789999999999</v>
+        <v>15476.669999999998</v>
       </c>
       <c r="F22" s="14">
         <f>[18]Main!$D$8</f>
@@ -6018,121 +8232,135 @@
       </c>
       <c r="G22" s="14">
         <f>[18]Main!$D$9</f>
-        <v>16279.789999999999</v>
+        <v>17776.669999999998</v>
       </c>
       <c r="H22" s="14">
-        <f>[18]Model!P$22</f>
+        <f>[18]Model!P$29</f>
         <v>815</v>
       </c>
       <c r="I22" s="14">
-        <f>[18]Model!Q$22</f>
+        <f>[18]Model!Q$29</f>
         <v>309</v>
       </c>
       <c r="J22" s="14">
-        <f>[18]Model!R$22</f>
+        <f>[18]Model!R$29</f>
         <v>746</v>
       </c>
       <c r="K22" s="14">
-        <f>[18]Model!S$22</f>
+        <f>[18]Model!S$29</f>
         <v>861</v>
       </c>
       <c r="L22" s="14">
-        <f>[18]Model!T$22</f>
+        <f>[18]Model!T$29</f>
         <v>921</v>
       </c>
       <c r="M22" s="14">
-        <f>[18]Model!U$22</f>
+        <f>[18]Model!U$29</f>
         <v>824</v>
       </c>
       <c r="N22" s="14">
-        <f>[18]Model!V$22</f>
-        <v>1009.4089999999989</v>
+        <f>[18]Model!V$29</f>
+        <v>995.46496000000059</v>
       </c>
       <c r="O22" s="14">
-        <f>[18]Model!W$22</f>
-        <v>1260.3274750399985</v>
+        <f>[18]Model!W$29</f>
+        <v>1247.4273649599995</v>
       </c>
       <c r="P22" s="14">
-        <f>[18]Model!X$22</f>
-        <v>1438.1055164480015</v>
+        <f>[18]Model!X$29</f>
+        <v>1426.3027815039991</v>
       </c>
       <c r="Q22" s="14">
-        <f>[18]Model!Y$22</f>
-        <v>1494.4098756374406</v>
+        <f>[18]Model!Y$29</f>
+        <v>1482.6656240783984</v>
       </c>
       <c r="R22" s="15">
         <f>$G22/M22</f>
-        <v>19.757026699029126</v>
+        <v>21.573628640776697</v>
       </c>
       <c r="S22" s="15">
         <f>$G22/N22</f>
-        <v>16.128041259786684</v>
+        <v>17.85765518054999</v>
       </c>
       <c r="T22" s="15">
         <f>$G22/O22</f>
-        <v>12.91711108613524</v>
+        <v>14.250665408939486</v>
       </c>
       <c r="U22" s="15">
         <f>$G22/P22</f>
-        <v>11.320302866377773</v>
+        <v>12.463461636984935</v>
       </c>
       <c r="V22" s="15">
         <f>$G22/Q22</f>
-        <v>10.893791767172212</v>
+        <v>11.989668952532501</v>
       </c>
       <c r="W22" s="15">
-        <f>G22/[18]Model!$AF$22</f>
-        <v>9.2229628905226502</v>
-      </c>
-      <c r="X22" s="23">
-        <f>[18]Model!$U$6</f>
+        <f>G22/[18]Model!$AF$29</f>
+        <v>10.147551233981767</v>
+      </c>
+      <c r="X22" s="20">
+        <f>[18]Model!$L$55</f>
+        <v>1.0410324431951277</v>
+      </c>
+      <c r="Y22" s="16">
+        <f>[18]Model!$L$56</f>
+        <v>-3.9415143556132737E-2</v>
+      </c>
+      <c r="Z22" s="16">
+        <f>AVERAGE(Y22,AL22)</f>
+        <v>-5.6562643826018777E-2</v>
+      </c>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="23">
+        <f>[18]Model!$U$13</f>
         <v>13702</v>
       </c>
-      <c r="Y22" s="26">
-        <f t="shared" si="31"/>
-        <v>1.1881323894321996</v>
-      </c>
-      <c r="Z22" s="25">
-        <f>[18]Model!T$29</f>
+      <c r="AE22" s="26">
+        <f t="shared" si="32"/>
+        <v>1.2973777550722521</v>
+      </c>
+      <c r="AF22" s="25">
+        <f>[18]Model!T$42</f>
         <v>6.3252777993628051E-2</v>
       </c>
-      <c r="AA22" s="25">
-        <f>[18]Model!U$29</f>
+      <c r="AG22" s="25">
+        <f>[18]Model!U$42</f>
         <v>1.3885843747716287E-3</v>
       </c>
-      <c r="AB22" s="25">
-        <f>[18]Model!$U$32</f>
+      <c r="AH22" s="25">
+        <f>[18]Model!$U$45</f>
         <v>0.18260108013428697</v>
       </c>
-      <c r="AC22" s="25">
-        <f>[18]Model!$U$35</f>
+      <c r="AI22" s="25">
+        <f>[18]Model!$U$48</f>
         <v>6.23996496861772E-2</v>
       </c>
-      <c r="AD22" s="16">
-        <f>[18]Model!$AJ$29</f>
+      <c r="AJ22" s="25"/>
+      <c r="AK22" s="16">
+        <f>[18]Model!$AJ$42</f>
         <v>0.09</v>
       </c>
-      <c r="AE22" s="16">
-        <f>[18]Model!$AJ$35</f>
-        <v>3.5247218209492504E-2</v>
-      </c>
-      <c r="AF22" s="11" t="str">
-        <f>[18]Model!$AJ$36</f>
+      <c r="AL22" s="16">
+        <f>[18]Model!$AJ$48</f>
+        <v>-7.3710144095904817E-2</v>
+      </c>
+      <c r="AM22" s="11" t="str">
+        <f>[18]Model!$AJ$49</f>
         <v>Fairly valued</v>
       </c>
-      <c r="AH22" s="11">
+      <c r="AO22" s="11">
         <v>1923</v>
       </c>
-      <c r="AJ22" s="18">
+      <c r="AQ22" s="18">
         <f>[18]Main!$E$3</f>
-        <v>45867</v>
-      </c>
-      <c r="AK22" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR22" s="18">
         <f>[18]Main!$G$3</f>
         <v>45953</v>
       </c>
     </row>
-    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B23" s="19" t="s">
         <v>67</v>
       </c>
@@ -6141,11 +8369,11 @@
       </c>
       <c r="D23" s="13">
         <f>[19]Main!$D$3</f>
-        <v>57.19</v>
+        <v>57.35</v>
       </c>
       <c r="E23" s="14">
         <f>[19]Main!$D$5</f>
-        <v>10494.365</v>
+        <v>10523.725</v>
       </c>
       <c r="F23" s="14">
         <f>[19]Main!$D$8</f>
@@ -6153,7 +8381,7 @@
       </c>
       <c r="G23" s="14">
         <f>[19]Main!$D$9</f>
-        <v>11094.365</v>
+        <v>11123.725</v>
       </c>
       <c r="H23" s="14">
         <f>[19]Model!P$22</f>
@@ -6196,78 +8424,91 @@
         <v>906.37830312002222</v>
       </c>
       <c r="R23" s="15">
-        <f t="shared" ref="R23:V23" si="38">$G23/M23</f>
-        <v>48.616849255039376</v>
+        <f t="shared" ref="R23:V23" si="39">$G23/M23</f>
+        <v>48.745508326029736</v>
       </c>
       <c r="S23" s="15">
-        <f t="shared" si="38"/>
-        <v>14.918667162200055</v>
+        <f t="shared" si="39"/>
+        <v>14.958147751479586</v>
       </c>
       <c r="T23" s="15">
-        <f t="shared" si="38"/>
-        <v>15.424729230087236</v>
+        <f t="shared" si="39"/>
+        <v>15.465549056205754</v>
       </c>
       <c r="U23" s="15">
-        <f t="shared" si="38"/>
-        <v>13.353810559761699</v>
+        <f t="shared" si="39"/>
+        <v>13.38914993051745</v>
       </c>
       <c r="V23" s="15">
-        <f t="shared" si="38"/>
-        <v>12.240324996538327</v>
+        <f t="shared" si="39"/>
+        <v>12.272717651899708</v>
       </c>
       <c r="W23" s="15">
         <f>G23/[19]Model!$AF$22</f>
-        <v>10.264552570282582</v>
-      </c>
-      <c r="X23" s="23">
+        <v>10.291716564207741</v>
+      </c>
+      <c r="X23" s="20">
+        <f>[19]Model!$L$38</f>
+        <v>0.92160107705053851</v>
+      </c>
+      <c r="Y23" s="16">
+        <f>[19]Model!$L$39</f>
+        <v>8.5068176352795399E-2</v>
+      </c>
+      <c r="Z23" s="16">
+        <f>AVERAGE(Y23,AL23)</f>
+        <v>-0.17386324663502323</v>
+      </c>
+      <c r="AD23" s="23">
         <f>[19]Model!$V$3</f>
         <v>7743.8040000000001</v>
       </c>
-      <c r="Y23" s="26">
-        <f t="shared" si="31"/>
-        <v>1.4326763693915807</v>
-      </c>
-      <c r="Z23" s="25">
+      <c r="AE23" s="26">
+        <f t="shared" si="32"/>
+        <v>1.4364677876661134</v>
+      </c>
+      <c r="AF23" s="25">
         <f>[19]Model!T$26</f>
         <v>0.16041143561957627</v>
       </c>
-      <c r="AA23" s="25">
+      <c r="AG23" s="25">
         <f>[19]Model!U$26</f>
         <v>0.21376103255195988</v>
       </c>
-      <c r="AB23" s="25">
+      <c r="AH23" s="25">
         <f>[19]Model!$U$27</f>
         <v>0.18032120349664568</v>
       </c>
-      <c r="AC23" s="25">
+      <c r="AI23" s="25">
         <f>[19]Model!$U$31</f>
         <v>8.4945345364129704E-2</v>
       </c>
-      <c r="AD23" s="16">
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="16">
         <f>[19]Model!$AI$28</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AE23" s="16">
+      <c r="AL23" s="16">
         <f>[19]Model!$AI$34</f>
-        <v>-0.43120780386203839</v>
-      </c>
-      <c r="AF23" s="11" t="str">
+        <v>-0.43279466962284185</v>
+      </c>
+      <c r="AM23" s="11" t="str">
         <f>[19]Model!$AI$35</f>
         <v>Overvalued</v>
       </c>
-      <c r="AH23" s="11">
+      <c r="AO23" s="11">
         <v>1969</v>
       </c>
-      <c r="AJ23" s="18">
+      <c r="AQ23" s="18">
         <f>[19]Main!$E$3</f>
-        <v>45903</v>
-      </c>
-      <c r="AK23" s="18">
+        <v>45934</v>
+      </c>
+      <c r="AR23" s="18">
         <f>[19]Main!$G$3</f>
         <v>45965</v>
       </c>
     </row>
-    <row r="24" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B24" s="19" t="s">
         <v>73</v>
       </c>
@@ -6331,78 +8572,91 @@
         <v>189.70135618560002</v>
       </c>
       <c r="R24" s="15">
-        <f t="shared" ref="R24" si="39">$G24/M24</f>
+        <f t="shared" ref="R24" si="40">$G24/M24</f>
         <v>115.44528301886793</v>
       </c>
       <c r="S24" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>115.72757095042404</v>
       </c>
       <c r="T24" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>84.768709132687491</v>
       </c>
       <c r="U24" s="15">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>72.031905293617854</v>
       </c>
       <c r="V24" s="15">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>64.50770962347454</v>
       </c>
       <c r="W24" s="15">
         <f>G24/[20]Model!$AF$43</f>
         <v>35.255116146867159</v>
       </c>
-      <c r="X24" s="14">
+      <c r="X24" s="20">
+        <f>[20]Model!$L$59</f>
+        <v>2.6322219832221987</v>
+      </c>
+      <c r="Y24" s="16">
+        <f>[20]Model!$L$60</f>
+        <v>-0.62009283169352469</v>
+      </c>
+      <c r="Z24" s="16">
+        <f>AVERAGE(Y24,AL24)</f>
+        <v>-0.71348010657152106</v>
+      </c>
+      <c r="AD24" s="14">
         <f>[20]Model!$V$26</f>
         <v>2587.8199999999997</v>
       </c>
-      <c r="Y24" s="20">
-        <f t="shared" si="31"/>
+      <c r="AE24" s="20">
+        <f t="shared" si="32"/>
         <v>4.7287678432039328</v>
       </c>
-      <c r="Z24" s="16">
+      <c r="AF24" s="16">
         <f>[20]Model!U$47</f>
         <v>0.21277747698971305</v>
       </c>
-      <c r="AA24" s="16">
+      <c r="AG24" s="16">
         <f>[20]Model!V$47</f>
         <v>0.1552767857142856</v>
       </c>
-      <c r="AB24" s="16">
+      <c r="AH24" s="16">
         <f>[20]Model!$V$48</f>
         <v>0.22716788648360398</v>
       </c>
-      <c r="AC24" s="16">
+      <c r="AI24" s="16">
         <f>[20]Model!$V$52</f>
         <v>9.599848521149075E-2</v>
       </c>
-      <c r="AD24" s="16">
+      <c r="AJ24" s="16"/>
+      <c r="AK24" s="16">
         <f>[20]Model!$AI$49</f>
         <v>0.09</v>
       </c>
-      <c r="AE24" s="16">
+      <c r="AL24" s="16">
         <f>[20]Model!$AI$55</f>
         <v>-0.80686738144951742</v>
       </c>
-      <c r="AF24" s="11" t="str">
+      <c r="AM24" s="11" t="str">
         <f>[20]Model!$AI$56</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH24" s="11">
+      <c r="AO24" s="11">
         <v>1892</v>
       </c>
-      <c r="AJ24" s="18">
+      <c r="AQ24" s="18">
         <f>[20]Main!$E$3</f>
         <v>45924</v>
       </c>
-      <c r="AK24" s="18">
+      <c r="AR24" s="18">
         <f>[20]Main!$G$3</f>
         <v>45968</v>
       </c>
     </row>
-    <row r="25" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B25" s="19" t="s">
         <v>68</v>
       </c>
@@ -6411,11 +8665,11 @@
       </c>
       <c r="D25" s="13">
         <f>[21]Main!$D$3</f>
-        <v>90.08</v>
+        <v>107.54</v>
       </c>
       <c r="E25" s="14">
         <f>[21]Main!$D$5</f>
-        <v>15205.504000000001</v>
+        <v>18152.752000000004</v>
       </c>
       <c r="F25" s="14">
         <f>[21]Main!$D$8</f>
@@ -6423,7 +8677,7 @@
       </c>
       <c r="G25" s="14">
         <f>[21]Main!$D$9</f>
-        <v>14591.704000000002</v>
+        <v>17538.952000000005</v>
       </c>
       <c r="H25" s="14">
         <f>[21]Model!P$22</f>
@@ -6466,92 +8720,106 @@
         <v>85.495337030527935</v>
       </c>
       <c r="R25" s="15">
-        <f t="shared" ref="R25" si="40">$G25/M25</f>
-        <v>895.19656441718109</v>
+        <f t="shared" ref="R25" si="41">$G25/M25</f>
+        <v>1076.0093251533783</v>
       </c>
       <c r="S25" s="15">
-        <f t="shared" si="33"/>
-        <v>730.68824697764694</v>
+        <f t="shared" si="34"/>
+        <v>878.27344158743199</v>
       </c>
       <c r="T25" s="15">
-        <f t="shared" si="34"/>
-        <v>309.01319648650241</v>
+        <f t="shared" si="35"/>
+        <v>371.42801283135509</v>
       </c>
       <c r="U25" s="15">
-        <f t="shared" si="35"/>
-        <v>206.11347980020346</v>
+        <f t="shared" si="36"/>
+        <v>247.74450117469067</v>
       </c>
       <c r="V25" s="15">
-        <f t="shared" si="36"/>
-        <v>170.67251275692055</v>
+        <f t="shared" si="37"/>
+        <v>205.1451296547009</v>
       </c>
       <c r="W25" s="15">
         <f>G25/[21]Model!$AF$22</f>
-        <v>78.909831938412125</v>
-      </c>
-      <c r="X25" s="14">
+        <v>94.848124296920872</v>
+      </c>
+      <c r="X25" s="20">
+        <f>[21]Model!$L$45</f>
+        <v>6.7830575859535163</v>
+      </c>
+      <c r="Y25" s="16">
+        <f>[21]Model!$L$46</f>
+        <v>-0.85257385960118948</v>
+      </c>
+      <c r="Z25" s="16">
+        <f>AVERAGE(Y25,AL25)</f>
+        <v>-0.8720193714588601</v>
+      </c>
+      <c r="AD25" s="14">
         <f>[21]Model!$V$7</f>
         <v>1297.6099999999999</v>
       </c>
-      <c r="Y25" s="20">
-        <f t="shared" si="31"/>
-        <v>11.245061305014605</v>
-      </c>
-      <c r="Z25" s="16">
+      <c r="AE25" s="20">
+        <f t="shared" si="32"/>
+        <v>13.51635082960212</v>
+      </c>
+      <c r="AF25" s="16">
         <f>[21]Model!U$28</f>
         <v>9.5651335454633113E-2</v>
       </c>
-      <c r="AA25" s="16">
+      <c r="AG25" s="16">
         <f>[21]Model!V$28</f>
         <v>0.14196074980198881</v>
       </c>
-      <c r="AB25" s="16">
+      <c r="AH25" s="16">
         <f>[21]Model!$V$31</f>
         <v>0.23128695062460972</v>
       </c>
-      <c r="AC25" s="16">
+      <c r="AI25" s="16">
         <f>[21]Model!$V$34</f>
         <v>2.1587580243678565E-2</v>
       </c>
-      <c r="AD25" s="16">
+      <c r="AJ25" s="16"/>
+      <c r="AK25" s="16">
         <f>[21]Model!$AI$29</f>
         <v>0.09</v>
       </c>
-      <c r="AE25" s="16">
+      <c r="AL25" s="16">
         <f>[21]Model!$AI$35</f>
-        <v>-0.87042777033592045</v>
-      </c>
-      <c r="AF25" s="11" t="str">
+        <v>-0.89146488331653073</v>
+      </c>
+      <c r="AM25" s="11" t="str">
         <f>[21]Model!$AI$36</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH25" s="11">
+      <c r="AO25" s="11">
         <v>1994</v>
       </c>
-      <c r="AJ25" s="18">
+      <c r="AQ25" s="18">
         <f>[21]Main!$E$3</f>
-        <v>45930</v>
-      </c>
-      <c r="AK25" s="18">
+        <v>45939</v>
+      </c>
+      <c r="AR25" s="18">
         <f>[21]Main!$G$3</f>
         <v>45960</v>
       </c>
     </row>
-    <row r="26" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
-      <c r="AC26" s="24"/>
-    </row>
-    <row r="27" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AD26" s="24"/>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="24"/>
+      <c r="AG26" s="24"/>
+      <c r="AH26" s="24"/>
+      <c r="AI26" s="24"/>
+      <c r="AJ26" s="24"/>
+    </row>
+    <row r="27" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B27" s="19" t="s">
         <v>72</v>
       </c>
@@ -6603,78 +8871,91 @@
         <v>200.07653520599999</v>
       </c>
       <c r="R27" s="15">
-        <f t="shared" ref="R27" si="41">$G27/M27</f>
+        <f t="shared" ref="R27" si="42">$G27/M27</f>
         <v>132.73644859813069</v>
       </c>
       <c r="S27" s="15">
-        <f t="shared" ref="S27" si="42">$G27/N27</f>
+        <f t="shared" ref="S27" si="43">$G27/N27</f>
         <v>73.343961635656939</v>
       </c>
       <c r="T27" s="15">
-        <f t="shared" ref="T27:T28" si="43">$G27/O27</f>
+        <f t="shared" ref="T27:T28" si="44">$G27/O27</f>
         <v>49.486524348833029</v>
       </c>
       <c r="U27" s="15">
-        <f t="shared" ref="U27:U28" si="44">$G27/P27</f>
+        <f t="shared" ref="U27:U28" si="45">$G27/P27</f>
         <v>39.51155848292143</v>
       </c>
       <c r="V27" s="15">
-        <f t="shared" ref="V27:V28" si="45">$G27/Q27</f>
+        <f t="shared" ref="V27:V28" si="46">$G27/Q27</f>
         <v>35.493417519892354</v>
       </c>
       <c r="W27" s="15">
         <f>G27/[22]Model!$AF$39</f>
         <v>22.535987037880979</v>
       </c>
-      <c r="X27" s="14">
+      <c r="X27" s="20">
+        <f>[22]Model!$L$54</f>
+        <v>4.3835802469135796</v>
+      </c>
+      <c r="Y27" s="16">
+        <f>[22]Model!$L$55</f>
+        <v>-0.77187596811896242</v>
+      </c>
+      <c r="Z27" s="16">
+        <f>AVERAGE(Y27,AL27)</f>
+        <v>-0.72227595642955145</v>
+      </c>
+      <c r="AD27" s="14">
         <f>[22]Model!$V$24</f>
         <v>1358.33</v>
       </c>
-      <c r="Y27" s="20">
-        <f>G27/X27</f>
+      <c r="AE27" s="20">
+        <f>G27/AD27</f>
         <v>5.2280373694168576</v>
       </c>
-      <c r="Z27" s="16">
+      <c r="AF27" s="16">
         <f>[22]Model!U$43</f>
         <v>0.23230686115613186</v>
       </c>
-      <c r="AA27" s="16">
+      <c r="AG27" s="16">
         <f>[22]Model!V$43</f>
         <v>0.19099517755370443</v>
       </c>
-      <c r="AB27" s="16">
+      <c r="AH27" s="16">
         <f>[22]Model!$V$44</f>
         <v>0.25505171791832615</v>
       </c>
-      <c r="AC27" s="16">
+      <c r="AI27" s="16">
         <f>[22]Model!$V$47</f>
         <v>0.1261351806998299</v>
       </c>
-      <c r="AD27" s="16">
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16">
         <f>[22]Model!$AI$45</f>
         <v>0.09</v>
       </c>
-      <c r="AE27" s="16">
+      <c r="AL27" s="16">
         <f>[22]Model!$AI$51</f>
         <v>-0.67267594474014047</v>
       </c>
-      <c r="AF27" s="11" t="str">
+      <c r="AM27" s="11" t="str">
         <f>[22]Model!$AI$52</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH27" s="11">
+      <c r="AO27" s="11">
         <v>1873</v>
       </c>
-      <c r="AJ27" s="18">
+      <c r="AQ27" s="18">
         <f>[22]Main!$E$3</f>
         <v>45903</v>
       </c>
-      <c r="AK27" s="18">
+      <c r="AR27" s="18">
         <f>[22]Main!$G$3</f>
         <v>45974</v>
       </c>
     </row>
-    <row r="28" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B28" s="19" t="s">
         <v>43</v>
       </c>
@@ -6683,11 +8964,11 @@
       </c>
       <c r="D28" s="13">
         <f>[23]Main!$D$3</f>
-        <v>10</v>
+        <v>11.52</v>
       </c>
       <c r="E28" s="14">
         <f>[23]Main!$D$5</f>
-        <v>1178</v>
+        <v>1357.0559999999998</v>
       </c>
       <c r="F28" s="14">
         <f>[23]Main!$D$8</f>
@@ -6695,7 +8976,7 @@
       </c>
       <c r="G28" s="14">
         <f>[23]Main!$D$9</f>
-        <v>1131.9000000000001</v>
+        <v>1310.9559999999999</v>
       </c>
       <c r="N28" s="14">
         <f>[23]Model!O$15</f>
@@ -6714,55 +8995,68 @@
         <v>-123.67537759999999</v>
       </c>
       <c r="S28" s="15">
-        <f t="shared" ref="S28" si="46">$G28/N28</f>
-        <v>-16.327443202307972</v>
+        <f t="shared" ref="S28" si="47">$G28/N28</f>
+        <v>-18.910292102416154</v>
       </c>
       <c r="T28" s="15">
-        <f t="shared" si="43"/>
-        <v>-12.413702340935387</v>
+        <f t="shared" si="44"/>
+        <v>-14.377434018962179</v>
       </c>
       <c r="U28" s="15">
-        <f t="shared" si="44"/>
-        <v>-10.2503145096059</v>
+        <f t="shared" si="45"/>
+        <v>-11.871818454152232</v>
       </c>
       <c r="V28" s="15">
-        <f t="shared" si="45"/>
-        <v>-9.1521855195855917</v>
+        <f t="shared" si="46"/>
+        <v>-10.59997572224918</v>
       </c>
       <c r="W28" s="15">
         <f>G28/[23]Model!$Y$15</f>
-        <v>7.7512385840070213</v>
-      </c>
-      <c r="X28" s="14">
+        <v>8.9774120762748542</v>
+      </c>
+      <c r="X28" s="20">
+        <f>[23]Model!$H$31</f>
+        <v>10.798649093904446</v>
+      </c>
+      <c r="Y28" s="16">
+        <f>[23]Model!$H$32</f>
+        <v>-0.90739582411614117</v>
+      </c>
+      <c r="Z28" s="16">
+        <f>AVERAGE(Y28,AL28)</f>
+        <v>-0.89047085067888254</v>
+      </c>
+      <c r="AD28" s="14">
         <f>[23]Model!$O$3</f>
         <v>12.3</v>
       </c>
-      <c r="Y28" s="20">
-        <f>G28/X28</f>
-        <v>92.024390243902445</v>
-      </c>
-      <c r="AB28" s="16">
+      <c r="AE28" s="20">
+        <f>G28/AD28</f>
+        <v>106.58178861788616</v>
+      </c>
+      <c r="AH28" s="16">
         <f>[23]Model!$O$20</f>
         <v>5.08130081300813E-2</v>
       </c>
-      <c r="AC28" s="16">
+      <c r="AI28" s="16">
         <f>[23]Model!$O$24</f>
         <v>-4.23780487804878</v>
       </c>
-      <c r="AD28" s="16">
+      <c r="AJ28" s="16"/>
+      <c r="AK28" s="16">
         <f>[23]Model!$AB$21</f>
         <v>0.11</v>
       </c>
-      <c r="AE28" s="16">
+      <c r="AL28" s="16">
         <f>[23]Model!$AB$27</f>
-        <v>-0.85432485058235097</v>
-      </c>
-      <c r="AF28" s="11" t="str">
+        <v>-0.87354587724162402</v>
+      </c>
+      <c r="AM28" s="11" t="str">
         <f>[23]Model!$AB$28</f>
         <v>Heavily overvalued</v>
       </c>
     </row>
-    <row r="29" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B29" s="19" t="s">
         <v>51</v>
       </c>
@@ -6771,11 +9065,11 @@
       </c>
       <c r="D29" s="13">
         <f>[24]Main!$D$3</f>
-        <v>9.0399999999999991</v>
+        <v>14.97</v>
       </c>
       <c r="E29" s="14">
         <f>[24]Main!$D$5</f>
-        <v>274.81599999999997</v>
+        <v>455.08800000000002</v>
       </c>
       <c r="F29" s="14">
         <f>[24]Main!$D$8</f>
@@ -6783,7 +9077,7 @@
       </c>
       <c r="G29" s="14">
         <f>[24]Main!$D$9</f>
-        <v>269.81599999999997</v>
+        <v>450.08800000000002</v>
       </c>
       <c r="L29" s="14">
         <f>[24]Model!$P$20</f>
@@ -6811,49 +9105,62 @@
       </c>
       <c r="W29" s="15">
         <f>G29/[24]Model!$AB$20</f>
-        <v>3.9629103845325151</v>
-      </c>
-      <c r="X29" s="23">
+        <v>6.6106472898325936</v>
+      </c>
+      <c r="X29" s="20">
+        <f>[24]Model!$L$35</f>
+        <v>8.5894656488549632</v>
+      </c>
+      <c r="Y29" s="16">
+        <f>[24]Model!$L$36</f>
+        <v>-0.88357832246138535</v>
+      </c>
+      <c r="Z29" s="16">
+        <f>AVERAGE(Y29,AL29)</f>
+        <v>-0.87539364362171912</v>
+      </c>
+      <c r="AD29" s="23">
         <f>[24]Model!$Q$3</f>
         <v>5.6</v>
       </c>
-      <c r="Y29" s="20">
-        <f>G29/X29</f>
-        <v>48.181428571428569</v>
-      </c>
-      <c r="AB29" s="25">
+      <c r="AE29" s="20">
+        <f>G29/AD29</f>
+        <v>80.372857142857157</v>
+      </c>
+      <c r="AH29" s="25">
         <f>[24]Model!$Q$26</f>
         <v>0.28571428571428564</v>
       </c>
-      <c r="AC29" s="25">
+      <c r="AI29" s="25">
         <f>[24]Model!$Q$30</f>
         <v>-3.0535714285714288</v>
       </c>
-      <c r="AD29" s="16">
+      <c r="AJ29" s="25"/>
+      <c r="AK29" s="16">
         <f>[24]Model!$AF$27</f>
         <v>0.12</v>
       </c>
-      <c r="AE29" s="16">
+      <c r="AL29" s="16">
         <f>[24]Model!$AF$33</f>
-        <v>-0.78010157110479306</v>
-      </c>
-      <c r="AF29" s="11" t="str">
+        <v>-0.86720896478205278</v>
+      </c>
+      <c r="AM29" s="11" t="str">
         <f>[24]Model!$AF$34</f>
         <v>Heavily overvalued</v>
       </c>
-      <c r="AH29" s="11">
+      <c r="AO29" s="11">
         <v>2019</v>
       </c>
-      <c r="AJ29" s="18">
+      <c r="AQ29" s="18">
         <f>[24]Main!$E$3</f>
-        <v>45903</v>
-      </c>
-      <c r="AK29" s="18">
+        <v>45933</v>
+      </c>
+      <c r="AR29" s="18">
         <f>[24]Main!$G$3</f>
         <v>45974</v>
       </c>
     </row>
-    <row r="30" spans="2:37" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B30" s="12"/>
       <c r="D30" s="13"/>
       <c r="E30" s="14"/>
@@ -6866,16 +9173,20 @@
       <c r="P30" s="14"/>
       <c r="Q30" s="14"/>
       <c r="W30" s="15"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="20"/>
-      <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="16"/>
-      <c r="AE30" s="16"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-    </row>
-    <row r="31" spans="2:37" x14ac:dyDescent="0.3">
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="20"/>
+      <c r="AH30" s="16"/>
+      <c r="AI30" s="16"/>
+      <c r="AJ30" s="16"/>
+      <c r="AK30" s="16"/>
+      <c r="AL30" s="16"/>
+      <c r="AQ30" s="18"/>
+      <c r="AR30" s="18"/>
+    </row>
+    <row r="31" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="B31" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="D31" s="13"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
@@ -6887,14 +9198,15 @@
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
       <c r="W31" s="15"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="20"/>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
-      <c r="AE31" s="16"/>
-      <c r="AJ31" s="18"/>
-      <c r="AK31" s="18"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="20"/>
+      <c r="AH31" s="16"/>
+      <c r="AI31" s="16"/>
+      <c r="AJ31" s="16"/>
+      <c r="AK31" s="16"/>
+      <c r="AL31" s="16"/>
+      <c r="AQ31" s="18"/>
+      <c r="AR31" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6925,5 +9237,2382 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <legacyDrawing r:id="rId26"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FB61A3-0296-4EF3-A3C7-6AA855DB950E}">
+  <dimension ref="B2:K86"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="27"/>
+    <col min="2" max="2" width="18.88671875" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="27"/>
+    <col min="5" max="5" width="10.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="34">
+        <v>842.3</v>
+      </c>
+      <c r="D11" s="34">
+        <v>848.3</v>
+      </c>
+      <c r="E11" s="35">
+        <v>848.3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="34">
+        <v>0</v>
+      </c>
+      <c r="D12" s="34">
+        <v>0</v>
+      </c>
+      <c r="E12" s="35">
+        <v>113.3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="34">
+        <v>67.3</v>
+      </c>
+      <c r="D13" s="34">
+        <v>11.8</v>
+      </c>
+      <c r="E13" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="36">
+        <f>SUM(C11:C13)</f>
+        <v>909.59999999999991</v>
+      </c>
+      <c r="D14" s="36">
+        <f>SUM(D11:D13)</f>
+        <v>860.09999999999991</v>
+      </c>
+      <c r="E14" s="37">
+        <f>SUM(E11:E13)</f>
+        <v>961.59999999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C18" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="34">
+        <v>5</v>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="G19" s="27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="34">
+        <v>25</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="G20" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="34">
+        <v>60</v>
+      </c>
+      <c r="D21" s="34"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C22" s="34"/>
+      <c r="D22" s="34">
+        <v>11.5</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C23" s="34"/>
+      <c r="D23" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C24" s="34"/>
+      <c r="D24" s="34">
+        <v>4.2</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C25" s="34"/>
+      <c r="D25" s="34">
+        <v>2</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C26" s="34"/>
+      <c r="D26" s="34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34">
+        <f>SUM(D22:D26)</f>
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34">
+        <f>C21-D27</f>
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="34">
+        <v>10</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="G29" s="27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="34">
+        <v>2.4</v>
+      </c>
+      <c r="D30" s="34"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C31" s="34"/>
+      <c r="D31" s="34">
+        <v>1</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C32" s="34"/>
+      <c r="D32" s="34">
+        <v>1</v>
+      </c>
+      <c r="G32" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C33" s="34"/>
+      <c r="D33" s="34">
+        <v>0.4</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34">
+        <f>SUM(D31:D33)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="34">
+        <v>68.3</v>
+      </c>
+      <c r="D35" s="34"/>
+      <c r="F35" s="27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="34">
+        <v>65</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="F36" s="27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="34">
+        <v>11.6</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="F37" s="27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="34">
+        <v>10.4</v>
+      </c>
+      <c r="D38" s="34"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C39" s="34"/>
+      <c r="D39" s="34">
+        <v>6.5</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C40" s="34"/>
+      <c r="D40" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34">
+        <f>SUM(D39:D40)</f>
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34">
+        <v>34</v>
+      </c>
+      <c r="G42" s="27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B43" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34">
+        <v>15.1</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" s="43">
+        <v>35.9</v>
+      </c>
+      <c r="D44" s="34"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C45" s="34"/>
+      <c r="D45" s="34">
+        <v>20.3</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C46" s="34"/>
+      <c r="D46" s="34">
+        <v>13.4</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C47" s="34"/>
+      <c r="D47" s="34">
+        <v>1</v>
+      </c>
+      <c r="G47" s="27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C48" s="34"/>
+      <c r="D48" s="34">
+        <v>1.2</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34">
+        <f>SUM(D45:D48)</f>
+        <v>35.900000000000006</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="43">
+        <f>D54</f>
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="D50" s="34"/>
+      <c r="G50" s="27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C51" s="34"/>
+      <c r="D51" s="34">
+        <v>5.7</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C52" s="34"/>
+      <c r="D52" s="34">
+        <v>2.6</v>
+      </c>
+      <c r="G52" s="27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C53" s="34"/>
+      <c r="D53" s="34">
+        <v>0.3</v>
+      </c>
+      <c r="G53" s="27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C54" s="34"/>
+      <c r="D54" s="34">
+        <f>SUM(D51:D53)</f>
+        <v>8.6000000000000014</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="43">
+        <f>D60</f>
+        <v>55.1</v>
+      </c>
+      <c r="D55" s="34"/>
+      <c r="G55" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C56" s="34"/>
+      <c r="D56" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G56" s="27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C57" s="34"/>
+      <c r="D57" s="34">
+        <v>42.5</v>
+      </c>
+      <c r="G57" s="27" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C58" s="34"/>
+      <c r="D58" s="34">
+        <v>2.1</v>
+      </c>
+      <c r="G58" s="27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C59" s="34"/>
+      <c r="D59" s="34">
+        <v>10.5</v>
+      </c>
+      <c r="G59" s="27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C60" s="34"/>
+      <c r="D60" s="34">
+        <f>SUM(D57:D59)</f>
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B61" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="34">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="D61" s="34"/>
+      <c r="G61" s="27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B62" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" s="34">
+        <v>47.1</v>
+      </c>
+      <c r="D62" s="34"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C63" s="34"/>
+      <c r="D63" s="34">
+        <v>19.8</v>
+      </c>
+      <c r="G63" s="27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C64" s="34"/>
+      <c r="D64" s="34">
+        <v>27.3</v>
+      </c>
+      <c r="G64" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C65" s="34"/>
+      <c r="D65" s="34">
+        <f>SUM(D63:D64)</f>
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B66" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" s="43">
+        <f>D70</f>
+        <v>1.8</v>
+      </c>
+      <c r="D66" s="34"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C67" s="34"/>
+      <c r="D67" s="34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G67" s="27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C68" s="34"/>
+      <c r="D68" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="G68" s="27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C69" s="34"/>
+      <c r="D69" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="G69" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C70" s="34"/>
+      <c r="D70" s="34">
+        <f>SUM(D67:D69)</f>
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B71" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C71" s="41">
+        <f>E14</f>
+        <v>961.59999999999991</v>
+      </c>
+      <c r="D71" s="41"/>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B72" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34">
+        <f>SUM(C19:C70)</f>
+        <v>565.9</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B73" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34">
+        <f>C71-D72</f>
+        <v>395.69999999999993</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B78" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="C78" s="27">
+        <v>197.40899999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B80" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C80" s="27">
+        <v>292.233</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="C82" s="27">
+        <v>301.07799999999997</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B84" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" s="27">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B86" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="C86" s="27">
+        <v>170.876</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12308D2B-9AD1-40AD-A926-C5ADF567E1FB}">
+  <dimension ref="B2:R118"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="27"/>
+    <col min="2" max="2" width="48.77734375" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B2" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42">
+        <v>27.6</v>
+      </c>
+      <c r="L5" s="42">
+        <v>43.3</v>
+      </c>
+      <c r="M5" s="42"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42">
+        <v>13.1</v>
+      </c>
+      <c r="R6" s="27" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42">
+        <v>15.2</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42">
+        <v>14.9</v>
+      </c>
+      <c r="R8" s="27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42">
+        <f>SUM(M6:M8)</f>
+        <v>43.199999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42">
+        <f>L5-M9</f>
+        <v>0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="R16" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B18" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B21" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="R21" s="27" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B22" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="R22" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B23" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B24" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B25" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B26" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B27" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B28" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42">
+        <v>15.2</v>
+      </c>
+      <c r="M28" s="42"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B29" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B30" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B31" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B32" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="42"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B41" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B44" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B45" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B46" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B47" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
+      <c r="R47" s="27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B48" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42"/>
+      <c r="M48" s="42"/>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B49" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B50" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42">
+        <f>SUM(L5:L49)</f>
+        <v>58.5</v>
+      </c>
+      <c r="M50" s="42"/>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B52" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="J52" s="42">
+        <v>2.681</v>
+      </c>
+      <c r="K52" s="42">
+        <v>2.2469999999999999</v>
+      </c>
+      <c r="L52" s="42">
+        <v>3.1869999999999998</v>
+      </c>
+      <c r="M52" s="42"/>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B54" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B56" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="42"/>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B57" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="J57" s="42">
+        <v>4.3360000000000003</v>
+      </c>
+      <c r="K57" s="42">
+        <v>2.0219999999999998</v>
+      </c>
+      <c r="L57" s="42">
+        <v>4.1580000000000004</v>
+      </c>
+      <c r="M57" s="42"/>
+      <c r="R57" s="27" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B58" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="J58" s="42">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="K58" s="42">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="L58" s="42">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="M58" s="42"/>
+      <c r="R58" s="27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B59" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="J59" s="42">
+        <v>8.1950000000000003</v>
+      </c>
+      <c r="K59" s="42">
+        <v>9.9049999999999994</v>
+      </c>
+      <c r="L59" s="42">
+        <v>11.48</v>
+      </c>
+      <c r="M59" s="42"/>
+      <c r="R59" s="27" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B60" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="J60" s="42">
+        <v>1.8720000000000001</v>
+      </c>
+      <c r="K60" s="42">
+        <v>2.3929999999999998</v>
+      </c>
+      <c r="L60" s="42">
+        <v>3.742</v>
+      </c>
+      <c r="M60" s="42"/>
+    </row>
+    <row r="61" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B61" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="J61" s="42">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="K61" s="42">
+        <v>0.126</v>
+      </c>
+      <c r="L61" s="42">
+        <v>1.9319999999999999</v>
+      </c>
+      <c r="M61" s="42"/>
+    </row>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B62" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" s="42">
+        <v>6.2169999999999996</v>
+      </c>
+      <c r="K62" s="42">
+        <v>5.2610000000000001</v>
+      </c>
+      <c r="L62" s="42">
+        <v>10.292999999999999</v>
+      </c>
+      <c r="M62" s="42"/>
+      <c r="R62" s="27" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B63" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="J63" s="42">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="K63" s="42">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="L63" s="42">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="M63" s="42"/>
+      <c r="R63" s="27" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B64" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="J64" s="42">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="K64" s="42">
+        <v>1.617</v>
+      </c>
+      <c r="L64" s="42">
+        <v>1.8340000000000001</v>
+      </c>
+      <c r="M64" s="42"/>
+      <c r="R64" s="27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B65" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="J65" s="42">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="K65" s="42">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="L65" s="42">
+        <v>1.2949999999999999</v>
+      </c>
+      <c r="M65" s="42"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B66" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="J66" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="K66" s="42">
+        <v>0.755</v>
+      </c>
+      <c r="L66" s="42">
+        <v>1.244</v>
+      </c>
+      <c r="M66" s="42"/>
+      <c r="R66" s="27" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B67" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="J67" s="42">
+        <v>2.331</v>
+      </c>
+      <c r="K67" s="42">
+        <v>1.92</v>
+      </c>
+      <c r="L67" s="42">
+        <v>1.8979999999999999</v>
+      </c>
+      <c r="M67" s="42"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B68" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="J68" s="42">
+        <v>2.181</v>
+      </c>
+      <c r="K68" s="42">
+        <v>2.4540000000000002</v>
+      </c>
+      <c r="L68" s="42">
+        <v>3.544</v>
+      </c>
+      <c r="M68" s="42"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B69" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="J69" s="44">
+        <f t="shared" ref="J69:K69" si="0">SUM(J57:J68)</f>
+        <v>27.603000000000002</v>
+      </c>
+      <c r="K69" s="44">
+        <f t="shared" si="0"/>
+        <v>28.198</v>
+      </c>
+      <c r="L69" s="44">
+        <f>SUM(L57:L68)</f>
+        <v>42.493000000000002</v>
+      </c>
+      <c r="M69" s="42"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B71" s="29" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B72" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="G72" s="27">
+        <v>74</v>
+      </c>
+      <c r="H72" s="27">
+        <v>47</v>
+      </c>
+      <c r="K72" s="27">
+        <v>13.3</v>
+      </c>
+      <c r="L72" s="27">
+        <v>13.1</v>
+      </c>
+      <c r="R72" s="45" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B73" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="G73" s="27">
+        <v>18</v>
+      </c>
+      <c r="H73" s="27">
+        <v>21</v>
+      </c>
+      <c r="K73" s="27">
+        <v>1.9</v>
+      </c>
+      <c r="L73" s="27">
+        <v>3.1</v>
+      </c>
+      <c r="R73" s="45" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B74" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="K74" s="27">
+        <v>2.4</v>
+      </c>
+      <c r="L74" s="27">
+        <v>3.5</v>
+      </c>
+      <c r="R74" s="45" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B75" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="G75" s="27">
+        <v>15</v>
+      </c>
+      <c r="H75" s="27">
+        <v>15</v>
+      </c>
+      <c r="K75" s="27">
+        <v>3.1</v>
+      </c>
+      <c r="L75" s="27">
+        <v>3.3</v>
+      </c>
+      <c r="R75" s="45" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B76" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="K76" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="L76" s="27">
+        <v>2</v>
+      </c>
+      <c r="R76" s="45" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B77" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="G77" s="27">
+        <v>20</v>
+      </c>
+      <c r="H77" s="27">
+        <v>12</v>
+      </c>
+      <c r="K77" s="27">
+        <v>3</v>
+      </c>
+      <c r="L77" s="27">
+        <v>2.5</v>
+      </c>
+      <c r="R77" s="45" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B78" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="H78" s="27">
+        <v>4</v>
+      </c>
+      <c r="K78" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L78" s="27">
+        <v>2.1</v>
+      </c>
+      <c r="R78" s="45" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B79" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G79" s="27">
+        <v>31</v>
+      </c>
+      <c r="K79" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="L79" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="R79" s="45" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B80" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="G80" s="27">
+        <v>26</v>
+      </c>
+      <c r="H80" s="27">
+        <v>24</v>
+      </c>
+      <c r="K80" s="27">
+        <v>1</v>
+      </c>
+      <c r="L80" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="R80" s="45" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="81" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B81" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="K81" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="L81" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="R81" s="45" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="82" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B82" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="K82" s="27">
+        <v>1.3</v>
+      </c>
+      <c r="L82" s="27">
+        <v>1.2</v>
+      </c>
+      <c r="R82" s="45" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="83" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B83" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="K83" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="L83" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="R83" s="45" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B84" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="H84" s="27">
+        <v>3</v>
+      </c>
+      <c r="K84" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="L84" s="27">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R84" s="45" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B85" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="K85" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="L85" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="R85" s="45" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B86" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="K86" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="L86" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="R86" s="45" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B87" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="G87" s="27">
+        <v>12</v>
+      </c>
+      <c r="H87" s="27">
+        <v>6</v>
+      </c>
+      <c r="K87" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="L87" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="R87" s="45" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B88" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="K88" s="30">
+        <f>SUM(K72:K87)</f>
+        <v>32.1</v>
+      </c>
+      <c r="L88" s="30">
+        <f>SUM(L72:L87)</f>
+        <v>35.100000000000009</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B89" s="30"/>
+      <c r="K89" s="30"/>
+      <c r="L89" s="30"/>
+    </row>
+    <row r="90" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B90" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="K90" s="30"/>
+      <c r="L90" s="30"/>
+    </row>
+    <row r="91" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B91" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42">
+        <v>5.3</v>
+      </c>
+      <c r="L91" s="42">
+        <v>10.3</v>
+      </c>
+      <c r="M91" s="42"/>
+      <c r="R91" s="45" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B92" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="H92" s="27">
+        <v>1</v>
+      </c>
+      <c r="J92" s="42"/>
+      <c r="K92" s="42">
+        <v>9.9</v>
+      </c>
+      <c r="L92" s="42">
+        <v>11.5</v>
+      </c>
+      <c r="M92" s="42"/>
+      <c r="R92" s="45" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B93" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="J93" s="42"/>
+      <c r="K93" s="42">
+        <v>0.1</v>
+      </c>
+      <c r="L93" s="42">
+        <v>2</v>
+      </c>
+      <c r="M93" s="42"/>
+      <c r="R93" s="45" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="94" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B94" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42">
+        <v>2.4</v>
+      </c>
+      <c r="L94" s="42">
+        <v>3.7</v>
+      </c>
+      <c r="M94" s="42"/>
+      <c r="R94" s="45" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="95" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B95" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="J95" s="42"/>
+      <c r="K95" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="L95" s="42">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M95" s="42"/>
+      <c r="R95" s="45" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="96" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B96" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="J96" s="42"/>
+      <c r="K96" s="42">
+        <v>2</v>
+      </c>
+      <c r="L96" s="42">
+        <v>4.2</v>
+      </c>
+      <c r="M96" s="42"/>
+      <c r="R96" s="45" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="97" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B97" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="J97" s="42"/>
+      <c r="K97" s="44">
+        <f>SUM(K91:K96)</f>
+        <v>20.5</v>
+      </c>
+      <c r="L97" s="44">
+        <f>SUM(L91:L96)</f>
+        <v>32.800000000000004</v>
+      </c>
+      <c r="M97" s="42"/>
+      <c r="R97" s="45"/>
+    </row>
+    <row r="99" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B99" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="L99" s="27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="100" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B100" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="G100" s="27">
+        <v>1</v>
+      </c>
+      <c r="H100" s="27">
+        <v>2</v>
+      </c>
+      <c r="K100" s="27">
+        <v>13.9</v>
+      </c>
+      <c r="L100" s="27">
+        <v>12.2</v>
+      </c>
+      <c r="R100" s="45" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="101" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B101" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="G101" s="27">
+        <v>3</v>
+      </c>
+      <c r="H101" s="27">
+        <v>2</v>
+      </c>
+      <c r="K101" s="27">
+        <v>8.6</v>
+      </c>
+      <c r="L101" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="R101" s="45" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="102" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B102" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="K102" s="27">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L102" s="27">
+        <v>3.6</v>
+      </c>
+      <c r="R102" s="45" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="103" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B103" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="K103" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="L103" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="R103" s="45" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="104" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B104" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="G104" s="27">
+        <v>1</v>
+      </c>
+      <c r="H104" s="27">
+        <v>1</v>
+      </c>
+      <c r="K104" s="27">
+        <v>1.6</v>
+      </c>
+      <c r="L104" s="27">
+        <v>2.8</v>
+      </c>
+      <c r="R104" s="45" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="105" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B105" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="H105" s="27">
+        <v>1</v>
+      </c>
+      <c r="K105" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L105" s="27">
+        <v>4</v>
+      </c>
+      <c r="R105" s="45" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B106" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="H106" s="27">
+        <v>2</v>
+      </c>
+      <c r="K106" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="L106" s="27">
+        <v>2</v>
+      </c>
+      <c r="R106" s="45" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="107" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B107" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="H107" s="27">
+        <v>1</v>
+      </c>
+      <c r="K107" s="27">
+        <v>0</v>
+      </c>
+      <c r="L107" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="R107" s="45" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="108" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B108" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="K108" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="L108" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="R108" s="45" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="109" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B109" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="H109" s="27">
+        <v>9</v>
+      </c>
+      <c r="K109" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="L109" s="27">
+        <v>2</v>
+      </c>
+      <c r="R109" s="45" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="110" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B110" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="L110" s="27">
+        <f>L99-L111</f>
+        <v>31.699999999999989</v>
+      </c>
+      <c r="R110" s="45"/>
+    </row>
+    <row r="111" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B111" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="K111" s="30">
+        <f>SUM(K100:K109)</f>
+        <v>27.8</v>
+      </c>
+      <c r="L111" s="30">
+        <f>SUM(L100:L109)</f>
+        <v>33.300000000000011</v>
+      </c>
+    </row>
+    <row r="113" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B113" s="29" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="114" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B114" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="K114" s="27">
+        <v>2.4</v>
+      </c>
+      <c r="L114" s="27">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="115" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B115" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="K115" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="L115" s="27">
+        <v>0.7</v>
+      </c>
+      <c r="R115" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="116" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B116" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="K116" s="27">
+        <v>4.7</v>
+      </c>
+      <c r="L116" s="27">
+        <v>13</v>
+      </c>
+      <c r="R116" s="27" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B117" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="K117" s="27">
+        <v>4.5</v>
+      </c>
+      <c r="L117" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="R117" s="27" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="118" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B118" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="K118" s="30">
+        <f>SUM(K114:K117)</f>
+        <v>13.1</v>
+      </c>
+      <c r="L118" s="30">
+        <f>SUM(L114:L117)</f>
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9042F9B-23BA-47F6-BE77-A5D7BD460F62}">
+  <dimension ref="B3:P27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="8.88671875" style="27"/>
+    <col min="4" max="4" width="10.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="27" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.77734375" style="27" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="27" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="M3" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="K19" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="N26" s="27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Financial Analysis/Models (Defence).xlsx
+++ b/Financial Analysis/Models (Defence).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBC367E-ACFD-40E5-91FC-0B39CF49BCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CAE64F-5439-4E3D-AF55-E1025C0378D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C6AEFCEA-ADAE-4BFE-85FB-A83490FE9071}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="FY2026 DoD Budget Materials" sheetId="2" r:id="rId2"/>
     <sheet name="DoD Products" sheetId="3" r:id="rId3"/>
     <sheet name="Future Products" sheetId="4" r:id="rId4"/>
+    <sheet name="Global Revenue" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
@@ -43,6 +43,7 @@
     <externalReference r:id="rId26"/>
     <externalReference r:id="rId27"/>
     <externalReference r:id="rId28"/>
+    <externalReference r:id="rId29"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -279,7 +280,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="428">
   <si>
     <t>Company</t>
   </si>
@@ -929,15 +930,6 @@
     <t>Anti-air/missile defence?</t>
   </si>
   <si>
-    <t>DoD 44</t>
-  </si>
-  <si>
-    <t>DoD 20</t>
-  </si>
-  <si>
-    <t>DoD 64</t>
-  </si>
-  <si>
     <t>identify, test and develop new hypersonic tech, analyse and upgrade capabilties of defence against hypersonic threats</t>
   </si>
   <si>
@@ -1362,6 +1354,216 @@
   </si>
   <si>
     <t>add confidence level later?</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>RTX</t>
+  </si>
+  <si>
+    <t>LMT</t>
+  </si>
+  <si>
+    <t>future product</t>
+  </si>
+  <si>
+    <t>RTX (probable)</t>
+  </si>
+  <si>
+    <t>NOC Aeronautics</t>
+  </si>
+  <si>
+    <t>GD Electric Boat</t>
+  </si>
+  <si>
+    <t>LMT Space</t>
+  </si>
+  <si>
+    <t>LMT Aeronautics</t>
+  </si>
+  <si>
+    <t>Boeing Defense</t>
+  </si>
+  <si>
+    <t>LMT/NOC</t>
+  </si>
+  <si>
+    <t>BA Defense</t>
+  </si>
+  <si>
+    <t>LMT/LHX</t>
+  </si>
+  <si>
+    <t>LMT SBIRS + NOC Polar</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>LMT Sikorsky</t>
+  </si>
+  <si>
+    <t>Textron Bell + BA JV</t>
+  </si>
+  <si>
+    <t>Textron Bell?</t>
+  </si>
+  <si>
+    <t>GA Aeronautical</t>
+  </si>
+  <si>
+    <t>General Atomics</t>
+  </si>
+  <si>
+    <t>AeroVironment</t>
+  </si>
+  <si>
+    <t>Archer Aviation</t>
+  </si>
+  <si>
+    <t>Sierra Nevada</t>
+  </si>
+  <si>
+    <t>Sierra Nevada + ERJ (A-29)</t>
+  </si>
+  <si>
+    <t>GD EB</t>
+  </si>
+  <si>
+    <t>GD EB + HII NNS</t>
+  </si>
+  <si>
+    <t>HII + GD Bath Iron Works</t>
+  </si>
+  <si>
+    <t>HII Newport News</t>
+  </si>
+  <si>
+    <t>Fincantieri</t>
+  </si>
+  <si>
+    <t>HII</t>
+  </si>
+  <si>
+    <t>GD NASSCO</t>
+  </si>
+  <si>
+    <t>ASB + LDOS</t>
+  </si>
+  <si>
+    <t>ASB + HII + LDOS</t>
+  </si>
+  <si>
+    <t>ASB + HII</t>
+  </si>
+  <si>
+    <t>SpaceX + LMT + BA (ULA)</t>
+  </si>
+  <si>
+    <t>LHX/NOC</t>
+  </si>
+  <si>
+    <t>BA/LMT/NOC</t>
+  </si>
+  <si>
+    <t>LHX + NOC (SDA)</t>
+  </si>
+  <si>
+    <t>LHX, RTX, HON, LMT</t>
+  </si>
+  <si>
+    <t>NOC, LHX, HON</t>
+  </si>
+  <si>
+    <t>HII, BAE, RTX, LHX</t>
+  </si>
+  <si>
+    <t>LHX, BAE, HON</t>
+  </si>
+  <si>
+    <t>tbd</t>
+  </si>
+  <si>
+    <t>LHX, RTX, Spirit</t>
+  </si>
+  <si>
+    <t>RTX, BAE</t>
+  </si>
+  <si>
+    <t>RTX, BAE, NOC</t>
+  </si>
+  <si>
+    <t>RTX, NOC, LHX</t>
+  </si>
+  <si>
+    <t>RTX, BA, BAE</t>
+  </si>
+  <si>
+    <t>RTX, NOC</t>
+  </si>
+  <si>
+    <t>RTX, Ball, Aerojet</t>
+  </si>
+  <si>
+    <t>York Space, Ball, RTX</t>
+  </si>
+  <si>
+    <t>RTX, BAE, LHX</t>
+  </si>
+  <si>
+    <t>RTX, Spirit, GE</t>
+  </si>
+  <si>
+    <t>RTX, GE, BAE</t>
+  </si>
+  <si>
+    <t>GE, RTX, HON</t>
+  </si>
+  <si>
+    <t>RTX, GE, LMT</t>
+  </si>
+  <si>
+    <t>GE, RTX</t>
+  </si>
+  <si>
+    <t>RR., BA.</t>
+  </si>
+  <si>
+    <t>LHX, RTX</t>
+  </si>
+  <si>
+    <t>RTX, LHX</t>
+  </si>
+  <si>
+    <t>LHX</t>
+  </si>
+  <si>
+    <t>HII NNS, BA., RTX, LHX</t>
+  </si>
+  <si>
+    <t>LHX, BA., HON</t>
+  </si>
+  <si>
+    <t>NOC, LHX</t>
+  </si>
+  <si>
+    <t>LHX, RTX, HON</t>
+  </si>
+  <si>
+    <t>NOC, Aerojet</t>
+  </si>
+  <si>
+    <t>RTX, LHX, Aerojet</t>
+  </si>
+  <si>
+    <t>Ball, RTX</t>
+  </si>
+  <si>
+    <t>RTX, BA.</t>
+  </si>
+  <si>
+    <t>IDIQ - indefinite delivery, indefinite quantity type contracts</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1823,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1716,6 +1918,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2109,6 +2312,7 @@
       <sheetName val="Main"/>
       <sheetName val="Model"/>
       <sheetName val="Charts"/>
+      <sheetName val="Products"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2140,96 +2344,97 @@
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="AA5">
-            <v>87203.32</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="U19">
-            <v>3510</v>
-          </cell>
-          <cell r="V19">
-            <v>-3109</v>
-          </cell>
-          <cell r="W19">
-            <v>3897</v>
-          </cell>
-          <cell r="X19">
-            <v>5216</v>
-          </cell>
-          <cell r="Y19">
-            <v>3195</v>
-          </cell>
-          <cell r="Z19">
-            <v>4774</v>
-          </cell>
-          <cell r="AA19">
-            <v>6597.7138400000167</v>
-          </cell>
-          <cell r="AB19">
-            <v>7570.8374651199974</v>
-          </cell>
-          <cell r="AC19">
-            <v>8157.0804411392028</v>
-          </cell>
-          <cell r="AD19">
-            <v>8502.7527649675394</v>
-          </cell>
-          <cell r="AK19">
-            <v>10539.84925860564</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="Z25">
-            <v>0.17147417295414979</v>
-          </cell>
-          <cell r="AA25">
-            <v>8.0077782456835722E-2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="AO26">
-            <v>0.06</v>
-          </cell>
-        </row>
         <row r="28">
           <cell r="AA28">
+            <v>87203.32</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="U42">
+            <v>3510</v>
+          </cell>
+          <cell r="V42">
+            <v>-3109</v>
+          </cell>
+          <cell r="W42">
+            <v>3897</v>
+          </cell>
+          <cell r="X42">
+            <v>5216</v>
+          </cell>
+          <cell r="Y42">
+            <v>3195</v>
+          </cell>
+          <cell r="Z42">
+            <v>4774</v>
+          </cell>
+          <cell r="AA42">
+            <v>6597.7138400000167</v>
+          </cell>
+          <cell r="AB42">
+            <v>7570.8374651199974</v>
+          </cell>
+          <cell r="AC42">
+            <v>8157.0804411392028</v>
+          </cell>
+          <cell r="AD42">
+            <v>8502.7527649675394</v>
+          </cell>
+          <cell r="AK42">
+            <v>10539.84925860564</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Z48">
+            <v>0.17147417295414979</v>
+          </cell>
+          <cell r="AA48">
+            <v>8.0077782456835722E-2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="AO49">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="AA51">
             <v>0.2026911899684555</v>
           </cell>
         </row>
-        <row r="31">
-          <cell r="AA31">
+        <row r="54">
+          <cell r="AA54">
             <v>9.8853831482562993E-2</v>
           </cell>
         </row>
-        <row r="32">
-          <cell r="AO32">
+        <row r="55">
+          <cell r="AO55">
             <v>-0.50596791605531888</v>
           </cell>
         </row>
-        <row r="33">
-          <cell r="AO33" t="str">
+        <row r="56">
+          <cell r="AO56" t="str">
             <v>Heavily overvalued</v>
           </cell>
         </row>
-        <row r="34">
-          <cell r="AA34">
+        <row r="57">
+          <cell r="AA57">
             <v>7.5658975369286591E-2</v>
           </cell>
         </row>
-        <row r="39">
-          <cell r="P39">
+        <row r="62">
+          <cell r="P62">
             <v>1.556568664405076</v>
           </cell>
         </row>
-        <row r="40">
-          <cell r="P40">
+        <row r="63">
+          <cell r="P63">
             <v>-0.35756126737768923</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5414,7 +5619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087AB355-3143-44BC-BC97-6E84672F8EDE}">
-  <dimension ref="B1:AR31"/>
+  <dimension ref="B1:AR35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -5595,39 +5800,39 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="7">
-        <f t="shared" ref="R3:Z3" si="0">TRIMMEAN(R4:R1048576,80%)</f>
+        <f>TRIMMEAN(R4:R1048576,80%)</f>
         <v>37.145030304683814</v>
       </c>
       <c r="S3" s="7">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(S4:S1048576,80%)</f>
         <v>28.580534120694068</v>
       </c>
       <c r="T3" s="7">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(T4:T1048576,80%)</f>
         <v>24.427824579001424</v>
       </c>
       <c r="U3" s="7">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(U4:U1048576,80%)</f>
         <v>23.633778698262194</v>
       </c>
       <c r="V3" s="7">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(V4:V1048576,80%)</f>
         <v>22.848814495815787</v>
       </c>
       <c r="W3" s="7">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(W4:W1048576,80%)</f>
         <v>18.941051843429769</v>
       </c>
       <c r="X3" s="21">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(X4:X1048576,80%)</f>
         <v>2.0229435907319835</v>
       </c>
       <c r="Y3" s="9">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(Y4:Y1048576,80%)</f>
         <v>-0.50309034649027118</v>
       </c>
       <c r="Z3" s="9">
-        <f t="shared" si="0"/>
+        <f>TRIMMEAN(Z4:Z1048576,80%)</f>
         <v>-0.44652164870768035</v>
       </c>
       <c r="AA3" s="9"/>
@@ -5635,35 +5840,35 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="8"/>
       <c r="AE3" s="21">
-        <f t="shared" ref="AE3:AL3" si="1">TRIMMEAN(AE4:AE1048576,80%)</f>
+        <f>TRIMMEAN(AE4:AE1048576,80%)</f>
         <v>2.9293484226775894</v>
       </c>
       <c r="AF3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AF4:AF1048576,80%)</f>
         <v>0.1016798832038464</v>
       </c>
       <c r="AG3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AG4:AG1048576,80%)</f>
         <v>9.9452943703817409E-2</v>
       </c>
       <c r="AH3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AH4:AH1048576,80%)</f>
         <v>0.20714909665930989</v>
       </c>
       <c r="AI3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AI4:AI1048576,80%)</f>
         <v>9.8848469126009128E-2</v>
       </c>
       <c r="AJ3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AJ4:AJ1048576,80%)</f>
         <v>9.2093150912362295E-2</v>
       </c>
       <c r="AK3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AK4:AK1048576,80%)</f>
         <v>0.08</v>
       </c>
       <c r="AL3" s="9">
-        <f t="shared" si="1"/>
+        <f>TRIMMEAN(AL4:AL1048576,80%)</f>
         <v>-0.46900509315888117</v>
       </c>
       <c r="AM3" s="10" t="e">
@@ -5696,83 +5901,83 @@
         <v>260163.33000000002</v>
       </c>
       <c r="H4" s="14">
-        <f>[1]Model!U$19</f>
+        <f>[1]Model!U$42</f>
         <v>3510</v>
       </c>
       <c r="I4" s="14">
-        <f>[1]Model!V$19</f>
+        <f>[1]Model!V$42</f>
         <v>-3109</v>
       </c>
       <c r="J4" s="14">
-        <f>[1]Model!W$19</f>
+        <f>[1]Model!W$42</f>
         <v>3897</v>
       </c>
       <c r="K4" s="14">
-        <f>[1]Model!X$19</f>
+        <f>[1]Model!X$42</f>
         <v>5216</v>
       </c>
       <c r="L4" s="14">
-        <f>[1]Model!Y$19</f>
+        <f>[1]Model!Y$42</f>
         <v>3195</v>
       </c>
       <c r="M4" s="14">
-        <f>[1]Model!Z$19</f>
+        <f>[1]Model!Z$42</f>
         <v>4774</v>
       </c>
       <c r="N4" s="14">
-        <f>[1]Model!AA$19</f>
+        <f>[1]Model!AA$42</f>
         <v>6597.7138400000167</v>
       </c>
       <c r="O4" s="14">
-        <f>[1]Model!AB$19</f>
+        <f>[1]Model!AB$42</f>
         <v>7570.8374651199974</v>
       </c>
       <c r="P4" s="14">
-        <f>[1]Model!AC$19</f>
+        <f>[1]Model!AC$42</f>
         <v>8157.0804411392028</v>
       </c>
       <c r="Q4" s="14">
-        <f>[1]Model!AD$19</f>
+        <f>[1]Model!AD$42</f>
         <v>8502.7527649675394</v>
       </c>
       <c r="R4" s="15">
-        <f t="shared" ref="R4" si="2">$G4/M4</f>
+        <f t="shared" ref="R4" si="0">$G4/M4</f>
         <v>54.495879765395898</v>
       </c>
       <c r="S4" s="15">
-        <f t="shared" ref="S4" si="3">$G4/N4</f>
+        <f t="shared" ref="S4" si="1">$G4/N4</f>
         <v>39.432345250063065</v>
       </c>
       <c r="T4" s="15">
-        <f t="shared" ref="T4" si="4">$G4/O4</f>
+        <f t="shared" ref="T4" si="2">$G4/O4</f>
         <v>34.3638773383542</v>
       </c>
       <c r="U4" s="15">
-        <f t="shared" ref="U4" si="5">$G4/P4</f>
+        <f t="shared" ref="U4" si="3">$G4/P4</f>
         <v>31.894172415892726</v>
       </c>
       <c r="V4" s="15">
-        <f t="shared" ref="V4" si="6">$G4/Q4</f>
+        <f t="shared" ref="V4" si="4">$G4/Q4</f>
         <v>30.597541430571425</v>
       </c>
       <c r="W4" s="15">
-        <f>G4/[1]Model!$AK$19</f>
+        <f>G4/[1]Model!$AK$42</f>
         <v>24.683780917225196</v>
       </c>
       <c r="X4" s="20">
-        <f>[1]Model!$P$39</f>
+        <f>[1]Model!$P$62</f>
         <v>1.556568664405076</v>
       </c>
       <c r="Y4" s="16">
-        <f>[1]Model!$P$40</f>
+        <f>[1]Model!$P$63</f>
         <v>-0.35756126737768923</v>
       </c>
       <c r="Z4" s="16">
-        <f t="shared" ref="Z4:Z16" si="7">AVERAGE(Y4,AL4)</f>
+        <f t="shared" ref="Z4:Z16" si="5">AVERAGE(Y4,AL4)</f>
         <v>-0.43176459171650405</v>
       </c>
       <c r="AD4" s="14">
-        <f>[1]Model!$AA$5</f>
+        <f>[1]Model!$AA$28</f>
         <v>87203.32</v>
       </c>
       <c r="AE4" s="20">
@@ -5780,35 +5985,35 @@
         <v>2.9834108380277264</v>
       </c>
       <c r="AF4" s="16">
-        <f>[1]Model!Z$25</f>
+        <f>[1]Model!Z$48</f>
         <v>0.17147417295414979</v>
       </c>
       <c r="AG4" s="16">
-        <f>[1]Model!AA$25</f>
+        <f>[1]Model!AA$48</f>
         <v>8.0077782456835722E-2</v>
       </c>
       <c r="AH4" s="16">
-        <f>[1]Model!$AA$28</f>
+        <f>[1]Model!$AA$51</f>
         <v>0.2026911899684555</v>
       </c>
       <c r="AI4" s="16">
-        <f>[1]Model!$AA$31</f>
+        <f>[1]Model!$AA$54</f>
         <v>9.8853831482562993E-2</v>
       </c>
       <c r="AJ4" s="16">
-        <f>[1]Model!$AA$34</f>
+        <f>[1]Model!$AA$57</f>
         <v>7.5658975369286591E-2</v>
       </c>
       <c r="AK4" s="16">
-        <f>[1]Model!$AO$26</f>
+        <f>[1]Model!$AO$49</f>
         <v>0.06</v>
       </c>
       <c r="AL4" s="16">
-        <f>[1]Model!$AO$32</f>
+        <f>[1]Model!$AO$55</f>
         <v>-0.50596791605531888</v>
       </c>
       <c r="AM4" s="11" t="str">
-        <f>[1]Model!$AO$33</f>
+        <f>[1]Model!$AO$56</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AO4" s="11">
@@ -5891,11 +6096,11 @@
         <v>-16.192035368421053</v>
       </c>
       <c r="U5" s="15">
-        <f t="shared" ref="U5:V6" si="8">$G5/P5</f>
+        <f t="shared" ref="U5:V6" si="6">$G5/P5</f>
         <v>58.621964814446763</v>
       </c>
       <c r="V5" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>43.807640449740965</v>
       </c>
       <c r="W5" s="15">
@@ -5911,7 +6116,7 @@
         <v>-0.19326159158587242</v>
       </c>
       <c r="Z5" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.33367759536537156</v>
       </c>
       <c r="AA5" s="14">
@@ -5931,7 +6136,7 @@
         <v>89475.77</v>
       </c>
       <c r="AE5" s="20">
-        <f t="shared" ref="AE5:AE8" si="9">G5/AD5</f>
+        <f t="shared" ref="AE5:AE8" si="7">G5/AD5</f>
         <v>2.1489663626253233</v>
       </c>
       <c r="AF5" s="16">
@@ -6043,19 +6248,19 @@
         <v>27.638453111305871</v>
       </c>
       <c r="S6" s="15">
-        <f t="shared" ref="S6:T6" si="10">$G6/N6</f>
+        <f t="shared" ref="S6:T6" si="8">$G6/N6</f>
         <v>25.25983105201702</v>
       </c>
       <c r="T6" s="15">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>24.352230718337395</v>
       </c>
       <c r="U6" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>22.800195718108814</v>
       </c>
       <c r="V6" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>21.428067137800639</v>
       </c>
       <c r="W6" s="15">
@@ -6071,7 +6276,7 @@
         <v>-0.50266168497541264</v>
       </c>
       <c r="Z6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.38303596027376657</v>
       </c>
       <c r="AD6" s="14">
@@ -6079,7 +6284,7 @@
         <v>41769.86</v>
       </c>
       <c r="AE6" s="20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>3.7749079120686542</v>
       </c>
       <c r="AF6" s="25">
@@ -6219,7 +6424,7 @@
         <v>-0.11857330460864102</v>
       </c>
       <c r="Z7" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.21499012297223874</v>
       </c>
       <c r="AD7" s="14">
@@ -6335,23 +6540,23 @@
         <v>7229.3492892684044</v>
       </c>
       <c r="R8" s="15">
-        <f t="shared" ref="R8" si="11">$G8/M8</f>
+        <f t="shared" ref="R8" si="9">$G8/M8</f>
         <v>25.409560532233886</v>
       </c>
       <c r="S8" s="15">
-        <f t="shared" ref="S8" si="12">$G8/N8</f>
+        <f t="shared" ref="S8" si="10">$G8/N8</f>
         <v>19.677209132580092</v>
       </c>
       <c r="T8" s="15">
-        <f t="shared" ref="T8" si="13">$G8/O8</f>
+        <f t="shared" ref="T8" si="11">$G8/O8</f>
         <v>19.261708991794382</v>
       </c>
       <c r="U8" s="15">
-        <f t="shared" ref="U8" si="14">$G8/P8</f>
+        <f t="shared" ref="U8" si="12">$G8/P8</f>
         <v>19.007115354099724</v>
       </c>
       <c r="V8" s="15">
-        <f t="shared" ref="V8" si="15">$G8/Q8</f>
+        <f t="shared" ref="V8" si="13">$G8/Q8</f>
         <v>18.754857397922322</v>
       </c>
       <c r="W8" s="15">
@@ -6367,7 +6572,7 @@
         <v>-0.56580875605241165</v>
       </c>
       <c r="Z8" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.42579573579547941</v>
       </c>
       <c r="AD8" s="14">
@@ -6375,7 +6580,7 @@
         <v>72581.52</v>
       </c>
       <c r="AE8" s="20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>1.8680432016303874</v>
       </c>
       <c r="AF8" s="25">
@@ -6483,23 +6688,23 @@
         <v>5481.8804852950607</v>
       </c>
       <c r="R9" s="15">
-        <f t="shared" ref="R9" si="16">$G9/M9</f>
+        <f t="shared" ref="R9" si="14">$G9/M9</f>
         <v>-184.72487256371815</v>
       </c>
       <c r="S9" s="15">
-        <f t="shared" ref="S9" si="17">$G9/N9</f>
+        <f t="shared" ref="S9" si="15">$G9/N9</f>
         <v>18.326678226112765</v>
       </c>
       <c r="T9" s="15">
-        <f t="shared" ref="T9" si="18">$G9/O9</f>
+        <f t="shared" ref="T9" si="16">$G9/O9</f>
         <v>24.849439290953406</v>
       </c>
       <c r="U9" s="15">
-        <f t="shared" ref="U9" si="19">$G9/P9</f>
+        <f t="shared" ref="U9" si="17">$G9/P9</f>
         <v>23.406509800216369</v>
       </c>
       <c r="V9" s="15">
-        <f t="shared" ref="V9" si="20">$G9/Q9</f>
+        <f t="shared" ref="V9" si="18">$G9/Q9</f>
         <v>22.476135758616085</v>
       </c>
       <c r="W9" s="15">
@@ -6515,7 +6720,7 @@
         <v>-0.55351566643662864</v>
       </c>
       <c r="Z9" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.44166882388829903</v>
       </c>
       <c r="AD9" s="14">
@@ -6523,7 +6728,7 @@
         <v>31734.280000000002</v>
       </c>
       <c r="AE9" s="20">
-        <f t="shared" ref="AE9" si="21">G9/AD9</f>
+        <f t="shared" ref="AE9" si="19">G9/AD9</f>
         <v>3.8825991955702159</v>
       </c>
       <c r="AF9" s="25">
@@ -6635,19 +6840,19 @@
         <v>24.088914230953517</v>
       </c>
       <c r="S10" s="15">
-        <f t="shared" ref="S10:V14" si="22">$G10/N10</f>
+        <f t="shared" ref="S10:V14" si="20">$G10/N10</f>
         <v>22.620395387674964</v>
       </c>
       <c r="T10" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>21.766074364731814</v>
       </c>
       <c r="U10" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>21.210225070356397</v>
       </c>
       <c r="V10" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>20.670545127100677</v>
       </c>
       <c r="W10" s="15">
@@ -6663,7 +6868,7 @@
         <v>-0.50818088011424845</v>
       </c>
       <c r="Z10" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.48532254105365091</v>
       </c>
       <c r="AD10" s="14">
@@ -6671,7 +6876,7 @@
         <v>42508.18</v>
       </c>
       <c r="AE10" s="20">
-        <f t="shared" ref="AE10:AE14" si="23">G10/AD10</f>
+        <f t="shared" ref="AE10:AE14" si="21">G10/AD10</f>
         <v>2.365359514333476</v>
       </c>
       <c r="AF10" s="25">
@@ -6779,23 +6984,23 @@
         <v>5139.2124562518457</v>
       </c>
       <c r="R11" s="15">
-        <f t="shared" ref="R11" si="24">$G11/M11</f>
+        <f t="shared" ref="R11" si="22">$G11/M11</f>
         <v>26.652771020624009</v>
       </c>
       <c r="S11" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>23.753986727053604</v>
       </c>
       <c r="T11" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>21.802623192142356</v>
       </c>
       <c r="U11" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>20.582511814672802</v>
       </c>
       <c r="V11" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>19.614051930734245</v>
       </c>
       <c r="W11" s="15">
@@ -6811,7 +7016,7 @@
         <v>-0.435639287711861</v>
       </c>
       <c r="Z11" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.41026508664784828</v>
       </c>
       <c r="AD11" s="14">
@@ -6819,7 +7024,7 @@
         <v>52106.25</v>
       </c>
       <c r="AE11" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1.9345237855343649</v>
       </c>
       <c r="AF11" s="16">
@@ -6927,23 +7132,23 @@
         <v>1588.4162624936125</v>
       </c>
       <c r="R12" s="15">
-        <f t="shared" ref="R12:V13" si="25">$G12/M12</f>
+        <f t="shared" ref="R12:V13" si="23">$G12/M12</f>
         <v>66.59591913393372</v>
       </c>
       <c r="S12" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>60.707353386766897</v>
       </c>
       <c r="T12" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>53.672211306920168</v>
       </c>
       <c r="U12" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>50.258171889122295</v>
       </c>
       <c r="V12" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>48.332343235694317</v>
       </c>
       <c r="W12" s="15">
@@ -6959,7 +7164,7 @@
         <v>-0.80991738120780687</v>
       </c>
       <c r="Z12" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.76267567438446748</v>
       </c>
       <c r="AA12" s="14">
@@ -7090,23 +7295,23 @@
         <v>2597.5219971524007</v>
       </c>
       <c r="R13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>48.769939117199392</v>
       </c>
       <c r="S13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>50.465435388137962</v>
       </c>
       <c r="T13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>44.368907355122417</v>
       </c>
       <c r="U13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>40.207979589322406</v>
       </c>
       <c r="V13" s="15">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>37.006635595532998</v>
       </c>
       <c r="W13" s="15">
@@ -7122,7 +7327,7 @@
         <v>-0.60530784999409626</v>
       </c>
       <c r="Z13" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.57480585497831804</v>
       </c>
       <c r="AD13" s="14">
@@ -7235,23 +7440,23 @@
         <v>3774.8694653950824</v>
       </c>
       <c r="R14" s="15">
-        <f t="shared" ref="R14" si="26">$G14/M14</f>
+        <f t="shared" ref="R14" si="24">$G14/M14</f>
         <v>34.027096114519431</v>
       </c>
       <c r="S14" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>22.311880923727148</v>
       </c>
       <c r="T14" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>20.328597250994147</v>
       </c>
       <c r="U14" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>18.702771500144515</v>
       </c>
       <c r="V14" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>17.631603055454015</v>
       </c>
       <c r="W14" s="15">
@@ -7267,7 +7472,7 @@
         <v>-0.45909521162312006</v>
       </c>
       <c r="Z14" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.29409758332501079</v>
       </c>
       <c r="AA14" s="14">
@@ -7287,7 +7492,7 @@
         <v>28248.11</v>
       </c>
       <c r="AE14" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>2.3561576332009468</v>
       </c>
       <c r="AF14" s="16">
@@ -7398,19 +7603,19 @@
         <v>44.781404127829553</v>
       </c>
       <c r="S15" s="15">
-        <f t="shared" ref="S15:V18" si="27">$G15/N15</f>
+        <f t="shared" ref="S15:V18" si="25">$G15/N15</f>
         <v>29.965150049817257</v>
       </c>
       <c r="T15" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>28.066563385194236</v>
       </c>
       <c r="U15" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>26.582890253395643</v>
       </c>
       <c r="V15" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>25.458143882180341</v>
       </c>
       <c r="W15" s="15">
@@ -7426,7 +7631,7 @@
         <v>-0.38687218718881322</v>
       </c>
       <c r="Z15" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.47734610923232346</v>
       </c>
       <c r="AD15" s="23">
@@ -7434,7 +7639,7 @@
         <v>21325</v>
       </c>
       <c r="AE15" s="26">
-        <f t="shared" ref="AE15:AE18" si="28">G15/AD15</f>
+        <f t="shared" ref="AE15:AE18" si="26">G15/AD15</f>
         <v>3.154122813599062</v>
       </c>
       <c r="AF15" s="25">
@@ -7542,23 +7747,23 @@
         <v>1905.822140949791</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" ref="R16" si="29">$G16/M16</f>
+        <f t="shared" ref="R16" si="27">$G16/M16</f>
         <v>61.21581036147181</v>
       </c>
       <c r="S16" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>38.734035816157068</v>
       </c>
       <c r="T16" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>34.089893408750115</v>
       </c>
       <c r="U16" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>31.674211018765618</v>
       </c>
       <c r="V16" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>29.945868910704167</v>
       </c>
       <c r="W16" s="15">
@@ -7574,7 +7779,7 @@
         <v>-0.31862663501046928</v>
       </c>
       <c r="Z16" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>-0.45603298290579602</v>
       </c>
       <c r="AD16" s="23">
@@ -7582,7 +7787,7 @@
         <v>20576.599999999999</v>
       </c>
       <c r="AE16" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>2.7736117725960558</v>
       </c>
       <c r="AF16" s="25">
@@ -7733,23 +7938,23 @@
         <v>1456.7690142637746</v>
       </c>
       <c r="R18" s="15">
-        <f t="shared" ref="R18" si="30">$G18/M18</f>
+        <f t="shared" ref="R18" si="28">$G18/M18</f>
         <v>30.47085561942847</v>
       </c>
       <c r="S18" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>32.847418103943696</v>
       </c>
       <c r="T18" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>25.717312311078611</v>
       </c>
       <c r="U18" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>25.33201483486426</v>
       </c>
       <c r="V18" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>25.1063604743707</v>
       </c>
       <c r="W18" s="15">
@@ -7773,7 +7978,7 @@
         <v>6448.74</v>
       </c>
       <c r="AE18" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>5.6715215685544775</v>
       </c>
       <c r="AF18" s="16">
@@ -7884,23 +8089,23 @@
         <v>1993.765444011</v>
       </c>
       <c r="R19" s="15">
-        <f t="shared" ref="R19:V19" si="31">$G19/M19</f>
+        <f t="shared" ref="R19:V19" si="29">$G19/M19</f>
         <v>30.251977611940294</v>
       </c>
       <c r="S19" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>31.87885020107046</v>
       </c>
       <c r="T19" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>17.898670569986351</v>
       </c>
       <c r="U19" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>16.898744377727255</v>
       </c>
       <c r="V19" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>16.265764911020835</v>
       </c>
       <c r="W19" s="15">
@@ -7924,7 +8129,7 @@
         <v>17763</v>
       </c>
       <c r="AE19" s="26">
-        <f t="shared" ref="AE19:AE25" si="32">G19/AD19</f>
+        <f t="shared" ref="AE19:AE25" si="30">G19/AD19</f>
         <v>1.8257118729944264</v>
       </c>
       <c r="AF19" s="25">
@@ -8032,23 +8237,23 @@
         <v>1981.3585502100002</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" ref="R20" si="33">$G20/M20</f>
+        <f t="shared" ref="R20" si="31">$G20/M20</f>
         <v>23.338846889952155</v>
       </c>
       <c r="S20" s="15">
-        <f t="shared" ref="S20:S25" si="34">$G20/N20</f>
+        <f t="shared" ref="S20:S25" si="32">$G20/N20</f>
         <v>19.662555639495466</v>
       </c>
       <c r="T20" s="15">
-        <f t="shared" ref="T20:T25" si="35">$G20/O20</f>
+        <f t="shared" ref="T20:T25" si="33">$G20/O20</f>
         <v>16.032369668047799</v>
       </c>
       <c r="U20" s="15">
-        <f t="shared" ref="U20:U25" si="36">$G20/P20</f>
+        <f t="shared" ref="U20:U25" si="34">$G20/P20</f>
         <v>15.277197591691403</v>
       </c>
       <c r="V20" s="15">
-        <f t="shared" ref="V20:V25" si="37">$G20/Q20</f>
+        <f t="shared" ref="V20:V25" si="35">$G20/Q20</f>
         <v>14.771134682765046</v>
       </c>
       <c r="W20" s="15">
@@ -8072,7 +8277,7 @@
         <v>16662</v>
       </c>
       <c r="AE20" s="26">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1.7565066618653224</v>
       </c>
       <c r="AF20" s="25">
@@ -8156,11 +8361,11 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
       <c r="R21" s="15">
-        <f t="shared" ref="R21" si="38">$G21/M21</f>
+        <f t="shared" ref="R21" si="36">$G21/M21</f>
         <v>64.150899999999993</v>
       </c>
       <c r="S21" s="15">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>47.326279668857218</v>
       </c>
       <c r="T21" s="15"/>
@@ -8189,7 +8394,7 @@
         <v>9401.5300000000007</v>
       </c>
       <c r="AE21" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>2.5246776854405608</v>
       </c>
       <c r="AF21" s="25"/>
@@ -8316,7 +8521,7 @@
         <v>13702</v>
       </c>
       <c r="AE22" s="26">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1.2973777550722521</v>
       </c>
       <c r="AF22" s="25">
@@ -8424,23 +8629,23 @@
         <v>906.37830312002222</v>
       </c>
       <c r="R23" s="15">
-        <f t="shared" ref="R23:V23" si="39">$G23/M23</f>
+        <f t="shared" ref="R23:V23" si="37">$G23/M23</f>
         <v>48.745508326029736</v>
       </c>
       <c r="S23" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>14.958147751479586</v>
       </c>
       <c r="T23" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>15.465549056205754</v>
       </c>
       <c r="U23" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>13.38914993051745</v>
       </c>
       <c r="V23" s="15">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>12.272717651899708</v>
       </c>
       <c r="W23" s="15">
@@ -8464,7 +8669,7 @@
         <v>7743.8040000000001</v>
       </c>
       <c r="AE23" s="26">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1.4364677876661134</v>
       </c>
       <c r="AF23" s="25">
@@ -8572,23 +8777,23 @@
         <v>189.70135618560002</v>
       </c>
       <c r="R24" s="15">
-        <f t="shared" ref="R24" si="40">$G24/M24</f>
+        <f t="shared" ref="R24" si="38">$G24/M24</f>
         <v>115.44528301886793</v>
       </c>
       <c r="S24" s="15">
+        <f t="shared" si="32"/>
+        <v>115.72757095042404</v>
+      </c>
+      <c r="T24" s="15">
+        <f t="shared" si="33"/>
+        <v>84.768709132687491</v>
+      </c>
+      <c r="U24" s="15">
         <f t="shared" si="34"/>
-        <v>115.72757095042404</v>
-      </c>
-      <c r="T24" s="15">
+        <v>72.031905293617854</v>
+      </c>
+      <c r="V24" s="15">
         <f t="shared" si="35"/>
-        <v>84.768709132687491</v>
-      </c>
-      <c r="U24" s="15">
-        <f t="shared" si="36"/>
-        <v>72.031905293617854</v>
-      </c>
-      <c r="V24" s="15">
-        <f t="shared" si="37"/>
         <v>64.50770962347454</v>
       </c>
       <c r="W24" s="15">
@@ -8612,7 +8817,7 @@
         <v>2587.8199999999997</v>
       </c>
       <c r="AE24" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>4.7287678432039328</v>
       </c>
       <c r="AF24" s="16">
@@ -8720,23 +8925,23 @@
         <v>85.495337030527935</v>
       </c>
       <c r="R25" s="15">
-        <f t="shared" ref="R25" si="41">$G25/M25</f>
+        <f t="shared" ref="R25" si="39">$G25/M25</f>
         <v>1076.0093251533783</v>
       </c>
       <c r="S25" s="15">
+        <f t="shared" si="32"/>
+        <v>878.27344158743199</v>
+      </c>
+      <c r="T25" s="15">
+        <f t="shared" si="33"/>
+        <v>371.42801283135509</v>
+      </c>
+      <c r="U25" s="15">
         <f t="shared" si="34"/>
-        <v>878.27344158743199</v>
-      </c>
-      <c r="T25" s="15">
+        <v>247.74450117469067</v>
+      </c>
+      <c r="V25" s="15">
         <f t="shared" si="35"/>
-        <v>371.42801283135509</v>
-      </c>
-      <c r="U25" s="15">
-        <f t="shared" si="36"/>
-        <v>247.74450117469067</v>
-      </c>
-      <c r="V25" s="15">
-        <f t="shared" si="37"/>
         <v>205.1451296547009</v>
       </c>
       <c r="W25" s="15">
@@ -8760,7 +8965,7 @@
         <v>1297.6099999999999</v>
       </c>
       <c r="AE25" s="20">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>13.51635082960212</v>
       </c>
       <c r="AF25" s="16">
@@ -8871,23 +9076,23 @@
         <v>200.07653520599999</v>
       </c>
       <c r="R27" s="15">
-        <f t="shared" ref="R27" si="42">$G27/M27</f>
+        <f t="shared" ref="R27" si="40">$G27/M27</f>
         <v>132.73644859813069</v>
       </c>
       <c r="S27" s="15">
-        <f t="shared" ref="S27" si="43">$G27/N27</f>
+        <f t="shared" ref="S27" si="41">$G27/N27</f>
         <v>73.343961635656939</v>
       </c>
       <c r="T27" s="15">
-        <f t="shared" ref="T27:T28" si="44">$G27/O27</f>
+        <f t="shared" ref="T27:T28" si="42">$G27/O27</f>
         <v>49.486524348833029</v>
       </c>
       <c r="U27" s="15">
-        <f t="shared" ref="U27:U28" si="45">$G27/P27</f>
+        <f t="shared" ref="U27:U28" si="43">$G27/P27</f>
         <v>39.51155848292143</v>
       </c>
       <c r="V27" s="15">
-        <f t="shared" ref="V27:V28" si="46">$G27/Q27</f>
+        <f t="shared" ref="V27:V28" si="44">$G27/Q27</f>
         <v>35.493417519892354</v>
       </c>
       <c r="W27" s="15">
@@ -8995,19 +9200,19 @@
         <v>-123.67537759999999</v>
       </c>
       <c r="S28" s="15">
-        <f t="shared" ref="S28" si="47">$G28/N28</f>
+        <f t="shared" ref="S28" si="45">$G28/N28</f>
         <v>-18.910292102416154</v>
       </c>
       <c r="T28" s="15">
+        <f t="shared" si="42"/>
+        <v>-14.377434018962179</v>
+      </c>
+      <c r="U28" s="15">
+        <f t="shared" si="43"/>
+        <v>-11.871818454152232</v>
+      </c>
+      <c r="V28" s="15">
         <f t="shared" si="44"/>
-        <v>-14.377434018962179</v>
-      </c>
-      <c r="U28" s="15">
-        <f t="shared" si="45"/>
-        <v>-11.871818454152232</v>
-      </c>
-      <c r="V28" s="15">
-        <f t="shared" si="46"/>
         <v>-10.59997572224918</v>
       </c>
       <c r="W28" s="15">
@@ -9207,6 +9412,26 @@
       <c r="AL31" s="16"/>
       <c r="AQ31" s="18"/>
       <c r="AR31" s="18"/>
+    </row>
+    <row r="32" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="B32" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="5" t="s">
+        <v>380</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9287,13 +9512,16 @@
         <v>101</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="s">
         <v>99</v>
       </c>
+      <c r="K8" s="27" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
@@ -9370,7 +9598,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
@@ -9923,7 +10151,7 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="29" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C78" s="27">
         <v>197.40899999999999</v>
@@ -9931,7 +10159,7 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="29" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C80" s="27">
         <v>292.233</v>
@@ -9939,7 +10167,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B82" s="29" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C82" s="27">
         <v>301.07799999999997</v>
@@ -9947,7 +10175,7 @@
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B84" s="29" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C84" s="27">
         <v>36.5</v>
@@ -9955,7 +10183,7 @@
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" s="29" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C86" s="27">
         <v>170.876</v>
@@ -9979,12 +10207,14 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="27"/>
     <col min="2" max="2" width="48.77734375" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="27"/>
+    <col min="3" max="3" width="8.88671875" style="27"/>
+    <col min="4" max="4" width="22.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="27"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B2" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>176</v>
@@ -9999,22 +10229,22 @@
         <v>214</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>177</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M2" s="27" t="s">
         <v>192</v>
@@ -10133,8 +10363,8 @@
       <c r="B11" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="H11" s="27" t="s">
-        <v>218</v>
+      <c r="H11" s="27">
+        <v>64</v>
       </c>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
@@ -10145,8 +10375,8 @@
       <c r="B12" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="27" t="s">
-        <v>216</v>
+      <c r="H12" s="27">
+        <v>44</v>
       </c>
       <c r="J12" s="42"/>
       <c r="K12" s="42"/>
@@ -10157,8 +10387,8 @@
       <c r="B13" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="H13" s="27" t="s">
-        <v>217</v>
+      <c r="H13" s="27">
+        <v>20</v>
       </c>
       <c r="J13" s="42"/>
       <c r="K13" s="42"/>
@@ -10197,7 +10427,7 @@
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J17" s="42"/>
       <c r="K17" s="42"/>
@@ -10206,7 +10436,7 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J18" s="42"/>
       <c r="K18" s="42"/>
@@ -10215,7 +10445,7 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J19" s="42"/>
       <c r="K19" s="42"/>
@@ -10233,31 +10463,31 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J21" s="42"/>
       <c r="K21" s="42"/>
       <c r="L21" s="42"/>
       <c r="M21" s="42"/>
       <c r="R21" s="27" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B22" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J22" s="42"/>
       <c r="K22" s="42"/>
       <c r="L22" s="42"/>
       <c r="M22" s="42"/>
       <c r="R22" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B23" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J23" s="42"/>
       <c r="K23" s="42"/>
@@ -10266,7 +10496,7 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B24" s="27" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J24" s="42"/>
       <c r="K24" s="42"/>
@@ -10275,7 +10505,7 @@
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B25" s="27" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
@@ -10284,7 +10514,7 @@
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B26" s="27" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J26" s="42"/>
       <c r="K26" s="42"/>
@@ -10293,7 +10523,7 @@
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B27" s="27" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J27" s="42"/>
       <c r="K27" s="42"/>
@@ -10302,7 +10532,7 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B28" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J28" s="42"/>
       <c r="K28" s="42"/>
@@ -10313,7 +10543,7 @@
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B29" s="27" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J29" s="42"/>
       <c r="K29" s="42"/>
@@ -10324,7 +10554,7 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B30" s="27" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J30" s="42"/>
       <c r="K30" s="42"/>
@@ -10333,7 +10563,7 @@
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B31" s="27" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J31" s="42"/>
       <c r="K31" s="42"/>
@@ -10342,7 +10572,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B32" s="27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J32" s="42"/>
       <c r="K32" s="42"/>
@@ -10351,7 +10581,7 @@
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B33" s="27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J33" s="42"/>
       <c r="K33" s="42"/>
@@ -10360,7 +10590,7 @@
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B34" s="27" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J34" s="42"/>
       <c r="K34" s="42"/>
@@ -10371,7 +10601,7 @@
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B35" s="27" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J35" s="42"/>
       <c r="K35" s="42"/>
@@ -10380,7 +10610,7 @@
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B36" s="27" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
@@ -10389,7 +10619,7 @@
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B37" s="27" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J37" s="42"/>
       <c r="K37" s="42"/>
@@ -10400,7 +10630,7 @@
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B38" s="27" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J38" s="42"/>
       <c r="K38" s="42"/>
@@ -10409,7 +10639,7 @@
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B39" s="27" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J39" s="42"/>
       <c r="K39" s="42"/>
@@ -10418,7 +10648,7 @@
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B40" s="27" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J40" s="42"/>
       <c r="K40" s="42"/>
@@ -10427,7 +10657,7 @@
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B41" s="27" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J41" s="42"/>
       <c r="K41" s="42"/>
@@ -10436,7 +10666,7 @@
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B42" s="27" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
@@ -10445,7 +10675,7 @@
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B43" s="27" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J43" s="42"/>
       <c r="K43" s="42"/>
@@ -10454,7 +10684,7 @@
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B44" s="27" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J44" s="42"/>
       <c r="K44" s="42"/>
@@ -10463,7 +10693,7 @@
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J45" s="42"/>
       <c r="K45" s="42"/>
@@ -10472,7 +10702,7 @@
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B46" s="27" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J46" s="42"/>
       <c r="K46" s="42"/>
@@ -10481,19 +10711,19 @@
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B47" s="27" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J47" s="42"/>
       <c r="K47" s="42"/>
       <c r="L47" s="42"/>
       <c r="M47" s="42"/>
       <c r="R47" s="27" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B48" s="27" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J48" s="42"/>
       <c r="K48" s="42"/>
@@ -10502,7 +10732,7 @@
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B49" s="27" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J49" s="42"/>
       <c r="K49" s="42"/>
@@ -10529,7 +10759,7 @@
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B52" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J52" s="42">
         <v>2.681</v>
@@ -10550,7 +10780,7 @@
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B54" s="29" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J54" s="42"/>
       <c r="K54" s="42"/>
@@ -10574,7 +10804,13 @@
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B57" s="27" t="s">
-        <v>262</v>
+        <v>259</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>396</v>
       </c>
       <c r="J57" s="42">
         <v>4.3360000000000003</v>
@@ -10587,12 +10823,18 @@
       </c>
       <c r="M57" s="42"/>
       <c r="R57" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B58" s="27" t="s">
-        <v>263</v>
+        <v>260</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>397</v>
       </c>
       <c r="J58" s="42">
         <v>0.92400000000000004</v>
@@ -10605,12 +10847,18 @@
       </c>
       <c r="M58" s="42"/>
       <c r="R58" s="27" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B59" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>398</v>
       </c>
       <c r="J59" s="42">
         <v>8.1950000000000003</v>
@@ -10623,12 +10871,18 @@
       </c>
       <c r="M59" s="42"/>
       <c r="R59" s="27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B60" s="27" t="s">
-        <v>265</v>
+        <v>262</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="E60" s="27" t="s">
+        <v>399</v>
       </c>
       <c r="J60" s="42">
         <v>1.8720000000000001</v>
@@ -10643,7 +10897,13 @@
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B61" s="27" t="s">
-        <v>266</v>
+        <v>263</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>400</v>
       </c>
       <c r="J61" s="42">
         <v>0.13400000000000001</v>
@@ -10655,11 +10915,20 @@
         <v>1.9319999999999999</v>
       </c>
       <c r="M61" s="42"/>
+      <c r="R61" s="27" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B62" s="27" t="s">
         <v>118</v>
       </c>
+      <c r="D62" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>401</v>
+      </c>
       <c r="J62" s="42">
         <v>6.2169999999999996</v>
       </c>
@@ -10671,12 +10940,18 @@
       </c>
       <c r="M62" s="42"/>
       <c r="R62" s="27" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B63" s="27" t="s">
-        <v>267</v>
+        <v>264</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>403</v>
       </c>
       <c r="J63" s="42">
         <v>2.1000000000000001E-2</v>
@@ -10689,12 +10964,18 @@
       </c>
       <c r="M63" s="42"/>
       <c r="R63" s="27" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B64" s="27" t="s">
-        <v>268</v>
+        <v>265</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>404</v>
       </c>
       <c r="J64" s="42">
         <v>0.71799999999999997</v>
@@ -10707,12 +10988,18 @@
       </c>
       <c r="M64" s="42"/>
       <c r="R64" s="27" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B65" s="27" t="s">
-        <v>269</v>
+        <v>266</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>405</v>
       </c>
       <c r="J65" s="42">
         <v>0.47399999999999998</v>
@@ -10727,7 +11014,13 @@
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B66" s="27" t="s">
-        <v>270</v>
+        <v>267</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>406</v>
       </c>
       <c r="J66" s="42">
         <v>0.2</v>
@@ -10740,12 +11033,18 @@
       </c>
       <c r="M66" s="42"/>
       <c r="R66" s="27" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B67" s="27" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>407</v>
       </c>
       <c r="J67" s="42">
         <v>2.331</v>
@@ -10760,7 +11059,13 @@
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B68" s="27" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>408</v>
       </c>
       <c r="J68" s="42">
         <v>2.181</v>
@@ -10793,12 +11098,18 @@
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B71" s="29" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B72" s="27" t="s">
-        <v>282</v>
+        <v>279</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>403</v>
       </c>
       <c r="G72" s="27">
         <v>74</v>
@@ -10813,12 +11124,18 @@
         <v>13.1</v>
       </c>
       <c r="R72" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B73" s="27" t="s">
-        <v>283</v>
+        <v>280</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>409</v>
       </c>
       <c r="G73" s="27">
         <v>18</v>
@@ -10833,13 +11150,19 @@
         <v>3.1</v>
       </c>
       <c r="R73" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B74" s="27" t="s">
         <v>175</v>
       </c>
+      <c r="D74" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>400</v>
+      </c>
       <c r="K74" s="27">
         <v>2.4</v>
       </c>
@@ -10847,12 +11170,18 @@
         <v>3.5</v>
       </c>
       <c r="R74" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B75" s="27" t="s">
-        <v>284</v>
+        <v>281</v>
+      </c>
+      <c r="D75" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="E75" s="27" t="s">
+        <v>410</v>
       </c>
       <c r="G75" s="27">
         <v>15</v>
@@ -10867,12 +11196,18 @@
         <v>3.3</v>
       </c>
       <c r="R75" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B76" s="27" t="s">
-        <v>285</v>
+        <v>282</v>
+      </c>
+      <c r="D76" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="E76" s="27" t="s">
+        <v>411</v>
       </c>
       <c r="K76" s="27">
         <v>1.7</v>
@@ -10881,12 +11216,18 @@
         <v>2</v>
       </c>
       <c r="R76" s="45" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B77" s="27" t="s">
-        <v>286</v>
+        <v>283</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="E77" s="27" t="s">
+        <v>412</v>
       </c>
       <c r="G77" s="27">
         <v>20</v>
@@ -10901,12 +11242,18 @@
         <v>2.5</v>
       </c>
       <c r="R77" s="45" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B78" s="27" t="s">
-        <v>287</v>
+        <v>284</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="E78" s="27" t="s">
+        <v>402</v>
       </c>
       <c r="H78" s="27">
         <v>4</v>
@@ -10918,12 +11265,18 @@
         <v>2.1</v>
       </c>
       <c r="R78" s="45" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B79" s="27" t="s">
-        <v>288</v>
+        <v>285</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>413</v>
       </c>
       <c r="G79" s="27">
         <v>31</v>
@@ -10935,12 +11288,18 @@
         <v>0.2</v>
       </c>
       <c r="R79" s="45" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B80" s="27" t="s">
-        <v>289</v>
+        <v>286</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>414</v>
       </c>
       <c r="G80" s="27">
         <v>26</v>
@@ -10955,12 +11314,18 @@
         <v>0.8</v>
       </c>
       <c r="R80" s="45" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B81" s="27" t="s">
-        <v>290</v>
+        <v>287</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>415</v>
       </c>
       <c r="K81" s="27">
         <v>0.6</v>
@@ -10969,12 +11334,18 @@
         <v>0.8</v>
       </c>
       <c r="R81" s="45" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B82" s="27" t="s">
-        <v>291</v>
+        <v>288</v>
+      </c>
+      <c r="D82" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>400</v>
       </c>
       <c r="K82" s="27">
         <v>1.3</v>
@@ -10983,12 +11354,18 @@
         <v>1.2</v>
       </c>
       <c r="R82" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B83" s="27" t="s">
-        <v>292</v>
+        <v>289</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>417</v>
       </c>
       <c r="K83" s="27">
         <v>0.7</v>
@@ -10997,12 +11374,18 @@
         <v>0.7</v>
       </c>
       <c r="R83" s="45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B84" s="27" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D84" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>411</v>
       </c>
       <c r="H84" s="27">
         <v>3</v>
@@ -11014,12 +11397,18 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="R84" s="45" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B85" s="27" t="s">
-        <v>294</v>
+        <v>291</v>
+      </c>
+      <c r="D85" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>416</v>
       </c>
       <c r="K85" s="27">
         <v>0.3</v>
@@ -11028,12 +11417,18 @@
         <v>0.3</v>
       </c>
       <c r="R85" s="45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B86" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>417</v>
       </c>
       <c r="K86" s="27">
         <v>0.8</v>
@@ -11042,12 +11437,18 @@
         <v>0.2</v>
       </c>
       <c r="R86" s="45" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B87" s="27" t="s">
-        <v>296</v>
+        <v>293</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>418</v>
       </c>
       <c r="G87" s="27">
         <v>12</v>
@@ -11062,7 +11463,7 @@
         <v>0.2</v>
       </c>
       <c r="R87" s="45" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.3">
@@ -11085,7 +11486,7 @@
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B90" s="29" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="K90" s="30"/>
       <c r="L90" s="30"/>
@@ -11094,6 +11495,12 @@
       <c r="B91" s="27" t="s">
         <v>118</v>
       </c>
+      <c r="D91" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="E91" s="27" t="s">
+        <v>401</v>
+      </c>
       <c r="J91" s="42"/>
       <c r="K91" s="42">
         <v>5.3</v>
@@ -11103,12 +11510,18 @@
       </c>
       <c r="M91" s="42"/>
       <c r="R91" s="45" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B92" s="27" t="s">
-        <v>280</v>
+        <v>277</v>
+      </c>
+      <c r="D92" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>419</v>
       </c>
       <c r="H92" s="27">
         <v>1</v>
@@ -11122,12 +11535,18 @@
       </c>
       <c r="M92" s="42"/>
       <c r="R92" s="45" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B93" s="27" t="s">
-        <v>281</v>
+        <v>278</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>400</v>
       </c>
       <c r="J93" s="42"/>
       <c r="K93" s="42">
@@ -11138,12 +11557,18 @@
       </c>
       <c r="M93" s="42"/>
       <c r="R93" s="45" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B94" s="27" t="s">
-        <v>315</v>
+        <v>312</v>
+      </c>
+      <c r="D94" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>420</v>
       </c>
       <c r="J94" s="42"/>
       <c r="K94" s="42">
@@ -11154,12 +11579,18 @@
       </c>
       <c r="M94" s="42"/>
       <c r="R94" s="45" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B95" s="27" t="s">
-        <v>316</v>
+        <v>313</v>
+      </c>
+      <c r="D95" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>421</v>
       </c>
       <c r="J95" s="42"/>
       <c r="K95" s="42">
@@ -11170,12 +11601,18 @@
       </c>
       <c r="M95" s="42"/>
       <c r="R95" s="45" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B96" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>422</v>
       </c>
       <c r="J96" s="42"/>
       <c r="K96" s="42">
@@ -11186,7 +11623,7 @@
       </c>
       <c r="M96" s="42"/>
       <c r="R96" s="45" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.3">
@@ -11207,7 +11644,7 @@
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B99" s="29" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L99" s="27">
         <v>65</v>
@@ -11215,7 +11652,10 @@
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B100" s="45" t="s">
-        <v>337</v>
+        <v>334</v>
+      </c>
+      <c r="D100" s="27" t="s">
+        <v>383</v>
       </c>
       <c r="G100" s="27">
         <v>1</v>
@@ -11230,12 +11670,15 @@
         <v>12.2</v>
       </c>
       <c r="R100" s="45" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="101" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B101" s="45" t="s">
-        <v>324</v>
+        <v>321</v>
+      </c>
+      <c r="D101" s="27" t="s">
+        <v>384</v>
       </c>
       <c r="G101" s="27">
         <v>3</v>
@@ -11250,12 +11693,15 @@
         <v>5.9</v>
       </c>
       <c r="R101" s="45" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B102" s="45" t="s">
-        <v>338</v>
+        <v>335</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>385</v>
       </c>
       <c r="K102" s="27">
         <v>2.2000000000000002</v>
@@ -11264,12 +11710,15 @@
         <v>3.6</v>
       </c>
       <c r="R102" s="45" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B103" s="45" t="s">
-        <v>327</v>
+        <v>324</v>
+      </c>
+      <c r="D103" s="27" t="s">
+        <v>386</v>
       </c>
       <c r="K103" s="27">
         <v>0.7</v>
@@ -11278,12 +11727,15 @@
         <v>0.1</v>
       </c>
       <c r="R103" s="45" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B104" s="45" t="s">
-        <v>339</v>
+        <v>336</v>
+      </c>
+      <c r="D104" s="27" t="s">
+        <v>387</v>
       </c>
       <c r="G104" s="27">
         <v>1</v>
@@ -11298,12 +11750,15 @@
         <v>2.8</v>
       </c>
       <c r="R104" s="45" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B105" s="45" t="s">
-        <v>328</v>
+        <v>325</v>
+      </c>
+      <c r="D105" s="27" t="s">
+        <v>387</v>
       </c>
       <c r="H105" s="27">
         <v>1</v>
@@ -11315,12 +11770,15 @@
         <v>4</v>
       </c>
       <c r="R105" s="45" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="106" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B106" s="45" t="s">
-        <v>350</v>
+        <v>347</v>
+      </c>
+      <c r="D106" s="27" t="s">
+        <v>388</v>
       </c>
       <c r="H106" s="27">
         <v>2</v>
@@ -11332,12 +11790,15 @@
         <v>2</v>
       </c>
       <c r="R106" s="45" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B107" s="45" t="s">
-        <v>329</v>
+        <v>326</v>
+      </c>
+      <c r="D107" s="27" t="s">
+        <v>389</v>
       </c>
       <c r="H107" s="27">
         <v>1</v>
@@ -11349,12 +11810,15 @@
         <v>0.6</v>
       </c>
       <c r="R107" s="45" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B108" s="45" t="s">
-        <v>330</v>
+        <v>327</v>
+      </c>
+      <c r="D108" s="27" t="s">
+        <v>390</v>
       </c>
       <c r="K108" s="27">
         <v>0.2</v>
@@ -11363,12 +11827,15 @@
         <v>0.1</v>
       </c>
       <c r="R108" s="45" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B109" s="45" t="s">
-        <v>331</v>
+        <v>328</v>
+      </c>
+      <c r="D109" s="27" t="s">
+        <v>391</v>
       </c>
       <c r="H109" s="27">
         <v>9</v>
@@ -11380,7 +11847,7 @@
         <v>2</v>
       </c>
       <c r="R109" s="45" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.3">
@@ -11408,12 +11875,18 @@
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B113" s="29" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B114" s="27" t="s">
-        <v>343</v>
+        <v>340</v>
+      </c>
+      <c r="D114" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>423</v>
       </c>
       <c r="K114" s="27">
         <v>2.4</v>
@@ -11424,7 +11897,13 @@
     </row>
     <row r="115" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B115" s="27" t="s">
-        <v>344</v>
+        <v>341</v>
+      </c>
+      <c r="D115" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>424</v>
       </c>
       <c r="K115" s="27">
         <v>1.5</v>
@@ -11433,12 +11912,18 @@
         <v>0.7</v>
       </c>
       <c r="R115" s="27" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="116" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B116" s="27" t="s">
-        <v>345</v>
+        <v>342</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>425</v>
       </c>
       <c r="K116" s="27">
         <v>4.7</v>
@@ -11447,12 +11932,18 @@
         <v>13</v>
       </c>
       <c r="R116" s="27" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B117" s="27" t="s">
-        <v>346</v>
+        <v>343</v>
+      </c>
+      <c r="D117" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>426</v>
       </c>
       <c r="K117" s="27">
         <v>4.5</v>
@@ -11461,7 +11952,7 @@
         <v>5.9</v>
       </c>
       <c r="R117" s="27" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="118" spans="2:18" x14ac:dyDescent="0.3">
@@ -11527,13 +12018,13 @@
         <v>177</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J3" s="27" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L3" s="27" t="s">
         <v>192</v>
@@ -11571,7 +12062,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
@@ -11615,4 +12106,16 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84EFC3DB-AA8F-45A3-B21B-CABA85CCB0AF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="46"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>